--- a/upload/orgao_sem_informacoes_classificadas.xlsx
+++ b/upload/orgao_sem_informacoes_classificadas.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD394BE3-3C64-458C-A0F1-18814C5C3656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="245">
+  <si>
+    <t>ano</t>
+  </si>
   <si>
     <t>orgao_entidade</t>
   </si>
@@ -64,36 +68,45 @@
     <t>AGE</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Advocacia-Geral do Estado de Minas Gerais (AGE-MG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://advocaciageral.mg.gov.br/icd/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Advocacia-Geral do Estado de Minas Gerais (AGE-MG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto, até a data 11.06.2025.</t>
   </si>
   <si>
-    <t>https://advocaciageral.mg.gov.br/icd/</t>
-  </si>
-  <si>
     <t>Agência de Desenvolvimento da Região Metropolitana de Belo Horizonte</t>
   </si>
   <si>
     <t>ARMBH</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o(a) Agência de Desenvolvimento da Região Metropolitana de Belo Horizonte – Agência RMBH, informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.agenciarmbh.mg.gov.br/transparencia/</t>
+  </si>
+  <si>
     <t>A Agência RMBH não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação).</t>
   </si>
   <si>
-    <t>https://www.agenciarmbh.mg.gov.br/transparencia/</t>
-  </si>
-  <si>
     <t>Agência de Desenvolvimento da Região Metropolitana do Vale do Aço</t>
   </si>
   <si>
     <t>ARMVA</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Agência de Desenvolvimento da Região Metropolitana do Vale do Aço informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto,</t>
+  </si>
+  <si>
+    <t>https://www.agenciarmva.mg.gov.br/classificacao-informacoes/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Agência de Desenvolvimento da Região Metropolitana do Vale do Aço informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
-    <t>https://www.agenciarmva.mg.gov.br/classificacao-informacoes/</t>
-  </si>
-  <si>
     <t>Agência Reguladora de Serviços de Abastecimento de Água e Esgotamento Sanitário do Estado de MG</t>
   </si>
   <si>
@@ -106,6 +119,18 @@
     <t>https://www.arsae.mg.gov.br/tra_informacoes/</t>
   </si>
   <si>
+    <t>Agência Reguladora de Transportes do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>ARTEMIG</t>
+  </si>
+  <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Agência Reguladora de Transportes de Minas Gerais (Artemig) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://artemig.mg.gov.br/artemig/informacoes-classificadas-e-desclassificadas/</t>
+  </si>
+  <si>
     <t>Banco de Desenvolvimento de Minas Gerais - BDMG</t>
   </si>
   <si>
@@ -118,30 +143,21 @@
     <t>https://www.bdmg.mg.gov.br/transparencia-documentos/?classificados</t>
   </si>
   <si>
-    <t>Companhia de Desenvolvimento Econômico de Minas Gerais - CODEMGE</t>
-  </si>
-  <si>
-    <t>CODEMGE</t>
-  </si>
-  <si>
-    <t>Em atendimento ao disposto no artigo 46 do Decreto 45.969/2012, a Companhia de Desenvolvimento de Minas Gerais (Codemge) apresenta o rol de informações classificadas com grau de sigilo no período de 01/06/2024 a 31/05/2025.</t>
-  </si>
-  <si>
-    <t>https://codemge.com.br/classificacao-da-informacao/</t>
-  </si>
-  <si>
     <t>Companhia de Gás de Minas Gerais - GASMIG</t>
   </si>
   <si>
     <t>GASMIG</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Gasmig informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://gasmig.com.br/transparencia/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Gasmig informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto.</t>
   </si>
   <si>
-    <t>https://gasmig.com.br/transparencia/</t>
-  </si>
-  <si>
     <t>Companhia de Habitação do Estado de Minas Gerais - COHAB</t>
   </si>
   <si>
@@ -160,6 +176,12 @@
     <t>COPASA</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Companhia de Saneamento de Minas Gerais – COPASA informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.copasa.com.br/wps/portal/internet/institucional/a-copasa/portal-da-transparencia/portal-da-transparencia</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Copasa Serviços de Saneamento Integrado do Norte e Nordeste de Minas Gerais S/A - COPANOR informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto.</t>
   </si>
   <si>
@@ -184,6 +206,12 @@
     <t>CEMIG</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Cemig informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.cemig.com.br/governanca/privacidade-e-transparencia/transparencia-lei-de-acesso-a-informacao-lai/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Companhia Energética de Minas Gerais -CEMIG informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
@@ -208,24 +236,33 @@
     <t>DER</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Departamento de Estradas de Rodagem do Estado de Minas Gerais informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Departamento de Estradas de Rodagem do Estado de Minas Gerais informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.der.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Departamento de Estradas de Rodagem de Minas Gerais (DER-MG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
-    <t>https://www.der.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Empresa de Assistência Técnica e Extensão Rural do Estado de Minas Gerais - EMATER</t>
   </si>
   <si>
     <t>EMATER</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.emater.mg.gov.br/portal.do?flagweb=novosite_pagina_interna&amp;id=20858</t>
+  </si>
+  <si>
     <t>Nos últimos 12 meses, a EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 24 da Lei nº 12.527/2011</t>
   </si>
   <si>
-    <t>https://www.emater.mg.gov.br/portal.do?flagweb=novosite_pagina_interna&amp;id=20858</t>
-  </si>
-  <si>
     <t>Empresa de Pesquisa Agropecuária de Minas Gerais - EPAMIG</t>
   </si>
   <si>
@@ -244,30 +281,42 @@
     <t>EMC</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a EMC – Empresa Mineira de Comunicação (EMC) declara que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://emc.mg.gov.br/institucional/transparencia/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a EMC – Empresa Mineira de Comunicação (EMC) declara que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto,</t>
   </si>
   <si>
-    <t>https://emc.mg.gov.br/institucional/transparencia/</t>
-  </si>
-  <si>
     <t>Escola de Saúde Pública do Estado de Minas Gerais - ESP</t>
   </si>
   <si>
     <t>ESP</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a  Escola de Saúde Pública  do Estado de Minas Gerais (ESP-MG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://esp.mg.gov.br/transparencia/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a  Escola de Saúde Pública  do Estado de Minas Gerais (ESP-MG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto.</t>
   </si>
   <si>
-    <t>https://esp.mg.gov.br/transparencia/</t>
-  </si>
-  <si>
     <t>Fundação Centro de Hematologia e Hemoterapia do Estado de Minas Gerais - HEMOMINAS</t>
   </si>
   <si>
     <t>HEMOMINAS</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº45.969/2012, a Fundação Centro de Hematologia e Hemoterapia do Estado de Minas Gerais - Hemominas - informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.hemominas.mg.gov.br/transparencia</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº45.969/2012, a Fundação Centro de Hematologia e Hemoterapia do Estado de Minas Gerais - Hemominas - informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto.</t>
   </si>
   <si>
@@ -292,6 +341,15 @@
     <t>FAPEMIG</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://fapemig.br/a-fapemig/transparencia/informacoes-classificadas-ou-desclassificadas</t>
+  </si>
+  <si>
     <t>Nos últimos 12 meses, a FAPEMIG não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no Art. 24 da Lei nº 12.527/2011 (Lei de Acesso à Informação)</t>
   </si>
   <si>
@@ -304,12 +362,15 @@
     <t>FAOP</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Arte de Ouro Preto informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado,  secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>http://www.faop.mg.gov.br/transparencia/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Arte de Ouro Preto | FAOP informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto e ultrassecreto</t>
   </si>
   <si>
-    <t>http://www.faop.mg.gov.br/transparencia/</t>
-  </si>
-  <si>
     <t>Fundação de Educação para o Trabalho de Minas Gerais - UTRAMIG</t>
   </si>
   <si>
@@ -388,12 +449,15 @@
     <t>IPSEMG</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Instituto de Previdência dos Servidores do Estado de Minas Gerais (Ipsemg) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.ipsemg.mg.gov.br/paginas/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Instituto de Previdência dos Servidores do Estado de Minas Gerais (Ipsemg) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto, até a data 19/03/2025.</t>
   </si>
   <si>
-    <t>https://www.ipsemg.mg.gov.br/paginas/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Instituto de Previdência dos Servidores Militares do Estado de Minas Gerais - IPSM</t>
   </si>
   <si>
@@ -418,18 +482,33 @@
     <t>https://www.ief.mg.gov.br/informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
   </si>
   <si>
+    <t>Instituto Estadual do Patrimônio Histórico e Artístico de Minas Gerais - IEPHA</t>
+  </si>
+  <si>
+    <t>IEPHA</t>
+  </si>
+  <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Instituto Estadual do Patrimônio Histórtico e Artístico de Minas Gerias (IEPHA-MG), informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.iepha.mg.gov.br/index.php/transparencia#informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>Instituto Mineiro de Agropecuária - IMA</t>
   </si>
   <si>
     <t>IMA</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Instituto Mineiro de Agropecuária - IMA informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.ima.mg.gov.br/transparencia#informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>O Instituto Mineiro de Agropecuária - IMA não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
-    <t>https://www.ima.mg.gov.br/transparencia#informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Instituto Mineiro de Gestão das Águas - IGAM</t>
   </si>
   <si>
@@ -442,30 +521,21 @@
     <t>https://igam.mg.gov.br/informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
   </si>
   <si>
-    <t>Instituto Estadual do Patrimônio Histórico e Artístico de Minas Gerais - IEPHA</t>
-  </si>
-  <si>
-    <t>IEPHA</t>
-  </si>
-  <si>
-    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Instituto Estadual do Patrimônio Histórtico e Artístico de Minas Gerias (IEPHA-MG), informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
-  </si>
-  <si>
-    <t>https://www.iepha.mg.gov.br/index.php/transparencia#informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Junta Comercial do Estado de Minas Gerais - JUCEMG</t>
   </si>
   <si>
     <t>JUCEMG</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Junta Comercial do Estado de Minas Gerais (Jucemg) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://jucemg.mg.gov.br/pagina/84/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>A Junta Comercial do Estado de Minas Gerais não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
-    <t>https://jucemg.mg.gov.br/pagina/84/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Loteria do Estado de Minas Gerais - LEMG</t>
   </si>
   <si>
@@ -496,24 +566,33 @@
     <t>MGI</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Minas Gerais Participações S.A. informa que não houve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.mgipart.com.br/transparencia/InformacoesClassificadas</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Minas Gerais Participações S.A.  informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
-    <t>https://www.mgipart.com.br/transparencia/InformacoesClassificadas</t>
-  </si>
-  <si>
     <t>Ouvidoria Geral do Estado de Minas Gerais - OGE</t>
   </si>
   <si>
     <t>OGE</t>
   </si>
   <si>
+    <t>A Ouvidoria-Geral do Estado não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta,</t>
+  </si>
+  <si>
+    <t>A Ouvidoria-Geral do Estado não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta,'</t>
+  </si>
+  <si>
+    <t>https://www.ouvidoriageral.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>A Ouvidoria-Geral do Estado não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
-    <t>https://www.ouvidoriageral.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Secretaria de Estado de Agricultura, Pecuária e Abastecimento - SEAPA</t>
   </si>
   <si>
@@ -544,6 +623,12 @@
     <t>SECOM</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, (a) Secretaria de Estado de Comunicação Social (Secom) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.comunicacao.mg.gov.br/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>https://www.comunicacao.mg.gov.br/portal-da-transparencia</t>
   </si>
   <si>
@@ -553,12 +638,15 @@
     <t>SECULT</t>
   </si>
   <si>
+    <t>Nos últimos 12 meses, a Secretaria de Estado de Cultura e Turismo (Secult/MG) não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta,</t>
+  </si>
+  <si>
+    <t>https://www.secult.mg.gov.br/component/content/article/94-transparencia/6265-transparencia?Itemid=437</t>
+  </si>
+  <si>
     <t>Nos últimos 12 meses, a Secretaria de Estado de Cultura e Turismo (Secult/MG) não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no Art. 24 da Lei nº 12.527/2011 (Lei de Acesso à Informação).</t>
   </si>
   <si>
-    <t>https://www.secult.mg.gov.br/component/content/article/94-transparencia/6265-transparencia?Itemid=437</t>
-  </si>
-  <si>
     <t>Secretaria de Estado de Desenvolvimento Econômico - SEDE</t>
   </si>
   <si>
@@ -601,10 +689,25 @@
     <t>SEGOV</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Governo informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.governo.mg.gov.br/Transparencia/Secretaria</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Governo informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
-    <t>https://www.governo.mg.gov.br/Transparencia/Secretaria</t>
+    <t>Secretaria de Estado de Infraestrutura e Mobilidade - SEINFRA</t>
+  </si>
+  <si>
+    <t>SEINFRA</t>
+  </si>
+  <si>
+    <t>A Secretaria de Estado de Infraestrutura, Mobilidade e Parcerias - SEINFRA não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
+  </si>
+  <si>
+    <t>http://www.infraestrutura.mg.gov.br/transparencia-publica/informacoes-classificadas-e-desclassificadas</t>
   </si>
   <si>
     <t>Secretaria de Estado de Planejamento e Gestão de Minas Gerais - SEPLAG</t>
@@ -631,62 +734,53 @@
     <t>https://www.saude.mg.gov.br/transparencia/</t>
   </si>
   <si>
-    <t>Secretaria de Estado de Infraestrutura e Mobilidade - SEINFRA</t>
-  </si>
-  <si>
-    <t>SEINFRA</t>
-  </si>
-  <si>
-    <t>A Secretaria de Estado de Infraestrutura, Mobilidade e Parcerias - SEINFRA não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
-  </si>
-  <si>
-    <t>http://www.infraestrutura.mg.gov.br/transparencia-publica/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Secretaria-Geral</t>
   </si>
   <si>
     <t>Geral</t>
   </si>
   <si>
+    <t>https://www.secretariageral.mg.gov.br/Transparencia/Secretaria</t>
+  </si>
+  <si>
     <t>Na Secretaria-Geral não houve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
-    <t>https://www.secretariageral.mg.gov.br/Transparencia/Secretaria</t>
-  </si>
-  <si>
     <t>Universidade do Estado de Minas Gerais - UEMG</t>
   </si>
   <si>
     <t>UEMG</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Universidade do Estado de Minas Gerais informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.uemg.br/transparencia2019#info-class-des</t>
+  </si>
+  <si>
     <t>A Universidade do Estado de Minas Gerais não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
-    <t>https://www.uemg.br/transparencia2019#info-class-des</t>
-  </si>
-  <si>
     <t>Universidade Estadual de Montes Claros - UNIMONTES</t>
   </si>
   <si>
     <t>UNIMONTES</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Universidade Estadual de Montes Claros informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://unimontes.br/transparencia/</t>
+  </si>
+  <si>
     <t>Nos últimos 12 meses, a Universidade Estadual de Montes Claros (Unimontes) não registrou informação sigilosa, considerada como aquela em que há restrição de acesso público, em razão de sua imprescindibilidade para a segurança da sociedade e do Estado (art. 3º, inciso XIV do Decreto Estadual nº 47.021/2016)</t>
-  </si>
-  <si>
-    <t>https://unimontes.br/transparencia/</t>
-  </si>
-  <si>
-    <t>ano</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,6 +796,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica Neue"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica Neue"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="Roboto"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -711,7 +824,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -719,18 +832,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1062,35 +1203,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G156"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K236"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1098,1490 +1241,1497 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1">
-        <v>46073</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>46139</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1">
-        <v>45705</v>
-      </c>
-      <c r="G3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>45819</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
       <c r="A4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1">
-        <v>45713</v>
-      </c>
-      <c r="G4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>45454</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
       <c r="A5">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1">
-        <v>45717</v>
-      </c>
-      <c r="G5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>45088</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15">
       <c r="A6">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1">
-        <v>45730</v>
+        <v>46126</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15">
       <c r="A7">
         <v>2025</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1">
-        <v>45730</v>
+        <v>45734</v>
       </c>
       <c r="G7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15">
       <c r="A8">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1">
-        <v>45733</v>
+        <v>45369</v>
       </c>
       <c r="G8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15">
       <c r="A9">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1">
-        <v>45733</v>
+        <v>45003</v>
       </c>
       <c r="G9" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15">
       <c r="A10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1">
-        <v>45734</v>
+        <v>46126</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15">
       <c r="A11">
         <v>2025</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="F11" s="1">
-        <v>45735</v>
+        <v>45820</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15">
       <c r="A12">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1">
-        <v>45735</v>
+        <v>45455</v>
       </c>
       <c r="G12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15">
       <c r="A13">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1">
-        <v>45735</v>
+        <v>45089</v>
       </c>
       <c r="G13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15">
       <c r="A14">
         <v>2025</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1">
-        <v>45735</v>
+        <v>45810</v>
       </c>
       <c r="G14" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15">
       <c r="A15">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1">
-        <v>45736</v>
+        <v>45445</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
       <c r="A16">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1">
-        <v>45736</v>
+        <v>45079</v>
       </c>
       <c r="G16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
       <c r="A17">
         <v>2025</v>
       </c>
       <c r="B17" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1">
-        <v>45737</v>
+        <v>46128</v>
       </c>
       <c r="G17" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15">
       <c r="A18">
         <v>2025</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>210</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="F18" s="1">
-        <v>45737</v>
+        <v>45747</v>
       </c>
       <c r="G18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15">
       <c r="A19">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="F19" s="1">
-        <v>45740</v>
+        <v>45382</v>
       </c>
       <c r="G19" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15">
       <c r="A20">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1">
-        <v>45741</v>
+        <v>45016</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15">
       <c r="A21">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>163</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1">
-        <v>45741</v>
-      </c>
-      <c r="G21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>46127</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15">
       <c r="A22">
         <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1">
-        <v>45742</v>
+        <v>46022</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15">
       <c r="A23">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1">
-        <v>45742</v>
+        <v>45657</v>
       </c>
       <c r="G23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
       <c r="A24">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="F24" s="1">
-        <v>45744</v>
+        <v>45291</v>
       </c>
       <c r="G24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15">
       <c r="A25">
         <v>2025</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
       <c r="F25" s="1">
-        <v>45744</v>
+        <v>45812</v>
       </c>
       <c r="G25" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15">
       <c r="A26">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F26" s="1">
-        <v>45747</v>
+        <v>45447</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15">
       <c r="A27">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s">
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1">
-        <v>45748</v>
+        <v>45081</v>
       </c>
       <c r="G27" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15">
       <c r="A28">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F28" s="1">
-        <v>45749</v>
-      </c>
-      <c r="G28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>46099</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15">
       <c r="A29">
         <v>2025</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1">
-        <v>45751</v>
+        <v>45780</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15">
       <c r="A30">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="F30" s="1">
-        <v>45756</v>
+        <v>45415</v>
       </c>
       <c r="G30" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15">
       <c r="A31">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F31" s="1">
-        <v>45780</v>
+        <v>45049</v>
       </c>
       <c r="G31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15">
       <c r="A32">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" t="s">
-        <v>72</v>
+        <v>51</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="F32" s="1">
-        <v>45792</v>
-      </c>
-      <c r="G32" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>46128</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15">
       <c r="A33">
         <v>2025</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>195</v>
+        <v>51</v>
       </c>
       <c r="E33" t="s">
-        <v>195</v>
+        <v>51</v>
       </c>
       <c r="F33" s="1">
-        <v>45805</v>
+        <v>45953</v>
       </c>
       <c r="G33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15">
       <c r="A34">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F34" s="1">
-        <v>45808</v>
+        <v>45588</v>
       </c>
       <c r="G34" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15">
       <c r="A35">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="F35" s="1">
-        <v>45808</v>
+        <v>45222</v>
       </c>
       <c r="G35" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15">
       <c r="A36">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="F36" s="1">
-        <v>45810</v>
-      </c>
-      <c r="G36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>46120</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15">
       <c r="A37">
         <v>2025</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="F37" s="1">
-        <v>45810</v>
+        <v>45735</v>
       </c>
       <c r="G37" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15">
       <c r="A38">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F38" s="1">
-        <v>45812</v>
+        <v>45370</v>
       </c>
       <c r="G38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15">
       <c r="A39">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="F39" s="1">
-        <v>45813</v>
+        <v>45004</v>
       </c>
       <c r="G39" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15">
       <c r="A40">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F40" s="1">
-        <v>45819</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>46073</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15">
       <c r="A41">
         <v>2025</v>
       </c>
       <c r="B41" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="F41" s="1">
-        <v>45819</v>
-      </c>
-      <c r="G41" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>45708</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15">
       <c r="A42">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="F42" s="1">
-        <v>45819</v>
-      </c>
-      <c r="G42" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>45342</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15">
       <c r="A43">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F43" s="1">
-        <v>45820</v>
-      </c>
-      <c r="G43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>44977</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75">
       <c r="A44">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E44" t="s">
-        <v>84</v>
+        <v>65</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="F44" s="1">
-        <v>45820</v>
-      </c>
-      <c r="G44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>46135</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15">
       <c r="A45">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B45" t="s">
-        <v>189</v>
+        <v>63</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>64</v>
       </c>
       <c r="D45" t="s">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="F45" s="1">
-        <v>45821</v>
+        <v>45657</v>
       </c>
       <c r="G45" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15">
       <c r="A46">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F46" s="1">
-        <v>45838</v>
+        <v>45291</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15">
       <c r="A47">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>132</v>
-      </c>
-      <c r="E47" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="F47" s="1">
-        <v>45840</v>
-      </c>
-      <c r="G47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>46140</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15">
       <c r="A48">
         <v>2025</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="E48" t="s">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="F48" s="1">
-        <v>45862</v>
+        <v>45883</v>
       </c>
       <c r="G48" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15">
       <c r="A49">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F49" s="1">
-        <v>45883</v>
+        <v>45518</v>
       </c>
       <c r="G49" t="s">
+        <v>72</v>
+      </c>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" ht="15">
+      <c r="A50">
+        <v>2023</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45152</v>
+      </c>
+      <c r="G50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15">
+      <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F51" s="1">
         <v>61</v>
       </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>2025</v>
-      </c>
-      <c r="B50" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F50" s="1">
-        <v>45953</v>
-      </c>
-      <c r="G50" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>2025</v>
-      </c>
-      <c r="B51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" t="s">
-        <v>51</v>
-      </c>
-      <c r="D51" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" t="s">
-        <v>52</v>
-      </c>
-      <c r="F51" s="1">
-        <v>46073</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="G51" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15">
       <c r="A52">
         <v>2025</v>
       </c>
       <c r="B52" t="s">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="C52" t="s">
-        <v>167</v>
+        <v>75</v>
+      </c>
+      <c r="D52" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45717</v>
       </c>
       <c r="G52" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15">
       <c r="A53">
         <v>2024</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="F53" s="1">
-        <v>45657</v>
+        <v>45352</v>
       </c>
       <c r="G53" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15">
       <c r="A54">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E54" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="F54" s="1">
-        <v>45657</v>
+        <v>44986</v>
       </c>
       <c r="G54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15">
       <c r="A55">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
-      </c>
-      <c r="E55" t="s">
-        <v>156</v>
+        <v>80</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="F55" s="1">
-        <v>45339</v>
-      </c>
-      <c r="G55" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>46125</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15">
       <c r="A56">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B56" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="E56" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="F56" s="1">
-        <v>45347</v>
+        <v>45742</v>
       </c>
       <c r="G56" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15">
       <c r="A57">
         <v>2024</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E57" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F57" s="1">
-        <v>45352</v>
+        <v>45377</v>
       </c>
       <c r="G57" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15">
       <c r="A58">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E58" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F58" s="1">
-        <v>45365</v>
+        <v>45011</v>
       </c>
       <c r="G58" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15">
       <c r="A59">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D59" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F59" s="1">
-        <v>45365</v>
-      </c>
-      <c r="G59" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>46120</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15">
       <c r="A60">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="E60" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="F60" s="1">
-        <v>45368</v>
+        <v>45792</v>
       </c>
       <c r="G60" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15">
       <c r="A61">
         <v>2024</v>
       </c>
       <c r="B61" t="s">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="C61" t="s">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="D61" t="s">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="E61" t="s">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="F61" s="1">
-        <v>45368</v>
+        <v>45427</v>
       </c>
       <c r="G61" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15">
       <c r="A62">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D62" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="E62" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="F62" s="1">
-        <v>45369</v>
+        <v>45061</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15">
       <c r="A63">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="F63" s="1">
-        <v>45370</v>
-      </c>
-      <c r="G63" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>46140</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15">
       <c r="A64">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="D64" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="E64" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="F64" s="1">
-        <v>45370</v>
+        <v>45730</v>
       </c>
       <c r="G64" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15">
       <c r="A65">
         <v>2024</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="D65" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="F65" s="1">
-        <v>45370</v>
+        <v>45365</v>
       </c>
       <c r="G65" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15">
       <c r="A66">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B66" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="D66" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="E66" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="F66" s="1">
-        <v>45370</v>
+        <v>44999</v>
       </c>
       <c r="G66" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15">
       <c r="A67">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B67" t="s">
         <v>94</v>
@@ -2596,2052 +2746,2814 @@
         <v>96</v>
       </c>
       <c r="F67" s="1">
-        <v>45371</v>
+        <v>45756</v>
       </c>
       <c r="G67" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" ht="15">
       <c r="A68">
         <v>2024</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E68" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F68" s="1">
-        <v>45371</v>
+        <v>45391</v>
       </c>
       <c r="G68" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15">
       <c r="A69">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="F69" s="1">
-        <v>45372</v>
+        <v>45025</v>
       </c>
       <c r="G69" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15">
       <c r="A70">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B70" t="s">
-        <v>209</v>
+        <v>98</v>
       </c>
       <c r="C70" t="s">
-        <v>210</v>
+        <v>99</v>
       </c>
       <c r="D70" t="s">
-        <v>211</v>
+        <v>100</v>
       </c>
       <c r="E70" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="F70" s="1">
-        <v>45372</v>
-      </c>
-      <c r="G70" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>46128</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15">
       <c r="A71">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B71" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="D71" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="E71" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="F71" s="1">
-        <v>45375</v>
+        <v>45820</v>
       </c>
       <c r="G71" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15">
       <c r="A72">
         <v>2024</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D72" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E72" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="F72" s="1">
-        <v>45376</v>
+        <v>45455</v>
       </c>
       <c r="G72" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15">
       <c r="A73">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="D73" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="E73" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="F73" s="1">
-        <v>45376</v>
+        <v>45089</v>
       </c>
       <c r="G73" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15">
       <c r="A74">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="C74" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="E74" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="F74" s="1">
-        <v>45377</v>
-      </c>
-      <c r="G74" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>46142</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15">
       <c r="A75">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B75" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E75" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F75" s="1">
-        <v>45377</v>
+        <v>45813</v>
       </c>
       <c r="G75" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15">
       <c r="A76">
         <v>2024</v>
       </c>
       <c r="B76" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="C76" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E76" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="F76" s="1">
-        <v>45379</v>
+        <v>45448</v>
       </c>
       <c r="G76" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15">
       <c r="A77">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B77" t="s">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="C77" t="s">
-        <v>206</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="E77" t="s">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="F77" s="1">
-        <v>45379</v>
+        <v>45082</v>
       </c>
       <c r="G77" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15">
       <c r="A78">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="E78" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="F78" s="1">
-        <v>45382</v>
+        <v>45730</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15">
       <c r="A79">
         <v>2024</v>
       </c>
       <c r="B79" t="s">
-        <v>201</v>
+        <v>110</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="E79" t="s">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="F79" s="1">
-        <v>45383</v>
+        <v>45365</v>
       </c>
       <c r="G79" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15">
       <c r="A80">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="C80" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="D80" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E80" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F80" s="1">
-        <v>45384</v>
+        <v>44999</v>
       </c>
       <c r="G80" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15">
       <c r="A81">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D81" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F81" s="1">
-        <v>45386</v>
+        <v>45736</v>
       </c>
       <c r="G81" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15">
       <c r="A82">
         <v>2024</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="C82" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="D82" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="E82" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="F82" s="1">
-        <v>45391</v>
+        <v>45371</v>
       </c>
       <c r="G82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15">
       <c r="A83">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="C83" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="D83" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="E83" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="F83" s="1">
-        <v>45415</v>
+        <v>45005</v>
       </c>
       <c r="G83" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15">
       <c r="A84">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C84" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="E84" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F84" s="1">
-        <v>45427</v>
+        <v>45838</v>
       </c>
       <c r="G84" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15">
       <c r="A85">
         <v>2024</v>
       </c>
       <c r="B85" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="C85" t="s">
-        <v>194</v>
+        <v>119</v>
       </c>
       <c r="D85" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="E85" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="F85" s="1">
-        <v>45440</v>
+        <v>45473</v>
       </c>
       <c r="G85" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15">
       <c r="A86">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="E86" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="F86" s="1">
-        <v>45443</v>
+        <v>45107</v>
       </c>
       <c r="G86" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15">
       <c r="A87">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B87" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D87" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E87" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F87" s="1">
-        <v>45443</v>
-      </c>
-      <c r="G87" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>46126</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15">
       <c r="A88">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="E88" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F88" s="1">
-        <v>45445</v>
+        <v>45742</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15">
       <c r="A89">
         <v>2024</v>
       </c>
       <c r="B89" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C89" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D89" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E89" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F89" s="1">
-        <v>45445</v>
+        <v>45377</v>
       </c>
       <c r="G89" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15">
       <c r="A90">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="E90" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="F90" s="1">
-        <v>45447</v>
+        <v>45011</v>
       </c>
       <c r="G90" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15">
       <c r="A91">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D91" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="E91" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="F91" s="1">
-        <v>45448</v>
+        <v>46127</v>
       </c>
       <c r="G91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15">
       <c r="A92">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="D92" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="E92" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="F92" s="1">
-        <v>45454</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>45808</v>
+      </c>
+      <c r="G92" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15">
       <c r="A93">
         <v>2024</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="E93" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="F93" s="1">
-        <v>45454</v>
+        <v>45443</v>
       </c>
       <c r="G93" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15">
       <c r="A94">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B94" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="C94" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="D94" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="E94" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="F94" s="1">
-        <v>45454</v>
+        <v>45077</v>
       </c>
       <c r="G94" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15">
       <c r="A95">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="E95" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="F95" s="1">
-        <v>45455</v>
+        <v>45736</v>
       </c>
       <c r="G95" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15">
       <c r="A96">
         <v>2024</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="C96" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="E96" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="F96" s="1">
-        <v>45455</v>
+        <v>45371</v>
       </c>
       <c r="G96" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15">
       <c r="A97">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B97" t="s">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="E97" t="s">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="F97" s="1">
-        <v>45456</v>
+        <v>45005</v>
       </c>
       <c r="G97" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15">
       <c r="A98">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="C98" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E98" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F98" s="1">
-        <v>45473</v>
+        <v>46121</v>
       </c>
       <c r="G98" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15">
       <c r="A99">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B99" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D99" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E99" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F99" s="1">
-        <v>45475</v>
+        <v>45735</v>
       </c>
       <c r="G99" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15">
       <c r="A100">
         <v>2024</v>
       </c>
       <c r="B100" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="C100" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="E100" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="F100" s="1">
-        <v>45497</v>
+        <v>45370</v>
       </c>
       <c r="G100" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15">
       <c r="A101">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B101" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="C101" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="D101" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="E101" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="F101" s="1">
-        <v>45518</v>
+        <v>45004</v>
       </c>
       <c r="G101" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="15">
       <c r="A102">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B102" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="C102" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="D102" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="E102" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="F102" s="1">
-        <v>45588</v>
+        <v>46126</v>
       </c>
       <c r="G102" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15">
       <c r="A103">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="C103" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="D103" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="E103" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F103" s="1">
-        <v>45342</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>45741</v>
+      </c>
+      <c r="G103" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15">
       <c r="A104">
         <v>2024</v>
       </c>
       <c r="B104" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="C104" t="s">
-        <v>167</v>
+        <v>140</v>
+      </c>
+      <c r="D104" t="s">
+        <v>141</v>
+      </c>
+      <c r="E104" t="s">
+        <v>141</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45376</v>
       </c>
       <c r="G104" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15">
       <c r="A105">
         <v>2023</v>
       </c>
       <c r="B105" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="C105" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D105" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="E105" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F105" s="1">
-        <v>45291</v>
+        <v>45010</v>
       </c>
       <c r="G105" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15">
       <c r="A106">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B106" t="s">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="C106" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="D106" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="E106" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="F106" s="1">
-        <v>45291</v>
+        <v>45751</v>
       </c>
       <c r="G106" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="15">
       <c r="A107">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B107" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C107" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D107" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="E107" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F107" s="1">
-        <v>44974</v>
+        <v>45386</v>
       </c>
       <c r="G107" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15">
       <c r="A108">
         <v>2023</v>
       </c>
       <c r="B108" t="s">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="C108" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="D108" t="s">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="E108" t="s">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="F108" s="1">
-        <v>44982</v>
+        <v>45020</v>
       </c>
       <c r="G108" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15">
       <c r="A109">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B109" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="C109" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="D109" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="E109" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="F109" s="1">
-        <v>44986</v>
+        <v>46120</v>
       </c>
       <c r="G109" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15">
       <c r="A110">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B110" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="C110" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="D110" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="E110" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="F110" s="1">
-        <v>44999</v>
+        <v>45810</v>
       </c>
       <c r="G110" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15">
       <c r="A111">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B111" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="C111" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="D111" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="E111" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="F111" s="1">
-        <v>44999</v>
+        <v>45445</v>
       </c>
       <c r="G111" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15">
       <c r="A112">
         <v>2023</v>
       </c>
       <c r="B112" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D112" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E112" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F112" s="1">
-        <v>45002</v>
+        <v>45079</v>
       </c>
       <c r="G112" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15">
       <c r="A113">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B113" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="C113" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D113" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E113" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="F113" s="1">
-        <v>45002</v>
+        <v>46126</v>
       </c>
       <c r="G113" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15">
       <c r="A114">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B114" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="C114" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="D114" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E114" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="F114" s="1">
-        <v>45003</v>
+        <v>45735</v>
       </c>
       <c r="G114" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="15">
       <c r="A115">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>151</v>
       </c>
       <c r="C115" t="s">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="D115" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="E115" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="F115" s="1">
-        <v>45004</v>
+        <v>45370</v>
       </c>
       <c r="G115" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15">
       <c r="A116">
         <v>2023</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="D116" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="E116" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="F116" s="1">
         <v>45004</v>
       </c>
       <c r="G116" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15">
       <c r="A117">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="C117" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="D117" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="E117" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="F117" s="1">
-        <v>45004</v>
+        <v>45840</v>
       </c>
       <c r="G117" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15">
       <c r="A118">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B118" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C118" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D118" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E118" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F118" s="1">
-        <v>45004</v>
+        <v>45475</v>
       </c>
       <c r="G118" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15">
       <c r="A119">
         <v>2023</v>
       </c>
       <c r="B119" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="C119" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="D119" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="E119" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="F119" s="1">
-        <v>45005</v>
+        <v>45109</v>
       </c>
       <c r="G119" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15">
       <c r="A120">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B120" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="C120" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="D120" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="E120" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="F120" s="1">
-        <v>45005</v>
+        <v>46139</v>
       </c>
       <c r="G120" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15">
       <c r="A121">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B121" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C121" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D121" t="s">
+        <v>164</v>
+      </c>
+      <c r="E121" t="s">
+        <v>164</v>
+      </c>
+      <c r="F121" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G121" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15">
+      <c r="A122">
+        <v>2024</v>
+      </c>
+      <c r="B122" t="s">
         <v>160</v>
       </c>
-      <c r="E121" t="s">
-        <v>160</v>
-      </c>
-      <c r="F121" s="1">
-        <v>45006</v>
-      </c>
-      <c r="G121" t="s">
+      <c r="C122" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122">
-        <v>2023</v>
-      </c>
-      <c r="B122" t="s">
-        <v>209</v>
-      </c>
-      <c r="C122" t="s">
-        <v>210</v>
-      </c>
       <c r="D122" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="E122" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="F122" s="1">
-        <v>45006</v>
+        <v>45384</v>
       </c>
       <c r="G122" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="15">
       <c r="A123">
         <v>2023</v>
       </c>
       <c r="B123" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C123" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="E123" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="F123" s="1">
-        <v>45009</v>
+        <v>45018</v>
       </c>
       <c r="G123" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15">
       <c r="A124">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B124" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C124" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="D124" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="E124" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="F124" s="1">
-        <v>45010</v>
+        <v>45744</v>
       </c>
       <c r="G124" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15">
       <c r="A125">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D125" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E125" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F125" s="1">
-        <v>45010</v>
+        <v>45379</v>
       </c>
       <c r="G125" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="15">
       <c r="A126">
         <v>2023</v>
       </c>
       <c r="B126" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="C126" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="D126" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="E126" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="F126" s="1">
-        <v>45011</v>
+        <v>45013</v>
       </c>
       <c r="G126" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="15">
       <c r="A127">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B127" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="C127" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="D127" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="E127" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="F127" s="1">
-        <v>45011</v>
+        <v>46120</v>
       </c>
       <c r="G127" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15">
       <c r="A128">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B128" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C128" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E128" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="F128" s="1">
-        <v>45013</v>
+        <v>45733</v>
       </c>
       <c r="G128" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="15">
       <c r="A129">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B129" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="C129" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="D129" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="E129" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="F129" s="1">
-        <v>45013</v>
+        <v>45368</v>
       </c>
       <c r="G129" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="15">
       <c r="A130">
         <v>2023</v>
       </c>
       <c r="B130" t="s">
-        <v>22</v>
+        <v>169</v>
       </c>
       <c r="C130" t="s">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="D130" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="E130" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="F130" s="1">
-        <v>45016</v>
+        <v>45002</v>
       </c>
       <c r="G130" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15">
       <c r="A131">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B131" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="C131" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="D131" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="E131" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="F131" s="1">
-        <v>45017</v>
+        <v>46127</v>
       </c>
       <c r="G131" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="15">
       <c r="A132">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="D132" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="E132" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="F132" s="1">
-        <v>45018</v>
+        <v>45735</v>
       </c>
       <c r="G132" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="15">
       <c r="A133">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B133" t="s">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="C133" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="D133" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="E133" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="F133" s="1">
-        <v>45020</v>
+        <v>45370</v>
       </c>
       <c r="G133" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="15">
       <c r="A134">
         <v>2023</v>
       </c>
       <c r="B134" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="C134" t="s">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="D134" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="E134" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="F134" s="1">
-        <v>45025</v>
+        <v>45004</v>
       </c>
       <c r="G134" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="15">
       <c r="A135">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B135" t="s">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="C135" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="D135" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="E135" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="F135" s="1">
-        <v>45049</v>
+        <v>46140</v>
       </c>
       <c r="G135" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="15">
       <c r="A136">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B136" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="C136" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="D136" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="E136" t="s">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="F136" s="1">
-        <v>45061</v>
+        <v>45705</v>
       </c>
       <c r="G136" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="15">
       <c r="A137">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B137" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C137" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D137" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E137" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F137" s="1">
-        <v>45074</v>
+        <v>45339</v>
       </c>
       <c r="G137" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="15">
       <c r="A138">
         <v>2023</v>
       </c>
       <c r="B138" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="C138" t="s">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="D138" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="E138" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F138" s="1">
-        <v>45077</v>
+        <v>44974</v>
       </c>
       <c r="G138" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="15">
       <c r="A139">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B139" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="C139" t="s">
-        <v>107</v>
+        <v>185</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="E139" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="F139" s="1">
-        <v>45077</v>
+        <v>45737</v>
       </c>
       <c r="G139" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="15">
       <c r="A140">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B140" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="C140" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="D140" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="E140" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="F140" s="1">
-        <v>45079</v>
+        <v>45372</v>
       </c>
       <c r="G140" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="15">
       <c r="A141">
         <v>2023</v>
       </c>
       <c r="B141" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="C141" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="D141" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="E141" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="F141" s="1">
-        <v>45079</v>
+        <v>45006</v>
       </c>
       <c r="G141" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="15">
       <c r="A142">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B142" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="C142" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="D142" t="s">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="E142" t="s">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="F142" s="1">
-        <v>45081</v>
+        <v>45741</v>
       </c>
       <c r="G142" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15">
       <c r="A143">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B143" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
       <c r="C143" t="s">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="D143" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="E143" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="F143" s="1">
-        <v>45082</v>
+        <v>45376</v>
       </c>
       <c r="G143" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="15">
       <c r="A144">
         <v>2023</v>
       </c>
       <c r="B144" t="s">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="C144" t="s">
-        <v>7</v>
+        <v>189</v>
       </c>
       <c r="D144" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="E144" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="F144" s="1">
-        <v>45088</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+        <v>45010</v>
+      </c>
+      <c r="G144" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="15">
       <c r="A145">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B145" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C145" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="D145" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="E145" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F145" s="1">
-        <v>45088</v>
+        <v>46128</v>
       </c>
       <c r="G145" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="15">
       <c r="A146">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B146" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C146" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D146" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="E146" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="F146" s="1">
-        <v>45088</v>
+        <v>45763</v>
       </c>
       <c r="G146" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="15">
       <c r="A147">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B147" t="s">
-        <v>14</v>
+        <v>192</v>
       </c>
       <c r="C147" t="s">
-        <v>15</v>
+        <v>193</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="E147" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="F147" s="1">
-        <v>45089</v>
+        <v>45398</v>
       </c>
       <c r="G147" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="15">
       <c r="A148">
         <v>2023</v>
       </c>
       <c r="B148" t="s">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="C148" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="D148" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="E148" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="F148" s="1">
-        <v>45089</v>
+        <v>45032</v>
       </c>
       <c r="G148" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="15">
       <c r="A149">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B149" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C149" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D149" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="E149" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F149" s="1">
-        <v>45090</v>
+        <v>46128</v>
       </c>
       <c r="G149" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="15">
       <c r="A150">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B150" t="s">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="C150" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="D150" t="s">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="E150" t="s">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="F150" s="1">
-        <v>45107</v>
+        <v>45819</v>
       </c>
       <c r="G150" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="15">
       <c r="A151">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B151" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="C151" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="D151" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="E151" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="F151" s="1">
-        <v>45109</v>
+        <v>45454</v>
       </c>
       <c r="G151" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="15">
       <c r="A152">
         <v>2023</v>
       </c>
       <c r="B152" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C152" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D152" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E152" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="F152" s="1">
-        <v>45131</v>
+        <v>45088</v>
       </c>
       <c r="G152" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="15">
       <c r="A153">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B153" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="C153" t="s">
-        <v>59</v>
+        <v>203</v>
       </c>
       <c r="D153" t="s">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="E153" t="s">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="F153" s="1">
-        <v>45152</v>
+        <v>45862</v>
       </c>
       <c r="G153" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="15">
       <c r="A154">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="s">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="C154" t="s">
-        <v>43</v>
+        <v>203</v>
       </c>
       <c r="D154" t="s">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="E154" t="s">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="F154" s="1">
-        <v>45222</v>
+        <v>45497</v>
       </c>
       <c r="G154" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="15">
       <c r="A155">
         <v>2023</v>
       </c>
       <c r="B155" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="C155" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="D155" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="E155" t="s">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="F155" s="1">
-        <v>44977</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>45131</v>
+      </c>
+      <c r="G155" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="15">
       <c r="A156">
+        <v>2026</v>
+      </c>
+      <c r="B156" t="s">
+        <v>206</v>
+      </c>
+      <c r="C156" t="s">
+        <v>207</v>
+      </c>
+      <c r="D156" t="s">
+        <v>208</v>
+      </c>
+      <c r="E156" t="s">
+        <v>208</v>
+      </c>
+      <c r="F156" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G156" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="15">
+      <c r="A157">
+        <v>2025</v>
+      </c>
+      <c r="B157" t="s">
+        <v>206</v>
+      </c>
+      <c r="C157" t="s">
+        <v>207</v>
+      </c>
+      <c r="D157" t="s">
+        <v>208</v>
+      </c>
+      <c r="E157" t="s">
+        <v>208</v>
+      </c>
+      <c r="F157" s="1">
+        <v>45819</v>
+      </c>
+      <c r="G157" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="15">
+      <c r="A158">
+        <v>2024</v>
+      </c>
+      <c r="B158" t="s">
+        <v>206</v>
+      </c>
+      <c r="C158" t="s">
+        <v>207</v>
+      </c>
+      <c r="D158" t="s">
+        <v>208</v>
+      </c>
+      <c r="E158" t="s">
+        <v>208</v>
+      </c>
+      <c r="F158" s="1">
+        <v>45454</v>
+      </c>
+      <c r="G158" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="15">
+      <c r="A159">
         <v>2023</v>
       </c>
-      <c r="B156" t="s">
-        <v>166</v>
-      </c>
-      <c r="C156" t="s">
-        <v>167</v>
-      </c>
-      <c r="G156" t="s">
-        <v>168</v>
-      </c>
+      <c r="B159" t="s">
+        <v>206</v>
+      </c>
+      <c r="C159" t="s">
+        <v>207</v>
+      </c>
+      <c r="D159" t="s">
+        <v>208</v>
+      </c>
+      <c r="E159" t="s">
+        <v>208</v>
+      </c>
+      <c r="F159" s="1">
+        <v>45088</v>
+      </c>
+      <c r="G159" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="15">
+      <c r="A160">
+        <v>2025</v>
+      </c>
+      <c r="B160" t="s">
+        <v>210</v>
+      </c>
+      <c r="C160" t="s">
+        <v>211</v>
+      </c>
+      <c r="D160" t="s">
+        <v>212</v>
+      </c>
+      <c r="E160" t="s">
+        <v>212</v>
+      </c>
+      <c r="F160" s="1">
+        <v>45740</v>
+      </c>
+      <c r="G160" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="15">
+      <c r="A161">
+        <v>2024</v>
+      </c>
+      <c r="B161" t="s">
+        <v>210</v>
+      </c>
+      <c r="C161" t="s">
+        <v>211</v>
+      </c>
+      <c r="D161" t="s">
+        <v>212</v>
+      </c>
+      <c r="E161" t="s">
+        <v>212</v>
+      </c>
+      <c r="F161" s="1">
+        <v>45375</v>
+      </c>
+      <c r="G161" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="15">
+      <c r="A162">
+        <v>2023</v>
+      </c>
+      <c r="B162" t="s">
+        <v>210</v>
+      </c>
+      <c r="C162" t="s">
+        <v>211</v>
+      </c>
+      <c r="D162" t="s">
+        <v>212</v>
+      </c>
+      <c r="E162" t="s">
+        <v>212</v>
+      </c>
+      <c r="F162" s="1">
+        <v>45009</v>
+      </c>
+      <c r="G162" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="15">
+      <c r="A163">
+        <v>2026</v>
+      </c>
+      <c r="B163" t="s">
+        <v>214</v>
+      </c>
+      <c r="C163" t="s">
+        <v>215</v>
+      </c>
+      <c r="D163" t="s">
+        <v>216</v>
+      </c>
+      <c r="E163" t="s">
+        <v>216</v>
+      </c>
+      <c r="F163" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G163" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="15">
+      <c r="A164">
+        <v>2025</v>
+      </c>
+      <c r="B164" t="s">
+        <v>214</v>
+      </c>
+      <c r="C164" t="s">
+        <v>215</v>
+      </c>
+      <c r="D164" t="s">
+        <v>218</v>
+      </c>
+      <c r="E164" t="s">
+        <v>218</v>
+      </c>
+      <c r="F164" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G164" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="15">
+      <c r="A165">
+        <v>2024</v>
+      </c>
+      <c r="B165" t="s">
+        <v>214</v>
+      </c>
+      <c r="C165" t="s">
+        <v>215</v>
+      </c>
+      <c r="D165" t="s">
+        <v>218</v>
+      </c>
+      <c r="E165" t="s">
+        <v>218</v>
+      </c>
+      <c r="F165" s="1">
+        <v>45368</v>
+      </c>
+      <c r="G165" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="15">
+      <c r="A166">
+        <v>2023</v>
+      </c>
+      <c r="B166" t="s">
+        <v>214</v>
+      </c>
+      <c r="C166" t="s">
+        <v>215</v>
+      </c>
+      <c r="D166" t="s">
+        <v>218</v>
+      </c>
+      <c r="E166" t="s">
+        <v>218</v>
+      </c>
+      <c r="F166" s="1">
+        <v>45002</v>
+      </c>
+      <c r="G166" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="15">
+      <c r="A167">
+        <v>2025</v>
+      </c>
+      <c r="B167" t="s">
+        <v>219</v>
+      </c>
+      <c r="C167" t="s">
+        <v>220</v>
+      </c>
+      <c r="D167" t="s">
+        <v>221</v>
+      </c>
+      <c r="E167" t="s">
+        <v>221</v>
+      </c>
+      <c r="F167" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G167" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="15">
+      <c r="A168">
+        <v>2024</v>
+      </c>
+      <c r="B168" t="s">
+        <v>219</v>
+      </c>
+      <c r="C168" t="s">
+        <v>220</v>
+      </c>
+      <c r="D168" t="s">
+        <v>221</v>
+      </c>
+      <c r="E168" t="s">
+        <v>221</v>
+      </c>
+      <c r="F168" s="1">
+        <v>45347</v>
+      </c>
+      <c r="G168" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="15">
+      <c r="A169">
+        <v>2023</v>
+      </c>
+      <c r="B169" t="s">
+        <v>219</v>
+      </c>
+      <c r="C169" t="s">
+        <v>220</v>
+      </c>
+      <c r="D169" t="s">
+        <v>221</v>
+      </c>
+      <c r="E169" t="s">
+        <v>221</v>
+      </c>
+      <c r="F169" s="1">
+        <v>44982</v>
+      </c>
+      <c r="G169" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="15">
+      <c r="A170">
+        <v>2025</v>
+      </c>
+      <c r="B170" t="s">
+        <v>223</v>
+      </c>
+      <c r="C170" t="s">
+        <v>224</v>
+      </c>
+      <c r="D170" t="s">
+        <v>225</v>
+      </c>
+      <c r="E170" t="s">
+        <v>225</v>
+      </c>
+      <c r="F170" s="1">
+        <v>45821</v>
+      </c>
+      <c r="G170" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="15">
+      <c r="A171">
+        <v>2024</v>
+      </c>
+      <c r="B171" t="s">
+        <v>223</v>
+      </c>
+      <c r="C171" t="s">
+        <v>224</v>
+      </c>
+      <c r="D171" t="s">
+        <v>225</v>
+      </c>
+      <c r="E171" t="s">
+        <v>225</v>
+      </c>
+      <c r="F171" s="1">
+        <v>45456</v>
+      </c>
+      <c r="G171" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="15">
+      <c r="A172">
+        <v>2023</v>
+      </c>
+      <c r="B172" t="s">
+        <v>223</v>
+      </c>
+      <c r="C172" t="s">
+        <v>224</v>
+      </c>
+      <c r="D172" t="s">
+        <v>225</v>
+      </c>
+      <c r="E172" t="s">
+        <v>225</v>
+      </c>
+      <c r="F172" s="1">
+        <v>45090</v>
+      </c>
+      <c r="G172" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="15">
+      <c r="A173">
+        <v>2025</v>
+      </c>
+      <c r="B173" t="s">
+        <v>227</v>
+      </c>
+      <c r="C173" t="s">
+        <v>228</v>
+      </c>
+      <c r="D173" t="s">
+        <v>229</v>
+      </c>
+      <c r="E173" t="s">
+        <v>229</v>
+      </c>
+      <c r="F173" s="1">
+        <v>45805</v>
+      </c>
+      <c r="G173" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="15">
+      <c r="A174">
+        <v>2024</v>
+      </c>
+      <c r="B174" t="s">
+        <v>227</v>
+      </c>
+      <c r="C174" t="s">
+        <v>228</v>
+      </c>
+      <c r="D174" t="s">
+        <v>229</v>
+      </c>
+      <c r="E174" t="s">
+        <v>229</v>
+      </c>
+      <c r="F174" s="1">
+        <v>45440</v>
+      </c>
+      <c r="G174" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="15">
+      <c r="A175">
+        <v>2023</v>
+      </c>
+      <c r="B175" t="s">
+        <v>227</v>
+      </c>
+      <c r="C175" t="s">
+        <v>228</v>
+      </c>
+      <c r="D175" t="s">
+        <v>229</v>
+      </c>
+      <c r="E175" t="s">
+        <v>229</v>
+      </c>
+      <c r="F175" s="1">
+        <v>45074</v>
+      </c>
+      <c r="G175" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="15">
+      <c r="A176">
+        <v>2026</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C176" t="s">
+        <v>232</v>
+      </c>
+      <c r="D176" t="s">
+        <v>216</v>
+      </c>
+      <c r="E176" t="s">
+        <v>216</v>
+      </c>
+      <c r="F176" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G176" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="15">
+      <c r="A177">
+        <v>2025</v>
+      </c>
+      <c r="B177" t="s">
+        <v>231</v>
+      </c>
+      <c r="C177" t="s">
+        <v>232</v>
+      </c>
+      <c r="D177" t="s">
+        <v>234</v>
+      </c>
+      <c r="E177" t="s">
+        <v>234</v>
+      </c>
+      <c r="F177" s="1">
+        <v>45748</v>
+      </c>
+      <c r="G177" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="15">
+      <c r="A178">
+        <v>2024</v>
+      </c>
+      <c r="B178" t="s">
+        <v>231</v>
+      </c>
+      <c r="C178" t="s">
+        <v>232</v>
+      </c>
+      <c r="D178" t="s">
+        <v>234</v>
+      </c>
+      <c r="E178" t="s">
+        <v>234</v>
+      </c>
+      <c r="F178" s="1">
+        <v>45383</v>
+      </c>
+      <c r="G178" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="15">
+      <c r="A179">
+        <v>2023</v>
+      </c>
+      <c r="B179" t="s">
+        <v>231</v>
+      </c>
+      <c r="C179" t="s">
+        <v>232</v>
+      </c>
+      <c r="D179" t="s">
+        <v>234</v>
+      </c>
+      <c r="E179" t="s">
+        <v>234</v>
+      </c>
+      <c r="F179" s="1">
+        <v>45017</v>
+      </c>
+      <c r="G179" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="15">
+      <c r="A180">
+        <v>2026</v>
+      </c>
+      <c r="B180" t="s">
+        <v>235</v>
+      </c>
+      <c r="C180" t="s">
+        <v>236</v>
+      </c>
+      <c r="D180" t="s">
+        <v>237</v>
+      </c>
+      <c r="E180" t="s">
+        <v>237</v>
+      </c>
+      <c r="F180" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G180" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="15">
+      <c r="A181">
+        <v>2025</v>
+      </c>
+      <c r="B181" t="s">
+        <v>235</v>
+      </c>
+      <c r="C181" t="s">
+        <v>236</v>
+      </c>
+      <c r="D181" t="s">
+        <v>239</v>
+      </c>
+      <c r="E181" t="s">
+        <v>239</v>
+      </c>
+      <c r="F181" s="1">
+        <v>45744</v>
+      </c>
+      <c r="G181" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="15">
+      <c r="A182">
+        <v>2024</v>
+      </c>
+      <c r="B182" t="s">
+        <v>235</v>
+      </c>
+      <c r="C182" t="s">
+        <v>236</v>
+      </c>
+      <c r="D182" t="s">
+        <v>239</v>
+      </c>
+      <c r="E182" t="s">
+        <v>239</v>
+      </c>
+      <c r="F182" s="1">
+        <v>45379</v>
+      </c>
+      <c r="G182" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="15">
+      <c r="A183">
+        <v>2023</v>
+      </c>
+      <c r="B183" t="s">
+        <v>235</v>
+      </c>
+      <c r="C183" t="s">
+        <v>236</v>
+      </c>
+      <c r="D183" t="s">
+        <v>239</v>
+      </c>
+      <c r="E183" t="s">
+        <v>239</v>
+      </c>
+      <c r="F183" s="1">
+        <v>45013</v>
+      </c>
+      <c r="G183" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="15">
+      <c r="A184">
+        <v>2026</v>
+      </c>
+      <c r="B184" t="s">
+        <v>240</v>
+      </c>
+      <c r="C184" t="s">
+        <v>241</v>
+      </c>
+      <c r="D184" t="s">
+        <v>242</v>
+      </c>
+      <c r="F184" s="1">
+        <v>46122</v>
+      </c>
+      <c r="G184" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="15">
+      <c r="A185">
+        <v>2025</v>
+      </c>
+      <c r="B185" t="s">
+        <v>240</v>
+      </c>
+      <c r="C185" t="s">
+        <v>241</v>
+      </c>
+      <c r="D185" t="s">
+        <v>244</v>
+      </c>
+      <c r="E185" t="s">
+        <v>244</v>
+      </c>
+      <c r="F185" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G185" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="15">
+      <c r="A186">
+        <v>2024</v>
+      </c>
+      <c r="B186" t="s">
+        <v>240</v>
+      </c>
+      <c r="C186" t="s">
+        <v>241</v>
+      </c>
+      <c r="D186" t="s">
+        <v>244</v>
+      </c>
+      <c r="E186" t="s">
+        <v>244</v>
+      </c>
+      <c r="F186" s="1">
+        <v>45372</v>
+      </c>
+      <c r="G186" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="15">
+      <c r="A187">
+        <v>2023</v>
+      </c>
+      <c r="B187" t="s">
+        <v>240</v>
+      </c>
+      <c r="C187" t="s">
+        <v>241</v>
+      </c>
+      <c r="D187" t="s">
+        <v>244</v>
+      </c>
+      <c r="E187" t="s">
+        <v>244</v>
+      </c>
+      <c r="F187" s="1">
+        <v>45006</v>
+      </c>
+      <c r="G187" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="236" spans="11:11">
+      <c r="K236" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1">
-    <sortState ref="A2:G156">
-      <sortCondition descending="1" ref="A1"/>
+  <autoFilter ref="A1:G187" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G187">
+      <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1"/>
-    <hyperlink ref="G103" r:id="rId2"/>
-    <hyperlink ref="G155" r:id="rId3"/>
-    <hyperlink ref="G51" r:id="rId4"/>
+    <hyperlink ref="G40" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G42" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G43" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G41" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G17" r:id="rId5" xr:uid="{3F701E59-5D29-4E9C-8705-ECF744F7C80B}"/>
+    <hyperlink ref="G21" r:id="rId6" xr:uid="{F86867FF-E0A1-4B23-8E20-1EE5F172C1F2}"/>
+    <hyperlink ref="G28" r:id="rId7" xr:uid="{7B92F4FE-45A5-4FC3-BEF6-89060A75A0CF}"/>
+    <hyperlink ref="G32" r:id="rId8" xr:uid="{44483B5F-1D9D-4382-A3BB-08CC848203BB}"/>
+    <hyperlink ref="G36" r:id="rId9" xr:uid="{80C8F108-86E1-4547-810D-49EE9748B088}"/>
+    <hyperlink ref="G44" r:id="rId10" xr:uid="{44A2B85F-2D5D-4501-BD0D-1A1075EEBD87}"/>
+    <hyperlink ref="G47" r:id="rId11" xr:uid="{974F12BA-311E-4775-9C79-6B2367EE4C00}"/>
+    <hyperlink ref="G51" r:id="rId12" xr:uid="{9FD43934-382B-448D-9E13-39FD5028C9E3}"/>
+    <hyperlink ref="G55" r:id="rId13" xr:uid="{F5EC8224-9440-476C-B04B-BCD61BFD11DD}"/>
+    <hyperlink ref="G59" r:id="rId14" xr:uid="{6715A407-CEDE-4462-83D2-BA6A21538E94}"/>
+    <hyperlink ref="G63" r:id="rId15" xr:uid="{8C180C1D-CF21-400B-8B35-ACDD613A2648}"/>
+    <hyperlink ref="G70" r:id="rId16" xr:uid="{E80524B7-0871-4464-985C-CA93DB159F96}"/>
+    <hyperlink ref="E70" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto" xr:uid="{44E53C8F-307F-4558-8C5E-5645D7067E09}"/>
+    <hyperlink ref="G74" r:id="rId18" xr:uid="{BB1A3C55-886C-4149-9192-8222A522CCA0}"/>
+    <hyperlink ref="G87" r:id="rId19" location="informacoes-classificadas-e-desclassificadas" xr:uid="{F06BDAE5-9ADF-4DA7-920D-01903454D462}"/>
+    <hyperlink ref="G103" r:id="rId20" xr:uid="{CD1703C5-F786-4C99-88D4-BEA8E70C4138}"/>
+    <hyperlink ref="G102" r:id="rId21" xr:uid="{C77BD8BE-59BD-4BD4-9FAB-2123370B5889}"/>
+    <hyperlink ref="G98" r:id="rId22" xr:uid="{9388516A-40C8-4110-A15B-D0B6EE32A150}"/>
+    <hyperlink ref="G109" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{3301EBB6-9A25-48B2-9D8C-70083F27B1EA}"/>
+    <hyperlink ref="G113" r:id="rId24" location="informacoes-classificadas-e-desclassificadas" xr:uid="{7434A183-8C1E-4E4A-8E52-8EF290090E88}"/>
+    <hyperlink ref="G120" r:id="rId25" xr:uid="{4A3115E8-4CE5-4DFF-BF8C-76F55E18523A}"/>
+    <hyperlink ref="G127" r:id="rId26" xr:uid="{E28EBD52-B071-49FC-B6F4-D7C185EC3BD1}"/>
+    <hyperlink ref="G131" r:id="rId27" xr:uid="{995FBC4C-1A02-4126-AA25-76E795A0EB48}"/>
+    <hyperlink ref="G135" r:id="rId28" xr:uid="{80237B8F-DF43-47F0-80AC-616D77A1082D}"/>
+    <hyperlink ref="G145" r:id="rId29" xr:uid="{6AC60654-C774-4732-B0F1-240E2D6C4490}"/>
+    <hyperlink ref="G149" r:id="rId30" xr:uid="{AAF4FD60-6234-4214-BA5D-07ACABA79556}"/>
+    <hyperlink ref="G156" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{6EF2BF0D-AFAC-4C21-81A1-0D63CF1FEEE4}"/>
+    <hyperlink ref="G163" r:id="rId32" xr:uid="{81356907-EB5D-4FC6-90E5-4BC94C925F5E}"/>
+    <hyperlink ref="G176" r:id="rId33" xr:uid="{89F50D9C-749D-4ED1-B9C3-FA541C5DBEA0}"/>
+    <hyperlink ref="G180" r:id="rId34" location="info-class-des" xr:uid="{9E908A83-E592-48E3-A960-E01C6B504A9F}"/>
+    <hyperlink ref="G184" r:id="rId35" xr:uid="{6ACD1A2A-A2ED-4326-AB6D-AC1CAEB49DD3}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/orgao_sem_informacoes_classificadas.xlsx
+++ b/upload/orgao_sem_informacoes_classificadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD394BE3-3C64-458C-A0F1-18814C5C3656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FD01EC8-9690-4F32-8863-92C1F067EC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="252">
   <si>
     <t>ano</t>
   </si>
@@ -113,12 +113,18 @@
     <t>ARSAE</t>
   </si>
   <si>
+    <t>No momento não existe conteúdo a ser publicado. A Arsae-MG informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta,</t>
+  </si>
+  <si>
+    <t>No momento não existe conteúdo a ser publicado. A Arsae-MG informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta,</t>
+  </si>
+  <si>
+    <t>https://www.arsae.mg.gov.br/tra_informacoes/</t>
+  </si>
+  <si>
     <t>No momento não existe conteúdo a ser publicado. A Arsae-MG informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
-    <t>https://www.arsae.mg.gov.br/tra_informacoes/</t>
-  </si>
-  <si>
     <t>Agência Reguladora de Transportes do Estado de Minas Gerais</t>
   </si>
   <si>
@@ -401,12 +407,15 @@
     <t>FHA</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação Helena Antipoff informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>http://fha.mg.gov.br/pagina/transparencia/transparencia</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação Helena Antipoff informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
-    <t>http://fha.mg.gov.br/pagina/transparencia/transparencia</t>
-  </si>
-  <si>
     <t>Fundação Hospitalar do Estado de Minas Gerais - FHEMIG</t>
   </si>
   <si>
@@ -437,12 +446,15 @@
     <t>IDENE</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Instituto de Desenvolvimento do Norte e Nordeste de Minas Gerais (Idene) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>http://www.idene.mg.gov.br/site/informacoes-classificadas-e-desclassificadas/</t>
+  </si>
+  <si>
     <t>Nos últimos 12 meses, o Instituto de Desenvolvimento do Norte e Nordeste de Minas Gerais (Idene) não teve informações classificadas ou desclassificadas nos graus de sigilo: reservada, secreta e ultrassecreta, definidos no Art. 24 da Lei nº 12.527/2011 (Lei de Acesso à Informação).</t>
   </si>
   <si>
-    <t>http://www.idene.mg.gov.br/site/informacoes-classificadas-e-desclassificadas/</t>
-  </si>
-  <si>
     <t>Instituto de Previdência dos Servidores do Estado de Minas Gerais - IPSEMG</t>
   </si>
   <si>
@@ -515,6 +527,9 @@
     <t>IGAM</t>
   </si>
   <si>
+    <t>O Instituto Mineiro de Gestão das Águas - Igam não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta</t>
+  </si>
+  <si>
     <t>O IGAM não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
@@ -611,12 +626,15 @@
     <t>SCC</t>
   </si>
   <si>
+    <t>Na Secretaria de Estado de Casa Civil não houve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta</t>
+  </si>
+  <si>
+    <t>https://www.casacivil.mg.gov.br/Transparencia/Secretaria</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Casa Civil informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
-    <t>https://www.casacivil.mg.gov.br/Transparencia/Secretaria</t>
-  </si>
-  <si>
     <t>Secretaria de Estado de Comunicação Social - SECOM</t>
   </si>
   <si>
@@ -704,10 +722,13 @@
     <t>SEINFRA</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Infraestrutura, Mobilidade e Parcerias (Seinfra) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>http://www.infraestrutura.mg.gov.br/transparencia-publica/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>A Secretaria de Estado de Infraestrutura, Mobilidade e Parcerias - SEINFRA não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
-  </si>
-  <si>
-    <t>http://www.infraestrutura.mg.gov.br/transparencia-publica/informacoes-classificadas-e-desclassificadas</t>
   </si>
   <si>
     <t>Secretaria de Estado de Planejamento e Gestão de Minas Gerais - SEPLAG</t>
@@ -780,7 +801,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,13 +836,38 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -853,7 +899,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -868,6 +914,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1204,10 +1254,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K236"/>
+  <dimension ref="A1:K242"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1514,7 +1565,7 @@
     </row>
     <row r="14" spans="1:7" ht="15">
       <c r="A14">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
@@ -1526,18 +1577,18 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1">
-        <v>45810</v>
+        <v>46154</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15">
       <c r="A15">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1546,21 +1597,21 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1">
-        <v>45445</v>
+        <v>45810</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15">
       <c r="A16">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -1569,142 +1620,142 @@
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F16" s="1">
-        <v>45079</v>
+        <v>45445</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="1">
+        <v>45079</v>
+      </c>
+      <c r="G17" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G17" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15">
       <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15">
+      <c r="A19" s="10">
         <v>2025</v>
       </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="E18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="1">
         <v>45747</v>
       </c>
-      <c r="G18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15">
-      <c r="A19">
-        <v>2024</v>
-      </c>
-      <c r="B19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="1">
-        <v>45382</v>
-      </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15">
       <c r="A20">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F20" s="1">
-        <v>45016</v>
+        <v>45382</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15">
       <c r="A21">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
         <v>34</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="1">
+        <v>45016</v>
+      </c>
+      <c r="G21" t="s">
         <v>35</v>
-      </c>
-      <c r="D21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46127</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15">
       <c r="A22">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
         <v>38</v>
@@ -1713,159 +1764,159 @@
         <v>38</v>
       </c>
       <c r="F22" s="1">
-        <v>46022</v>
-      </c>
-      <c r="G22" t="s">
-        <v>37</v>
+        <v>46127</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15">
       <c r="A23">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F23" s="1">
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="G23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15">
       <c r="A24">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F24" s="1">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="G24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15">
       <c r="A25">
+        <v>2023</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="1">
+        <v>45291</v>
+      </c>
+      <c r="G25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15">
+      <c r="A26" s="10">
         <v>2025</v>
       </c>
-      <c r="B25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="B26" t="s">
         <v>41</v>
       </c>
-      <c r="E25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="1">
         <v>45812</v>
       </c>
-      <c r="G25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15">
-      <c r="A26">
-        <v>2024</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="1">
-        <v>45447</v>
-      </c>
       <c r="G26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15">
       <c r="A27">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F27" s="1">
-        <v>45081</v>
+        <v>45447</v>
       </c>
       <c r="G27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15">
       <c r="A28">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" t="s">
         <v>43</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="1">
+        <v>45081</v>
+      </c>
+      <c r="G28" t="s">
         <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="1">
-        <v>46099</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15">
       <c r="A29">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
         <v>47</v>
@@ -1874,182 +1925,182 @@
         <v>47</v>
       </c>
       <c r="F29" s="1">
-        <v>45780</v>
-      </c>
-      <c r="G29" t="s">
+        <v>46099</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15">
       <c r="A30">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F30" s="1">
-        <v>45415</v>
+        <v>45780</v>
       </c>
       <c r="G30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15">
       <c r="A31">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F31" s="1">
-        <v>45049</v>
+        <v>45415</v>
       </c>
       <c r="G31" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15">
       <c r="A32">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" t="s">
         <v>49</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="1">
+        <v>45049</v>
+      </c>
+      <c r="G32" t="s">
         <v>50</v>
-      </c>
-      <c r="D32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15">
       <c r="A33">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="F33" s="1">
-        <v>45953</v>
-      </c>
-      <c r="G33" t="s">
-        <v>52</v>
+        <v>46128</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15">
       <c r="A34">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F34" s="1">
-        <v>45588</v>
+        <v>45953</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15">
       <c r="A35">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F35" s="1">
-        <v>45222</v>
+        <v>45588</v>
       </c>
       <c r="G35" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15">
       <c r="A36">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" t="s">
         <v>53</v>
       </c>
-      <c r="C36" t="s">
+      <c r="E36" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="1">
+        <v>45222</v>
+      </c>
+      <c r="G36" t="s">
         <v>54</v>
-      </c>
-      <c r="D36" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" t="s">
-        <v>55</v>
-      </c>
-      <c r="F36" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15">
       <c r="A37">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D37" t="s">
         <v>57</v>
@@ -2058,525 +2109,525 @@
         <v>57</v>
       </c>
       <c r="F37" s="1">
-        <v>45735</v>
-      </c>
-      <c r="G37" t="s">
+        <v>46120</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15">
       <c r="A38">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F38" s="1">
-        <v>45370</v>
+        <v>45735</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15">
       <c r="A39">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F39" s="1">
-        <v>45004</v>
+        <v>45370</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15">
       <c r="A40">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" t="s">
         <v>59</v>
       </c>
-      <c r="C40" t="s">
+      <c r="E40" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G40" t="s">
         <v>60</v>
-      </c>
-      <c r="D40" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="1">
-        <v>46073</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15">
       <c r="A41">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F41" s="1">
-        <v>45708</v>
+        <v>46073</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15">
       <c r="A42">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F42" s="1">
-        <v>45342</v>
+        <v>45708</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15">
       <c r="A43">
+        <v>2024</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="1">
+        <v>45342</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15">
+      <c r="A44">
         <v>2023</v>
       </c>
-      <c r="B43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43" t="s">
-        <v>60</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="B44" t="s">
         <v>61</v>
       </c>
-      <c r="E43" t="s">
-        <v>61</v>
-      </c>
-      <c r="F43" s="1">
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="1">
         <v>44977</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75">
-      <c r="A44">
+      <c r="G44" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75">
+      <c r="A45">
         <v>2026</v>
       </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="B45" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="C45" t="s">
         <v>66</v>
       </c>
-      <c r="F44" s="1">
+      <c r="D45" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="1">
         <v>46135</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15">
-      <c r="A45">
-        <v>2024</v>
-      </c>
-      <c r="B45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" t="s">
-        <v>64</v>
-      </c>
-      <c r="D45" t="s">
-        <v>68</v>
-      </c>
-      <c r="E45" t="s">
-        <v>68</v>
-      </c>
-      <c r="F45" s="1">
-        <v>45657</v>
-      </c>
-      <c r="G45" t="s">
-        <v>67</v>
+      <c r="G45" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15">
       <c r="A46">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E46" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F46" s="1">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="G46" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15">
       <c r="A47">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B47" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" t="s">
+        <v>70</v>
+      </c>
+      <c r="E47" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" s="1">
+        <v>45291</v>
+      </c>
+      <c r="G47" t="s">
         <v>69</v>
-      </c>
-      <c r="C47" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" t="s">
-        <v>71</v>
-      </c>
-      <c r="F47" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15">
       <c r="A48">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
         <v>73</v>
       </c>
-      <c r="E48" t="s">
-        <v>73</v>
-      </c>
       <c r="F48" s="1">
-        <v>45883</v>
-      </c>
-      <c r="G48" t="s">
-        <v>72</v>
+        <v>46140</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F49" s="1">
-        <v>45518</v>
+        <v>45883</v>
       </c>
       <c r="G49" t="s">
-        <v>72</v>
-      </c>
-      <c r="I49" s="1"/>
+        <v>74</v>
+      </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F50" s="1">
-        <v>45152</v>
+        <v>45518</v>
       </c>
       <c r="G50" t="s">
-        <v>72</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45152</v>
+      </c>
+      <c r="G51" t="s">
         <v>74</v>
-      </c>
-      <c r="C51" t="s">
-        <v>75</v>
-      </c>
-      <c r="D51" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" t="s">
-        <v>76</v>
-      </c>
-      <c r="F51" s="1">
-        <v>61</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D52" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E52" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F52" s="1">
-        <v>45717</v>
-      </c>
-      <c r="G52" t="s">
-        <v>77</v>
+        <v>61</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F53" s="1">
-        <v>45352</v>
+        <v>45717</v>
       </c>
       <c r="G53" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E54" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F54" s="1">
-        <v>44986</v>
+        <v>45352</v>
       </c>
       <c r="G54" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" t="s">
         <v>78</v>
       </c>
-      <c r="C55" t="s">
+      <c r="E55" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55" s="1">
+        <v>44986</v>
+      </c>
+      <c r="G55" t="s">
         <v>79</v>
-      </c>
-      <c r="D55" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F55" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D56" t="s">
         <v>82</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="7" t="s">
         <v>82</v>
       </c>
       <c r="F56" s="1">
-        <v>45742</v>
-      </c>
-      <c r="G56" t="s">
-        <v>81</v>
+        <v>46125</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E57" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F57" s="1">
-        <v>45377</v>
+        <v>45742</v>
       </c>
       <c r="G57" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E58" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F58" s="1">
-        <v>45011</v>
+        <v>45377</v>
       </c>
       <c r="G58" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B59" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" t="s">
+        <v>84</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45011</v>
+      </c>
+      <c r="G59" t="s">
         <v>83</v>
-      </c>
-      <c r="C59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" t="s">
-        <v>85</v>
-      </c>
-      <c r="E59" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D60" t="s">
         <v>87</v>
@@ -2585,90 +2636,90 @@
         <v>87</v>
       </c>
       <c r="F60" s="1">
-        <v>45792</v>
-      </c>
-      <c r="G60" t="s">
-        <v>86</v>
+        <v>46120</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E61" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F61" s="1">
-        <v>45427</v>
+        <v>45792</v>
       </c>
       <c r="G61" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F62" s="1">
-        <v>45061</v>
+        <v>45427</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" t="s">
+        <v>89</v>
+      </c>
+      <c r="E63" t="s">
+        <v>89</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45061</v>
+      </c>
+      <c r="G63" t="s">
         <v>88</v>
-      </c>
-      <c r="C63" t="s">
-        <v>89</v>
-      </c>
-      <c r="D63" t="s">
-        <v>90</v>
-      </c>
-      <c r="E63" t="s">
-        <v>90</v>
-      </c>
-      <c r="F63" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D64" t="s">
         <v>92</v>
@@ -2677,251 +2728,251 @@
         <v>92</v>
       </c>
       <c r="F64" s="1">
-        <v>45730</v>
-      </c>
-      <c r="G64" t="s">
+        <v>46140</v>
+      </c>
+      <c r="G64" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15">
       <c r="A65">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E65" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F65" s="1">
-        <v>45365</v>
+        <v>45730</v>
       </c>
       <c r="G65" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15">
       <c r="A66">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C66" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D66" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E66" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F66" s="1">
-        <v>44999</v>
+        <v>45365</v>
       </c>
       <c r="G66" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15">
       <c r="A67">
+        <v>2023</v>
+      </c>
+      <c r="B67" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" t="s">
+        <v>94</v>
+      </c>
+      <c r="E67" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" s="1">
+        <v>44999</v>
+      </c>
+      <c r="G67" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15">
+      <c r="A68" s="10">
         <v>2025</v>
       </c>
-      <c r="B67" t="s">
-        <v>94</v>
-      </c>
-      <c r="C67" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="B68" t="s">
         <v>96</v>
       </c>
-      <c r="E67" t="s">
-        <v>96</v>
-      </c>
-      <c r="F67" s="1">
+      <c r="C68" t="s">
+        <v>97</v>
+      </c>
+      <c r="D68" t="s">
+        <v>98</v>
+      </c>
+      <c r="E68" t="s">
+        <v>98</v>
+      </c>
+      <c r="F68" s="1">
         <v>45756</v>
       </c>
-      <c r="G67" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15">
-      <c r="A68">
-        <v>2024</v>
-      </c>
-      <c r="B68" t="s">
-        <v>94</v>
-      </c>
-      <c r="C68" t="s">
-        <v>95</v>
-      </c>
-      <c r="D68" t="s">
-        <v>96</v>
-      </c>
-      <c r="E68" t="s">
-        <v>96</v>
-      </c>
-      <c r="F68" s="1">
-        <v>45391</v>
-      </c>
       <c r="G68" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15">
       <c r="A69">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D69" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E69" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F69" s="1">
-        <v>45025</v>
+        <v>45391</v>
       </c>
       <c r="G69" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15">
       <c r="A70">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B70" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" t="s">
         <v>98</v>
       </c>
-      <c r="C70" t="s">
+      <c r="E70" t="s">
+        <v>98</v>
+      </c>
+      <c r="F70" s="1">
+        <v>45025</v>
+      </c>
+      <c r="G70" t="s">
         <v>99</v>
-      </c>
-      <c r="D70" t="s">
-        <v>100</v>
-      </c>
-      <c r="E70" t="s">
-        <v>101</v>
-      </c>
-      <c r="F70" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15">
       <c r="A71">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E71" t="s">
         <v>103</v>
       </c>
       <c r="F71" s="1">
-        <v>45820</v>
-      </c>
-      <c r="G71" t="s">
+        <v>46128</v>
+      </c>
+      <c r="G71" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15">
       <c r="A72">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D72" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E72" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F72" s="1">
-        <v>45455</v>
+        <v>45820</v>
       </c>
       <c r="G72" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15">
       <c r="A73">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C73" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D73" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E73" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F73" s="1">
-        <v>45089</v>
+        <v>45455</v>
       </c>
       <c r="G73" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15">
       <c r="A74">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B74" t="s">
+        <v>100</v>
+      </c>
+      <c r="C74" t="s">
+        <v>101</v>
+      </c>
+      <c r="D74" t="s">
         <v>105</v>
       </c>
-      <c r="C74" t="s">
+      <c r="E74" t="s">
+        <v>105</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45089</v>
+      </c>
+      <c r="G74" t="s">
         <v>106</v>
-      </c>
-      <c r="D74" t="s">
-        <v>107</v>
-      </c>
-      <c r="E74" t="s">
-        <v>107</v>
-      </c>
-      <c r="F74" s="1">
-        <v>46142</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15">
       <c r="A75">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D75" t="s">
         <v>109</v>
@@ -2930,274 +2981,271 @@
         <v>109</v>
       </c>
       <c r="F75" s="1">
-        <v>45813</v>
-      </c>
-      <c r="G75" t="s">
-        <v>108</v>
+        <v>46142</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15">
       <c r="A76">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D76" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E76" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F76" s="1">
-        <v>45448</v>
+        <v>45813</v>
       </c>
       <c r="G76" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15">
       <c r="A77">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B77" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D77" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E77" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F77" s="1">
-        <v>45082</v>
+        <v>45448</v>
       </c>
       <c r="G77" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15">
       <c r="A78">
+        <v>2023</v>
+      </c>
+      <c r="B78" t="s">
+        <v>107</v>
+      </c>
+      <c r="C78" t="s">
+        <v>108</v>
+      </c>
+      <c r="D78" t="s">
+        <v>111</v>
+      </c>
+      <c r="E78" t="s">
+        <v>111</v>
+      </c>
+      <c r="F78" s="1">
+        <v>45082</v>
+      </c>
+      <c r="G78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15">
+      <c r="A79" s="11">
         <v>2025</v>
       </c>
-      <c r="B78" t="s">
-        <v>110</v>
-      </c>
-      <c r="C78" t="s">
-        <v>111</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="B79" t="s">
         <v>112</v>
       </c>
-      <c r="E78" t="s">
-        <v>112</v>
-      </c>
-      <c r="F78" s="1">
+      <c r="C79" t="s">
+        <v>113</v>
+      </c>
+      <c r="D79" t="s">
+        <v>114</v>
+      </c>
+      <c r="E79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F79" s="1">
         <v>45730</v>
       </c>
-      <c r="G78" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15">
-      <c r="A79">
-        <v>2024</v>
-      </c>
-      <c r="B79" t="s">
-        <v>110</v>
-      </c>
-      <c r="C79" t="s">
-        <v>111</v>
-      </c>
-      <c r="D79" t="s">
-        <v>112</v>
-      </c>
-      <c r="E79" t="s">
-        <v>112</v>
-      </c>
-      <c r="F79" s="1">
-        <v>45365</v>
-      </c>
       <c r="G79" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15">
       <c r="A80">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B80" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C80" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D80" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F80" s="1">
-        <v>44999</v>
+        <v>45365</v>
       </c>
       <c r="G80" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15">
       <c r="A81">
+        <v>2023</v>
+      </c>
+      <c r="B81" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" t="s">
+        <v>113</v>
+      </c>
+      <c r="D81" t="s">
+        <v>114</v>
+      </c>
+      <c r="E81" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" s="1">
+        <v>44999</v>
+      </c>
+      <c r="G81" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15">
+      <c r="A82" s="12">
         <v>2025</v>
       </c>
-      <c r="B81" t="s">
-        <v>114</v>
-      </c>
-      <c r="C81" t="s">
-        <v>115</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="B82" t="s">
         <v>116</v>
       </c>
-      <c r="E81" t="s">
-        <v>116</v>
-      </c>
-      <c r="F81" s="1">
+      <c r="C82" t="s">
+        <v>117</v>
+      </c>
+      <c r="D82" t="s">
+        <v>118</v>
+      </c>
+      <c r="E82" t="s">
+        <v>118</v>
+      </c>
+      <c r="F82" s="1">
         <v>45736</v>
       </c>
-      <c r="G81" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15">
-      <c r="A82">
-        <v>2024</v>
-      </c>
-      <c r="B82" t="s">
-        <v>114</v>
-      </c>
-      <c r="C82" t="s">
-        <v>115</v>
-      </c>
-      <c r="D82" t="s">
-        <v>116</v>
-      </c>
-      <c r="E82" t="s">
-        <v>116</v>
-      </c>
-      <c r="F82" s="1">
-        <v>45371</v>
-      </c>
       <c r="G82" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15">
       <c r="A83">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D83" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E83" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F83" s="1">
-        <v>45005</v>
+        <v>45371</v>
       </c>
       <c r="G83" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15">
       <c r="A84">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B84" t="s">
+        <v>116</v>
+      </c>
+      <c r="C84" t="s">
+        <v>117</v>
+      </c>
+      <c r="D84" t="s">
         <v>118</v>
       </c>
-      <c r="C84" t="s">
+      <c r="E84" t="s">
+        <v>118</v>
+      </c>
+      <c r="F84" s="1">
+        <v>45005</v>
+      </c>
+      <c r="G84" t="s">
         <v>119</v>
-      </c>
-      <c r="D84" t="s">
-        <v>120</v>
-      </c>
-      <c r="E84" t="s">
-        <v>120</v>
-      </c>
-      <c r="F84" s="1">
-        <v>45838</v>
-      </c>
-      <c r="G84" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15">
       <c r="A85">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B85" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D85" t="s">
-        <v>120</v>
-      </c>
-      <c r="E85" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F85" s="1">
-        <v>45473</v>
-      </c>
-      <c r="G85" t="s">
-        <v>121</v>
+        <v>46128</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15">
       <c r="A86">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B86" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D86" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E86" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F86" s="1">
-        <v>45107</v>
+        <v>45838</v>
       </c>
       <c r="G86" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15">
       <c r="A87">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B87" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D87" t="s">
         <v>124</v>
@@ -3206,21 +3254,21 @@
         <v>124</v>
       </c>
       <c r="F87" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>125</v>
+        <v>45473</v>
+      </c>
+      <c r="G87" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15">
       <c r="A88">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
         <v>124</v>
@@ -3229,401 +3277,401 @@
         <v>124</v>
       </c>
       <c r="F88" s="1">
-        <v>45742</v>
+        <v>45107</v>
       </c>
       <c r="G88" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15">
       <c r="A89">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C89" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D89" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E89" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F89" s="1">
-        <v>45377</v>
-      </c>
-      <c r="G89" t="s">
-        <v>125</v>
+        <v>46126</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15">
       <c r="A90">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B90" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C90" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F90" s="1">
-        <v>45011</v>
+        <v>45742</v>
       </c>
       <c r="G90" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15">
       <c r="A91">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B91" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" t="s">
         <v>126</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>127</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>127</v>
+      </c>
+      <c r="F91" s="1">
+        <v>45377</v>
+      </c>
+      <c r="G91" t="s">
         <v>128</v>
-      </c>
-      <c r="E91" t="s">
-        <v>128</v>
-      </c>
-      <c r="F91" s="1">
-        <v>46127</v>
-      </c>
-      <c r="G91" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15">
       <c r="A92">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B92" t="s">
+        <v>125</v>
+      </c>
+      <c r="C92" t="s">
         <v>126</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>127</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
+        <v>127</v>
+      </c>
+      <c r="F92" s="1">
+        <v>45011</v>
+      </c>
+      <c r="G92" t="s">
         <v>128</v>
-      </c>
-      <c r="E92" t="s">
-        <v>128</v>
-      </c>
-      <c r="F92" s="1">
-        <v>45808</v>
-      </c>
-      <c r="G92" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15">
       <c r="A93">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B93" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D93" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E93" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F93" s="1">
-        <v>45443</v>
+        <v>46127</v>
       </c>
       <c r="G93" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15">
       <c r="A94">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B94" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C94" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E94" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F94" s="1">
-        <v>45077</v>
+        <v>45808</v>
       </c>
       <c r="G94" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15">
       <c r="A95">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B95" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95" t="s">
         <v>130</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>131</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
+        <v>131</v>
+      </c>
+      <c r="F95" s="1">
+        <v>45443</v>
+      </c>
+      <c r="G95" t="s">
         <v>132</v>
-      </c>
-      <c r="E95" t="s">
-        <v>132</v>
-      </c>
-      <c r="F95" s="1">
-        <v>45736</v>
-      </c>
-      <c r="G95" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15">
       <c r="A96">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B96" t="s">
+        <v>129</v>
+      </c>
+      <c r="C96" t="s">
         <v>130</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>131</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>131</v>
+      </c>
+      <c r="F96" s="1">
+        <v>45077</v>
+      </c>
+      <c r="G96" t="s">
         <v>132</v>
-      </c>
-      <c r="E96" t="s">
-        <v>132</v>
-      </c>
-      <c r="F96" s="1">
-        <v>45371</v>
-      </c>
-      <c r="G96" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15">
       <c r="A97">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D97" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E97" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F97" s="1">
-        <v>45005</v>
-      </c>
-      <c r="G97" t="s">
-        <v>133</v>
+        <v>46135</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
       <c r="A98">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B98" t="s">
+        <v>133</v>
+      </c>
+      <c r="C98" t="s">
         <v>134</v>
       </c>
-      <c r="C98" t="s">
-        <v>135</v>
-      </c>
       <c r="D98" t="s">
+        <v>137</v>
+      </c>
+      <c r="E98" t="s">
+        <v>137</v>
+      </c>
+      <c r="F98" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G98" t="s">
         <v>136</v>
-      </c>
-      <c r="E98" t="s">
-        <v>136</v>
-      </c>
-      <c r="F98" s="1">
-        <v>46121</v>
-      </c>
-      <c r="G98" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15">
       <c r="A99">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B99" t="s">
+        <v>133</v>
+      </c>
+      <c r="C99" t="s">
         <v>134</v>
       </c>
-      <c r="C99" t="s">
-        <v>135</v>
-      </c>
       <c r="D99" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E99" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F99" s="1">
-        <v>45735</v>
+        <v>45371</v>
       </c>
       <c r="G99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15">
       <c r="A100">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B100" t="s">
+        <v>133</v>
+      </c>
+      <c r="C100" t="s">
         <v>134</v>
       </c>
-      <c r="C100" t="s">
-        <v>135</v>
-      </c>
       <c r="D100" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E100" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F100" s="1">
-        <v>45370</v>
+        <v>45005</v>
       </c>
       <c r="G100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15">
       <c r="A101">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B101" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C101" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D101" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E101" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F101" s="1">
-        <v>45004</v>
+        <v>46121</v>
       </c>
       <c r="G101" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15">
       <c r="A102">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B102" t="s">
+        <v>138</v>
+      </c>
+      <c r="C102" t="s">
         <v>139</v>
       </c>
-      <c r="C102" t="s">
-        <v>140</v>
-      </c>
       <c r="D102" t="s">
+        <v>142</v>
+      </c>
+      <c r="E102" t="s">
+        <v>142</v>
+      </c>
+      <c r="F102" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G102" t="s">
         <v>141</v>
-      </c>
-      <c r="E102" t="s">
-        <v>141</v>
-      </c>
-      <c r="F102" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G102" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15">
       <c r="A103">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B103" t="s">
+        <v>138</v>
+      </c>
+      <c r="C103" t="s">
         <v>139</v>
       </c>
-      <c r="C103" t="s">
-        <v>140</v>
-      </c>
       <c r="D103" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" t="s">
+        <v>142</v>
+      </c>
+      <c r="F103" s="1">
+        <v>45370</v>
+      </c>
+      <c r="G103" t="s">
         <v>141</v>
-      </c>
-      <c r="E103" t="s">
-        <v>141</v>
-      </c>
-      <c r="F103" s="1">
-        <v>45741</v>
-      </c>
-      <c r="G103" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15">
       <c r="A104">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B104" t="s">
+        <v>138</v>
+      </c>
+      <c r="C104" t="s">
         <v>139</v>
       </c>
-      <c r="C104" t="s">
-        <v>140</v>
-      </c>
       <c r="D104" t="s">
+        <v>142</v>
+      </c>
+      <c r="E104" t="s">
+        <v>142</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G104" t="s">
         <v>141</v>
-      </c>
-      <c r="E104" t="s">
-        <v>141</v>
-      </c>
-      <c r="F104" s="1">
-        <v>45376</v>
-      </c>
-      <c r="G104" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15">
       <c r="A105">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B105" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D105" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E105" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F105" s="1">
-        <v>45010</v>
+        <v>46126</v>
       </c>
       <c r="G105" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15">
@@ -3643,7 +3691,7 @@
         <v>145</v>
       </c>
       <c r="F106" s="1">
-        <v>45751</v>
+        <v>45741</v>
       </c>
       <c r="G106" t="s">
         <v>146</v>
@@ -3666,7 +3714,7 @@
         <v>145</v>
       </c>
       <c r="F107" s="1">
-        <v>45386</v>
+        <v>45376</v>
       </c>
       <c r="G107" t="s">
         <v>146</v>
@@ -3689,15 +3737,15 @@
         <v>145</v>
       </c>
       <c r="F108" s="1">
-        <v>45020</v>
+        <v>45010</v>
       </c>
       <c r="G108" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15">
-      <c r="A109">
-        <v>2026</v>
+      <c r="A109" s="10">
+        <v>2025</v>
       </c>
       <c r="B109" t="s">
         <v>147</v>
@@ -3712,7 +3760,7 @@
         <v>149</v>
       </c>
       <c r="F109" s="1">
-        <v>46120</v>
+        <v>45751</v>
       </c>
       <c r="G109" t="s">
         <v>150</v>
@@ -3720,7 +3768,7 @@
     </row>
     <row r="110" spans="1:7" ht="15">
       <c r="A110">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B110" t="s">
         <v>147</v>
@@ -3735,7 +3783,7 @@
         <v>149</v>
       </c>
       <c r="F110" s="1">
-        <v>45810</v>
+        <v>45386</v>
       </c>
       <c r="G110" t="s">
         <v>150</v>
@@ -3743,7 +3791,7 @@
     </row>
     <row r="111" spans="1:7" ht="15">
       <c r="A111">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B111" t="s">
         <v>147</v>
@@ -3758,7 +3806,7 @@
         <v>149</v>
       </c>
       <c r="F111" s="1">
-        <v>45445</v>
+        <v>45020</v>
       </c>
       <c r="G111" t="s">
         <v>150</v>
@@ -3766,30 +3814,30 @@
     </row>
     <row r="112" spans="1:7" ht="15">
       <c r="A112">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B112" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C112" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D112" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E112" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F112" s="1">
-        <v>45079</v>
+        <v>46120</v>
       </c>
       <c r="G112" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15">
       <c r="A113">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B113" t="s">
         <v>151</v>
@@ -3804,7 +3852,7 @@
         <v>153</v>
       </c>
       <c r="F113" s="1">
-        <v>46126</v>
+        <v>45810</v>
       </c>
       <c r="G113" t="s">
         <v>154</v>
@@ -3812,7 +3860,7 @@
     </row>
     <row r="114" spans="1:7" ht="15">
       <c r="A114">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B114" t="s">
         <v>151</v>
@@ -3821,13 +3869,13 @@
         <v>152</v>
       </c>
       <c r="D114" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E114" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F114" s="1">
-        <v>45735</v>
+        <v>45445</v>
       </c>
       <c r="G114" t="s">
         <v>154</v>
@@ -3835,7 +3883,7 @@
     </row>
     <row r="115" spans="1:7" ht="15">
       <c r="A115">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B115" t="s">
         <v>151</v>
@@ -3844,13 +3892,13 @@
         <v>152</v>
       </c>
       <c r="D115" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E115" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F115" s="1">
-        <v>45370</v>
+        <v>45079</v>
       </c>
       <c r="G115" t="s">
         <v>154</v>
@@ -3858,25 +3906,25 @@
     </row>
     <row r="116" spans="1:7" ht="15">
       <c r="A116">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B116" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C116" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D116" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E116" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F116" s="1">
-        <v>45004</v>
+        <v>46126</v>
       </c>
       <c r="G116" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15">
@@ -3884,22 +3932,22 @@
         <v>2025</v>
       </c>
       <c r="B117" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" t="s">
         <v>156</v>
       </c>
-      <c r="C117" t="s">
-        <v>157</v>
-      </c>
       <c r="D117" t="s">
+        <v>159</v>
+      </c>
+      <c r="E117" t="s">
+        <v>159</v>
+      </c>
+      <c r="F117" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G117" t="s">
         <v>158</v>
-      </c>
-      <c r="E117" t="s">
-        <v>158</v>
-      </c>
-      <c r="F117" s="1">
-        <v>45840</v>
-      </c>
-      <c r="G117" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15">
@@ -3907,22 +3955,22 @@
         <v>2024</v>
       </c>
       <c r="B118" t="s">
+        <v>155</v>
+      </c>
+      <c r="C118" t="s">
         <v>156</v>
       </c>
-      <c r="C118" t="s">
-        <v>157</v>
-      </c>
       <c r="D118" t="s">
+        <v>159</v>
+      </c>
+      <c r="E118" t="s">
+        <v>159</v>
+      </c>
+      <c r="F118" s="1">
+        <v>45370</v>
+      </c>
+      <c r="G118" t="s">
         <v>158</v>
-      </c>
-      <c r="E118" t="s">
-        <v>158</v>
-      </c>
-      <c r="F118" s="1">
-        <v>45475</v>
-      </c>
-      <c r="G118" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15">
@@ -3930,26 +3978,26 @@
         <v>2023</v>
       </c>
       <c r="B119" t="s">
+        <v>155</v>
+      </c>
+      <c r="C119" t="s">
         <v>156</v>
       </c>
-      <c r="C119" t="s">
-        <v>157</v>
-      </c>
       <c r="D119" t="s">
+        <v>159</v>
+      </c>
+      <c r="E119" t="s">
+        <v>159</v>
+      </c>
+      <c r="F119" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G119" t="s">
         <v>158</v>
       </c>
-      <c r="E119" t="s">
-        <v>158</v>
-      </c>
-      <c r="F119" s="1">
-        <v>45109</v>
-      </c>
-      <c r="G119" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="120" spans="1:7" ht="15">
-      <c r="A120">
+      <c r="A120" s="10">
         <v>2026</v>
       </c>
       <c r="B120" t="s">
@@ -3965,10 +4013,7 @@
         <v>162</v>
       </c>
       <c r="F120" s="1">
-        <v>46139</v>
-      </c>
-      <c r="G120" t="s">
-        <v>163</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15">
@@ -3982,16 +4027,16 @@
         <v>161</v>
       </c>
       <c r="D121" t="s">
+        <v>163</v>
+      </c>
+      <c r="E121" t="s">
+        <v>163</v>
+      </c>
+      <c r="F121" s="1">
+        <v>45840</v>
+      </c>
+      <c r="G121" t="s">
         <v>164</v>
-      </c>
-      <c r="E121" t="s">
-        <v>164</v>
-      </c>
-      <c r="F121" s="1">
-        <v>45749</v>
-      </c>
-      <c r="G121" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15">
@@ -4005,16 +4050,16 @@
         <v>161</v>
       </c>
       <c r="D122" t="s">
+        <v>163</v>
+      </c>
+      <c r="E122" t="s">
+        <v>163</v>
+      </c>
+      <c r="F122" s="1">
+        <v>45475</v>
+      </c>
+      <c r="G122" t="s">
         <v>164</v>
-      </c>
-      <c r="E122" t="s">
-        <v>164</v>
-      </c>
-      <c r="F122" s="1">
-        <v>45384</v>
-      </c>
-      <c r="G122" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15">
@@ -4028,21 +4073,21 @@
         <v>161</v>
       </c>
       <c r="D123" t="s">
+        <v>163</v>
+      </c>
+      <c r="E123" t="s">
+        <v>163</v>
+      </c>
+      <c r="F123" s="1">
+        <v>45109</v>
+      </c>
+      <c r="G123" t="s">
         <v>164</v>
-      </c>
-      <c r="E123" t="s">
-        <v>164</v>
-      </c>
-      <c r="F123" s="1">
-        <v>45018</v>
-      </c>
-      <c r="G123" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15">
       <c r="A124">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B124" t="s">
         <v>165</v>
@@ -4057,7 +4102,7 @@
         <v>167</v>
       </c>
       <c r="F124" s="1">
-        <v>45744</v>
+        <v>46139</v>
       </c>
       <c r="G124" t="s">
         <v>168</v>
@@ -4065,7 +4110,7 @@
     </row>
     <row r="125" spans="1:7" ht="15">
       <c r="A125">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B125" t="s">
         <v>165</v>
@@ -4074,13 +4119,13 @@
         <v>166</v>
       </c>
       <c r="D125" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E125" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F125" s="1">
-        <v>45379</v>
+        <v>45749</v>
       </c>
       <c r="G125" t="s">
         <v>168</v>
@@ -4088,7 +4133,7 @@
     </row>
     <row r="126" spans="1:7" ht="15">
       <c r="A126">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B126" t="s">
         <v>165</v>
@@ -4097,13 +4142,13 @@
         <v>166</v>
       </c>
       <c r="D126" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E126" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F126" s="1">
-        <v>45013</v>
+        <v>45384</v>
       </c>
       <c r="G126" t="s">
         <v>168</v>
@@ -4111,48 +4156,48 @@
     </row>
     <row r="127" spans="1:7" ht="15">
       <c r="A127">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B127" t="s">
+        <v>165</v>
+      </c>
+      <c r="C127" t="s">
+        <v>166</v>
+      </c>
+      <c r="D127" t="s">
         <v>169</v>
       </c>
-      <c r="C127" t="s">
+      <c r="E127" t="s">
+        <v>169</v>
+      </c>
+      <c r="F127" s="1">
+        <v>45018</v>
+      </c>
+      <c r="G127" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15">
+      <c r="A128" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B128" t="s">
         <v>170</v>
       </c>
-      <c r="D127" t="s">
+      <c r="C128" t="s">
         <v>171</v>
       </c>
-      <c r="E127" t="s">
-        <v>171</v>
-      </c>
-      <c r="F127" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G127" t="s">
+      <c r="D128" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="15">
-      <c r="A128">
-        <v>2025</v>
-      </c>
-      <c r="B128" t="s">
-        <v>169</v>
-      </c>
-      <c r="C128" t="s">
-        <v>170</v>
-      </c>
-      <c r="D128" t="s">
-        <v>171</v>
-      </c>
       <c r="E128" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F128" s="1">
-        <v>45733</v>
+        <v>45744</v>
       </c>
       <c r="G128" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15">
@@ -4160,22 +4205,22 @@
         <v>2024</v>
       </c>
       <c r="B129" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C129" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D129" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E129" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F129" s="1">
-        <v>45368</v>
+        <v>45379</v>
       </c>
       <c r="G129" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15">
@@ -4183,22 +4228,22 @@
         <v>2023</v>
       </c>
       <c r="B130" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C130" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D130" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E130" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F130" s="1">
-        <v>45002</v>
+        <v>45013</v>
       </c>
       <c r="G130" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15">
@@ -4206,22 +4251,22 @@
         <v>2026</v>
       </c>
       <c r="B131" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C131" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D131" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E131" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F131" s="1">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="G131" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15">
@@ -4229,22 +4274,22 @@
         <v>2025</v>
       </c>
       <c r="B132" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C132" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D132" t="s">
+        <v>176</v>
+      </c>
+      <c r="E132" t="s">
+        <v>176</v>
+      </c>
+      <c r="F132" s="1">
+        <v>45733</v>
+      </c>
+      <c r="G132" t="s">
         <v>177</v>
-      </c>
-      <c r="E132" t="s">
-        <v>177</v>
-      </c>
-      <c r="F132" s="1">
-        <v>45735</v>
-      </c>
-      <c r="G132" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15">
@@ -4252,22 +4297,22 @@
         <v>2024</v>
       </c>
       <c r="B133" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C133" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D133" t="s">
+        <v>176</v>
+      </c>
+      <c r="E133" t="s">
+        <v>176</v>
+      </c>
+      <c r="F133" s="1">
+        <v>45368</v>
+      </c>
+      <c r="G133" t="s">
         <v>177</v>
-      </c>
-      <c r="E133" t="s">
-        <v>177</v>
-      </c>
-      <c r="F133" s="1">
-        <v>45370</v>
-      </c>
-      <c r="G133" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15">
@@ -4275,22 +4320,22 @@
         <v>2023</v>
       </c>
       <c r="B134" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C134" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D134" t="s">
+        <v>176</v>
+      </c>
+      <c r="E134" t="s">
+        <v>176</v>
+      </c>
+      <c r="F134" s="1">
+        <v>45002</v>
+      </c>
+      <c r="G134" t="s">
         <v>177</v>
-      </c>
-      <c r="E134" t="s">
-        <v>177</v>
-      </c>
-      <c r="F134" s="1">
-        <v>45004</v>
-      </c>
-      <c r="G134" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15">
@@ -4307,13 +4352,13 @@
         <v>180</v>
       </c>
       <c r="E135" t="s">
+        <v>180</v>
+      </c>
+      <c r="F135" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G135" t="s">
         <v>181</v>
-      </c>
-      <c r="F135" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G135" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15">
@@ -4327,16 +4372,16 @@
         <v>179</v>
       </c>
       <c r="D136" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E136" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F136" s="1">
-        <v>45705</v>
+        <v>45735</v>
       </c>
       <c r="G136" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15">
@@ -4350,16 +4395,16 @@
         <v>179</v>
       </c>
       <c r="D137" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E137" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F137" s="1">
-        <v>45339</v>
+        <v>45370</v>
       </c>
       <c r="G137" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15">
@@ -4373,36 +4418,36 @@
         <v>179</v>
       </c>
       <c r="D138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F138" s="1">
-        <v>44974</v>
+        <v>45004</v>
       </c>
       <c r="G138" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15">
       <c r="A139">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B139" t="s">
+        <v>183</v>
+      </c>
+      <c r="C139" t="s">
         <v>184</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
         <v>185</v>
-      </c>
-      <c r="D139" t="s">
-        <v>186</v>
       </c>
       <c r="E139" t="s">
         <v>186</v>
       </c>
       <c r="F139" s="1">
-        <v>45737</v>
+        <v>46140</v>
       </c>
       <c r="G139" t="s">
         <v>187</v>
@@ -4410,22 +4455,22 @@
     </row>
     <row r="140" spans="1:7" ht="15">
       <c r="A140">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B140" t="s">
+        <v>183</v>
+      </c>
+      <c r="C140" t="s">
         <v>184</v>
       </c>
-      <c r="C140" t="s">
-        <v>185</v>
-      </c>
       <c r="D140" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E140" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F140" s="1">
-        <v>45372</v>
+        <v>45705</v>
       </c>
       <c r="G140" t="s">
         <v>187</v>
@@ -4433,22 +4478,22 @@
     </row>
     <row r="141" spans="1:7" ht="15">
       <c r="A141">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B141" t="s">
+        <v>183</v>
+      </c>
+      <c r="C141" t="s">
         <v>184</v>
       </c>
-      <c r="C141" t="s">
-        <v>185</v>
-      </c>
       <c r="D141" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E141" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F141" s="1">
-        <v>45006</v>
+        <v>45339</v>
       </c>
       <c r="G141" t="s">
         <v>187</v>
@@ -4456,137 +4501,137 @@
     </row>
     <row r="142" spans="1:7" ht="15">
       <c r="A142">
+        <v>2023</v>
+      </c>
+      <c r="B142" t="s">
+        <v>183</v>
+      </c>
+      <c r="C142" t="s">
+        <v>184</v>
+      </c>
+      <c r="D142" t="s">
+        <v>188</v>
+      </c>
+      <c r="E142" t="s">
+        <v>188</v>
+      </c>
+      <c r="F142" s="1">
+        <v>44974</v>
+      </c>
+      <c r="G142" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15">
+      <c r="A143" s="10">
         <v>2025</v>
       </c>
-      <c r="B142" t="s">
-        <v>188</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="B143" t="s">
         <v>189</v>
       </c>
-      <c r="D142" t="s">
+      <c r="C143" t="s">
         <v>190</v>
       </c>
-      <c r="E142" t="s">
-        <v>190</v>
-      </c>
-      <c r="F142" s="1">
-        <v>45741</v>
-      </c>
-      <c r="G142" t="s">
+      <c r="D143" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="15">
-      <c r="A143">
-        <v>2024</v>
-      </c>
-      <c r="B143" t="s">
-        <v>188</v>
-      </c>
-      <c r="C143" t="s">
-        <v>189</v>
-      </c>
-      <c r="D143" t="s">
-        <v>190</v>
-      </c>
       <c r="E143" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F143" s="1">
-        <v>45376</v>
+        <v>45737</v>
       </c>
       <c r="G143" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="15">
       <c r="A144">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B144" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C144" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D144" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E144" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F144" s="1">
-        <v>45010</v>
+        <v>45372</v>
       </c>
       <c r="G144" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15">
       <c r="A145">
+        <v>2023</v>
+      </c>
+      <c r="B145" t="s">
+        <v>189</v>
+      </c>
+      <c r="C145" t="s">
+        <v>190</v>
+      </c>
+      <c r="D145" t="s">
+        <v>191</v>
+      </c>
+      <c r="E145" t="s">
+        <v>191</v>
+      </c>
+      <c r="F145" s="1">
+        <v>45006</v>
+      </c>
+      <c r="G145" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="15">
+      <c r="A146" s="10">
         <v>2026</v>
       </c>
-      <c r="B145" t="s">
-        <v>192</v>
-      </c>
-      <c r="C145" t="s">
+      <c r="B146" t="s">
         <v>193</v>
       </c>
-      <c r="D145" t="s">
+      <c r="C146" t="s">
         <v>194</v>
       </c>
-      <c r="E145" t="s">
-        <v>194</v>
-      </c>
-      <c r="F145" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G145" t="s">
+      <c r="D146" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="15">
-      <c r="A146">
-        <v>2025</v>
-      </c>
-      <c r="B146" t="s">
-        <v>192</v>
-      </c>
-      <c r="C146" t="s">
-        <v>193</v>
-      </c>
-      <c r="D146" t="s">
-        <v>194</v>
-      </c>
       <c r="E146" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F146" s="1">
-        <v>45763</v>
+        <v>46125</v>
       </c>
       <c r="G146" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15">
-      <c r="A147">
-        <v>2024</v>
+      <c r="A147" s="13">
+        <v>2025</v>
       </c>
       <c r="B147" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D147" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E147" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F147" s="1">
-        <v>45398</v>
+        <v>45741</v>
       </c>
       <c r="G147" t="s">
         <v>196</v>
@@ -4594,22 +4639,22 @@
     </row>
     <row r="148" spans="1:7" ht="15">
       <c r="A148">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B148" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C148" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D148" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E148" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F148" s="1">
-        <v>45032</v>
+        <v>45376</v>
       </c>
       <c r="G148" t="s">
         <v>196</v>
@@ -4617,381 +4662,381 @@
     </row>
     <row r="149" spans="1:7" ht="15">
       <c r="A149">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B149" t="s">
+        <v>193</v>
+      </c>
+      <c r="C149" t="s">
+        <v>194</v>
+      </c>
+      <c r="D149" t="s">
         <v>197</v>
       </c>
-      <c r="C149" t="s">
-        <v>198</v>
-      </c>
-      <c r="D149" t="s">
-        <v>199</v>
-      </c>
       <c r="E149" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F149" s="1">
-        <v>46128</v>
+        <v>45010</v>
       </c>
       <c r="G149" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15">
       <c r="A150">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B150" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C150" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D150" t="s">
+        <v>200</v>
+      </c>
+      <c r="E150" t="s">
+        <v>200</v>
+      </c>
+      <c r="F150" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G150" t="s">
         <v>201</v>
-      </c>
-      <c r="E150" t="s">
-        <v>201</v>
-      </c>
-      <c r="F150" s="1">
-        <v>45819</v>
-      </c>
-      <c r="G150" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15">
       <c r="A151">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B151" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C151" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D151" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E151" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F151" s="1">
-        <v>45454</v>
+        <v>45763</v>
       </c>
       <c r="G151" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="15">
       <c r="A152">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B152" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C152" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D152" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E152" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F152" s="1">
-        <v>45088</v>
+        <v>45398</v>
       </c>
       <c r="G152" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15">
       <c r="A153">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B153" t="s">
+        <v>198</v>
+      </c>
+      <c r="C153" t="s">
+        <v>199</v>
+      </c>
+      <c r="D153" t="s">
+        <v>200</v>
+      </c>
+      <c r="E153" t="s">
+        <v>200</v>
+      </c>
+      <c r="F153" s="1">
+        <v>45032</v>
+      </c>
+      <c r="G153" t="s">
         <v>202</v>
-      </c>
-      <c r="C153" t="s">
-        <v>203</v>
-      </c>
-      <c r="D153" t="s">
-        <v>204</v>
-      </c>
-      <c r="E153" t="s">
-        <v>204</v>
-      </c>
-      <c r="F153" s="1">
-        <v>45862</v>
-      </c>
-      <c r="G153" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15">
       <c r="A154">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B154" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C154" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D154" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E154" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F154" s="1">
-        <v>45497</v>
+        <v>46128</v>
       </c>
       <c r="G154" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15">
       <c r="A155">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B155" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C155" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D155" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E155" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F155" s="1">
-        <v>45131</v>
+        <v>45819</v>
       </c>
       <c r="G155" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15">
       <c r="A156">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B156" t="s">
+        <v>203</v>
+      </c>
+      <c r="C156" t="s">
+        <v>204</v>
+      </c>
+      <c r="D156" t="s">
+        <v>207</v>
+      </c>
+      <c r="E156" t="s">
+        <v>207</v>
+      </c>
+      <c r="F156" s="1">
+        <v>45454</v>
+      </c>
+      <c r="G156" t="s">
         <v>206</v>
-      </c>
-      <c r="C156" t="s">
-        <v>207</v>
-      </c>
-      <c r="D156" t="s">
-        <v>208</v>
-      </c>
-      <c r="E156" t="s">
-        <v>208</v>
-      </c>
-      <c r="F156" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G156" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15">
       <c r="A157">
+        <v>2023</v>
+      </c>
+      <c r="B157" t="s">
+        <v>203</v>
+      </c>
+      <c r="C157" t="s">
+        <v>204</v>
+      </c>
+      <c r="D157" t="s">
+        <v>207</v>
+      </c>
+      <c r="E157" t="s">
+        <v>207</v>
+      </c>
+      <c r="F157" s="1">
+        <v>45088</v>
+      </c>
+      <c r="G157" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="15">
+      <c r="A158" s="10">
         <v>2025</v>
       </c>
-      <c r="B157" t="s">
-        <v>206</v>
-      </c>
-      <c r="C157" t="s">
-        <v>207</v>
-      </c>
-      <c r="D157" t="s">
+      <c r="B158" t="s">
         <v>208</v>
       </c>
-      <c r="E157" t="s">
-        <v>208</v>
-      </c>
-      <c r="F157" s="1">
-        <v>45819</v>
-      </c>
-      <c r="G157" t="s">
+      <c r="C158" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="15">
-      <c r="A158">
-        <v>2024</v>
-      </c>
-      <c r="B158" t="s">
-        <v>206</v>
-      </c>
-      <c r="C158" t="s">
-        <v>207</v>
-      </c>
       <c r="D158" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E158" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F158" s="1">
-        <v>45454</v>
+        <v>45862</v>
       </c>
       <c r="G158" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15">
       <c r="A159">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B159" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C159" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D159" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E159" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F159" s="1">
-        <v>45088</v>
+        <v>45497</v>
       </c>
       <c r="G159" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15">
       <c r="A160">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B160" t="s">
+        <v>208</v>
+      </c>
+      <c r="C160" t="s">
+        <v>209</v>
+      </c>
+      <c r="D160" t="s">
         <v>210</v>
       </c>
-      <c r="C160" t="s">
+      <c r="E160" t="s">
+        <v>210</v>
+      </c>
+      <c r="F160" s="1">
+        <v>45131</v>
+      </c>
+      <c r="G160" t="s">
         <v>211</v>
-      </c>
-      <c r="D160" t="s">
-        <v>212</v>
-      </c>
-      <c r="E160" t="s">
-        <v>212</v>
-      </c>
-      <c r="F160" s="1">
-        <v>45740</v>
-      </c>
-      <c r="G160" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15">
       <c r="A161">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B161" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C161" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D161" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E161" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F161" s="1">
-        <v>45375</v>
+        <v>46128</v>
       </c>
       <c r="G161" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15">
       <c r="A162">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B162" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C162" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D162" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E162" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F162" s="1">
-        <v>45009</v>
+        <v>45819</v>
       </c>
       <c r="G162" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15">
       <c r="A163">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B163" t="s">
+        <v>212</v>
+      </c>
+      <c r="C163" t="s">
+        <v>213</v>
+      </c>
+      <c r="D163" t="s">
         <v>214</v>
       </c>
-      <c r="C163" t="s">
+      <c r="E163" t="s">
+        <v>214</v>
+      </c>
+      <c r="F163" s="1">
+        <v>45454</v>
+      </c>
+      <c r="G163" t="s">
         <v>215</v>
-      </c>
-      <c r="D163" t="s">
-        <v>216</v>
-      </c>
-      <c r="E163" t="s">
-        <v>216</v>
-      </c>
-      <c r="F163" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G163" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15">
       <c r="A164">
+        <v>2023</v>
+      </c>
+      <c r="B164" t="s">
+        <v>212</v>
+      </c>
+      <c r="C164" t="s">
+        <v>213</v>
+      </c>
+      <c r="D164" t="s">
+        <v>214</v>
+      </c>
+      <c r="E164" t="s">
+        <v>214</v>
+      </c>
+      <c r="F164" s="1">
+        <v>45088</v>
+      </c>
+      <c r="G164" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="15">
+      <c r="A165" s="10">
         <v>2025</v>
       </c>
-      <c r="B164" t="s">
-        <v>214</v>
-      </c>
-      <c r="C164" t="s">
-        <v>215</v>
-      </c>
-      <c r="D164" t="s">
-        <v>218</v>
-      </c>
-      <c r="E164" t="s">
-        <v>218</v>
-      </c>
-      <c r="F164" s="1">
-        <v>45733</v>
-      </c>
-      <c r="G164" t="s">
+      <c r="B165" t="s">
+        <v>216</v>
+      </c>
+      <c r="C165" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="15">
-      <c r="A165">
-        <v>2024</v>
-      </c>
-      <c r="B165" t="s">
-        <v>214</v>
-      </c>
-      <c r="C165" t="s">
-        <v>215</v>
       </c>
       <c r="D165" t="s">
         <v>218</v>
@@ -5000,21 +5045,21 @@
         <v>218</v>
       </c>
       <c r="F165" s="1">
-        <v>45368</v>
+        <v>45740</v>
       </c>
       <c r="G165" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15">
       <c r="A166">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B166" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C166" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D166" t="s">
         <v>218</v>
@@ -5023,148 +5068,148 @@
         <v>218</v>
       </c>
       <c r="F166" s="1">
-        <v>45002</v>
+        <v>45375</v>
       </c>
       <c r="G166" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15">
       <c r="A167">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B167" t="s">
+        <v>216</v>
+      </c>
+      <c r="C167" t="s">
+        <v>217</v>
+      </c>
+      <c r="D167" t="s">
+        <v>218</v>
+      </c>
+      <c r="E167" t="s">
+        <v>218</v>
+      </c>
+      <c r="F167" s="1">
+        <v>45009</v>
+      </c>
+      <c r="G167" t="s">
         <v>219</v>
-      </c>
-      <c r="C167" t="s">
-        <v>220</v>
-      </c>
-      <c r="D167" t="s">
-        <v>221</v>
-      </c>
-      <c r="E167" t="s">
-        <v>221</v>
-      </c>
-      <c r="F167" s="1">
-        <v>45713</v>
-      </c>
-      <c r="G167" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15">
       <c r="A168">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B168" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C168" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D168" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E168" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F168" s="1">
-        <v>45347</v>
+        <v>46125</v>
       </c>
       <c r="G168" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15">
       <c r="A169">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B169" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C169" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D169" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E169" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F169" s="1">
-        <v>44982</v>
+        <v>45733</v>
       </c>
       <c r="G169" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15">
       <c r="A170">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B170" t="s">
+        <v>220</v>
+      </c>
+      <c r="C170" t="s">
+        <v>221</v>
+      </c>
+      <c r="D170" t="s">
+        <v>224</v>
+      </c>
+      <c r="E170" t="s">
+        <v>224</v>
+      </c>
+      <c r="F170" s="1">
+        <v>45368</v>
+      </c>
+      <c r="G170" t="s">
         <v>223</v>
-      </c>
-      <c r="C170" t="s">
-        <v>224</v>
-      </c>
-      <c r="D170" t="s">
-        <v>225</v>
-      </c>
-      <c r="E170" t="s">
-        <v>225</v>
-      </c>
-      <c r="F170" s="1">
-        <v>45821</v>
-      </c>
-      <c r="G170" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15">
       <c r="A171">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B171" t="s">
+        <v>220</v>
+      </c>
+      <c r="C171" t="s">
+        <v>221</v>
+      </c>
+      <c r="D171" t="s">
+        <v>224</v>
+      </c>
+      <c r="E171" t="s">
+        <v>224</v>
+      </c>
+      <c r="F171" s="1">
+        <v>45002</v>
+      </c>
+      <c r="G171" t="s">
         <v>223</v>
-      </c>
-      <c r="C171" t="s">
-        <v>224</v>
-      </c>
-      <c r="D171" t="s">
-        <v>225</v>
-      </c>
-      <c r="E171" t="s">
-        <v>225</v>
-      </c>
-      <c r="F171" s="1">
-        <v>45456</v>
-      </c>
-      <c r="G171" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15">
       <c r="A172">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B172" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C172" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D172" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E172" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F172" s="1">
-        <v>45090</v>
+        <v>46121</v>
       </c>
       <c r="G172" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15">
@@ -5172,10 +5217,10 @@
         <v>2025</v>
       </c>
       <c r="B173" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C173" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D173" t="s">
         <v>229</v>
@@ -5184,10 +5229,10 @@
         <v>229</v>
       </c>
       <c r="F173" s="1">
-        <v>45805</v>
+        <v>45713</v>
       </c>
       <c r="G173" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15">
@@ -5195,10 +5240,10 @@
         <v>2024</v>
       </c>
       <c r="B174" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C174" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D174" t="s">
         <v>229</v>
@@ -5207,10 +5252,10 @@
         <v>229</v>
       </c>
       <c r="F174" s="1">
-        <v>45440</v>
+        <v>45347</v>
       </c>
       <c r="G174" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15">
@@ -5218,10 +5263,10 @@
         <v>2023</v>
       </c>
       <c r="B175" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C175" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D175" t="s">
         <v>229</v>
@@ -5230,30 +5275,30 @@
         <v>229</v>
       </c>
       <c r="F175" s="1">
-        <v>45074</v>
+        <v>44982</v>
       </c>
       <c r="G175" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="15">
+      <c r="A176" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B176" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" ht="15">
-      <c r="A176">
-        <v>2026</v>
-      </c>
-      <c r="B176" s="9" t="s">
+      <c r="C176" t="s">
         <v>231</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>232</v>
       </c>
-      <c r="D176" t="s">
-        <v>216</v>
-      </c>
       <c r="E176" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="F176" s="1">
-        <v>46125</v>
+        <v>45821</v>
       </c>
       <c r="G176" t="s">
         <v>233</v>
@@ -5261,22 +5306,22 @@
     </row>
     <row r="177" spans="1:7" ht="15">
       <c r="A177">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B177" t="s">
+        <v>230</v>
+      </c>
+      <c r="C177" t="s">
         <v>231</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>232</v>
       </c>
-      <c r="D177" t="s">
-        <v>234</v>
-      </c>
       <c r="E177" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F177" s="1">
-        <v>45748</v>
+        <v>45456</v>
       </c>
       <c r="G177" t="s">
         <v>233</v>
@@ -5284,194 +5329,197 @@
     </row>
     <row r="178" spans="1:7" ht="15">
       <c r="A178">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B178" t="s">
+        <v>230</v>
+      </c>
+      <c r="C178" t="s">
         <v>231</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
         <v>232</v>
       </c>
-      <c r="D178" t="s">
-        <v>234</v>
-      </c>
       <c r="E178" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F178" s="1">
-        <v>45383</v>
+        <v>45090</v>
       </c>
       <c r="G178" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15">
-      <c r="A179">
-        <v>2023</v>
+      <c r="A179" s="10">
+        <v>2025</v>
       </c>
       <c r="B179" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C179" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D179" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E179" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F179" s="1">
-        <v>45017</v>
+        <v>45805</v>
       </c>
       <c r="G179" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15">
       <c r="A180">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B180" t="s">
+        <v>234</v>
+      </c>
+      <c r="C180" t="s">
         <v>235</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>236</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
+        <v>236</v>
+      </c>
+      <c r="F180" s="1">
+        <v>45440</v>
+      </c>
+      <c r="G180" t="s">
         <v>237</v>
-      </c>
-      <c r="E180" t="s">
-        <v>237</v>
-      </c>
-      <c r="F180" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G180" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15">
       <c r="A181">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B181" t="s">
+        <v>234</v>
+      </c>
+      <c r="C181" t="s">
         <v>235</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181" t="s">
         <v>236</v>
       </c>
-      <c r="D181" t="s">
-        <v>239</v>
-      </c>
       <c r="E181" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F181" s="1">
-        <v>45744</v>
+        <v>45074</v>
       </c>
       <c r="G181" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15">
       <c r="A182">
-        <v>2024</v>
-      </c>
-      <c r="B182" t="s">
-        <v>235</v>
+        <v>2026</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>238</v>
       </c>
       <c r="C182" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D182" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="E182" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="F182" s="1">
-        <v>45379</v>
+        <v>46125</v>
       </c>
       <c r="G182" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15">
       <c r="A183">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B183" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C183" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D183" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E183" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F183" s="1">
-        <v>45013</v>
+        <v>45748</v>
       </c>
       <c r="G183" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15">
       <c r="A184">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B184" t="s">
+        <v>238</v>
+      </c>
+      <c r="C184" t="s">
+        <v>239</v>
+      </c>
+      <c r="D184" t="s">
+        <v>241</v>
+      </c>
+      <c r="E184" t="s">
+        <v>241</v>
+      </c>
+      <c r="F184" s="1">
+        <v>45383</v>
+      </c>
+      <c r="G184" t="s">
         <v>240</v>
-      </c>
-      <c r="C184" t="s">
-        <v>241</v>
-      </c>
-      <c r="D184" t="s">
-        <v>242</v>
-      </c>
-      <c r="F184" s="1">
-        <v>46122</v>
-      </c>
-      <c r="G184" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15">
       <c r="A185">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B185" t="s">
+        <v>238</v>
+      </c>
+      <c r="C185" t="s">
+        <v>239</v>
+      </c>
+      <c r="D185" t="s">
+        <v>241</v>
+      </c>
+      <c r="E185" t="s">
+        <v>241</v>
+      </c>
+      <c r="F185" s="1">
+        <v>45017</v>
+      </c>
+      <c r="G185" t="s">
         <v>240</v>
-      </c>
-      <c r="C185" t="s">
-        <v>241</v>
-      </c>
-      <c r="D185" t="s">
-        <v>244</v>
-      </c>
-      <c r="E185" t="s">
-        <v>244</v>
-      </c>
-      <c r="F185" s="1">
-        <v>45737</v>
-      </c>
-      <c r="G185" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15">
       <c r="A186">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B186" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C186" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D186" t="s">
         <v>244</v>
@@ -5480,80 +5528,220 @@
         <v>244</v>
       </c>
       <c r="F186" s="1">
-        <v>45372</v>
+        <v>46128</v>
       </c>
       <c r="G186" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15">
       <c r="A187">
+        <v>2025</v>
+      </c>
+      <c r="B187" t="s">
+        <v>242</v>
+      </c>
+      <c r="C187" t="s">
+        <v>243</v>
+      </c>
+      <c r="D187" t="s">
+        <v>246</v>
+      </c>
+      <c r="E187" t="s">
+        <v>246</v>
+      </c>
+      <c r="F187" s="1">
+        <v>45744</v>
+      </c>
+      <c r="G187" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="15">
+      <c r="A188">
+        <v>2024</v>
+      </c>
+      <c r="B188" t="s">
+        <v>242</v>
+      </c>
+      <c r="C188" t="s">
+        <v>243</v>
+      </c>
+      <c r="D188" t="s">
+        <v>246</v>
+      </c>
+      <c r="E188" t="s">
+        <v>246</v>
+      </c>
+      <c r="F188" s="1">
+        <v>45379</v>
+      </c>
+      <c r="G188" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="15">
+      <c r="A189">
         <v>2023</v>
       </c>
-      <c r="B187" t="s">
-        <v>240</v>
-      </c>
-      <c r="C187" t="s">
-        <v>241</v>
-      </c>
-      <c r="D187" t="s">
-        <v>244</v>
-      </c>
-      <c r="E187" t="s">
-        <v>244</v>
-      </c>
-      <c r="F187" s="1">
+      <c r="B189" t="s">
+        <v>242</v>
+      </c>
+      <c r="C189" t="s">
+        <v>243</v>
+      </c>
+      <c r="D189" t="s">
+        <v>246</v>
+      </c>
+      <c r="E189" t="s">
+        <v>246</v>
+      </c>
+      <c r="F189" s="1">
+        <v>45013</v>
+      </c>
+      <c r="G189" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="15">
+      <c r="A190">
+        <v>2026</v>
+      </c>
+      <c r="B190" t="s">
+        <v>247</v>
+      </c>
+      <c r="C190" t="s">
+        <v>248</v>
+      </c>
+      <c r="D190" t="s">
+        <v>249</v>
+      </c>
+      <c r="F190" s="1">
+        <v>46122</v>
+      </c>
+      <c r="G190" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="15">
+      <c r="A191">
+        <v>2025</v>
+      </c>
+      <c r="B191" t="s">
+        <v>247</v>
+      </c>
+      <c r="C191" t="s">
+        <v>248</v>
+      </c>
+      <c r="D191" t="s">
+        <v>251</v>
+      </c>
+      <c r="E191" t="s">
+        <v>251</v>
+      </c>
+      <c r="F191" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G191" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="15">
+      <c r="A192">
+        <v>2024</v>
+      </c>
+      <c r="B192" t="s">
+        <v>247</v>
+      </c>
+      <c r="C192" t="s">
+        <v>248</v>
+      </c>
+      <c r="D192" t="s">
+        <v>251</v>
+      </c>
+      <c r="E192" t="s">
+        <v>251</v>
+      </c>
+      <c r="F192" s="1">
+        <v>45372</v>
+      </c>
+      <c r="G192" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="15">
+      <c r="A193">
+        <v>2023</v>
+      </c>
+      <c r="B193" t="s">
+        <v>247</v>
+      </c>
+      <c r="C193" t="s">
+        <v>248</v>
+      </c>
+      <c r="D193" t="s">
+        <v>251</v>
+      </c>
+      <c r="E193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F193" s="1">
         <v>45006</v>
       </c>
-      <c r="G187" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="236" spans="11:11">
-      <c r="K236" s="1"/>
+      <c r="G193" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="242" spans="11:11">
+      <c r="K242" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G187" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G187">
+  <autoFilter ref="A1:G193" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G193">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G40" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G42" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G43" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G41" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G17" r:id="rId5" xr:uid="{3F701E59-5D29-4E9C-8705-ECF744F7C80B}"/>
-    <hyperlink ref="G21" r:id="rId6" xr:uid="{F86867FF-E0A1-4B23-8E20-1EE5F172C1F2}"/>
-    <hyperlink ref="G28" r:id="rId7" xr:uid="{7B92F4FE-45A5-4FC3-BEF6-89060A75A0CF}"/>
-    <hyperlink ref="G32" r:id="rId8" xr:uid="{44483B5F-1D9D-4382-A3BB-08CC848203BB}"/>
-    <hyperlink ref="G36" r:id="rId9" xr:uid="{80C8F108-86E1-4547-810D-49EE9748B088}"/>
-    <hyperlink ref="G44" r:id="rId10" xr:uid="{44A2B85F-2D5D-4501-BD0D-1A1075EEBD87}"/>
-    <hyperlink ref="G47" r:id="rId11" xr:uid="{974F12BA-311E-4775-9C79-6B2367EE4C00}"/>
-    <hyperlink ref="G51" r:id="rId12" xr:uid="{9FD43934-382B-448D-9E13-39FD5028C9E3}"/>
-    <hyperlink ref="G55" r:id="rId13" xr:uid="{F5EC8224-9440-476C-B04B-BCD61BFD11DD}"/>
-    <hyperlink ref="G59" r:id="rId14" xr:uid="{6715A407-CEDE-4462-83D2-BA6A21538E94}"/>
-    <hyperlink ref="G63" r:id="rId15" xr:uid="{8C180C1D-CF21-400B-8B35-ACDD613A2648}"/>
-    <hyperlink ref="G70" r:id="rId16" xr:uid="{E80524B7-0871-4464-985C-CA93DB159F96}"/>
-    <hyperlink ref="E70" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto" xr:uid="{44E53C8F-307F-4558-8C5E-5645D7067E09}"/>
-    <hyperlink ref="G74" r:id="rId18" xr:uid="{BB1A3C55-886C-4149-9192-8222A522CCA0}"/>
-    <hyperlink ref="G87" r:id="rId19" location="informacoes-classificadas-e-desclassificadas" xr:uid="{F06BDAE5-9ADF-4DA7-920D-01903454D462}"/>
-    <hyperlink ref="G103" r:id="rId20" xr:uid="{CD1703C5-F786-4C99-88D4-BEA8E70C4138}"/>
-    <hyperlink ref="G102" r:id="rId21" xr:uid="{C77BD8BE-59BD-4BD4-9FAB-2123370B5889}"/>
-    <hyperlink ref="G98" r:id="rId22" xr:uid="{9388516A-40C8-4110-A15B-D0B6EE32A150}"/>
-    <hyperlink ref="G109" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{3301EBB6-9A25-48B2-9D8C-70083F27B1EA}"/>
-    <hyperlink ref="G113" r:id="rId24" location="informacoes-classificadas-e-desclassificadas" xr:uid="{7434A183-8C1E-4E4A-8E52-8EF290090E88}"/>
-    <hyperlink ref="G120" r:id="rId25" xr:uid="{4A3115E8-4CE5-4DFF-BF8C-76F55E18523A}"/>
-    <hyperlink ref="G127" r:id="rId26" xr:uid="{E28EBD52-B071-49FC-B6F4-D7C185EC3BD1}"/>
-    <hyperlink ref="G131" r:id="rId27" xr:uid="{995FBC4C-1A02-4126-AA25-76E795A0EB48}"/>
-    <hyperlink ref="G135" r:id="rId28" xr:uid="{80237B8F-DF43-47F0-80AC-616D77A1082D}"/>
-    <hyperlink ref="G145" r:id="rId29" xr:uid="{6AC60654-C774-4732-B0F1-240E2D6C4490}"/>
-    <hyperlink ref="G149" r:id="rId30" xr:uid="{AAF4FD60-6234-4214-BA5D-07ACABA79556}"/>
-    <hyperlink ref="G156" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{6EF2BF0D-AFAC-4C21-81A1-0D63CF1FEEE4}"/>
-    <hyperlink ref="G163" r:id="rId32" xr:uid="{81356907-EB5D-4FC6-90E5-4BC94C925F5E}"/>
-    <hyperlink ref="G176" r:id="rId33" xr:uid="{89F50D9C-749D-4ED1-B9C3-FA541C5DBEA0}"/>
-    <hyperlink ref="G180" r:id="rId34" location="info-class-des" xr:uid="{9E908A83-E592-48E3-A960-E01C6B504A9F}"/>
-    <hyperlink ref="G184" r:id="rId35" xr:uid="{6ACD1A2A-A2ED-4326-AB6D-AC1CAEB49DD3}"/>
+    <hyperlink ref="G41" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G43" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G44" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G42" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G18" r:id="rId5" xr:uid="{3F701E59-5D29-4E9C-8705-ECF744F7C80B}"/>
+    <hyperlink ref="G22" r:id="rId6" xr:uid="{F86867FF-E0A1-4B23-8E20-1EE5F172C1F2}"/>
+    <hyperlink ref="G29" r:id="rId7" xr:uid="{7B92F4FE-45A5-4FC3-BEF6-89060A75A0CF}"/>
+    <hyperlink ref="G33" r:id="rId8" xr:uid="{44483B5F-1D9D-4382-A3BB-08CC848203BB}"/>
+    <hyperlink ref="G37" r:id="rId9" xr:uid="{80C8F108-86E1-4547-810D-49EE9748B088}"/>
+    <hyperlink ref="G45" r:id="rId10" xr:uid="{44A2B85F-2D5D-4501-BD0D-1A1075EEBD87}"/>
+    <hyperlink ref="G48" r:id="rId11" xr:uid="{974F12BA-311E-4775-9C79-6B2367EE4C00}"/>
+    <hyperlink ref="G52" r:id="rId12" xr:uid="{9FD43934-382B-448D-9E13-39FD5028C9E3}"/>
+    <hyperlink ref="G56" r:id="rId13" xr:uid="{F5EC8224-9440-476C-B04B-BCD61BFD11DD}"/>
+    <hyperlink ref="G60" r:id="rId14" xr:uid="{6715A407-CEDE-4462-83D2-BA6A21538E94}"/>
+    <hyperlink ref="G64" r:id="rId15" xr:uid="{8C180C1D-CF21-400B-8B35-ACDD613A2648}"/>
+    <hyperlink ref="G71" r:id="rId16" xr:uid="{E80524B7-0871-4464-985C-CA93DB159F96}"/>
+    <hyperlink ref="E71" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto" xr:uid="{44E53C8F-307F-4558-8C5E-5645D7067E09}"/>
+    <hyperlink ref="G75" r:id="rId18" xr:uid="{BB1A3C55-886C-4149-9192-8222A522CCA0}"/>
+    <hyperlink ref="G89" r:id="rId19" location="informacoes-classificadas-e-desclassificadas" xr:uid="{F06BDAE5-9ADF-4DA7-920D-01903454D462}"/>
+    <hyperlink ref="G106" r:id="rId20" xr:uid="{CD1703C5-F786-4C99-88D4-BEA8E70C4138}"/>
+    <hyperlink ref="G105" r:id="rId21" xr:uid="{C77BD8BE-59BD-4BD4-9FAB-2123370B5889}"/>
+    <hyperlink ref="G101" r:id="rId22" xr:uid="{9388516A-40C8-4110-A15B-D0B6EE32A150}"/>
+    <hyperlink ref="G112" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{3301EBB6-9A25-48B2-9D8C-70083F27B1EA}"/>
+    <hyperlink ref="G116" r:id="rId24" location="informacoes-classificadas-e-desclassificadas" xr:uid="{7434A183-8C1E-4E4A-8E52-8EF290090E88}"/>
+    <hyperlink ref="G124" r:id="rId25" xr:uid="{4A3115E8-4CE5-4DFF-BF8C-76F55E18523A}"/>
+    <hyperlink ref="G131" r:id="rId26" xr:uid="{E28EBD52-B071-49FC-B6F4-D7C185EC3BD1}"/>
+    <hyperlink ref="G135" r:id="rId27" xr:uid="{995FBC4C-1A02-4126-AA25-76E795A0EB48}"/>
+    <hyperlink ref="G139" r:id="rId28" xr:uid="{80237B8F-DF43-47F0-80AC-616D77A1082D}"/>
+    <hyperlink ref="G150" r:id="rId29" xr:uid="{6AC60654-C774-4732-B0F1-240E2D6C4490}"/>
+    <hyperlink ref="G154" r:id="rId30" xr:uid="{AAF4FD60-6234-4214-BA5D-07ACABA79556}"/>
+    <hyperlink ref="G161" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{6EF2BF0D-AFAC-4C21-81A1-0D63CF1FEEE4}"/>
+    <hyperlink ref="G168" r:id="rId32" xr:uid="{81356907-EB5D-4FC6-90E5-4BC94C925F5E}"/>
+    <hyperlink ref="G182" r:id="rId33" xr:uid="{89F50D9C-749D-4ED1-B9C3-FA541C5DBEA0}"/>
+    <hyperlink ref="G186" r:id="rId34" location="info-class-des" xr:uid="{9E908A83-E592-48E3-A960-E01C6B504A9F}"/>
+    <hyperlink ref="G190" r:id="rId35" xr:uid="{6ACD1A2A-A2ED-4326-AB6D-AC1CAEB49DD3}"/>
+    <hyperlink ref="G85" r:id="rId36" xr:uid="{E8F08860-DEED-4B1D-A48C-6C1359300175}"/>
+    <hyperlink ref="G97" r:id="rId37" xr:uid="{0E98023C-AB1F-4285-BFD2-EFD188CCDF4C}"/>
+    <hyperlink ref="G172" r:id="rId38" xr:uid="{9F2C91F1-3B9F-4B72-A797-85FFBDD348E1}"/>
+    <hyperlink ref="G14" r:id="rId39" xr:uid="{3841C1FD-CD06-45B5-9491-60778AF8477D}"/>
+    <hyperlink ref="G146" r:id="rId40" xr:uid="{50E2C31A-C16A-4D5A-AC7B-F44D64FFCDE4}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/orgao_sem_informacoes_classificadas.xlsx
+++ b/upload/orgao_sem_informacoes_classificadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FD01EC8-9690-4F32-8863-92C1F067EC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{764A000E-CD73-484A-8F8E-4C10E958276C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="258">
   <si>
     <t>ano</t>
   </si>
@@ -173,6 +173,9 @@
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Companhia de Habitação do Estado de Minas Gerais informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
+    <t>https://www.cohab.mg.gov.br/MenuHorizontal/Transparencia/informacoes.php</t>
+  </si>
+  <si>
     <t>http://www.cohab.mg.gov.br/informacoes-classificadas-desclassificadas/</t>
   </si>
   <si>
@@ -335,12 +338,15 @@
     <t>FCS</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação Clóvis Salgado informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto.</t>
+  </si>
+  <si>
+    <t>https://fcs.mg.gov.br/informacoes-classificadas-e-desclassificadas/</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação Clóvis Salgado informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
-    <t>https://fcs.mg.gov.br/informacoes-classificadas-e-desclassificadas/</t>
-  </si>
-  <si>
     <t>Fundação de Amparo à Pesquisa do Estado de Minas Gerais - FAPEMIG</t>
   </si>
   <si>
@@ -560,6 +566,9 @@
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Loteria do Estado de Minas Gerais (LEMG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
+    <t>http://www.loteriamineira.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>https://www.loteriamineira.mg.gov.br/transparencia/informacoes-classificadas-e-desclassificadas</t>
   </si>
   <si>
@@ -608,6 +617,12 @@
     <t>A Ouvidoria-Geral do Estado não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Agricultura, Pecuária e Abastecimento informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.mg.gov.br/agricultura/pagina/informacoes-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>Secretaria de Estado de Agricultura, Pecuária e Abastecimento - SEAPA</t>
   </si>
   <si>
@@ -617,9 +632,6 @@
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Agricultura, Pecuária e Abastecimento informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto2</t>
   </si>
   <si>
-    <t>https://www.mg.gov.br/agricultura/pagina/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Secretaria de Estado de Casa Civil - SCC</t>
   </si>
   <si>
@@ -671,12 +683,15 @@
     <t>SEDE</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Desenvolvimento Econômico (Sede) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://desenvolvimento.mg.gov.br/inicio/transparencia</t>
+  </si>
+  <si>
     <t>A Secretaria de Estado de Desenvolvimento Econômico (Sede) não teve informações desclassificadas e/ou classificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527, de 18 de novembro de 2011 (Lei de Acesso à Informação) </t>
   </si>
   <si>
-    <t>https://desenvolvimento.mg.gov.br/inicio/transparencia</t>
-  </si>
-  <si>
     <t>Secretaria de Estado de Desenvolvimento Social - SEDESE</t>
   </si>
   <si>
@@ -695,10 +710,13 @@
     <t>SEE</t>
   </si>
   <si>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Educação informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
+  </si>
+  <si>
+    <t>https://www.educacao.mg.gov.br/acesso-rapido/transparencia/</t>
+  </si>
+  <si>
     <t>A Secretaria de Estado de Educação não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no Art. 23 da Lei nº 12.527/2011 (Lei de Acesso à Informação)</t>
-  </si>
-  <si>
-    <t>https://www.educacao.mg.gov.br/acesso-rapido/transparencia/</t>
   </si>
   <si>
     <t>Secretaria de Estado de Governo - SEGOV</t>
@@ -801,7 +819,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -842,6 +860,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -899,7 +923,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -916,8 +940,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1254,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K242"/>
+  <dimension ref="A1:K251"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
@@ -1679,8 +1704,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15">
-      <c r="A19" s="10">
-        <v>2025</v>
+      <c r="A19">
+        <v>2026</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
@@ -1695,15 +1720,15 @@
         <v>34</v>
       </c>
       <c r="F19" s="1">
-        <v>45747</v>
-      </c>
-      <c r="G19" t="s">
+        <v>46112</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15">
       <c r="A20">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B20" t="s">
         <v>32</v>
@@ -1718,7 +1743,7 @@
         <v>34</v>
       </c>
       <c r="F20" s="1">
-        <v>45382</v>
+        <v>45747</v>
       </c>
       <c r="G20" t="s">
         <v>35</v>
@@ -1726,7 +1751,7 @@
     </row>
     <row r="21" spans="1:7" ht="15">
       <c r="A21">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
@@ -1741,7 +1766,7 @@
         <v>34</v>
       </c>
       <c r="F21" s="1">
-        <v>45016</v>
+        <v>45382</v>
       </c>
       <c r="G21" t="s">
         <v>35</v>
@@ -1749,30 +1774,30 @@
     </row>
     <row r="22" spans="1:7" ht="15">
       <c r="A22">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F22" s="1">
-        <v>46127</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>39</v>
+        <v>45016</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15">
       <c r="A23">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
@@ -1781,21 +1806,21 @@
         <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1">
-        <v>46022</v>
-      </c>
-      <c r="G23" t="s">
+        <v>46127</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15">
       <c r="A24">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B24" t="s">
         <v>36</v>
@@ -1810,7 +1835,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="1">
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="G24" t="s">
         <v>39</v>
@@ -1818,7 +1843,7 @@
     </row>
     <row r="25" spans="1:7" ht="15">
       <c r="A25">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
@@ -1833,38 +1858,38 @@
         <v>40</v>
       </c>
       <c r="F25" s="1">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="G25" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15">
-      <c r="A26" s="10">
-        <v>2025</v>
+      <c r="A26">
+        <v>2023</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F26" s="1">
-        <v>45812</v>
+        <v>45291</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15">
       <c r="A27">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
@@ -1879,7 +1904,7 @@
         <v>43</v>
       </c>
       <c r="F27" s="1">
-        <v>45447</v>
+        <v>46161</v>
       </c>
       <c r="G27" t="s">
         <v>44</v>
@@ -1887,7 +1912,7 @@
     </row>
     <row r="28" spans="1:7" ht="15">
       <c r="A28">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
@@ -1902,1146 +1927,1146 @@
         <v>43</v>
       </c>
       <c r="F28" s="1">
-        <v>45081</v>
+        <v>45812</v>
       </c>
       <c r="G28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15">
       <c r="A29">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="1">
+        <v>45447</v>
+      </c>
+      <c r="G29" t="s">
         <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" t="s">
-        <v>47</v>
-      </c>
-      <c r="F29" s="1">
-        <v>46099</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15">
       <c r="A30">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="1">
+        <v>45081</v>
+      </c>
+      <c r="G30" t="s">
         <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" s="1">
-        <v>45780</v>
-      </c>
-      <c r="G30" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15">
       <c r="A31">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46099</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="E31" t="s">
-        <v>49</v>
-      </c>
-      <c r="F31" s="1">
-        <v>45415</v>
-      </c>
-      <c r="G31" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15">
       <c r="A32">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F32" s="1">
-        <v>45049</v>
+        <v>45780</v>
       </c>
       <c r="G32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15">
       <c r="A33">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="1">
+        <v>45415</v>
+      </c>
+      <c r="G33" t="s">
         <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15">
       <c r="A34">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="1">
+        <v>45049</v>
+      </c>
+      <c r="G34" t="s">
         <v>51</v>
-      </c>
-      <c r="C34" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" s="1">
-        <v>45953</v>
-      </c>
-      <c r="G34" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15">
       <c r="A35">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="F35" s="1">
-        <v>45588</v>
-      </c>
-      <c r="G35" t="s">
-        <v>54</v>
+        <v>46128</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15">
       <c r="A36">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" s="1">
-        <v>45222</v>
+        <v>45953</v>
       </c>
       <c r="G36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15">
       <c r="A37">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="1">
+        <v>45588</v>
+      </c>
+      <c r="G37" t="s">
         <v>55</v>
-      </c>
-      <c r="C37" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F37" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15">
       <c r="A38">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="1">
+        <v>45222</v>
+      </c>
+      <c r="G38" t="s">
         <v>55</v>
-      </c>
-      <c r="C38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" s="1">
-        <v>45735</v>
-      </c>
-      <c r="G38" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15">
       <c r="A39">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46120</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="E39" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="1">
-        <v>45370</v>
-      </c>
-      <c r="G39" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15">
       <c r="A40">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F40" s="1">
-        <v>45004</v>
+        <v>45735</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15">
       <c r="A41">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" s="1">
+        <v>45370</v>
+      </c>
+      <c r="G41" t="s">
         <v>61</v>
-      </c>
-      <c r="C41" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" t="s">
-        <v>63</v>
-      </c>
-      <c r="F41" s="1">
-        <v>46073</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15">
       <c r="A42">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G42" t="s">
         <v>61</v>
-      </c>
-      <c r="C42" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" t="s">
-        <v>63</v>
-      </c>
-      <c r="E42" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" s="1">
-        <v>45708</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15">
       <c r="A43">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F43" s="1">
-        <v>45342</v>
+        <v>46073</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15">
       <c r="A44">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" s="1">
+        <v>45708</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15">
+      <c r="A45">
+        <v>2024</v>
+      </c>
+      <c r="B45" t="s">
         <v>62</v>
       </c>
-      <c r="D44" t="s">
+      <c r="C45" t="s">
         <v>63</v>
       </c>
-      <c r="E44" t="s">
-        <v>63</v>
-      </c>
-      <c r="F44" s="1">
-        <v>44977</v>
-      </c>
-      <c r="G44" s="2" t="s">
+      <c r="D45" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75">
-      <c r="A45">
-        <v>2026</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="E45" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="1">
+        <v>45342</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C45" t="s">
-        <v>66</v>
-      </c>
-      <c r="D45" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F45" s="1">
-        <v>46135</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15">
       <c r="A46">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="1">
+        <v>44977</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47" spans="1:7" ht="15.75">
+      <c r="A47">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="s">
         <v>66</v>
       </c>
-      <c r="D46" t="s">
+      <c r="C47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47" s="1">
+        <v>46135</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="E46" t="s">
-        <v>70</v>
-      </c>
-      <c r="F46" s="1">
-        <v>45657</v>
-      </c>
-      <c r="G46" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15">
-      <c r="A47">
-        <v>2023</v>
-      </c>
-      <c r="B47" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47" t="s">
-        <v>70</v>
-      </c>
-      <c r="E47" t="s">
-        <v>70</v>
-      </c>
-      <c r="F47" s="1">
-        <v>45291</v>
-      </c>
-      <c r="G47" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15">
       <c r="A48">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
         <v>71</v>
       </c>
-      <c r="C48" t="s">
-        <v>72</v>
-      </c>
-      <c r="D48" t="s">
-        <v>73</v>
+      <c r="E48" t="s">
+        <v>71</v>
       </c>
       <c r="F48" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>74</v>
+        <v>45657</v>
+      </c>
+      <c r="G48" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" t="s">
         <v>71</v>
       </c>
-      <c r="C49" t="s">
-        <v>72</v>
-      </c>
-      <c r="D49" t="s">
-        <v>75</v>
-      </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F49" s="1">
-        <v>45883</v>
+        <v>45291</v>
       </c>
       <c r="G49" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46140</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E50" t="s">
-        <v>75</v>
-      </c>
-      <c r="F50" s="1">
-        <v>45518</v>
-      </c>
-      <c r="G50" t="s">
-        <v>74</v>
-      </c>
-      <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45883</v>
+      </c>
+      <c r="G51" t="s">
         <v>75</v>
-      </c>
-      <c r="E51" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="1">
-        <v>45152</v>
-      </c>
-      <c r="G51" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" t="s">
         <v>76</v>
       </c>
-      <c r="C52" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" t="s">
-        <v>78</v>
-      </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F52" s="1">
-        <v>61</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>45518</v>
+      </c>
+      <c r="G52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" t="s">
         <v>76</v>
       </c>
-      <c r="C53" t="s">
-        <v>77</v>
-      </c>
-      <c r="D53" t="s">
-        <v>78</v>
-      </c>
       <c r="E53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F53" s="1">
-        <v>45717</v>
+        <v>45152</v>
       </c>
       <c r="G53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F54" s="1">
-        <v>45352</v>
-      </c>
-      <c r="G54" t="s">
-        <v>79</v>
+        <v>46082</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F55" s="1">
-        <v>44986</v>
+        <v>45717</v>
       </c>
       <c r="G55" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B56" t="s">
+        <v>77</v>
+      </c>
+      <c r="C56" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" s="1">
+        <v>45352</v>
+      </c>
+      <c r="G56" t="s">
         <v>80</v>
-      </c>
-      <c r="C56" t="s">
-        <v>81</v>
-      </c>
-      <c r="D56" t="s">
-        <v>82</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F56" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C57" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57" s="1">
+        <v>44986</v>
+      </c>
+      <c r="G57" t="s">
         <v>80</v>
-      </c>
-      <c r="C57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" t="s">
-        <v>84</v>
-      </c>
-      <c r="E57" t="s">
-        <v>84</v>
-      </c>
-      <c r="F57" s="1">
-        <v>45742</v>
-      </c>
-      <c r="G57" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="E58" t="s">
-        <v>84</v>
-      </c>
-      <c r="F58" s="1">
-        <v>45377</v>
-      </c>
-      <c r="G58" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45742</v>
+      </c>
+      <c r="G59" t="s">
         <v>84</v>
-      </c>
-      <c r="E59" t="s">
-        <v>84</v>
-      </c>
-      <c r="F59" s="1">
-        <v>45011</v>
-      </c>
-      <c r="G59" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B60" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" t="s">
         <v>85</v>
       </c>
-      <c r="C60" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" t="s">
-        <v>87</v>
-      </c>
       <c r="E60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F60" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>88</v>
+        <v>45377</v>
+      </c>
+      <c r="G60" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B61" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" t="s">
         <v>85</v>
       </c>
-      <c r="C61" t="s">
-        <v>86</v>
-      </c>
-      <c r="D61" t="s">
-        <v>89</v>
-      </c>
       <c r="E61" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F61" s="1">
-        <v>45792</v>
+        <v>45011</v>
       </c>
       <c r="G61" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B62" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46120</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="E62" t="s">
-        <v>89</v>
-      </c>
-      <c r="F62" s="1">
-        <v>45427</v>
-      </c>
-      <c r="G62" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D63" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45792</v>
+      </c>
+      <c r="G63" t="s">
         <v>89</v>
-      </c>
-      <c r="E63" t="s">
-        <v>89</v>
-      </c>
-      <c r="F63" s="1">
-        <v>45061</v>
-      </c>
-      <c r="G63" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" t="s">
         <v>90</v>
       </c>
-      <c r="C64" t="s">
-        <v>91</v>
-      </c>
-      <c r="D64" t="s">
-        <v>92</v>
-      </c>
       <c r="E64" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F64" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>93</v>
+        <v>45427</v>
+      </c>
+      <c r="G64" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15">
       <c r="A65">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B65" t="s">
+        <v>86</v>
+      </c>
+      <c r="C65" t="s">
+        <v>87</v>
+      </c>
+      <c r="D65" t="s">
         <v>90</v>
       </c>
-      <c r="C65" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65" t="s">
-        <v>94</v>
-      </c>
       <c r="E65" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F65" s="1">
-        <v>45730</v>
+        <v>45061</v>
       </c>
       <c r="G65" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15">
       <c r="A66">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="1">
+        <v>46140</v>
+      </c>
+      <c r="G66" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="E66" t="s">
-        <v>94</v>
-      </c>
-      <c r="F66" s="1">
-        <v>45365</v>
-      </c>
-      <c r="G66" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15">
       <c r="A67">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C67" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" t="s">
+        <v>95</v>
+      </c>
+      <c r="E67" t="s">
+        <v>95</v>
+      </c>
+      <c r="F67" s="1">
+        <v>45730</v>
+      </c>
+      <c r="G67" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15">
+      <c r="A68">
+        <v>2024</v>
+      </c>
+      <c r="B68" t="s">
         <v>91</v>
       </c>
-      <c r="D67" t="s">
-        <v>94</v>
-      </c>
-      <c r="E67" t="s">
-        <v>94</v>
-      </c>
-      <c r="F67" s="1">
-        <v>44999</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="C68" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="15">
-      <c r="A68" s="10">
-        <v>2025</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="E68" t="s">
+        <v>95</v>
+      </c>
+      <c r="F68" s="1">
+        <v>45365</v>
+      </c>
+      <c r="G68" t="s">
         <v>96</v>
-      </c>
-      <c r="C68" t="s">
-        <v>97</v>
-      </c>
-      <c r="D68" t="s">
-        <v>98</v>
-      </c>
-      <c r="E68" t="s">
-        <v>98</v>
-      </c>
-      <c r="F68" s="1">
-        <v>45756</v>
-      </c>
-      <c r="G68" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15">
       <c r="A69">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B69" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" t="s">
+        <v>92</v>
+      </c>
+      <c r="D69" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" t="s">
+        <v>95</v>
+      </c>
+      <c r="F69" s="1">
+        <v>44999</v>
+      </c>
+      <c r="G69" t="s">
         <v>96</v>
-      </c>
-      <c r="C69" t="s">
-        <v>97</v>
-      </c>
-      <c r="D69" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" t="s">
-        <v>98</v>
-      </c>
-      <c r="F69" s="1">
-        <v>45391</v>
-      </c>
-      <c r="G69" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15">
       <c r="A70">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E70" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F70" s="1">
-        <v>45025</v>
-      </c>
-      <c r="G70" t="s">
-        <v>99</v>
+        <v>46161</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15">
       <c r="A71">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B71" t="s">
+        <v>97</v>
+      </c>
+      <c r="C71" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" t="s">
+        <v>101</v>
+      </c>
+      <c r="E71" t="s">
+        <v>101</v>
+      </c>
+      <c r="F71" s="1">
+        <v>45756</v>
+      </c>
+      <c r="G71" t="s">
         <v>100</v>
-      </c>
-      <c r="C71" t="s">
-        <v>101</v>
-      </c>
-      <c r="D71" t="s">
-        <v>102</v>
-      </c>
-      <c r="E71" t="s">
-        <v>103</v>
-      </c>
-      <c r="F71" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15">
       <c r="A72">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B72" t="s">
+        <v>97</v>
+      </c>
+      <c r="C72" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" t="s">
+        <v>101</v>
+      </c>
+      <c r="E72" t="s">
+        <v>101</v>
+      </c>
+      <c r="F72" s="1">
+        <v>45391</v>
+      </c>
+      <c r="G72" t="s">
         <v>100</v>
-      </c>
-      <c r="C72" t="s">
-        <v>101</v>
-      </c>
-      <c r="D72" t="s">
-        <v>105</v>
-      </c>
-      <c r="E72" t="s">
-        <v>105</v>
-      </c>
-      <c r="F72" s="1">
-        <v>45820</v>
-      </c>
-      <c r="G72" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15">
       <c r="A73">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B73" t="s">
+        <v>97</v>
+      </c>
+      <c r="C73" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" t="s">
+        <v>101</v>
+      </c>
+      <c r="E73" t="s">
+        <v>101</v>
+      </c>
+      <c r="F73" s="1">
+        <v>45025</v>
+      </c>
+      <c r="G73" t="s">
         <v>100</v>
-      </c>
-      <c r="C73" t="s">
-        <v>101</v>
-      </c>
-      <c r="D73" t="s">
-        <v>105</v>
-      </c>
-      <c r="E73" t="s">
-        <v>105</v>
-      </c>
-      <c r="F73" s="1">
-        <v>45455</v>
-      </c>
-      <c r="G73" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15">
       <c r="A74">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C74" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E74" t="s">
         <v>105</v>
       </c>
       <c r="F74" s="1">
-        <v>45089</v>
-      </c>
-      <c r="G74" t="s">
+        <v>46128</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15">
       <c r="A75">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B75" t="s">
+        <v>102</v>
+      </c>
+      <c r="C75" t="s">
+        <v>103</v>
+      </c>
+      <c r="D75" t="s">
         <v>107</v>
       </c>
-      <c r="C75" t="s">
+      <c r="E75" t="s">
+        <v>107</v>
+      </c>
+      <c r="F75" s="1">
+        <v>45820</v>
+      </c>
+      <c r="G75" t="s">
         <v>108</v>
-      </c>
-      <c r="D75" t="s">
-        <v>109</v>
-      </c>
-      <c r="E75" t="s">
-        <v>109</v>
-      </c>
-      <c r="F75" s="1">
-        <v>46142</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15">
       <c r="A76">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B76" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" t="s">
         <v>107</v>
       </c>
-      <c r="C76" t="s">
+      <c r="E76" t="s">
+        <v>107</v>
+      </c>
+      <c r="F76" s="1">
+        <v>45455</v>
+      </c>
+      <c r="G76" t="s">
         <v>108</v>
-      </c>
-      <c r="D76" t="s">
-        <v>111</v>
-      </c>
-      <c r="E76" t="s">
-        <v>111</v>
-      </c>
-      <c r="F76" s="1">
-        <v>45813</v>
-      </c>
-      <c r="G76" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15">
       <c r="A77">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B77" t="s">
+        <v>102</v>
+      </c>
+      <c r="C77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" t="s">
         <v>107</v>
       </c>
-      <c r="C77" t="s">
+      <c r="E77" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="1">
+        <v>45089</v>
+      </c>
+      <c r="G77" t="s">
         <v>108</v>
-      </c>
-      <c r="D77" t="s">
-        <v>111</v>
-      </c>
-      <c r="E77" t="s">
-        <v>111</v>
-      </c>
-      <c r="F77" s="1">
-        <v>45448</v>
-      </c>
-      <c r="G77" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15">
       <c r="A78">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
         <v>111</v>
@@ -3050,33 +3075,33 @@
         <v>111</v>
       </c>
       <c r="F78" s="1">
-        <v>45082</v>
-      </c>
-      <c r="G78" t="s">
+        <v>46142</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15">
+      <c r="A79">
+        <v>2025</v>
+      </c>
+      <c r="B79" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="15">
-      <c r="A79" s="11">
-        <v>2025</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
+        <v>113</v>
+      </c>
+      <c r="F79" s="1">
+        <v>45813</v>
+      </c>
+      <c r="G79" t="s">
         <v>112</v>
-      </c>
-      <c r="C79" t="s">
-        <v>113</v>
-      </c>
-      <c r="D79" t="s">
-        <v>114</v>
-      </c>
-      <c r="E79" t="s">
-        <v>114</v>
-      </c>
-      <c r="F79" s="1">
-        <v>45730</v>
-      </c>
-      <c r="G79" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15">
@@ -3084,22 +3109,22 @@
         <v>2024</v>
       </c>
       <c r="B80" t="s">
+        <v>109</v>
+      </c>
+      <c r="C80" t="s">
+        <v>110</v>
+      </c>
+      <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" t="s">
+        <v>113</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45448</v>
+      </c>
+      <c r="G80" t="s">
         <v>112</v>
-      </c>
-      <c r="C80" t="s">
-        <v>113</v>
-      </c>
-      <c r="D80" t="s">
-        <v>114</v>
-      </c>
-      <c r="E80" t="s">
-        <v>114</v>
-      </c>
-      <c r="F80" s="1">
-        <v>45365</v>
-      </c>
-      <c r="G80" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15">
@@ -3107,45 +3132,45 @@
         <v>2023</v>
       </c>
       <c r="B81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" t="s">
+        <v>110</v>
+      </c>
+      <c r="D81" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" t="s">
+        <v>113</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45082</v>
+      </c>
+      <c r="G81" t="s">
         <v>112</v>
       </c>
-      <c r="C81" t="s">
-        <v>113</v>
-      </c>
-      <c r="D81" t="s">
+    </row>
+    <row r="82" spans="1:7" ht="15">
+      <c r="A82" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B82" t="s">
         <v>114</v>
       </c>
-      <c r="E81" t="s">
-        <v>114</v>
-      </c>
-      <c r="F81" s="1">
-        <v>44999</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="C82" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="15">
-      <c r="A82" s="12">
-        <v>2025</v>
-      </c>
-      <c r="B82" t="s">
+      <c r="D82" t="s">
         <v>116</v>
       </c>
-      <c r="C82" t="s">
+      <c r="E82" t="s">
+        <v>116</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45730</v>
+      </c>
+      <c r="G82" t="s">
         <v>117</v>
-      </c>
-      <c r="D82" t="s">
-        <v>118</v>
-      </c>
-      <c r="E82" t="s">
-        <v>118</v>
-      </c>
-      <c r="F82" s="1">
-        <v>45736</v>
-      </c>
-      <c r="G82" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15">
@@ -3153,22 +3178,22 @@
         <v>2024</v>
       </c>
       <c r="B83" t="s">
+        <v>114</v>
+      </c>
+      <c r="C83" t="s">
+        <v>115</v>
+      </c>
+      <c r="D83" t="s">
         <v>116</v>
       </c>
-      <c r="C83" t="s">
+      <c r="E83" t="s">
+        <v>116</v>
+      </c>
+      <c r="F83" s="1">
+        <v>45365</v>
+      </c>
+      <c r="G83" t="s">
         <v>117</v>
-      </c>
-      <c r="D83" t="s">
-        <v>118</v>
-      </c>
-      <c r="E83" t="s">
-        <v>118</v>
-      </c>
-      <c r="F83" s="1">
-        <v>45371</v>
-      </c>
-      <c r="G83" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15">
@@ -3176,65 +3201,68 @@
         <v>2023</v>
       </c>
       <c r="B84" t="s">
+        <v>114</v>
+      </c>
+      <c r="C84" t="s">
+        <v>115</v>
+      </c>
+      <c r="D84" t="s">
         <v>116</v>
       </c>
-      <c r="C84" t="s">
+      <c r="E84" t="s">
+        <v>116</v>
+      </c>
+      <c r="F84" s="1">
+        <v>44999</v>
+      </c>
+      <c r="G84" t="s">
         <v>117</v>
       </c>
-      <c r="D84" t="s">
+    </row>
+    <row r="85" spans="1:7" ht="15">
+      <c r="A85" s="14">
+        <v>2026</v>
+      </c>
+      <c r="B85" t="s">
         <v>118</v>
       </c>
-      <c r="E84" t="s">
+      <c r="C85" t="s">
+        <v>119</v>
+      </c>
+      <c r="D85" t="s">
+        <v>120</v>
+      </c>
+      <c r="E85" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G85" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15">
+      <c r="A86" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B86" t="s">
         <v>118</v>
       </c>
-      <c r="F84" s="1">
-        <v>45005</v>
-      </c>
-      <c r="G84" t="s">
+      <c r="C86" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="15">
-      <c r="A85">
-        <v>2026</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="D86" t="s">
         <v>120</v>
       </c>
-      <c r="C85" t="s">
+      <c r="E86" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G86" t="s">
         <v>121</v>
-      </c>
-      <c r="D85" t="s">
-        <v>122</v>
-      </c>
-      <c r="F85" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15">
-      <c r="A86">
-        <v>2025</v>
-      </c>
-      <c r="B86" t="s">
-        <v>120</v>
-      </c>
-      <c r="C86" t="s">
-        <v>121</v>
-      </c>
-      <c r="D86" t="s">
-        <v>124</v>
-      </c>
-      <c r="E86" t="s">
-        <v>124</v>
-      </c>
-      <c r="F86" s="1">
-        <v>45838</v>
-      </c>
-      <c r="G86" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15">
@@ -3242,22 +3270,22 @@
         <v>2024</v>
       </c>
       <c r="B87" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" t="s">
+        <v>119</v>
+      </c>
+      <c r="D87" t="s">
         <v>120</v>
       </c>
-      <c r="C87" t="s">
+      <c r="E87" t="s">
+        <v>120</v>
+      </c>
+      <c r="F87" s="1">
+        <v>45371</v>
+      </c>
+      <c r="G87" t="s">
         <v>121</v>
-      </c>
-      <c r="D87" t="s">
-        <v>124</v>
-      </c>
-      <c r="E87" t="s">
-        <v>124</v>
-      </c>
-      <c r="F87" s="1">
-        <v>45473</v>
-      </c>
-      <c r="G87" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15">
@@ -3265,22 +3293,22 @@
         <v>2023</v>
       </c>
       <c r="B88" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" t="s">
+        <v>119</v>
+      </c>
+      <c r="D88" t="s">
         <v>120</v>
       </c>
-      <c r="C88" t="s">
+      <c r="E88" t="s">
+        <v>120</v>
+      </c>
+      <c r="F88" s="1">
+        <v>45005</v>
+      </c>
+      <c r="G88" t="s">
         <v>121</v>
-      </c>
-      <c r="D88" t="s">
-        <v>124</v>
-      </c>
-      <c r="E88" t="s">
-        <v>124</v>
-      </c>
-      <c r="F88" s="1">
-        <v>45107</v>
-      </c>
-      <c r="G88" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15">
@@ -3288,22 +3316,19 @@
         <v>2026</v>
       </c>
       <c r="B89" t="s">
+        <v>122</v>
+      </c>
+      <c r="C89" t="s">
+        <v>123</v>
+      </c>
+      <c r="D89" t="s">
+        <v>124</v>
+      </c>
+      <c r="F89" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G89" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C89" t="s">
-        <v>126</v>
-      </c>
-      <c r="D89" t="s">
-        <v>127</v>
-      </c>
-      <c r="E89" t="s">
-        <v>127</v>
-      </c>
-      <c r="F89" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15">
@@ -3311,22 +3336,22 @@
         <v>2025</v>
       </c>
       <c r="B90" t="s">
+        <v>122</v>
+      </c>
+      <c r="C90" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" t="s">
+        <v>126</v>
+      </c>
+      <c r="E90" t="s">
+        <v>126</v>
+      </c>
+      <c r="F90" s="1">
+        <v>45838</v>
+      </c>
+      <c r="G90" t="s">
         <v>125</v>
-      </c>
-      <c r="C90" t="s">
-        <v>126</v>
-      </c>
-      <c r="D90" t="s">
-        <v>127</v>
-      </c>
-      <c r="E90" t="s">
-        <v>127</v>
-      </c>
-      <c r="F90" s="1">
-        <v>45742</v>
-      </c>
-      <c r="G90" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15">
@@ -3334,22 +3359,22 @@
         <v>2024</v>
       </c>
       <c r="B91" t="s">
+        <v>122</v>
+      </c>
+      <c r="C91" t="s">
+        <v>123</v>
+      </c>
+      <c r="D91" t="s">
+        <v>126</v>
+      </c>
+      <c r="E91" t="s">
+        <v>126</v>
+      </c>
+      <c r="F91" s="1">
+        <v>45473</v>
+      </c>
+      <c r="G91" t="s">
         <v>125</v>
-      </c>
-      <c r="C91" t="s">
-        <v>126</v>
-      </c>
-      <c r="D91" t="s">
-        <v>127</v>
-      </c>
-      <c r="E91" t="s">
-        <v>127</v>
-      </c>
-      <c r="F91" s="1">
-        <v>45377</v>
-      </c>
-      <c r="G91" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15">
@@ -3357,22 +3382,22 @@
         <v>2023</v>
       </c>
       <c r="B92" t="s">
+        <v>122</v>
+      </c>
+      <c r="C92" t="s">
+        <v>123</v>
+      </c>
+      <c r="D92" t="s">
+        <v>126</v>
+      </c>
+      <c r="E92" t="s">
+        <v>126</v>
+      </c>
+      <c r="F92" s="1">
+        <v>45107</v>
+      </c>
+      <c r="G92" t="s">
         <v>125</v>
-      </c>
-      <c r="C92" t="s">
-        <v>126</v>
-      </c>
-      <c r="D92" t="s">
-        <v>127</v>
-      </c>
-      <c r="E92" t="s">
-        <v>127</v>
-      </c>
-      <c r="F92" s="1">
-        <v>45011</v>
-      </c>
-      <c r="G92" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15">
@@ -3380,22 +3405,22 @@
         <v>2026</v>
       </c>
       <c r="B93" t="s">
+        <v>127</v>
+      </c>
+      <c r="C93" t="s">
+        <v>128</v>
+      </c>
+      <c r="D93" t="s">
         <v>129</v>
       </c>
-      <c r="C93" t="s">
+      <c r="E93" t="s">
+        <v>129</v>
+      </c>
+      <c r="F93" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G93" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="D93" t="s">
-        <v>131</v>
-      </c>
-      <c r="E93" t="s">
-        <v>131</v>
-      </c>
-      <c r="F93" s="1">
-        <v>46127</v>
-      </c>
-      <c r="G93" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15">
@@ -3403,22 +3428,22 @@
         <v>2025</v>
       </c>
       <c r="B94" t="s">
+        <v>127</v>
+      </c>
+      <c r="C94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" t="s">
         <v>129</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94" t="s">
+        <v>129</v>
+      </c>
+      <c r="F94" s="1">
+        <v>45742</v>
+      </c>
+      <c r="G94" t="s">
         <v>130</v>
-      </c>
-      <c r="D94" t="s">
-        <v>131</v>
-      </c>
-      <c r="E94" t="s">
-        <v>131</v>
-      </c>
-      <c r="F94" s="1">
-        <v>45808</v>
-      </c>
-      <c r="G94" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15">
@@ -3426,22 +3451,22 @@
         <v>2024</v>
       </c>
       <c r="B95" t="s">
+        <v>127</v>
+      </c>
+      <c r="C95" t="s">
+        <v>128</v>
+      </c>
+      <c r="D95" t="s">
         <v>129</v>
       </c>
-      <c r="C95" t="s">
+      <c r="E95" t="s">
+        <v>129</v>
+      </c>
+      <c r="F95" s="1">
+        <v>45377</v>
+      </c>
+      <c r="G95" t="s">
         <v>130</v>
-      </c>
-      <c r="D95" t="s">
-        <v>131</v>
-      </c>
-      <c r="E95" t="s">
-        <v>131</v>
-      </c>
-      <c r="F95" s="1">
-        <v>45443</v>
-      </c>
-      <c r="G95" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15">
@@ -3449,22 +3474,22 @@
         <v>2023</v>
       </c>
       <c r="B96" t="s">
+        <v>127</v>
+      </c>
+      <c r="C96" t="s">
+        <v>128</v>
+      </c>
+      <c r="D96" t="s">
         <v>129</v>
       </c>
-      <c r="C96" t="s">
+      <c r="E96" t="s">
+        <v>129</v>
+      </c>
+      <c r="F96" s="1">
+        <v>45011</v>
+      </c>
+      <c r="G96" t="s">
         <v>130</v>
-      </c>
-      <c r="D96" t="s">
-        <v>131</v>
-      </c>
-      <c r="E96" t="s">
-        <v>131</v>
-      </c>
-      <c r="F96" s="1">
-        <v>45077</v>
-      </c>
-      <c r="G96" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15">
@@ -3472,22 +3497,22 @@
         <v>2026</v>
       </c>
       <c r="B97" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" t="s">
+        <v>132</v>
+      </c>
+      <c r="D97" t="s">
         <v>133</v>
       </c>
-      <c r="C97" t="s">
+      <c r="E97" t="s">
+        <v>133</v>
+      </c>
+      <c r="F97" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G97" t="s">
         <v>134</v>
-      </c>
-      <c r="D97" t="s">
-        <v>135</v>
-      </c>
-      <c r="E97" t="s">
-        <v>135</v>
-      </c>
-      <c r="F97" s="1">
-        <v>46135</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
@@ -3495,22 +3520,22 @@
         <v>2025</v>
       </c>
       <c r="B98" t="s">
+        <v>131</v>
+      </c>
+      <c r="C98" t="s">
+        <v>132</v>
+      </c>
+      <c r="D98" t="s">
         <v>133</v>
       </c>
-      <c r="C98" t="s">
+      <c r="E98" t="s">
+        <v>133</v>
+      </c>
+      <c r="F98" s="1">
+        <v>45808</v>
+      </c>
+      <c r="G98" t="s">
         <v>134</v>
-      </c>
-      <c r="D98" t="s">
-        <v>137</v>
-      </c>
-      <c r="E98" t="s">
-        <v>137</v>
-      </c>
-      <c r="F98" s="1">
-        <v>45736</v>
-      </c>
-      <c r="G98" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15">
@@ -3518,22 +3543,22 @@
         <v>2024</v>
       </c>
       <c r="B99" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99" t="s">
+        <v>132</v>
+      </c>
+      <c r="D99" t="s">
         <v>133</v>
       </c>
-      <c r="C99" t="s">
+      <c r="E99" t="s">
+        <v>133</v>
+      </c>
+      <c r="F99" s="1">
+        <v>45443</v>
+      </c>
+      <c r="G99" t="s">
         <v>134</v>
-      </c>
-      <c r="D99" t="s">
-        <v>137</v>
-      </c>
-      <c r="E99" t="s">
-        <v>137</v>
-      </c>
-      <c r="F99" s="1">
-        <v>45371</v>
-      </c>
-      <c r="G99" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15">
@@ -3541,22 +3566,22 @@
         <v>2023</v>
       </c>
       <c r="B100" t="s">
+        <v>131</v>
+      </c>
+      <c r="C100" t="s">
+        <v>132</v>
+      </c>
+      <c r="D100" t="s">
         <v>133</v>
       </c>
-      <c r="C100" t="s">
+      <c r="E100" t="s">
+        <v>133</v>
+      </c>
+      <c r="F100" s="1">
+        <v>45077</v>
+      </c>
+      <c r="G100" t="s">
         <v>134</v>
-      </c>
-      <c r="D100" t="s">
-        <v>137</v>
-      </c>
-      <c r="E100" t="s">
-        <v>137</v>
-      </c>
-      <c r="F100" s="1">
-        <v>45005</v>
-      </c>
-      <c r="G100" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15">
@@ -3564,22 +3589,22 @@
         <v>2026</v>
       </c>
       <c r="B101" t="s">
+        <v>135</v>
+      </c>
+      <c r="C101" t="s">
+        <v>136</v>
+      </c>
+      <c r="D101" t="s">
+        <v>137</v>
+      </c>
+      <c r="E101" t="s">
+        <v>137</v>
+      </c>
+      <c r="F101" s="1">
+        <v>46135</v>
+      </c>
+      <c r="G101" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C101" t="s">
-        <v>139</v>
-      </c>
-      <c r="D101" t="s">
-        <v>140</v>
-      </c>
-      <c r="E101" t="s">
-        <v>140</v>
-      </c>
-      <c r="F101" s="1">
-        <v>46121</v>
-      </c>
-      <c r="G101" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15">
@@ -3587,22 +3612,22 @@
         <v>2025</v>
       </c>
       <c r="B102" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" t="s">
+        <v>136</v>
+      </c>
+      <c r="D102" t="s">
+        <v>139</v>
+      </c>
+      <c r="E102" t="s">
+        <v>139</v>
+      </c>
+      <c r="F102" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G102" t="s">
         <v>138</v>
-      </c>
-      <c r="C102" t="s">
-        <v>139</v>
-      </c>
-      <c r="D102" t="s">
-        <v>142</v>
-      </c>
-      <c r="E102" t="s">
-        <v>142</v>
-      </c>
-      <c r="F102" s="1">
-        <v>45735</v>
-      </c>
-      <c r="G102" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15">
@@ -3610,22 +3635,22 @@
         <v>2024</v>
       </c>
       <c r="B103" t="s">
+        <v>135</v>
+      </c>
+      <c r="C103" t="s">
+        <v>136</v>
+      </c>
+      <c r="D103" t="s">
+        <v>139</v>
+      </c>
+      <c r="E103" t="s">
+        <v>139</v>
+      </c>
+      <c r="F103" s="1">
+        <v>45371</v>
+      </c>
+      <c r="G103" t="s">
         <v>138</v>
-      </c>
-      <c r="C103" t="s">
-        <v>139</v>
-      </c>
-      <c r="D103" t="s">
-        <v>142</v>
-      </c>
-      <c r="E103" t="s">
-        <v>142</v>
-      </c>
-      <c r="F103" s="1">
-        <v>45370</v>
-      </c>
-      <c r="G103" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15">
@@ -3633,22 +3658,22 @@
         <v>2023</v>
       </c>
       <c r="B104" t="s">
+        <v>135</v>
+      </c>
+      <c r="C104" t="s">
+        <v>136</v>
+      </c>
+      <c r="D104" t="s">
+        <v>139</v>
+      </c>
+      <c r="E104" t="s">
+        <v>139</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45005</v>
+      </c>
+      <c r="G104" t="s">
         <v>138</v>
-      </c>
-      <c r="C104" t="s">
-        <v>139</v>
-      </c>
-      <c r="D104" t="s">
-        <v>142</v>
-      </c>
-      <c r="E104" t="s">
-        <v>142</v>
-      </c>
-      <c r="F104" s="1">
-        <v>45004</v>
-      </c>
-      <c r="G104" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15">
@@ -3656,22 +3681,22 @@
         <v>2026</v>
       </c>
       <c r="B105" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105" t="s">
+        <v>141</v>
+      </c>
+      <c r="D105" t="s">
+        <v>142</v>
+      </c>
+      <c r="E105" t="s">
+        <v>142</v>
+      </c>
+      <c r="F105" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G105" t="s">
         <v>143</v>
-      </c>
-      <c r="C105" t="s">
-        <v>144</v>
-      </c>
-      <c r="D105" t="s">
-        <v>145</v>
-      </c>
-      <c r="E105" t="s">
-        <v>145</v>
-      </c>
-      <c r="F105" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G105" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15">
@@ -3679,22 +3704,22 @@
         <v>2025</v>
       </c>
       <c r="B106" t="s">
+        <v>140</v>
+      </c>
+      <c r="C106" t="s">
+        <v>141</v>
+      </c>
+      <c r="D106" t="s">
+        <v>144</v>
+      </c>
+      <c r="E106" t="s">
+        <v>144</v>
+      </c>
+      <c r="F106" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G106" t="s">
         <v>143</v>
-      </c>
-      <c r="C106" t="s">
-        <v>144</v>
-      </c>
-      <c r="D106" t="s">
-        <v>145</v>
-      </c>
-      <c r="E106" t="s">
-        <v>145</v>
-      </c>
-      <c r="F106" s="1">
-        <v>45741</v>
-      </c>
-      <c r="G106" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15">
@@ -3702,22 +3727,22 @@
         <v>2024</v>
       </c>
       <c r="B107" t="s">
+        <v>140</v>
+      </c>
+      <c r="C107" t="s">
+        <v>141</v>
+      </c>
+      <c r="D107" t="s">
+        <v>144</v>
+      </c>
+      <c r="E107" t="s">
+        <v>144</v>
+      </c>
+      <c r="F107" s="1">
+        <v>45370</v>
+      </c>
+      <c r="G107" t="s">
         <v>143</v>
-      </c>
-      <c r="C107" t="s">
-        <v>144</v>
-      </c>
-      <c r="D107" t="s">
-        <v>145</v>
-      </c>
-      <c r="E107" t="s">
-        <v>145</v>
-      </c>
-      <c r="F107" s="1">
-        <v>45376</v>
-      </c>
-      <c r="G107" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15">
@@ -3725,137 +3750,137 @@
         <v>2023</v>
       </c>
       <c r="B108" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108" t="s">
+        <v>141</v>
+      </c>
+      <c r="D108" t="s">
+        <v>144</v>
+      </c>
+      <c r="E108" t="s">
+        <v>144</v>
+      </c>
+      <c r="F108" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G108" t="s">
         <v>143</v>
       </c>
-      <c r="C108" t="s">
-        <v>144</v>
-      </c>
-      <c r="D108" t="s">
+    </row>
+    <row r="109" spans="1:7" ht="15">
+      <c r="A109">
+        <v>2026</v>
+      </c>
+      <c r="B109" t="s">
         <v>145</v>
       </c>
-      <c r="E108" t="s">
-        <v>145</v>
-      </c>
-      <c r="F108" s="1">
-        <v>45010</v>
-      </c>
-      <c r="G108" t="s">
+      <c r="C109" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="15">
-      <c r="A109" s="10">
-        <v>2025</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
         <v>147</v>
       </c>
-      <c r="C109" t="s">
+      <c r="E109" t="s">
+        <v>147</v>
+      </c>
+      <c r="F109" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G109" t="s">
         <v>148</v>
-      </c>
-      <c r="D109" t="s">
-        <v>149</v>
-      </c>
-      <c r="E109" t="s">
-        <v>149</v>
-      </c>
-      <c r="F109" s="1">
-        <v>45751</v>
-      </c>
-      <c r="G109" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15">
       <c r="A110">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B110" t="s">
+        <v>145</v>
+      </c>
+      <c r="C110" t="s">
+        <v>146</v>
+      </c>
+      <c r="D110" t="s">
         <v>147</v>
       </c>
-      <c r="C110" t="s">
+      <c r="E110" t="s">
+        <v>147</v>
+      </c>
+      <c r="F110" s="1">
+        <v>45741</v>
+      </c>
+      <c r="G110" t="s">
         <v>148</v>
-      </c>
-      <c r="D110" t="s">
-        <v>149</v>
-      </c>
-      <c r="E110" t="s">
-        <v>149</v>
-      </c>
-      <c r="F110" s="1">
-        <v>45386</v>
-      </c>
-      <c r="G110" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15">
       <c r="A111">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B111" t="s">
+        <v>145</v>
+      </c>
+      <c r="C111" t="s">
+        <v>146</v>
+      </c>
+      <c r="D111" t="s">
         <v>147</v>
       </c>
-      <c r="C111" t="s">
+      <c r="E111" t="s">
+        <v>147</v>
+      </c>
+      <c r="F111" s="1">
+        <v>45376</v>
+      </c>
+      <c r="G111" t="s">
         <v>148</v>
-      </c>
-      <c r="D111" t="s">
-        <v>149</v>
-      </c>
-      <c r="E111" t="s">
-        <v>149</v>
-      </c>
-      <c r="F111" s="1">
-        <v>45020</v>
-      </c>
-      <c r="G111" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15">
       <c r="A112">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B112" t="s">
+        <v>145</v>
+      </c>
+      <c r="C112" t="s">
+        <v>146</v>
+      </c>
+      <c r="D112" t="s">
+        <v>147</v>
+      </c>
+      <c r="E112" t="s">
+        <v>147</v>
+      </c>
+      <c r="F112" s="1">
+        <v>45010</v>
+      </c>
+      <c r="G112" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15">
+      <c r="A113" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B113" t="s">
+        <v>149</v>
+      </c>
+      <c r="C113" t="s">
+        <v>150</v>
+      </c>
+      <c r="D113" t="s">
         <v>151</v>
       </c>
-      <c r="C112" t="s">
+      <c r="E113" t="s">
+        <v>151</v>
+      </c>
+      <c r="F113" s="1">
+        <v>45751</v>
+      </c>
+      <c r="G113" t="s">
         <v>152</v>
-      </c>
-      <c r="D112" t="s">
-        <v>153</v>
-      </c>
-      <c r="E112" t="s">
-        <v>153</v>
-      </c>
-      <c r="F112" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G112" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="15">
-      <c r="A113">
-        <v>2025</v>
-      </c>
-      <c r="B113" t="s">
-        <v>151</v>
-      </c>
-      <c r="C113" t="s">
-        <v>152</v>
-      </c>
-      <c r="D113" t="s">
-        <v>153</v>
-      </c>
-      <c r="E113" t="s">
-        <v>153</v>
-      </c>
-      <c r="F113" s="1">
-        <v>45810</v>
-      </c>
-      <c r="G113" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15">
@@ -3863,22 +3888,22 @@
         <v>2024</v>
       </c>
       <c r="B114" t="s">
+        <v>149</v>
+      </c>
+      <c r="C114" t="s">
+        <v>150</v>
+      </c>
+      <c r="D114" t="s">
         <v>151</v>
       </c>
-      <c r="C114" t="s">
+      <c r="E114" t="s">
+        <v>151</v>
+      </c>
+      <c r="F114" s="1">
+        <v>45386</v>
+      </c>
+      <c r="G114" t="s">
         <v>152</v>
-      </c>
-      <c r="D114" t="s">
-        <v>153</v>
-      </c>
-      <c r="E114" t="s">
-        <v>153</v>
-      </c>
-      <c r="F114" s="1">
-        <v>45445</v>
-      </c>
-      <c r="G114" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15">
@@ -3886,22 +3911,22 @@
         <v>2023</v>
       </c>
       <c r="B115" t="s">
+        <v>149</v>
+      </c>
+      <c r="C115" t="s">
+        <v>150</v>
+      </c>
+      <c r="D115" t="s">
         <v>151</v>
       </c>
-      <c r="C115" t="s">
+      <c r="E115" t="s">
+        <v>151</v>
+      </c>
+      <c r="F115" s="1">
+        <v>45020</v>
+      </c>
+      <c r="G115" t="s">
         <v>152</v>
-      </c>
-      <c r="D115" t="s">
-        <v>153</v>
-      </c>
-      <c r="E115" t="s">
-        <v>153</v>
-      </c>
-      <c r="F115" s="1">
-        <v>45079</v>
-      </c>
-      <c r="G115" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15">
@@ -3909,22 +3934,22 @@
         <v>2026</v>
       </c>
       <c r="B116" t="s">
+        <v>153</v>
+      </c>
+      <c r="C116" t="s">
+        <v>154</v>
+      </c>
+      <c r="D116" t="s">
         <v>155</v>
       </c>
-      <c r="C116" t="s">
+      <c r="E116" t="s">
+        <v>155</v>
+      </c>
+      <c r="F116" s="1">
+        <v>46120</v>
+      </c>
+      <c r="G116" t="s">
         <v>156</v>
-      </c>
-      <c r="D116" t="s">
-        <v>157</v>
-      </c>
-      <c r="E116" t="s">
-        <v>157</v>
-      </c>
-      <c r="F116" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G116" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15">
@@ -3932,22 +3957,22 @@
         <v>2025</v>
       </c>
       <c r="B117" t="s">
+        <v>153</v>
+      </c>
+      <c r="C117" t="s">
+        <v>154</v>
+      </c>
+      <c r="D117" t="s">
         <v>155</v>
       </c>
-      <c r="C117" t="s">
+      <c r="E117" t="s">
+        <v>155</v>
+      </c>
+      <c r="F117" s="1">
+        <v>45810</v>
+      </c>
+      <c r="G117" t="s">
         <v>156</v>
-      </c>
-      <c r="D117" t="s">
-        <v>159</v>
-      </c>
-      <c r="E117" t="s">
-        <v>159</v>
-      </c>
-      <c r="F117" s="1">
-        <v>45735</v>
-      </c>
-      <c r="G117" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15">
@@ -3955,22 +3980,22 @@
         <v>2024</v>
       </c>
       <c r="B118" t="s">
+        <v>153</v>
+      </c>
+      <c r="C118" t="s">
+        <v>154</v>
+      </c>
+      <c r="D118" t="s">
         <v>155</v>
       </c>
-      <c r="C118" t="s">
+      <c r="E118" t="s">
+        <v>155</v>
+      </c>
+      <c r="F118" s="1">
+        <v>45445</v>
+      </c>
+      <c r="G118" t="s">
         <v>156</v>
-      </c>
-      <c r="D118" t="s">
-        <v>159</v>
-      </c>
-      <c r="E118" t="s">
-        <v>159</v>
-      </c>
-      <c r="F118" s="1">
-        <v>45370</v>
-      </c>
-      <c r="G118" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15">
@@ -3978,42 +4003,45 @@
         <v>2023</v>
       </c>
       <c r="B119" t="s">
+        <v>153</v>
+      </c>
+      <c r="C119" t="s">
+        <v>154</v>
+      </c>
+      <c r="D119" t="s">
         <v>155</v>
       </c>
-      <c r="C119" t="s">
+      <c r="E119" t="s">
+        <v>155</v>
+      </c>
+      <c r="F119" s="1">
+        <v>45079</v>
+      </c>
+      <c r="G119" t="s">
         <v>156</v>
       </c>
-      <c r="D119" t="s">
+    </row>
+    <row r="120" spans="1:7" ht="15">
+      <c r="A120">
+        <v>2026</v>
+      </c>
+      <c r="B120" t="s">
+        <v>157</v>
+      </c>
+      <c r="C120" t="s">
+        <v>158</v>
+      </c>
+      <c r="D120" t="s">
         <v>159</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E120" t="s">
         <v>159</v>
       </c>
-      <c r="F119" s="1">
-        <v>45004</v>
-      </c>
-      <c r="G119" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="15">
-      <c r="A120" s="10">
-        <v>2026</v>
-      </c>
-      <c r="B120" t="s">
+      <c r="F120" s="1">
+        <v>46126</v>
+      </c>
+      <c r="G120" t="s">
         <v>160</v>
-      </c>
-      <c r="C120" t="s">
-        <v>161</v>
-      </c>
-      <c r="D120" t="s">
-        <v>162</v>
-      </c>
-      <c r="E120" t="s">
-        <v>162</v>
-      </c>
-      <c r="F120" s="1">
-        <v>46120</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15">
@@ -4021,22 +4049,22 @@
         <v>2025</v>
       </c>
       <c r="B121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C121" t="s">
+        <v>158</v>
+      </c>
+      <c r="D121" t="s">
+        <v>161</v>
+      </c>
+      <c r="E121" t="s">
+        <v>161</v>
+      </c>
+      <c r="F121" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G121" t="s">
         <v>160</v>
-      </c>
-      <c r="C121" t="s">
-        <v>161</v>
-      </c>
-      <c r="D121" t="s">
-        <v>163</v>
-      </c>
-      <c r="E121" t="s">
-        <v>163</v>
-      </c>
-      <c r="F121" s="1">
-        <v>45840</v>
-      </c>
-      <c r="G121" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15">
@@ -4044,22 +4072,22 @@
         <v>2024</v>
       </c>
       <c r="B122" t="s">
+        <v>157</v>
+      </c>
+      <c r="C122" t="s">
+        <v>158</v>
+      </c>
+      <c r="D122" t="s">
+        <v>161</v>
+      </c>
+      <c r="E122" t="s">
+        <v>161</v>
+      </c>
+      <c r="F122" s="1">
+        <v>45370</v>
+      </c>
+      <c r="G122" t="s">
         <v>160</v>
-      </c>
-      <c r="C122" t="s">
-        <v>161</v>
-      </c>
-      <c r="D122" t="s">
-        <v>163</v>
-      </c>
-      <c r="E122" t="s">
-        <v>163</v>
-      </c>
-      <c r="F122" s="1">
-        <v>45475</v>
-      </c>
-      <c r="G122" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15">
@@ -4067,45 +4095,42 @@
         <v>2023</v>
       </c>
       <c r="B123" t="s">
+        <v>157</v>
+      </c>
+      <c r="C123" t="s">
+        <v>158</v>
+      </c>
+      <c r="D123" t="s">
+        <v>161</v>
+      </c>
+      <c r="E123" t="s">
+        <v>161</v>
+      </c>
+      <c r="F123" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G123" t="s">
         <v>160</v>
       </c>
-      <c r="C123" t="s">
-        <v>161</v>
-      </c>
-      <c r="D123" t="s">
+    </row>
+    <row r="124" spans="1:7" ht="15">
+      <c r="A124" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B124" t="s">
+        <v>162</v>
+      </c>
+      <c r="C124" t="s">
         <v>163</v>
       </c>
-      <c r="E123" t="s">
-        <v>163</v>
-      </c>
-      <c r="F123" s="1">
-        <v>45109</v>
-      </c>
-      <c r="G123" t="s">
+      <c r="D124" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="15">
-      <c r="A124">
-        <v>2026</v>
-      </c>
-      <c r="B124" t="s">
-        <v>165</v>
-      </c>
-      <c r="C124" t="s">
-        <v>166</v>
-      </c>
-      <c r="D124" t="s">
-        <v>167</v>
-      </c>
       <c r="E124" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F124" s="1">
-        <v>46139</v>
-      </c>
-      <c r="G124" t="s">
-        <v>168</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15">
@@ -4113,22 +4138,22 @@
         <v>2025</v>
       </c>
       <c r="B125" t="s">
+        <v>162</v>
+      </c>
+      <c r="C125" t="s">
+        <v>163</v>
+      </c>
+      <c r="D125" t="s">
         <v>165</v>
       </c>
-      <c r="C125" t="s">
+      <c r="E125" t="s">
+        <v>165</v>
+      </c>
+      <c r="F125" s="1">
+        <v>45840</v>
+      </c>
+      <c r="G125" t="s">
         <v>166</v>
-      </c>
-      <c r="D125" t="s">
-        <v>169</v>
-      </c>
-      <c r="E125" t="s">
-        <v>169</v>
-      </c>
-      <c r="F125" s="1">
-        <v>45749</v>
-      </c>
-      <c r="G125" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15">
@@ -4136,22 +4161,22 @@
         <v>2024</v>
       </c>
       <c r="B126" t="s">
+        <v>162</v>
+      </c>
+      <c r="C126" t="s">
+        <v>163</v>
+      </c>
+      <c r="D126" t="s">
         <v>165</v>
       </c>
-      <c r="C126" t="s">
+      <c r="E126" t="s">
+        <v>165</v>
+      </c>
+      <c r="F126" s="1">
+        <v>45475</v>
+      </c>
+      <c r="G126" t="s">
         <v>166</v>
-      </c>
-      <c r="D126" t="s">
-        <v>169</v>
-      </c>
-      <c r="E126" t="s">
-        <v>169</v>
-      </c>
-      <c r="F126" s="1">
-        <v>45384</v>
-      </c>
-      <c r="G126" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15">
@@ -4159,424 +4184,424 @@
         <v>2023</v>
       </c>
       <c r="B127" t="s">
+        <v>162</v>
+      </c>
+      <c r="C127" t="s">
+        <v>163</v>
+      </c>
+      <c r="D127" t="s">
         <v>165</v>
       </c>
-      <c r="C127" t="s">
+      <c r="E127" t="s">
+        <v>165</v>
+      </c>
+      <c r="F127" s="1">
+        <v>45109</v>
+      </c>
+      <c r="G127" t="s">
         <v>166</v>
       </c>
-      <c r="D127" t="s">
+    </row>
+    <row r="128" spans="1:7" ht="15">
+      <c r="A128">
+        <v>2026</v>
+      </c>
+      <c r="B128" t="s">
+        <v>167</v>
+      </c>
+      <c r="C128" t="s">
+        <v>168</v>
+      </c>
+      <c r="D128" t="s">
         <v>169</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E128" t="s">
         <v>169</v>
       </c>
-      <c r="F127" s="1">
-        <v>45018</v>
-      </c>
-      <c r="G127" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="15">
-      <c r="A128" s="10">
-        <v>2025</v>
-      </c>
-      <c r="B128" t="s">
+      <c r="F128" s="1">
+        <v>46139</v>
+      </c>
+      <c r="G128" t="s">
         <v>170</v>
-      </c>
-      <c r="C128" t="s">
-        <v>171</v>
-      </c>
-      <c r="D128" t="s">
-        <v>172</v>
-      </c>
-      <c r="E128" t="s">
-        <v>172</v>
-      </c>
-      <c r="F128" s="1">
-        <v>45744</v>
-      </c>
-      <c r="G128" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15">
       <c r="A129">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B129" t="s">
+        <v>167</v>
+      </c>
+      <c r="C129" t="s">
+        <v>168</v>
+      </c>
+      <c r="D129" t="s">
+        <v>171</v>
+      </c>
+      <c r="E129" t="s">
+        <v>171</v>
+      </c>
+      <c r="F129" s="1">
+        <v>45749</v>
+      </c>
+      <c r="G129" t="s">
         <v>170</v>
-      </c>
-      <c r="C129" t="s">
-        <v>171</v>
-      </c>
-      <c r="D129" t="s">
-        <v>172</v>
-      </c>
-      <c r="E129" t="s">
-        <v>172</v>
-      </c>
-      <c r="F129" s="1">
-        <v>45379</v>
-      </c>
-      <c r="G129" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15">
       <c r="A130">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B130" t="s">
+        <v>167</v>
+      </c>
+      <c r="C130" t="s">
+        <v>168</v>
+      </c>
+      <c r="D130" t="s">
+        <v>171</v>
+      </c>
+      <c r="E130" t="s">
+        <v>171</v>
+      </c>
+      <c r="F130" s="1">
+        <v>45384</v>
+      </c>
+      <c r="G130" t="s">
         <v>170</v>
-      </c>
-      <c r="C130" t="s">
-        <v>171</v>
-      </c>
-      <c r="D130" t="s">
-        <v>172</v>
-      </c>
-      <c r="E130" t="s">
-        <v>172</v>
-      </c>
-      <c r="F130" s="1">
-        <v>45013</v>
-      </c>
-      <c r="G130" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15">
       <c r="A131">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B131" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C131" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D131" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E131" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F131" s="1">
-        <v>46120</v>
+        <v>45018</v>
       </c>
       <c r="G131" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15">
       <c r="A132">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B132" t="s">
+        <v>172</v>
+      </c>
+      <c r="C132" t="s">
+        <v>173</v>
+      </c>
+      <c r="D132" t="s">
         <v>174</v>
       </c>
-      <c r="C132" t="s">
+      <c r="E132" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F132" s="1">
+        <v>46161</v>
+      </c>
+      <c r="G132" t="s">
         <v>175</v>
-      </c>
-      <c r="D132" t="s">
-        <v>176</v>
-      </c>
-      <c r="E132" t="s">
-        <v>176</v>
-      </c>
-      <c r="F132" s="1">
-        <v>45733</v>
-      </c>
-      <c r="G132" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15">
       <c r="A133">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B133" t="s">
+        <v>172</v>
+      </c>
+      <c r="C133" t="s">
+        <v>173</v>
+      </c>
+      <c r="D133" t="s">
         <v>174</v>
       </c>
-      <c r="C133" t="s">
-        <v>175</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
+        <v>174</v>
+      </c>
+      <c r="F133" s="1">
+        <v>45744</v>
+      </c>
+      <c r="G133" t="s">
         <v>176</v>
-      </c>
-      <c r="E133" t="s">
-        <v>176</v>
-      </c>
-      <c r="F133" s="1">
-        <v>45368</v>
-      </c>
-      <c r="G133" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15">
       <c r="A134">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B134" t="s">
+        <v>172</v>
+      </c>
+      <c r="C134" t="s">
+        <v>173</v>
+      </c>
+      <c r="D134" t="s">
         <v>174</v>
       </c>
-      <c r="C134" t="s">
-        <v>175</v>
-      </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
+        <v>174</v>
+      </c>
+      <c r="F134" s="1">
+        <v>45379</v>
+      </c>
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="E134" t="s">
-        <v>176</v>
-      </c>
-      <c r="F134" s="1">
-        <v>45002</v>
-      </c>
-      <c r="G134" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15">
       <c r="A135">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B135" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C135" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D135" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E135" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F135" s="1">
-        <v>46127</v>
+        <v>45013</v>
       </c>
       <c r="G135" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15">
       <c r="A136">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B136" t="s">
+        <v>177</v>
+      </c>
+      <c r="C136" t="s">
         <v>178</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>179</v>
       </c>
-      <c r="D136" t="s">
-        <v>182</v>
-      </c>
       <c r="E136" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F136" s="1">
-        <v>45735</v>
+        <v>46120</v>
       </c>
       <c r="G136" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15">
       <c r="A137">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B137" t="s">
+        <v>177</v>
+      </c>
+      <c r="C137" t="s">
         <v>178</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
         <v>179</v>
       </c>
-      <c r="D137" t="s">
-        <v>182</v>
-      </c>
       <c r="E137" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F137" s="1">
-        <v>45370</v>
+        <v>45733</v>
       </c>
       <c r="G137" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15">
       <c r="A138">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B138" t="s">
+        <v>177</v>
+      </c>
+      <c r="C138" t="s">
         <v>178</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>179</v>
       </c>
-      <c r="D138" t="s">
-        <v>182</v>
-      </c>
       <c r="E138" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F138" s="1">
-        <v>45004</v>
+        <v>45368</v>
       </c>
       <c r="G138" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15">
       <c r="A139">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B139" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C139" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E139" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F139" s="1">
-        <v>46140</v>
+        <v>45002</v>
       </c>
       <c r="G139" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="15">
       <c r="A140">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B140" t="s">
+        <v>181</v>
+      </c>
+      <c r="C140" t="s">
+        <v>182</v>
+      </c>
+      <c r="D140" t="s">
         <v>183</v>
       </c>
-      <c r="C140" t="s">
+      <c r="E140" t="s">
+        <v>183</v>
+      </c>
+      <c r="F140" s="1">
+        <v>46127</v>
+      </c>
+      <c r="G140" t="s">
         <v>184</v>
-      </c>
-      <c r="D140" t="s">
-        <v>188</v>
-      </c>
-      <c r="E140" t="s">
-        <v>188</v>
-      </c>
-      <c r="F140" s="1">
-        <v>45705</v>
-      </c>
-      <c r="G140" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="15">
       <c r="A141">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B141" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C141" t="s">
+        <v>182</v>
+      </c>
+      <c r="D141" t="s">
+        <v>185</v>
+      </c>
+      <c r="E141" t="s">
+        <v>185</v>
+      </c>
+      <c r="F141" s="1">
+        <v>45735</v>
+      </c>
+      <c r="G141" t="s">
         <v>184</v>
-      </c>
-      <c r="D141" t="s">
-        <v>188</v>
-      </c>
-      <c r="E141" t="s">
-        <v>188</v>
-      </c>
-      <c r="F141" s="1">
-        <v>45339</v>
-      </c>
-      <c r="G141" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="15">
       <c r="A142">
+        <v>2024</v>
+      </c>
+      <c r="B142" t="s">
+        <v>181</v>
+      </c>
+      <c r="C142" t="s">
+        <v>182</v>
+      </c>
+      <c r="D142" t="s">
+        <v>185</v>
+      </c>
+      <c r="E142" t="s">
+        <v>185</v>
+      </c>
+      <c r="F142" s="1">
+        <v>45370</v>
+      </c>
+      <c r="G142" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15">
+      <c r="A143">
         <v>2023</v>
       </c>
-      <c r="B142" t="s">
-        <v>183</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="B143" t="s">
+        <v>181</v>
+      </c>
+      <c r="C143" t="s">
+        <v>182</v>
+      </c>
+      <c r="D143" t="s">
+        <v>185</v>
+      </c>
+      <c r="E143" t="s">
+        <v>185</v>
+      </c>
+      <c r="F143" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G143" t="s">
         <v>184</v>
-      </c>
-      <c r="D142" t="s">
-        <v>188</v>
-      </c>
-      <c r="E142" t="s">
-        <v>188</v>
-      </c>
-      <c r="F142" s="1">
-        <v>44974</v>
-      </c>
-      <c r="G142" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="15">
-      <c r="A143" s="10">
-        <v>2025</v>
-      </c>
-      <c r="B143" t="s">
-        <v>189</v>
-      </c>
-      <c r="C143" t="s">
-        <v>190</v>
-      </c>
-      <c r="D143" t="s">
-        <v>191</v>
-      </c>
-      <c r="E143" t="s">
-        <v>191</v>
-      </c>
-      <c r="F143" s="1">
-        <v>45737</v>
-      </c>
-      <c r="G143" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="15">
       <c r="A144">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B144" t="s">
+        <v>186</v>
+      </c>
+      <c r="C144" t="s">
+        <v>187</v>
+      </c>
+      <c r="D144" t="s">
+        <v>188</v>
+      </c>
+      <c r="E144" t="s">
         <v>189</v>
       </c>
-      <c r="C144" t="s">
+      <c r="F144" s="1">
+        <v>46140</v>
+      </c>
+      <c r="G144" t="s">
         <v>190</v>
-      </c>
-      <c r="D144" t="s">
-        <v>191</v>
-      </c>
-      <c r="E144" t="s">
-        <v>191</v>
-      </c>
-      <c r="F144" s="1">
-        <v>45372</v>
-      </c>
-      <c r="G144" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15">
       <c r="A145">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B145" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C145" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D145" t="s">
         <v>191</v>
@@ -4585,429 +4610,423 @@
         <v>191</v>
       </c>
       <c r="F145" s="1">
-        <v>45006</v>
+        <v>45705</v>
       </c>
       <c r="G145" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="15">
-      <c r="A146" s="10">
-        <v>2026</v>
+      <c r="A146">
+        <v>2024</v>
       </c>
       <c r="B146" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C146" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D146" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E146" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F146" s="1">
-        <v>46125</v>
+        <v>45339</v>
       </c>
       <c r="G146" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15">
-      <c r="A147" s="13">
-        <v>2025</v>
+      <c r="A147">
+        <v>2023</v>
       </c>
       <c r="B147" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C147" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D147" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E147" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F147" s="1">
-        <v>45741</v>
+        <v>44974</v>
       </c>
       <c r="G147" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="15">
       <c r="A148">
-        <v>2024</v>
-      </c>
-      <c r="B148" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D148" t="s">
+        <v>192</v>
+      </c>
+      <c r="E148" t="s">
+        <v>192</v>
+      </c>
+      <c r="F148" s="1">
+        <v>46162</v>
+      </c>
+      <c r="G148" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C148" t="s">
+    </row>
+    <row r="149" spans="1:7" ht="15">
+      <c r="A149" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B149" t="s">
         <v>194</v>
       </c>
-      <c r="D148" t="s">
-        <v>197</v>
-      </c>
-      <c r="E148" t="s">
-        <v>197</v>
-      </c>
-      <c r="F148" s="1">
-        <v>45376</v>
-      </c>
-      <c r="G148" t="s">
+      <c r="C149" t="s">
+        <v>195</v>
+      </c>
+      <c r="D149" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="15">
-      <c r="A149">
-        <v>2023</v>
-      </c>
-      <c r="B149" t="s">
+      <c r="E149" t="s">
+        <v>196</v>
+      </c>
+      <c r="F149" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G149" t="s">
         <v>193</v>
-      </c>
-      <c r="C149" t="s">
-        <v>194</v>
-      </c>
-      <c r="D149" t="s">
-        <v>197</v>
-      </c>
-      <c r="E149" t="s">
-        <v>197</v>
-      </c>
-      <c r="F149" s="1">
-        <v>45010</v>
-      </c>
-      <c r="G149" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15">
       <c r="A150">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B150" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C150" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D150" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E150" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F150" s="1">
-        <v>46128</v>
+        <v>45372</v>
       </c>
       <c r="G150" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15">
       <c r="A151">
+        <v>2023</v>
+      </c>
+      <c r="B151" t="s">
+        <v>194</v>
+      </c>
+      <c r="C151" t="s">
+        <v>195</v>
+      </c>
+      <c r="D151" t="s">
+        <v>196</v>
+      </c>
+      <c r="E151" t="s">
+        <v>196</v>
+      </c>
+      <c r="F151" s="1">
+        <v>45006</v>
+      </c>
+      <c r="G151" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="15">
+      <c r="A152" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B152" t="s">
+        <v>197</v>
+      </c>
+      <c r="C152" t="s">
+        <v>198</v>
+      </c>
+      <c r="D152" t="s">
+        <v>199</v>
+      </c>
+      <c r="E152" t="s">
+        <v>199</v>
+      </c>
+      <c r="F152" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G152" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="15">
+      <c r="A153" s="12">
         <v>2025</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B153" t="s">
+        <v>197</v>
+      </c>
+      <c r="C153" t="s">
         <v>198</v>
       </c>
-      <c r="C151" t="s">
-        <v>199</v>
-      </c>
-      <c r="D151" t="s">
+      <c r="D153" t="s">
+        <v>201</v>
+      </c>
+      <c r="E153" t="s">
+        <v>201</v>
+      </c>
+      <c r="F153" s="1">
+        <v>45741</v>
+      </c>
+      <c r="G153" t="s">
         <v>200</v>
-      </c>
-      <c r="E151" t="s">
-        <v>200</v>
-      </c>
-      <c r="F151" s="1">
-        <v>45763</v>
-      </c>
-      <c r="G151" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="15">
-      <c r="A152">
-        <v>2024</v>
-      </c>
-      <c r="B152" t="s">
-        <v>198</v>
-      </c>
-      <c r="C152" t="s">
-        <v>199</v>
-      </c>
-      <c r="D152" t="s">
-        <v>200</v>
-      </c>
-      <c r="E152" t="s">
-        <v>200</v>
-      </c>
-      <c r="F152" s="1">
-        <v>45398</v>
-      </c>
-      <c r="G152" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="15">
-      <c r="A153">
-        <v>2023</v>
-      </c>
-      <c r="B153" t="s">
-        <v>198</v>
-      </c>
-      <c r="C153" t="s">
-        <v>199</v>
-      </c>
-      <c r="D153" t="s">
-        <v>200</v>
-      </c>
-      <c r="E153" t="s">
-        <v>200</v>
-      </c>
-      <c r="F153" s="1">
-        <v>45032</v>
-      </c>
-      <c r="G153" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15">
       <c r="A154">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B154" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C154" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D154" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E154" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F154" s="1">
-        <v>46128</v>
+        <v>45376</v>
       </c>
       <c r="G154" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15">
       <c r="A155">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B155" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C155" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D155" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E155" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F155" s="1">
-        <v>45819</v>
+        <v>45010</v>
       </c>
       <c r="G155" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15">
       <c r="A156">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B156" t="s">
+        <v>202</v>
+      </c>
+      <c r="C156" t="s">
         <v>203</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
         <v>204</v>
       </c>
-      <c r="D156" t="s">
-        <v>207</v>
-      </c>
       <c r="E156" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F156" s="1">
-        <v>45454</v>
+        <v>46128</v>
       </c>
       <c r="G156" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15">
       <c r="A157">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B157" t="s">
+        <v>202</v>
+      </c>
+      <c r="C157" t="s">
         <v>203</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D157" t="s">
         <v>204</v>
       </c>
-      <c r="D157" t="s">
-        <v>207</v>
-      </c>
       <c r="E157" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F157" s="1">
-        <v>45088</v>
+        <v>45763</v>
       </c>
       <c r="G157" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15">
-      <c r="A158" s="10">
-        <v>2025</v>
+      <c r="A158">
+        <v>2024</v>
       </c>
       <c r="B158" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C158" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D158" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E158" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F158" s="1">
-        <v>45862</v>
+        <v>45398</v>
       </c>
       <c r="G158" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15">
       <c r="A159">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B159" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C159" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D159" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E159" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F159" s="1">
-        <v>45497</v>
+        <v>45032</v>
       </c>
       <c r="G159" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15">
       <c r="A160">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B160" t="s">
+        <v>207</v>
+      </c>
+      <c r="C160" t="s">
         <v>208</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>209</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
+        <v>209</v>
+      </c>
+      <c r="F160" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G160" t="s">
         <v>210</v>
-      </c>
-      <c r="E160" t="s">
-        <v>210</v>
-      </c>
-      <c r="F160" s="1">
-        <v>45131</v>
-      </c>
-      <c r="G160" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15">
       <c r="A161">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B161" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C161" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D161" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E161" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F161" s="1">
-        <v>46128</v>
+        <v>45819</v>
       </c>
       <c r="G161" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15">
       <c r="A162">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B162" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C162" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D162" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E162" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F162" s="1">
-        <v>45819</v>
+        <v>45454</v>
       </c>
       <c r="G162" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15">
       <c r="A163">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B163" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C163" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D163" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E163" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F163" s="1">
-        <v>45454</v>
+        <v>45088</v>
       </c>
       <c r="G163" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15">
       <c r="A164">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B164" t="s">
         <v>212</v>
@@ -5022,33 +5041,33 @@
         <v>214</v>
       </c>
       <c r="F164" s="1">
-        <v>45088</v>
-      </c>
-      <c r="G164" t="s">
+        <v>46170</v>
+      </c>
+      <c r="G164" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15">
-      <c r="A165" s="10">
+      <c r="A165">
         <v>2025</v>
       </c>
       <c r="B165" t="s">
+        <v>212</v>
+      </c>
+      <c r="C165" t="s">
+        <v>213</v>
+      </c>
+      <c r="D165" t="s">
         <v>216</v>
       </c>
-      <c r="C165" t="s">
-        <v>217</v>
-      </c>
-      <c r="D165" t="s">
-        <v>218</v>
-      </c>
       <c r="E165" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F165" s="1">
-        <v>45740</v>
+        <v>45862</v>
       </c>
       <c r="G165" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15">
@@ -5056,22 +5075,22 @@
         <v>2024</v>
       </c>
       <c r="B166" t="s">
+        <v>212</v>
+      </c>
+      <c r="C166" t="s">
+        <v>213</v>
+      </c>
+      <c r="D166" t="s">
         <v>216</v>
       </c>
-      <c r="C166" t="s">
-        <v>217</v>
-      </c>
-      <c r="D166" t="s">
-        <v>218</v>
-      </c>
       <c r="E166" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F166" s="1">
-        <v>45375</v>
+        <v>45497</v>
       </c>
       <c r="G166" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15">
@@ -5079,22 +5098,22 @@
         <v>2023</v>
       </c>
       <c r="B167" t="s">
+        <v>212</v>
+      </c>
+      <c r="C167" t="s">
+        <v>213</v>
+      </c>
+      <c r="D167" t="s">
         <v>216</v>
       </c>
-      <c r="C167" t="s">
-        <v>217</v>
-      </c>
-      <c r="D167" t="s">
-        <v>218</v>
-      </c>
       <c r="E167" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F167" s="1">
-        <v>45009</v>
+        <v>45131</v>
       </c>
       <c r="G167" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15">
@@ -5102,22 +5121,22 @@
         <v>2026</v>
       </c>
       <c r="B168" t="s">
+        <v>217</v>
+      </c>
+      <c r="C168" t="s">
+        <v>218</v>
+      </c>
+      <c r="D168" t="s">
+        <v>219</v>
+      </c>
+      <c r="E168" t="s">
+        <v>219</v>
+      </c>
+      <c r="F168" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G168" t="s">
         <v>220</v>
-      </c>
-      <c r="C168" t="s">
-        <v>221</v>
-      </c>
-      <c r="D168" t="s">
-        <v>222</v>
-      </c>
-      <c r="E168" t="s">
-        <v>222</v>
-      </c>
-      <c r="F168" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G168" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15">
@@ -5125,22 +5144,22 @@
         <v>2025</v>
       </c>
       <c r="B169" t="s">
+        <v>217</v>
+      </c>
+      <c r="C169" t="s">
+        <v>218</v>
+      </c>
+      <c r="D169" t="s">
+        <v>219</v>
+      </c>
+      <c r="E169" t="s">
+        <v>219</v>
+      </c>
+      <c r="F169" s="1">
+        <v>45819</v>
+      </c>
+      <c r="G169" t="s">
         <v>220</v>
-      </c>
-      <c r="C169" t="s">
-        <v>221</v>
-      </c>
-      <c r="D169" t="s">
-        <v>224</v>
-      </c>
-      <c r="E169" t="s">
-        <v>224</v>
-      </c>
-      <c r="F169" s="1">
-        <v>45733</v>
-      </c>
-      <c r="G169" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15">
@@ -5148,22 +5167,22 @@
         <v>2024</v>
       </c>
       <c r="B170" t="s">
+        <v>217</v>
+      </c>
+      <c r="C170" t="s">
+        <v>218</v>
+      </c>
+      <c r="D170" t="s">
+        <v>219</v>
+      </c>
+      <c r="E170" t="s">
+        <v>219</v>
+      </c>
+      <c r="F170" s="1">
+        <v>45454</v>
+      </c>
+      <c r="G170" t="s">
         <v>220</v>
-      </c>
-      <c r="C170" t="s">
-        <v>221</v>
-      </c>
-      <c r="D170" t="s">
-        <v>224</v>
-      </c>
-      <c r="E170" t="s">
-        <v>224</v>
-      </c>
-      <c r="F170" s="1">
-        <v>45368</v>
-      </c>
-      <c r="G170" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15">
@@ -5171,22 +5190,22 @@
         <v>2023</v>
       </c>
       <c r="B171" t="s">
+        <v>217</v>
+      </c>
+      <c r="C171" t="s">
+        <v>218</v>
+      </c>
+      <c r="D171" t="s">
+        <v>219</v>
+      </c>
+      <c r="E171" t="s">
+        <v>219</v>
+      </c>
+      <c r="F171" s="1">
+        <v>45088</v>
+      </c>
+      <c r="G171" t="s">
         <v>220</v>
-      </c>
-      <c r="C171" t="s">
-        <v>221</v>
-      </c>
-      <c r="D171" t="s">
-        <v>224</v>
-      </c>
-      <c r="E171" t="s">
-        <v>224</v>
-      </c>
-      <c r="F171" s="1">
-        <v>45002</v>
-      </c>
-      <c r="G171" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15">
@@ -5194,22 +5213,22 @@
         <v>2026</v>
       </c>
       <c r="B172" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C172" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D172" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E172" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F172" s="1">
-        <v>46121</v>
-      </c>
-      <c r="G172" t="s">
-        <v>228</v>
+        <v>46162</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15">
@@ -5217,22 +5236,22 @@
         <v>2025</v>
       </c>
       <c r="B173" t="s">
+        <v>221</v>
+      </c>
+      <c r="C173" t="s">
+        <v>222</v>
+      </c>
+      <c r="D173" t="s">
         <v>225</v>
       </c>
-      <c r="C173" t="s">
-        <v>226</v>
-      </c>
-      <c r="D173" t="s">
-        <v>229</v>
-      </c>
       <c r="E173" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F173" s="1">
-        <v>45713</v>
+        <v>45740</v>
       </c>
       <c r="G173" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15">
@@ -5240,22 +5259,22 @@
         <v>2024</v>
       </c>
       <c r="B174" t="s">
+        <v>221</v>
+      </c>
+      <c r="C174" t="s">
+        <v>222</v>
+      </c>
+      <c r="D174" t="s">
         <v>225</v>
       </c>
-      <c r="C174" t="s">
-        <v>226</v>
-      </c>
-      <c r="D174" t="s">
-        <v>229</v>
-      </c>
       <c r="E174" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F174" s="1">
-        <v>45347</v>
+        <v>45375</v>
       </c>
       <c r="G174" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15">
@@ -5263,485 +5282,700 @@
         <v>2023</v>
       </c>
       <c r="B175" t="s">
+        <v>221</v>
+      </c>
+      <c r="C175" t="s">
+        <v>222</v>
+      </c>
+      <c r="D175" t="s">
         <v>225</v>
       </c>
-      <c r="C175" t="s">
+      <c r="E175" t="s">
+        <v>225</v>
+      </c>
+      <c r="F175" s="1">
+        <v>45009</v>
+      </c>
+      <c r="G175" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="15">
+      <c r="A176">
+        <v>2026</v>
+      </c>
+      <c r="B176" t="s">
         <v>226</v>
       </c>
-      <c r="D175" t="s">
+      <c r="C176" t="s">
+        <v>227</v>
+      </c>
+      <c r="D176" t="s">
+        <v>228</v>
+      </c>
+      <c r="E176" t="s">
+        <v>228</v>
+      </c>
+      <c r="F176" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G176" t="s">
         <v>229</v>
-      </c>
-      <c r="E175" t="s">
-        <v>229</v>
-      </c>
-      <c r="F175" s="1">
-        <v>44982</v>
-      </c>
-      <c r="G175" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="15">
-      <c r="A176" s="10">
-        <v>2025</v>
-      </c>
-      <c r="B176" t="s">
-        <v>230</v>
-      </c>
-      <c r="C176" t="s">
-        <v>231</v>
-      </c>
-      <c r="D176" t="s">
-        <v>232</v>
-      </c>
-      <c r="E176" t="s">
-        <v>232</v>
-      </c>
-      <c r="F176" s="1">
-        <v>45821</v>
-      </c>
-      <c r="G176" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15">
       <c r="A177">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B177" t="s">
+        <v>226</v>
+      </c>
+      <c r="C177" t="s">
+        <v>227</v>
+      </c>
+      <c r="D177" t="s">
         <v>230</v>
       </c>
-      <c r="C177" t="s">
-        <v>231</v>
-      </c>
-      <c r="D177" t="s">
-        <v>232</v>
-      </c>
       <c r="E177" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F177" s="1">
-        <v>45456</v>
+        <v>45733</v>
       </c>
       <c r="G177" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15">
       <c r="A178">
+        <v>2024</v>
+      </c>
+      <c r="B178" t="s">
+        <v>226</v>
+      </c>
+      <c r="C178" t="s">
+        <v>227</v>
+      </c>
+      <c r="D178" t="s">
+        <v>230</v>
+      </c>
+      <c r="E178" t="s">
+        <v>230</v>
+      </c>
+      <c r="F178" s="1">
+        <v>45368</v>
+      </c>
+      <c r="G178" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="15">
+      <c r="A179">
         <v>2023</v>
       </c>
-      <c r="B178" t="s">
+      <c r="B179" t="s">
+        <v>226</v>
+      </c>
+      <c r="C179" t="s">
+        <v>227</v>
+      </c>
+      <c r="D179" t="s">
         <v>230</v>
       </c>
-      <c r="C178" t="s">
-        <v>231</v>
-      </c>
-      <c r="D178" t="s">
-        <v>232</v>
-      </c>
-      <c r="E178" t="s">
-        <v>232</v>
-      </c>
-      <c r="F178" s="1">
-        <v>45090</v>
-      </c>
-      <c r="G178" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="15">
-      <c r="A179" s="10">
-        <v>2025</v>
-      </c>
-      <c r="B179" t="s">
-        <v>234</v>
-      </c>
-      <c r="C179" t="s">
-        <v>235</v>
-      </c>
-      <c r="D179" t="s">
-        <v>236</v>
-      </c>
       <c r="E179" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F179" s="1">
-        <v>45805</v>
+        <v>45002</v>
       </c>
       <c r="G179" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15">
       <c r="A180">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B180" t="s">
+        <v>231</v>
+      </c>
+      <c r="C180" t="s">
+        <v>232</v>
+      </c>
+      <c r="D180" t="s">
+        <v>233</v>
+      </c>
+      <c r="E180" t="s">
+        <v>233</v>
+      </c>
+      <c r="F180" s="1">
+        <v>46121</v>
+      </c>
+      <c r="G180" t="s">
         <v>234</v>
-      </c>
-      <c r="C180" t="s">
-        <v>235</v>
-      </c>
-      <c r="D180" t="s">
-        <v>236</v>
-      </c>
-      <c r="E180" t="s">
-        <v>236</v>
-      </c>
-      <c r="F180" s="1">
-        <v>45440</v>
-      </c>
-      <c r="G180" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15">
       <c r="A181">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B181" t="s">
+        <v>231</v>
+      </c>
+      <c r="C181" t="s">
+        <v>232</v>
+      </c>
+      <c r="D181" t="s">
+        <v>235</v>
+      </c>
+      <c r="E181" t="s">
+        <v>235</v>
+      </c>
+      <c r="F181" s="1">
+        <v>45713</v>
+      </c>
+      <c r="G181" t="s">
         <v>234</v>
-      </c>
-      <c r="C181" t="s">
-        <v>235</v>
-      </c>
-      <c r="D181" t="s">
-        <v>236</v>
-      </c>
-      <c r="E181" t="s">
-        <v>236</v>
-      </c>
-      <c r="F181" s="1">
-        <v>45074</v>
-      </c>
-      <c r="G181" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15">
       <c r="A182">
-        <v>2026</v>
-      </c>
-      <c r="B182" s="9" t="s">
-        <v>238</v>
+        <v>2024</v>
+      </c>
+      <c r="B182" t="s">
+        <v>231</v>
       </c>
       <c r="C182" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D182" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="E182" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="F182" s="1">
-        <v>46125</v>
+        <v>45347</v>
       </c>
       <c r="G182" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15">
       <c r="A183">
+        <v>2023</v>
+      </c>
+      <c r="B183" t="s">
+        <v>231</v>
+      </c>
+      <c r="C183" t="s">
+        <v>232</v>
+      </c>
+      <c r="D183" t="s">
+        <v>235</v>
+      </c>
+      <c r="E183" t="s">
+        <v>235</v>
+      </c>
+      <c r="F183" s="1">
+        <v>44982</v>
+      </c>
+      <c r="G183" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="15">
+      <c r="A184" s="10">
         <v>2025</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B184" t="s">
+        <v>236</v>
+      </c>
+      <c r="C184" t="s">
+        <v>237</v>
+      </c>
+      <c r="D184" t="s">
         <v>238</v>
       </c>
-      <c r="C183" t="s">
+      <c r="E184" t="s">
+        <v>238</v>
+      </c>
+      <c r="F184" s="1">
+        <v>45821</v>
+      </c>
+      <c r="G184" t="s">
         <v>239</v>
-      </c>
-      <c r="D183" t="s">
-        <v>241</v>
-      </c>
-      <c r="E183" t="s">
-        <v>241</v>
-      </c>
-      <c r="F183" s="1">
-        <v>45748</v>
-      </c>
-      <c r="G183" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="15">
-      <c r="A184">
-        <v>2024</v>
-      </c>
-      <c r="B184" t="s">
-        <v>238</v>
-      </c>
-      <c r="C184" t="s">
-        <v>239</v>
-      </c>
-      <c r="D184" t="s">
-        <v>241</v>
-      </c>
-      <c r="E184" t="s">
-        <v>241</v>
-      </c>
-      <c r="F184" s="1">
-        <v>45383</v>
-      </c>
-      <c r="G184" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15">
       <c r="A185">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B185" t="s">
+        <v>236</v>
+      </c>
+      <c r="C185" t="s">
+        <v>237</v>
+      </c>
+      <c r="D185" t="s">
         <v>238</v>
       </c>
-      <c r="C185" t="s">
+      <c r="E185" t="s">
+        <v>238</v>
+      </c>
+      <c r="F185" s="1">
+        <v>45456</v>
+      </c>
+      <c r="G185" t="s">
         <v>239</v>
-      </c>
-      <c r="D185" t="s">
-        <v>241</v>
-      </c>
-      <c r="E185" t="s">
-        <v>241</v>
-      </c>
-      <c r="F185" s="1">
-        <v>45017</v>
-      </c>
-      <c r="G185" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15">
       <c r="A186">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B186" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C186" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D186" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E186" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F186" s="1">
-        <v>46128</v>
+        <v>45090</v>
       </c>
       <c r="G186" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15">
       <c r="A187">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B187" t="s">
+        <v>240</v>
+      </c>
+      <c r="C187" t="s">
+        <v>241</v>
+      </c>
+      <c r="D187" t="s">
         <v>242</v>
       </c>
-      <c r="C187" t="s">
+      <c r="E187" t="s">
+        <v>242</v>
+      </c>
+      <c r="F187" s="1">
+        <v>46170</v>
+      </c>
+      <c r="G187" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="D187" t="s">
-        <v>246</v>
-      </c>
-      <c r="E187" t="s">
-        <v>246</v>
-      </c>
-      <c r="F187" s="1">
-        <v>45744</v>
-      </c>
-      <c r="G187" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15">
       <c r="A188">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B188" t="s">
+        <v>240</v>
+      </c>
+      <c r="C188" t="s">
+        <v>241</v>
+      </c>
+      <c r="D188" t="s">
         <v>242</v>
       </c>
-      <c r="C188" t="s">
+      <c r="E188" t="s">
+        <v>242</v>
+      </c>
+      <c r="F188" s="1">
+        <v>45805</v>
+      </c>
+      <c r="G188" t="s">
         <v>243</v>
-      </c>
-      <c r="D188" t="s">
-        <v>246</v>
-      </c>
-      <c r="E188" t="s">
-        <v>246</v>
-      </c>
-      <c r="F188" s="1">
-        <v>45379</v>
-      </c>
-      <c r="G188" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15">
       <c r="A189">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B189" t="s">
+        <v>240</v>
+      </c>
+      <c r="C189" t="s">
+        <v>241</v>
+      </c>
+      <c r="D189" t="s">
         <v>242</v>
       </c>
-      <c r="C189" t="s">
+      <c r="E189" t="s">
+        <v>242</v>
+      </c>
+      <c r="F189" s="1">
+        <v>45440</v>
+      </c>
+      <c r="G189" t="s">
         <v>243</v>
-      </c>
-      <c r="D189" t="s">
-        <v>246</v>
-      </c>
-      <c r="E189" t="s">
-        <v>246</v>
-      </c>
-      <c r="F189" s="1">
-        <v>45013</v>
-      </c>
-      <c r="G189" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15">
       <c r="A190">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B190" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C190" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D190" t="s">
-        <v>249</v>
+        <v>242</v>
+      </c>
+      <c r="E190" t="s">
+        <v>242</v>
       </c>
       <c r="F190" s="1">
-        <v>46122</v>
+        <v>45074</v>
       </c>
       <c r="G190" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15">
       <c r="A191">
-        <v>2025</v>
-      </c>
-      <c r="B191" t="s">
-        <v>247</v>
+        <v>2026</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>244</v>
       </c>
       <c r="C191" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D191" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="E191" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="F191" s="1">
-        <v>45737</v>
+        <v>46125</v>
       </c>
       <c r="G191" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15">
       <c r="A192">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B192" t="s">
+        <v>244</v>
+      </c>
+      <c r="C192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D192" t="s">
         <v>247</v>
       </c>
-      <c r="C192" t="s">
-        <v>248</v>
-      </c>
-      <c r="D192" t="s">
-        <v>251</v>
-      </c>
       <c r="E192" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F192" s="1">
-        <v>45372</v>
+        <v>45748</v>
       </c>
       <c r="G192" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15">
       <c r="A193">
+        <v>2024</v>
+      </c>
+      <c r="B193" t="s">
+        <v>244</v>
+      </c>
+      <c r="C193" t="s">
+        <v>245</v>
+      </c>
+      <c r="D193" t="s">
+        <v>247</v>
+      </c>
+      <c r="E193" t="s">
+        <v>247</v>
+      </c>
+      <c r="F193" s="1">
+        <v>45383</v>
+      </c>
+      <c r="G193" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="15">
+      <c r="A194">
         <v>2023</v>
       </c>
-      <c r="B193" t="s">
+      <c r="B194" t="s">
+        <v>244</v>
+      </c>
+      <c r="C194" t="s">
+        <v>245</v>
+      </c>
+      <c r="D194" t="s">
         <v>247</v>
       </c>
-      <c r="C193" t="s">
+      <c r="E194" t="s">
+        <v>247</v>
+      </c>
+      <c r="F194" s="1">
+        <v>45017</v>
+      </c>
+      <c r="G194" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="15">
+      <c r="A195">
+        <v>2026</v>
+      </c>
+      <c r="B195" t="s">
         <v>248</v>
       </c>
-      <c r="D193" t="s">
+      <c r="C195" t="s">
+        <v>249</v>
+      </c>
+      <c r="D195" t="s">
+        <v>250</v>
+      </c>
+      <c r="E195" t="s">
+        <v>250</v>
+      </c>
+      <c r="F195" s="1">
+        <v>46128</v>
+      </c>
+      <c r="G195" t="s">
         <v>251</v>
       </c>
-      <c r="E193" t="s">
+    </row>
+    <row r="196" spans="1:7" ht="15">
+      <c r="A196">
+        <v>2025</v>
+      </c>
+      <c r="B196" t="s">
+        <v>248</v>
+      </c>
+      <c r="C196" t="s">
+        <v>249</v>
+      </c>
+      <c r="D196" t="s">
+        <v>252</v>
+      </c>
+      <c r="E196" t="s">
+        <v>252</v>
+      </c>
+      <c r="F196" s="1">
+        <v>45744</v>
+      </c>
+      <c r="G196" t="s">
         <v>251</v>
       </c>
-      <c r="F193" s="1">
+    </row>
+    <row r="197" spans="1:7" ht="15">
+      <c r="A197">
+        <v>2024</v>
+      </c>
+      <c r="B197" t="s">
+        <v>248</v>
+      </c>
+      <c r="C197" t="s">
+        <v>249</v>
+      </c>
+      <c r="D197" t="s">
+        <v>252</v>
+      </c>
+      <c r="E197" t="s">
+        <v>252</v>
+      </c>
+      <c r="F197" s="1">
+        <v>45379</v>
+      </c>
+      <c r="G197" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="15">
+      <c r="A198">
+        <v>2023</v>
+      </c>
+      <c r="B198" t="s">
+        <v>248</v>
+      </c>
+      <c r="C198" t="s">
+        <v>249</v>
+      </c>
+      <c r="D198" t="s">
+        <v>252</v>
+      </c>
+      <c r="E198" t="s">
+        <v>252</v>
+      </c>
+      <c r="F198" s="1">
+        <v>45013</v>
+      </c>
+      <c r="G198" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="15">
+      <c r="A199">
+        <v>2026</v>
+      </c>
+      <c r="B199" t="s">
+        <v>253</v>
+      </c>
+      <c r="C199" t="s">
+        <v>254</v>
+      </c>
+      <c r="D199" t="s">
+        <v>255</v>
+      </c>
+      <c r="F199" s="1">
+        <v>46122</v>
+      </c>
+      <c r="G199" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="15">
+      <c r="A200">
+        <v>2025</v>
+      </c>
+      <c r="B200" t="s">
+        <v>253</v>
+      </c>
+      <c r="C200" t="s">
+        <v>254</v>
+      </c>
+      <c r="D200" t="s">
+        <v>257</v>
+      </c>
+      <c r="E200" t="s">
+        <v>257</v>
+      </c>
+      <c r="F200" s="1">
+        <v>45737</v>
+      </c>
+      <c r="G200" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="15">
+      <c r="A201">
+        <v>2024</v>
+      </c>
+      <c r="B201" t="s">
+        <v>253</v>
+      </c>
+      <c r="C201" t="s">
+        <v>254</v>
+      </c>
+      <c r="D201" t="s">
+        <v>257</v>
+      </c>
+      <c r="E201" t="s">
+        <v>257</v>
+      </c>
+      <c r="F201" s="1">
+        <v>45372</v>
+      </c>
+      <c r="G201" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="15">
+      <c r="A202">
+        <v>2023</v>
+      </c>
+      <c r="B202" t="s">
+        <v>253</v>
+      </c>
+      <c r="C202" t="s">
+        <v>254</v>
+      </c>
+      <c r="D202" t="s">
+        <v>257</v>
+      </c>
+      <c r="E202" t="s">
+        <v>257</v>
+      </c>
+      <c r="F202" s="1">
         <v>45006</v>
       </c>
-      <c r="G193" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="242" spans="11:11">
-      <c r="K242" s="1"/>
+      <c r="G202" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="251" spans="11:11">
+      <c r="K251" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G193" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G193">
+  <autoFilter ref="A1:G202" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G202">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G41" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G43" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G44" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G42" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G43" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G45" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="G46" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G44" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="G18" r:id="rId5" xr:uid="{3F701E59-5D29-4E9C-8705-ECF744F7C80B}"/>
-    <hyperlink ref="G22" r:id="rId6" xr:uid="{F86867FF-E0A1-4B23-8E20-1EE5F172C1F2}"/>
-    <hyperlink ref="G29" r:id="rId7" xr:uid="{7B92F4FE-45A5-4FC3-BEF6-89060A75A0CF}"/>
-    <hyperlink ref="G33" r:id="rId8" xr:uid="{44483B5F-1D9D-4382-A3BB-08CC848203BB}"/>
-    <hyperlink ref="G37" r:id="rId9" xr:uid="{80C8F108-86E1-4547-810D-49EE9748B088}"/>
-    <hyperlink ref="G45" r:id="rId10" xr:uid="{44A2B85F-2D5D-4501-BD0D-1A1075EEBD87}"/>
-    <hyperlink ref="G48" r:id="rId11" xr:uid="{974F12BA-311E-4775-9C79-6B2367EE4C00}"/>
-    <hyperlink ref="G52" r:id="rId12" xr:uid="{9FD43934-382B-448D-9E13-39FD5028C9E3}"/>
-    <hyperlink ref="G56" r:id="rId13" xr:uid="{F5EC8224-9440-476C-B04B-BCD61BFD11DD}"/>
-    <hyperlink ref="G60" r:id="rId14" xr:uid="{6715A407-CEDE-4462-83D2-BA6A21538E94}"/>
-    <hyperlink ref="G64" r:id="rId15" xr:uid="{8C180C1D-CF21-400B-8B35-ACDD613A2648}"/>
-    <hyperlink ref="G71" r:id="rId16" xr:uid="{E80524B7-0871-4464-985C-CA93DB159F96}"/>
-    <hyperlink ref="E71" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto" xr:uid="{44E53C8F-307F-4558-8C5E-5645D7067E09}"/>
-    <hyperlink ref="G75" r:id="rId18" xr:uid="{BB1A3C55-886C-4149-9192-8222A522CCA0}"/>
-    <hyperlink ref="G89" r:id="rId19" location="informacoes-classificadas-e-desclassificadas" xr:uid="{F06BDAE5-9ADF-4DA7-920D-01903454D462}"/>
-    <hyperlink ref="G106" r:id="rId20" xr:uid="{CD1703C5-F786-4C99-88D4-BEA8E70C4138}"/>
-    <hyperlink ref="G105" r:id="rId21" xr:uid="{C77BD8BE-59BD-4BD4-9FAB-2123370B5889}"/>
-    <hyperlink ref="G101" r:id="rId22" xr:uid="{9388516A-40C8-4110-A15B-D0B6EE32A150}"/>
-    <hyperlink ref="G112" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{3301EBB6-9A25-48B2-9D8C-70083F27B1EA}"/>
-    <hyperlink ref="G116" r:id="rId24" location="informacoes-classificadas-e-desclassificadas" xr:uid="{7434A183-8C1E-4E4A-8E52-8EF290090E88}"/>
-    <hyperlink ref="G124" r:id="rId25" xr:uid="{4A3115E8-4CE5-4DFF-BF8C-76F55E18523A}"/>
-    <hyperlink ref="G131" r:id="rId26" xr:uid="{E28EBD52-B071-49FC-B6F4-D7C185EC3BD1}"/>
-    <hyperlink ref="G135" r:id="rId27" xr:uid="{995FBC4C-1A02-4126-AA25-76E795A0EB48}"/>
-    <hyperlink ref="G139" r:id="rId28" xr:uid="{80237B8F-DF43-47F0-80AC-616D77A1082D}"/>
-    <hyperlink ref="G150" r:id="rId29" xr:uid="{6AC60654-C774-4732-B0F1-240E2D6C4490}"/>
-    <hyperlink ref="G154" r:id="rId30" xr:uid="{AAF4FD60-6234-4214-BA5D-07ACABA79556}"/>
-    <hyperlink ref="G161" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{6EF2BF0D-AFAC-4C21-81A1-0D63CF1FEEE4}"/>
-    <hyperlink ref="G168" r:id="rId32" xr:uid="{81356907-EB5D-4FC6-90E5-4BC94C925F5E}"/>
-    <hyperlink ref="G182" r:id="rId33" xr:uid="{89F50D9C-749D-4ED1-B9C3-FA541C5DBEA0}"/>
-    <hyperlink ref="G186" r:id="rId34" location="info-class-des" xr:uid="{9E908A83-E592-48E3-A960-E01C6B504A9F}"/>
-    <hyperlink ref="G190" r:id="rId35" xr:uid="{6ACD1A2A-A2ED-4326-AB6D-AC1CAEB49DD3}"/>
-    <hyperlink ref="G85" r:id="rId36" xr:uid="{E8F08860-DEED-4B1D-A48C-6C1359300175}"/>
-    <hyperlink ref="G97" r:id="rId37" xr:uid="{0E98023C-AB1F-4285-BFD2-EFD188CCDF4C}"/>
-    <hyperlink ref="G172" r:id="rId38" xr:uid="{9F2C91F1-3B9F-4B72-A797-85FFBDD348E1}"/>
+    <hyperlink ref="G23" r:id="rId6" xr:uid="{F86867FF-E0A1-4B23-8E20-1EE5F172C1F2}"/>
+    <hyperlink ref="G31" r:id="rId7" xr:uid="{7B92F4FE-45A5-4FC3-BEF6-89060A75A0CF}"/>
+    <hyperlink ref="G35" r:id="rId8" xr:uid="{44483B5F-1D9D-4382-A3BB-08CC848203BB}"/>
+    <hyperlink ref="G39" r:id="rId9" xr:uid="{80C8F108-86E1-4547-810D-49EE9748B088}"/>
+    <hyperlink ref="G47" r:id="rId10" xr:uid="{44A2B85F-2D5D-4501-BD0D-1A1075EEBD87}"/>
+    <hyperlink ref="G50" r:id="rId11" xr:uid="{974F12BA-311E-4775-9C79-6B2367EE4C00}"/>
+    <hyperlink ref="G54" r:id="rId12" xr:uid="{9FD43934-382B-448D-9E13-39FD5028C9E3}"/>
+    <hyperlink ref="G58" r:id="rId13" xr:uid="{F5EC8224-9440-476C-B04B-BCD61BFD11DD}"/>
+    <hyperlink ref="G62" r:id="rId14" xr:uid="{6715A407-CEDE-4462-83D2-BA6A21538E94}"/>
+    <hyperlink ref="G66" r:id="rId15" xr:uid="{8C180C1D-CF21-400B-8B35-ACDD613A2648}"/>
+    <hyperlink ref="G74" r:id="rId16" xr:uid="{E80524B7-0871-4464-985C-CA93DB159F96}"/>
+    <hyperlink ref="E74" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto" xr:uid="{44E53C8F-307F-4558-8C5E-5645D7067E09}"/>
+    <hyperlink ref="G78" r:id="rId18" xr:uid="{BB1A3C55-886C-4149-9192-8222A522CCA0}"/>
+    <hyperlink ref="G93" r:id="rId19" location="informacoes-classificadas-e-desclassificadas" xr:uid="{F06BDAE5-9ADF-4DA7-920D-01903454D462}"/>
+    <hyperlink ref="G110" r:id="rId20" xr:uid="{CD1703C5-F786-4C99-88D4-BEA8E70C4138}"/>
+    <hyperlink ref="G109" r:id="rId21" xr:uid="{C77BD8BE-59BD-4BD4-9FAB-2123370B5889}"/>
+    <hyperlink ref="G105" r:id="rId22" xr:uid="{9388516A-40C8-4110-A15B-D0B6EE32A150}"/>
+    <hyperlink ref="G116" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{3301EBB6-9A25-48B2-9D8C-70083F27B1EA}"/>
+    <hyperlink ref="G120" r:id="rId24" location="informacoes-classificadas-e-desclassificadas" xr:uid="{7434A183-8C1E-4E4A-8E52-8EF290090E88}"/>
+    <hyperlink ref="G128" r:id="rId25" xr:uid="{4A3115E8-4CE5-4DFF-BF8C-76F55E18523A}"/>
+    <hyperlink ref="G136" r:id="rId26" xr:uid="{E28EBD52-B071-49FC-B6F4-D7C185EC3BD1}"/>
+    <hyperlink ref="G140" r:id="rId27" xr:uid="{995FBC4C-1A02-4126-AA25-76E795A0EB48}"/>
+    <hyperlink ref="G144" r:id="rId28" xr:uid="{80237B8F-DF43-47F0-80AC-616D77A1082D}"/>
+    <hyperlink ref="G156" r:id="rId29" xr:uid="{6AC60654-C774-4732-B0F1-240E2D6C4490}"/>
+    <hyperlink ref="G160" r:id="rId30" xr:uid="{AAF4FD60-6234-4214-BA5D-07ACABA79556}"/>
+    <hyperlink ref="G168" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{6EF2BF0D-AFAC-4C21-81A1-0D63CF1FEEE4}"/>
+    <hyperlink ref="G176" r:id="rId32" xr:uid="{81356907-EB5D-4FC6-90E5-4BC94C925F5E}"/>
+    <hyperlink ref="G191" r:id="rId33" xr:uid="{89F50D9C-749D-4ED1-B9C3-FA541C5DBEA0}"/>
+    <hyperlink ref="G195" r:id="rId34" location="info-class-des" xr:uid="{9E908A83-E592-48E3-A960-E01C6B504A9F}"/>
+    <hyperlink ref="G199" r:id="rId35" xr:uid="{6ACD1A2A-A2ED-4326-AB6D-AC1CAEB49DD3}"/>
+    <hyperlink ref="G89" r:id="rId36" xr:uid="{E8F08860-DEED-4B1D-A48C-6C1359300175}"/>
+    <hyperlink ref="G101" r:id="rId37" xr:uid="{0E98023C-AB1F-4285-BFD2-EFD188CCDF4C}"/>
+    <hyperlink ref="G180" r:id="rId38" xr:uid="{9F2C91F1-3B9F-4B72-A797-85FFBDD348E1}"/>
     <hyperlink ref="G14" r:id="rId39" xr:uid="{3841C1FD-CD06-45B5-9491-60778AF8477D}"/>
-    <hyperlink ref="G146" r:id="rId40" xr:uid="{50E2C31A-C16A-4D5A-AC7B-F44D64FFCDE4}"/>
+    <hyperlink ref="G152" r:id="rId40" xr:uid="{50E2C31A-C16A-4D5A-AC7B-F44D64FFCDE4}"/>
+    <hyperlink ref="G70" r:id="rId41" xr:uid="{412A2619-2166-4F75-B6DF-857DB3022D0B}"/>
+    <hyperlink ref="G27" r:id="rId42" xr:uid="{CFD576E9-D051-4785-9895-0E307BF07A08}"/>
+    <hyperlink ref="G132" r:id="rId43" xr:uid="{10B23B64-B59B-4B30-BA79-B99439662FFE}"/>
+    <hyperlink ref="G172" r:id="rId44" xr:uid="{27BD0F6F-7EC5-4457-BF58-174C23DCA541}"/>
+    <hyperlink ref="G148" r:id="rId45" xr:uid="{A44713B8-367B-4042-8C89-E38A146C20FF}"/>
+    <hyperlink ref="G19" r:id="rId46" xr:uid="{CEFC8C9F-1526-42F4-87B8-14AC13D05E87}"/>
+    <hyperlink ref="G187" r:id="rId47" xr:uid="{7DF0A33C-D34B-4B22-B997-A95185545180}"/>
+    <hyperlink ref="G164" r:id="rId48" xr:uid="{E197C950-CA23-4E94-BD2B-35727B2E87CC}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/orgao_sem_informacoes_classificadas.xlsx
+++ b/upload/orgao_sem_informacoes_classificadas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{764A000E-CD73-484A-8F8E-4C10E958276C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA30334D-865D-46AF-91E5-831F9CDC9B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="258">
   <si>
     <t>ano</t>
   </si>
@@ -923,7 +923,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -943,6 +943,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1280,7 +1281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K251"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.28515625" customWidth="1"/>
@@ -1335,7 +1336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1358,7 +1359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -1381,7 +1382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -1404,7 +1405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -1427,7 +1428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>2025</v>
       </c>
@@ -1450,7 +1451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -1473,7 +1474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -1496,7 +1497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2026</v>
       </c>
@@ -1519,7 +1520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1542,7 +1543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -1565,7 +1566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2023</v>
       </c>
@@ -1588,7 +1589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2026</v>
       </c>
@@ -1611,7 +1612,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2025</v>
       </c>
@@ -1634,7 +1635,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -1657,7 +1658,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2023</v>
       </c>
@@ -1680,7 +1681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -1703,7 +1704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2026</v>
       </c>
@@ -1726,7 +1727,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2025</v>
       </c>
@@ -1749,7 +1750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2024</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2023</v>
       </c>
@@ -1795,7 +1796,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>2026</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>2025</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>2024</v>
       </c>
@@ -1864,7 +1865,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>2023</v>
       </c>
@@ -1887,7 +1888,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>2026</v>
       </c>
@@ -1910,7 +1911,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>2025</v>
       </c>
@@ -1933,7 +1934,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>2024</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>2023</v>
       </c>
@@ -1979,7 +1980,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>2026</v>
       </c>
@@ -2002,7 +2003,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>2025</v>
       </c>
@@ -2025,7 +2026,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>2024</v>
       </c>
@@ -2048,7 +2049,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>2023</v>
       </c>
@@ -2071,7 +2072,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>2026</v>
       </c>
@@ -2094,7 +2095,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>2025</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>2024</v>
       </c>
@@ -2140,7 +2141,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>2023</v>
       </c>
@@ -2163,7 +2164,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>2026</v>
       </c>
@@ -2186,7 +2187,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>2025</v>
       </c>
@@ -2209,7 +2210,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>2024</v>
       </c>
@@ -2232,7 +2233,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>2023</v>
       </c>
@@ -2255,7 +2256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>2026</v>
       </c>
@@ -2278,7 +2279,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>2025</v>
       </c>
@@ -2301,7 +2302,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>2024</v>
       </c>
@@ -2324,7 +2325,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>2023</v>
       </c>
@@ -2370,7 +2371,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>2024</v>
       </c>
@@ -2393,7 +2394,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15">
+    <row r="49" spans="1:9">
       <c r="A49">
         <v>2023</v>
       </c>
@@ -2416,7 +2417,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15">
+    <row r="50" spans="1:9">
       <c r="A50">
         <v>2026</v>
       </c>
@@ -2436,7 +2437,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15">
+    <row r="51" spans="1:9">
       <c r="A51">
         <v>2025</v>
       </c>
@@ -2459,7 +2460,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15">
+    <row r="52" spans="1:9">
       <c r="A52">
         <v>2024</v>
       </c>
@@ -2483,7 +2484,7 @@
       </c>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" spans="1:9" ht="15">
+    <row r="53" spans="1:9">
       <c r="A53">
         <v>2023</v>
       </c>
@@ -2506,7 +2507,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15">
+    <row r="54" spans="1:9">
       <c r="A54">
         <v>2026</v>
       </c>
@@ -2529,7 +2530,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15">
+    <row r="55" spans="1:9">
       <c r="A55">
         <v>2025</v>
       </c>
@@ -2552,7 +2553,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15">
+    <row r="56" spans="1:9">
       <c r="A56">
         <v>2024</v>
       </c>
@@ -2575,7 +2576,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15">
+    <row r="57" spans="1:9">
       <c r="A57">
         <v>2023</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15">
+    <row r="58" spans="1:9">
       <c r="A58">
         <v>2026</v>
       </c>
@@ -2621,7 +2622,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15">
+    <row r="59" spans="1:9">
       <c r="A59">
         <v>2025</v>
       </c>
@@ -2644,7 +2645,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15">
+    <row r="60" spans="1:9">
       <c r="A60">
         <v>2024</v>
       </c>
@@ -2667,7 +2668,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15">
+    <row r="61" spans="1:9">
       <c r="A61">
         <v>2023</v>
       </c>
@@ -2690,7 +2691,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15">
+    <row r="62" spans="1:9">
       <c r="A62">
         <v>2026</v>
       </c>
@@ -2713,7 +2714,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15">
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>2025</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15">
+    <row r="64" spans="1:9">
       <c r="A64">
         <v>2024</v>
       </c>
@@ -2759,7 +2760,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>2023</v>
       </c>
@@ -2782,7 +2783,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>2026</v>
       </c>
@@ -2805,7 +2806,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>2025</v>
       </c>
@@ -2828,7 +2829,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>2024</v>
       </c>
@@ -2851,7 +2852,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>2023</v>
       </c>
@@ -2874,7 +2875,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>2026</v>
       </c>
@@ -2897,7 +2898,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>2025</v>
       </c>
@@ -2920,7 +2921,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>2024</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>2023</v>
       </c>
@@ -2966,7 +2967,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>2026</v>
       </c>
@@ -2989,7 +2990,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>2025</v>
       </c>
@@ -3012,7 +3013,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>2024</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15">
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>2023</v>
       </c>
@@ -3058,7 +3059,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15">
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>2026</v>
       </c>
@@ -3081,7 +3082,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15">
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>2025</v>
       </c>
@@ -3104,7 +3105,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15">
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>2024</v>
       </c>
@@ -3127,7 +3128,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15">
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>2023</v>
       </c>
@@ -3150,7 +3151,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15">
+    <row r="82" spans="1:7">
       <c r="A82" s="11">
         <v>2025</v>
       </c>
@@ -3173,7 +3174,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>2024</v>
       </c>
@@ -3196,7 +3197,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>2023</v>
       </c>
@@ -3219,7 +3220,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15">
+    <row r="85" spans="1:7">
       <c r="A85" s="14">
         <v>2026</v>
       </c>
@@ -3242,7 +3243,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15">
+    <row r="86" spans="1:7">
       <c r="A86" s="14">
         <v>2025</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>2024</v>
       </c>
@@ -3288,7 +3289,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15">
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>2023</v>
       </c>
@@ -3311,7 +3312,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15">
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>2026</v>
       </c>
@@ -3331,7 +3332,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15">
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>2025</v>
       </c>
@@ -3354,7 +3355,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>2024</v>
       </c>
@@ -3377,7 +3378,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>2023</v>
       </c>
@@ -3400,7 +3401,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>2026</v>
       </c>
@@ -3423,7 +3424,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>2025</v>
       </c>
@@ -3446,7 +3447,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>2024</v>
       </c>
@@ -3469,7 +3470,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>2023</v>
       </c>
@@ -3492,7 +3493,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15">
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>2026</v>
       </c>
@@ -3515,7 +3516,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15">
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>2025</v>
       </c>
@@ -3538,7 +3539,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15">
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>2024</v>
       </c>
@@ -3561,7 +3562,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15">
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>2023</v>
       </c>
@@ -3584,7 +3585,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15">
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>2026</v>
       </c>
@@ -3607,7 +3608,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>2025</v>
       </c>
@@ -3630,7 +3631,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>2024</v>
       </c>
@@ -3653,7 +3654,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>2023</v>
       </c>
@@ -3676,7 +3677,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>2026</v>
       </c>
@@ -3699,7 +3700,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>2025</v>
       </c>
@@ -3722,7 +3723,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>2024</v>
       </c>
@@ -3745,7 +3746,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>2023</v>
       </c>
@@ -3768,7 +3769,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15">
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>2026</v>
       </c>
@@ -3791,7 +3792,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15">
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>2025</v>
       </c>
@@ -3814,7 +3815,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15">
+    <row r="111" spans="1:7">
       <c r="A111">
         <v>2024</v>
       </c>
@@ -3837,7 +3838,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15">
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>2023</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15">
+    <row r="113" spans="1:7">
       <c r="A113" s="10">
         <v>2025</v>
       </c>
@@ -3883,7 +3884,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>2024</v>
       </c>
@@ -3906,7 +3907,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>2023</v>
       </c>
@@ -3929,7 +3930,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15">
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>2026</v>
       </c>
@@ -3952,7 +3953,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15">
+    <row r="117" spans="1:7">
       <c r="A117">
         <v>2025</v>
       </c>
@@ -3975,7 +3976,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15">
+    <row r="118" spans="1:7">
       <c r="A118">
         <v>2024</v>
       </c>
@@ -3998,7 +3999,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15">
+    <row r="119" spans="1:7">
       <c r="A119">
         <v>2023</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15">
+    <row r="120" spans="1:7">
       <c r="A120">
         <v>2026</v>
       </c>
@@ -4044,7 +4045,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15">
+    <row r="121" spans="1:7">
       <c r="A121">
         <v>2025</v>
       </c>
@@ -4067,7 +4068,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>2024</v>
       </c>
@@ -4090,7 +4091,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>2023</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15">
+    <row r="124" spans="1:7">
       <c r="A124" s="10">
         <v>2026</v>
       </c>
@@ -4133,7 +4134,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15">
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>2025</v>
       </c>
@@ -4156,7 +4157,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15">
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>2024</v>
       </c>
@@ -4179,7 +4180,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15">
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>2023</v>
       </c>
@@ -4202,7 +4203,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15">
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>2026</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>2025</v>
       </c>
@@ -4248,7 +4249,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15">
+    <row r="130" spans="1:7">
       <c r="A130">
         <v>2024</v>
       </c>
@@ -4271,7 +4272,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>2023</v>
       </c>
@@ -4294,7 +4295,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>2026</v>
       </c>
@@ -4317,7 +4318,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>2025</v>
       </c>
@@ -4340,7 +4341,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>2024</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>2023</v>
       </c>
@@ -4386,7 +4387,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>2026</v>
       </c>
@@ -4409,7 +4410,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15">
+    <row r="137" spans="1:7">
       <c r="A137">
         <v>2025</v>
       </c>
@@ -4432,7 +4433,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15">
+    <row r="138" spans="1:7">
       <c r="A138">
         <v>2024</v>
       </c>
@@ -4455,7 +4456,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15">
+    <row r="139" spans="1:7">
       <c r="A139">
         <v>2023</v>
       </c>
@@ -4478,7 +4479,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15">
+    <row r="140" spans="1:7">
       <c r="A140">
         <v>2026</v>
       </c>
@@ -4501,7 +4502,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15">
+    <row r="141" spans="1:7">
       <c r="A141">
         <v>2025</v>
       </c>
@@ -4524,7 +4525,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>2024</v>
       </c>
@@ -4547,7 +4548,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>2023</v>
       </c>
@@ -4570,7 +4571,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>2026</v>
       </c>
@@ -4593,7 +4594,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="15">
+    <row r="145" spans="1:7">
       <c r="A145">
         <v>2025</v>
       </c>
@@ -4616,7 +4617,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15">
+    <row r="146" spans="1:7">
       <c r="A146">
         <v>2024</v>
       </c>
@@ -4639,7 +4640,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15">
+    <row r="147" spans="1:7">
       <c r="A147">
         <v>2023</v>
       </c>
@@ -4662,10 +4663,16 @@
         <v>190</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15">
+    <row r="148" spans="1:7">
       <c r="A148">
         <v>2026</v>
       </c>
+      <c r="B148" t="s">
+        <v>194</v>
+      </c>
+      <c r="C148" t="s">
+        <v>195</v>
+      </c>
       <c r="D148" t="s">
         <v>192</v>
       </c>
@@ -4679,7 +4686,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15">
+    <row r="149" spans="1:7">
       <c r="A149" s="10">
         <v>2025</v>
       </c>
@@ -4702,7 +4709,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15">
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>2024</v>
       </c>
@@ -4725,7 +4732,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15">
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>2023</v>
       </c>
@@ -4748,7 +4755,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15">
+    <row r="152" spans="1:7">
       <c r="A152" s="10">
         <v>2026</v>
       </c>
@@ -4771,7 +4778,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15">
+    <row r="153" spans="1:7">
       <c r="A153" s="12">
         <v>2025</v>
       </c>
@@ -4794,7 +4801,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="15">
+    <row r="154" spans="1:7">
       <c r="A154">
         <v>2024</v>
       </c>
@@ -4817,7 +4824,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="15">
+    <row r="155" spans="1:7">
       <c r="A155">
         <v>2023</v>
       </c>
@@ -4840,7 +4847,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15">
+    <row r="156" spans="1:7">
       <c r="A156">
         <v>2026</v>
       </c>
@@ -4863,7 +4870,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="15">
+    <row r="157" spans="1:7">
       <c r="A157">
         <v>2025</v>
       </c>
@@ -4886,7 +4893,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="15">
+    <row r="158" spans="1:7">
       <c r="A158">
         <v>2024</v>
       </c>
@@ -4909,7 +4916,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="15">
+    <row r="159" spans="1:7">
       <c r="A159">
         <v>2023</v>
       </c>
@@ -4932,7 +4939,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="15">
+    <row r="160" spans="1:7">
       <c r="A160">
         <v>2026</v>
       </c>
@@ -4955,7 +4962,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15">
+    <row r="161" spans="1:7">
       <c r="A161">
         <v>2025</v>
       </c>
@@ -4978,7 +4985,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15">
+    <row r="162" spans="1:7">
       <c r="A162">
         <v>2024</v>
       </c>
@@ -5001,7 +5008,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15">
+    <row r="163" spans="1:7">
       <c r="A163">
         <v>2023</v>
       </c>
@@ -5024,7 +5031,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15">
+    <row r="164" spans="1:7">
       <c r="A164">
         <v>2026</v>
       </c>
@@ -5047,7 +5054,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15">
+    <row r="165" spans="1:7">
       <c r="A165">
         <v>2025</v>
       </c>
@@ -5066,11 +5073,11 @@
       <c r="F165" s="1">
         <v>45862</v>
       </c>
-      <c r="G165" t="s">
+      <c r="G165" s="15" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15">
+    <row r="166" spans="1:7">
       <c r="A166">
         <v>2024</v>
       </c>
@@ -5093,7 +5100,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15">
+    <row r="167" spans="1:7">
       <c r="A167">
         <v>2023</v>
       </c>
@@ -5116,7 +5123,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15">
+    <row r="168" spans="1:7">
       <c r="A168">
         <v>2026</v>
       </c>
@@ -5139,7 +5146,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15">
+    <row r="169" spans="1:7">
       <c r="A169">
         <v>2025</v>
       </c>
@@ -5162,7 +5169,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15">
+    <row r="170" spans="1:7">
       <c r="A170">
         <v>2024</v>
       </c>
@@ -5185,7 +5192,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15">
+    <row r="171" spans="1:7">
       <c r="A171">
         <v>2023</v>
       </c>
@@ -5208,7 +5215,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15">
+    <row r="172" spans="1:7">
       <c r="A172">
         <v>2026</v>
       </c>
@@ -5231,7 +5238,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="15">
+    <row r="173" spans="1:7">
       <c r="A173">
         <v>2025</v>
       </c>
@@ -5254,7 +5261,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15">
+    <row r="174" spans="1:7">
       <c r="A174">
         <v>2024</v>
       </c>
@@ -5277,7 +5284,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15">
+    <row r="175" spans="1:7">
       <c r="A175">
         <v>2023</v>
       </c>
@@ -5300,7 +5307,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15">
+    <row r="176" spans="1:7">
       <c r="A176">
         <v>2026</v>
       </c>
@@ -5323,7 +5330,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15">
+    <row r="177" spans="1:7">
       <c r="A177">
         <v>2025</v>
       </c>
@@ -5346,7 +5353,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15">
+    <row r="178" spans="1:7">
       <c r="A178">
         <v>2024</v>
       </c>
@@ -5369,7 +5376,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15">
+    <row r="179" spans="1:7">
       <c r="A179">
         <v>2023</v>
       </c>
@@ -5392,7 +5399,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15">
+    <row r="180" spans="1:7">
       <c r="A180">
         <v>2026</v>
       </c>
@@ -5415,7 +5422,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="15">
+    <row r="181" spans="1:7">
       <c r="A181">
         <v>2025</v>
       </c>
@@ -5438,7 +5445,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15">
+    <row r="182" spans="1:7">
       <c r="A182">
         <v>2024</v>
       </c>
@@ -5461,7 +5468,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15">
+    <row r="183" spans="1:7">
       <c r="A183">
         <v>2023</v>
       </c>
@@ -5484,7 +5491,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15">
+    <row r="184" spans="1:7">
       <c r="A184" s="10">
         <v>2025</v>
       </c>
@@ -5507,7 +5514,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15">
+    <row r="185" spans="1:7">
       <c r="A185">
         <v>2024</v>
       </c>
@@ -5530,7 +5537,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15">
+    <row r="186" spans="1:7">
       <c r="A186">
         <v>2023</v>
       </c>
@@ -5553,7 +5560,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15">
+    <row r="187" spans="1:7">
       <c r="A187">
         <v>2026</v>
       </c>
@@ -5576,7 +5583,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15">
+    <row r="188" spans="1:7">
       <c r="A188">
         <v>2025</v>
       </c>
@@ -5599,7 +5606,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15">
+    <row r="189" spans="1:7">
       <c r="A189">
         <v>2024</v>
       </c>
@@ -5622,7 +5629,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15">
+    <row r="190" spans="1:7">
       <c r="A190">
         <v>2023</v>
       </c>
@@ -5645,7 +5652,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15">
+    <row r="191" spans="1:7">
       <c r="A191">
         <v>2026</v>
       </c>
@@ -5668,7 +5675,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15">
+    <row r="192" spans="1:7">
       <c r="A192">
         <v>2025</v>
       </c>
@@ -5691,7 +5698,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15">
+    <row r="193" spans="1:7">
       <c r="A193">
         <v>2024</v>
       </c>
@@ -5714,7 +5721,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15">
+    <row r="194" spans="1:7">
       <c r="A194">
         <v>2023</v>
       </c>
@@ -5737,7 +5744,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15">
+    <row r="195" spans="1:7">
       <c r="A195">
         <v>2026</v>
       </c>
@@ -5760,7 +5767,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="15">
+    <row r="196" spans="1:7">
       <c r="A196">
         <v>2025</v>
       </c>
@@ -5779,11 +5786,11 @@
       <c r="F196" s="1">
         <v>45744</v>
       </c>
-      <c r="G196" t="s">
+      <c r="G196" s="15" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="15">
+    <row r="197" spans="1:7">
       <c r="A197">
         <v>2024</v>
       </c>
@@ -5806,7 +5813,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="15">
+    <row r="198" spans="1:7">
       <c r="A198">
         <v>2023</v>
       </c>
@@ -5829,7 +5836,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15">
+    <row r="199" spans="1:7">
       <c r="A199">
         <v>2026</v>
       </c>
@@ -5849,7 +5856,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="15">
+    <row r="200" spans="1:7">
       <c r="A200">
         <v>2025</v>
       </c>
@@ -5872,7 +5879,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="15">
+    <row r="201" spans="1:7">
       <c r="A201">
         <v>2024</v>
       </c>
@@ -5895,7 +5902,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15">
+    <row r="202" spans="1:7">
       <c r="A202">
         <v>2023</v>
       </c>

--- a/upload/orgao_sem_informacoes_classificadas.xlsx
+++ b/upload/orgao_sem_informacoes_classificadas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA30334D-865D-46AF-91E5-831F9CDC9B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3223EA1F-5529-4FA6-A31B-EFBE6A582F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="257">
   <si>
     <t>ano</t>
   </si>
@@ -113,10 +113,7 @@
     <t>ARSAE</t>
   </si>
   <si>
-    <t>No momento não existe conteúdo a ser publicado. A Arsae-MG informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta,</t>
-  </si>
-  <si>
-    <t>No momento não existe conteúdo a ser publicado. A Arsae-MG informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta,</t>
+    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Agência Reguladora de Saneamento e Energia de Minas Gerais (Arsae-MG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
     <t>https://www.arsae.mg.gov.br/tra_informacoes/</t>
@@ -617,16 +614,16 @@
     <t>A Ouvidoria-Geral do Estado não teve informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
   </si>
   <si>
+    <t>Secretaria de Estado de Agricultura, Pecuária e Abastecimento - SEAPA</t>
+  </si>
+  <si>
+    <t>SEAPA</t>
+  </si>
+  <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Agricultura, Pecuária e Abastecimento informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
   </si>
   <si>
     <t>https://www.mg.gov.br/agricultura/pagina/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
-    <t>Secretaria de Estado de Agricultura, Pecuária e Abastecimento - SEAPA</t>
-  </si>
-  <si>
-    <t>SEAPA</t>
   </si>
   <si>
     <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Secretaria de Estado de Agricultura, Pecuária e Abastecimento informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto2</t>
@@ -923,7 +920,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -943,7 +940,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1281,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K251"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.28515625" customWidth="1"/>
@@ -1336,7 +1332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="15">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1359,7 +1355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -1382,7 +1378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -1405,7 +1401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="15">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -1428,7 +1424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" ht="15">
       <c r="A7">
         <v>2025</v>
       </c>
@@ -1451,7 +1447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" ht="15">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -1474,7 +1470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" ht="15">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -1497,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" ht="15">
       <c r="A10">
         <v>2026</v>
       </c>
@@ -1520,7 +1516,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" ht="15">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1543,7 +1539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" ht="15">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -1566,7 +1562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" ht="15">
       <c r="A13">
         <v>2023</v>
       </c>
@@ -1589,7 +1585,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" ht="15">
       <c r="A14">
         <v>2026</v>
       </c>
@@ -1603,16 +1599,16 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46176</v>
+      </c>
+      <c r="G14" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="1">
-        <v>46154</v>
-      </c>
-      <c r="G14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+    </row>
+    <row r="15" spans="1:7" ht="15">
       <c r="A15">
         <v>2025</v>
       </c>
@@ -1623,19 +1619,19 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1">
         <v>45810</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -1646,19 +1642,19 @@
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1">
         <v>45445</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15">
       <c r="A17">
         <v>2023</v>
       </c>
@@ -1669,683 +1665,683 @@
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1">
         <v>45079</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15">
       <c r="A18">
         <v>2026</v>
       </c>
       <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1">
         <v>46128</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15">
       <c r="A19">
         <v>2026</v>
       </c>
       <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" s="1">
         <v>46112</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15">
       <c r="A20">
         <v>2025</v>
       </c>
       <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>33</v>
       </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1">
         <v>45747</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15">
       <c r="A21">
         <v>2024</v>
       </c>
       <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
         <v>32</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>33</v>
       </c>
-      <c r="D21" t="s">
-        <v>34</v>
-      </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21" s="1">
         <v>45382</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15">
       <c r="A22">
         <v>2023</v>
       </c>
       <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
         <v>32</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>33</v>
       </c>
-      <c r="D22" t="s">
-        <v>34</v>
-      </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" s="1">
         <v>45016</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15">
       <c r="A23">
         <v>2026</v>
       </c>
       <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
         <v>36</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>37</v>
       </c>
-      <c r="D23" t="s">
-        <v>38</v>
-      </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" s="1">
         <v>46127</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15">
       <c r="A24">
         <v>2025</v>
       </c>
       <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F24" s="1">
         <v>46022</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15">
       <c r="A25">
         <v>2024</v>
       </c>
       <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
         <v>36</v>
       </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F25" s="1">
         <v>45657</v>
       </c>
       <c r="G25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15">
       <c r="A26">
         <v>2023</v>
       </c>
       <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
         <v>36</v>
       </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" s="1">
         <v>45291</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15">
       <c r="A27">
         <v>2026</v>
       </c>
       <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
         <v>41</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>42</v>
       </c>
-      <c r="D27" t="s">
-        <v>43</v>
-      </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F27" s="1">
         <v>46161</v>
       </c>
       <c r="G27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15">
       <c r="A28">
         <v>2025</v>
       </c>
       <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
         <v>41</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>42</v>
       </c>
-      <c r="D28" t="s">
-        <v>43</v>
-      </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" s="1">
         <v>45812</v>
       </c>
       <c r="G28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15">
       <c r="A29">
         <v>2024</v>
       </c>
       <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
         <v>41</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>42</v>
       </c>
-      <c r="D29" t="s">
-        <v>43</v>
-      </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F29" s="1">
         <v>45447</v>
       </c>
       <c r="G29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15">
       <c r="A30">
         <v>2023</v>
       </c>
       <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" t="s">
         <v>41</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>42</v>
       </c>
-      <c r="D30" t="s">
-        <v>43</v>
-      </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" s="1">
         <v>45081</v>
       </c>
       <c r="G30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15">
       <c r="A31">
         <v>2026</v>
       </c>
       <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
         <v>46</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>47</v>
       </c>
-      <c r="D31" t="s">
-        <v>48</v>
-      </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F31" s="1">
         <v>46099</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15">
       <c r="A32">
         <v>2025</v>
       </c>
       <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" t="s">
         <v>46</v>
       </c>
-      <c r="C32" t="s">
-        <v>47</v>
-      </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F32" s="1">
         <v>45780</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15">
       <c r="A33">
         <v>2024</v>
       </c>
       <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
         <v>46</v>
       </c>
-      <c r="C33" t="s">
-        <v>47</v>
-      </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F33" s="1">
         <v>45415</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15">
       <c r="A34">
         <v>2023</v>
       </c>
       <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
         <v>46</v>
       </c>
-      <c r="C34" t="s">
-        <v>47</v>
-      </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F34" s="1">
         <v>45049</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15">
       <c r="A35">
         <v>2026</v>
       </c>
       <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
         <v>52</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>53</v>
       </c>
-      <c r="D35" t="s">
-        <v>54</v>
-      </c>
       <c r="E35" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F35" s="1">
         <v>46128</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15">
       <c r="A36">
         <v>2025</v>
       </c>
       <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="s">
         <v>52</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>53</v>
       </c>
-      <c r="D36" t="s">
-        <v>54</v>
-      </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F36" s="1">
         <v>45953</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15">
       <c r="A37">
         <v>2024</v>
       </c>
       <c r="B37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" t="s">
         <v>52</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>53</v>
       </c>
-      <c r="D37" t="s">
-        <v>54</v>
-      </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F37" s="1">
         <v>45588</v>
       </c>
       <c r="G37" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15">
       <c r="A38">
         <v>2023</v>
       </c>
       <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
         <v>52</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>53</v>
       </c>
-      <c r="D38" t="s">
-        <v>54</v>
-      </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F38" s="1">
         <v>45222</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15">
       <c r="A39">
         <v>2026</v>
       </c>
       <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
         <v>56</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>57</v>
       </c>
-      <c r="D39" t="s">
-        <v>58</v>
-      </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F39" s="1">
         <v>46120</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15">
       <c r="A40">
         <v>2025</v>
       </c>
       <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
         <v>56</v>
       </c>
-      <c r="C40" t="s">
-        <v>57</v>
-      </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F40" s="1">
         <v>45735</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15">
       <c r="A41">
         <v>2024</v>
       </c>
       <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" t="s">
         <v>56</v>
       </c>
-      <c r="C41" t="s">
-        <v>57</v>
-      </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F41" s="1">
         <v>45370</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15">
       <c r="A42">
         <v>2023</v>
       </c>
       <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
         <v>56</v>
       </c>
-      <c r="C42" t="s">
-        <v>57</v>
-      </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F42" s="1">
         <v>45004</v>
       </c>
       <c r="G42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15">
       <c r="A43">
         <v>2026</v>
       </c>
       <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" t="s">
         <v>62</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>63</v>
       </c>
-      <c r="D43" t="s">
-        <v>64</v>
-      </c>
       <c r="E43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F43" s="1">
         <v>46073</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15">
       <c r="A44">
         <v>2025</v>
       </c>
       <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
         <v>62</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>63</v>
       </c>
-      <c r="D44" t="s">
-        <v>64</v>
-      </c>
       <c r="E44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F44" s="1">
         <v>45708</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15">
       <c r="A45">
         <v>2024</v>
       </c>
       <c r="B45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s">
         <v>62</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>63</v>
       </c>
-      <c r="D45" t="s">
-        <v>64</v>
-      </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F45" s="1">
         <v>45342</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15">
       <c r="A46">
         <v>2023</v>
       </c>
       <c r="B46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" t="s">
         <v>62</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>63</v>
       </c>
-      <c r="D46" t="s">
-        <v>64</v>
-      </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F46" s="1">
         <v>44977</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75">
@@ -2353,3576 +2349,3576 @@
         <v>2026</v>
       </c>
       <c r="B47" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" t="s">
         <v>66</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>67</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="F47" s="1">
         <v>46135</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15">
       <c r="A48">
         <v>2024</v>
       </c>
       <c r="B48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" t="s">
         <v>66</v>
       </c>
-      <c r="C48" t="s">
-        <v>67</v>
-      </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F48" s="1">
         <v>45657</v>
       </c>
       <c r="G48" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15">
       <c r="A49">
         <v>2023</v>
       </c>
       <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" t="s">
         <v>66</v>
       </c>
-      <c r="C49" t="s">
-        <v>67</v>
-      </c>
       <c r="D49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F49" s="1">
         <v>45291</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15">
       <c r="A50">
         <v>2026</v>
       </c>
       <c r="B50" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" t="s">
         <v>72</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>73</v>
-      </c>
-      <c r="D50" t="s">
-        <v>74</v>
       </c>
       <c r="F50" s="1">
         <v>46140</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15">
       <c r="A51">
         <v>2025</v>
       </c>
       <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" t="s">
         <v>72</v>
       </c>
-      <c r="C51" t="s">
-        <v>73</v>
-      </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F51" s="1">
         <v>45883</v>
       </c>
       <c r="G51" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15">
       <c r="A52">
         <v>2024</v>
       </c>
       <c r="B52" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" t="s">
         <v>72</v>
       </c>
-      <c r="C52" t="s">
-        <v>73</v>
-      </c>
       <c r="D52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F52" s="1">
         <v>45518</v>
       </c>
       <c r="G52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" ht="15">
       <c r="A53">
         <v>2023</v>
       </c>
       <c r="B53" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" t="s">
         <v>72</v>
       </c>
-      <c r="C53" t="s">
-        <v>73</v>
-      </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F53" s="1">
         <v>45152</v>
       </c>
       <c r="G53" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15">
       <c r="A54">
         <v>2026</v>
       </c>
       <c r="B54" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" t="s">
         <v>77</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>78</v>
       </c>
-      <c r="D54" t="s">
-        <v>79</v>
-      </c>
       <c r="E54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F54" s="1">
         <v>46082</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15">
       <c r="A55">
         <v>2025</v>
       </c>
       <c r="B55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" t="s">
         <v>77</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>78</v>
       </c>
-      <c r="D55" t="s">
-        <v>79</v>
-      </c>
       <c r="E55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F55" s="1">
         <v>45717</v>
       </c>
       <c r="G55" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15">
       <c r="A56">
         <v>2024</v>
       </c>
       <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" t="s">
         <v>77</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>78</v>
       </c>
-      <c r="D56" t="s">
-        <v>79</v>
-      </c>
       <c r="E56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F56" s="1">
         <v>45352</v>
       </c>
       <c r="G56" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15">
       <c r="A57">
         <v>2023</v>
       </c>
       <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" t="s">
         <v>77</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>78</v>
       </c>
-      <c r="D57" t="s">
-        <v>79</v>
-      </c>
       <c r="E57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F57" s="1">
         <v>44986</v>
       </c>
       <c r="G57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15">
       <c r="A58">
         <v>2026</v>
       </c>
       <c r="B58" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" t="s">
         <v>81</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>82</v>
       </c>
-      <c r="D58" t="s">
-        <v>83</v>
-      </c>
       <c r="E58" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F58" s="1">
         <v>46125</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15">
       <c r="A59">
         <v>2025</v>
       </c>
       <c r="B59" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" t="s">
         <v>81</v>
       </c>
-      <c r="C59" t="s">
-        <v>82</v>
-      </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F59" s="1">
         <v>45742</v>
       </c>
       <c r="G59" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15">
       <c r="A60">
         <v>2024</v>
       </c>
       <c r="B60" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" t="s">
         <v>81</v>
       </c>
-      <c r="C60" t="s">
-        <v>82</v>
-      </c>
       <c r="D60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F60" s="1">
         <v>45377</v>
       </c>
       <c r="G60" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15">
       <c r="A61">
         <v>2023</v>
       </c>
       <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61" t="s">
         <v>81</v>
       </c>
-      <c r="C61" t="s">
-        <v>82</v>
-      </c>
       <c r="D61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F61" s="1">
         <v>45011</v>
       </c>
       <c r="G61" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15">
       <c r="A62">
         <v>2026</v>
       </c>
       <c r="B62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" t="s">
         <v>86</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>87</v>
       </c>
-      <c r="D62" t="s">
-        <v>88</v>
-      </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F62" s="1">
         <v>46120</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15">
       <c r="A63">
         <v>2025</v>
       </c>
       <c r="B63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" t="s">
         <v>86</v>
       </c>
-      <c r="C63" t="s">
-        <v>87</v>
-      </c>
       <c r="D63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F63" s="1">
         <v>45792</v>
       </c>
       <c r="G63" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15">
       <c r="A64">
         <v>2024</v>
       </c>
       <c r="B64" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" t="s">
         <v>86</v>
       </c>
-      <c r="C64" t="s">
-        <v>87</v>
-      </c>
       <c r="D64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F64" s="1">
         <v>45427</v>
       </c>
       <c r="G64" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15">
       <c r="A65">
         <v>2023</v>
       </c>
       <c r="B65" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" t="s">
         <v>86</v>
       </c>
-      <c r="C65" t="s">
-        <v>87</v>
-      </c>
       <c r="D65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F65" s="1">
         <v>45061</v>
       </c>
       <c r="G65" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15">
       <c r="A66">
         <v>2026</v>
       </c>
       <c r="B66" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" t="s">
         <v>91</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>92</v>
       </c>
-      <c r="D66" t="s">
-        <v>93</v>
-      </c>
       <c r="E66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F66" s="1">
         <v>46140</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15">
       <c r="A67">
         <v>2025</v>
       </c>
       <c r="B67" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" t="s">
         <v>91</v>
       </c>
-      <c r="C67" t="s">
-        <v>92</v>
-      </c>
       <c r="D67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F67" s="1">
         <v>45730</v>
       </c>
       <c r="G67" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15">
       <c r="A68">
         <v>2024</v>
       </c>
       <c r="B68" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" t="s">
         <v>91</v>
       </c>
-      <c r="C68" t="s">
-        <v>92</v>
-      </c>
       <c r="D68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F68" s="1">
         <v>45365</v>
       </c>
       <c r="G68" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15">
       <c r="A69">
         <v>2023</v>
       </c>
       <c r="B69" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" t="s">
         <v>91</v>
       </c>
-      <c r="C69" t="s">
-        <v>92</v>
-      </c>
       <c r="D69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F69" s="1">
         <v>44999</v>
       </c>
       <c r="G69" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15">
       <c r="A70">
         <v>2026</v>
       </c>
       <c r="B70" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" t="s">
         <v>97</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>98</v>
       </c>
-      <c r="D70" t="s">
-        <v>99</v>
-      </c>
       <c r="E70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F70" s="1">
         <v>46161</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15">
       <c r="A71">
         <v>2025</v>
       </c>
       <c r="B71" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71" t="s">
         <v>97</v>
       </c>
-      <c r="C71" t="s">
-        <v>98</v>
-      </c>
       <c r="D71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F71" s="1">
         <v>45756</v>
       </c>
       <c r="G71" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15">
       <c r="A72">
         <v>2024</v>
       </c>
       <c r="B72" t="s">
+        <v>96</v>
+      </c>
+      <c r="C72" t="s">
         <v>97</v>
       </c>
-      <c r="C72" t="s">
-        <v>98</v>
-      </c>
       <c r="D72" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E72" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F72" s="1">
         <v>45391</v>
       </c>
       <c r="G72" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15">
       <c r="A73">
         <v>2023</v>
       </c>
       <c r="B73" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" t="s">
         <v>97</v>
       </c>
-      <c r="C73" t="s">
-        <v>98</v>
-      </c>
       <c r="D73" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E73" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F73" s="1">
         <v>45025</v>
       </c>
       <c r="G73" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15">
       <c r="A74">
         <v>2026</v>
       </c>
       <c r="B74" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" t="s">
         <v>102</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>103</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>104</v>
-      </c>
-      <c r="E74" t="s">
-        <v>105</v>
       </c>
       <c r="F74" s="1">
         <v>46128</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15">
       <c r="A75">
         <v>2025</v>
       </c>
       <c r="B75" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75" t="s">
         <v>102</v>
       </c>
-      <c r="C75" t="s">
-        <v>103</v>
-      </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F75" s="1">
         <v>45820</v>
       </c>
       <c r="G75" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15">
       <c r="A76">
         <v>2024</v>
       </c>
       <c r="B76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" t="s">
         <v>102</v>
       </c>
-      <c r="C76" t="s">
-        <v>103</v>
-      </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F76" s="1">
         <v>45455</v>
       </c>
       <c r="G76" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15">
       <c r="A77">
         <v>2023</v>
       </c>
       <c r="B77" t="s">
+        <v>101</v>
+      </c>
+      <c r="C77" t="s">
         <v>102</v>
       </c>
-      <c r="C77" t="s">
-        <v>103</v>
-      </c>
       <c r="D77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F77" s="1">
         <v>45089</v>
       </c>
       <c r="G77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15">
       <c r="A78">
         <v>2026</v>
       </c>
       <c r="B78" t="s">
+        <v>108</v>
+      </c>
+      <c r="C78" t="s">
         <v>109</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>110</v>
       </c>
-      <c r="D78" t="s">
-        <v>111</v>
-      </c>
       <c r="E78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F78" s="1">
         <v>46142</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15">
       <c r="A79">
         <v>2025</v>
       </c>
       <c r="B79" t="s">
+        <v>108</v>
+      </c>
+      <c r="C79" t="s">
         <v>109</v>
       </c>
-      <c r="C79" t="s">
-        <v>110</v>
-      </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F79" s="1">
         <v>45813</v>
       </c>
       <c r="G79" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15">
       <c r="A80">
         <v>2024</v>
       </c>
       <c r="B80" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" t="s">
         <v>109</v>
       </c>
-      <c r="C80" t="s">
-        <v>110</v>
-      </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E80" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F80" s="1">
         <v>45448</v>
       </c>
       <c r="G80" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15">
       <c r="A81">
         <v>2023</v>
       </c>
       <c r="B81" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81" t="s">
         <v>109</v>
       </c>
-      <c r="C81" t="s">
-        <v>110</v>
-      </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F81" s="1">
         <v>45082</v>
       </c>
       <c r="G81" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15">
       <c r="A82" s="11">
         <v>2025</v>
       </c>
       <c r="B82" t="s">
+        <v>113</v>
+      </c>
+      <c r="C82" t="s">
         <v>114</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>115</v>
       </c>
-      <c r="D82" t="s">
-        <v>116</v>
-      </c>
       <c r="E82" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F82" s="1">
         <v>45730</v>
       </c>
       <c r="G82" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15">
       <c r="A83">
         <v>2024</v>
       </c>
       <c r="B83" t="s">
+        <v>113</v>
+      </c>
+      <c r="C83" t="s">
         <v>114</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>115</v>
       </c>
-      <c r="D83" t="s">
-        <v>116</v>
-      </c>
       <c r="E83" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F83" s="1">
         <v>45365</v>
       </c>
       <c r="G83" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15">
       <c r="A84">
         <v>2023</v>
       </c>
       <c r="B84" t="s">
+        <v>113</v>
+      </c>
+      <c r="C84" t="s">
         <v>114</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>115</v>
       </c>
-      <c r="D84" t="s">
-        <v>116</v>
-      </c>
       <c r="E84" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F84" s="1">
         <v>44999</v>
       </c>
       <c r="G84" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15">
       <c r="A85" s="14">
         <v>2026</v>
       </c>
       <c r="B85" t="s">
+        <v>117</v>
+      </c>
+      <c r="C85" t="s">
         <v>118</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>119</v>
       </c>
-      <c r="D85" t="s">
-        <v>120</v>
-      </c>
       <c r="E85" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F85" s="1">
         <v>46168</v>
       </c>
       <c r="G85" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15">
       <c r="A86" s="14">
         <v>2025</v>
       </c>
       <c r="B86" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" t="s">
         <v>118</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>119</v>
       </c>
-      <c r="D86" t="s">
-        <v>120</v>
-      </c>
       <c r="E86" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F86" s="1">
         <v>45736</v>
       </c>
       <c r="G86" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15">
       <c r="A87">
         <v>2024</v>
       </c>
       <c r="B87" t="s">
+        <v>117</v>
+      </c>
+      <c r="C87" t="s">
         <v>118</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>119</v>
       </c>
-      <c r="D87" t="s">
-        <v>120</v>
-      </c>
       <c r="E87" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F87" s="1">
         <v>45371</v>
       </c>
       <c r="G87" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15">
       <c r="A88">
         <v>2023</v>
       </c>
       <c r="B88" t="s">
+        <v>117</v>
+      </c>
+      <c r="C88" t="s">
         <v>118</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>119</v>
       </c>
-      <c r="D88" t="s">
-        <v>120</v>
-      </c>
       <c r="E88" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F88" s="1">
         <v>45005</v>
       </c>
       <c r="G88" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15">
       <c r="A89">
         <v>2026</v>
       </c>
       <c r="B89" t="s">
+        <v>121</v>
+      </c>
+      <c r="C89" t="s">
         <v>122</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>123</v>
-      </c>
-      <c r="D89" t="s">
-        <v>124</v>
       </c>
       <c r="F89" s="1">
         <v>46128</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15">
       <c r="A90">
         <v>2025</v>
       </c>
       <c r="B90" t="s">
+        <v>121</v>
+      </c>
+      <c r="C90" t="s">
         <v>122</v>
       </c>
-      <c r="C90" t="s">
-        <v>123</v>
-      </c>
       <c r="D90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F90" s="1">
         <v>45838</v>
       </c>
       <c r="G90" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15">
       <c r="A91">
         <v>2024</v>
       </c>
       <c r="B91" t="s">
+        <v>121</v>
+      </c>
+      <c r="C91" t="s">
         <v>122</v>
       </c>
-      <c r="C91" t="s">
-        <v>123</v>
-      </c>
       <c r="D91" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E91" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F91" s="1">
         <v>45473</v>
       </c>
       <c r="G91" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15">
       <c r="A92">
         <v>2023</v>
       </c>
       <c r="B92" t="s">
+        <v>121</v>
+      </c>
+      <c r="C92" t="s">
         <v>122</v>
       </c>
-      <c r="C92" t="s">
-        <v>123</v>
-      </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F92" s="1">
         <v>45107</v>
       </c>
       <c r="G92" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15">
       <c r="A93">
         <v>2026</v>
       </c>
       <c r="B93" t="s">
+        <v>126</v>
+      </c>
+      <c r="C93" t="s">
         <v>127</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>128</v>
       </c>
-      <c r="D93" t="s">
-        <v>129</v>
-      </c>
       <c r="E93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F93" s="1">
         <v>46126</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15">
       <c r="A94">
         <v>2025</v>
       </c>
       <c r="B94" t="s">
+        <v>126</v>
+      </c>
+      <c r="C94" t="s">
         <v>127</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>128</v>
       </c>
-      <c r="D94" t="s">
-        <v>129</v>
-      </c>
       <c r="E94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F94" s="1">
         <v>45742</v>
       </c>
       <c r="G94" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15">
       <c r="A95">
         <v>2024</v>
       </c>
       <c r="B95" t="s">
+        <v>126</v>
+      </c>
+      <c r="C95" t="s">
         <v>127</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>128</v>
       </c>
-      <c r="D95" t="s">
-        <v>129</v>
-      </c>
       <c r="E95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F95" s="1">
         <v>45377</v>
       </c>
       <c r="G95" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15">
       <c r="A96">
         <v>2023</v>
       </c>
       <c r="B96" t="s">
+        <v>126</v>
+      </c>
+      <c r="C96" t="s">
         <v>127</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>128</v>
       </c>
-      <c r="D96" t="s">
-        <v>129</v>
-      </c>
       <c r="E96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F96" s="1">
         <v>45011</v>
       </c>
       <c r="G96" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15">
       <c r="A97">
         <v>2026</v>
       </c>
       <c r="B97" t="s">
+        <v>130</v>
+      </c>
+      <c r="C97" t="s">
         <v>131</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>132</v>
       </c>
-      <c r="D97" t="s">
-        <v>133</v>
-      </c>
       <c r="E97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F97" s="1">
         <v>46127</v>
       </c>
       <c r="G97" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15">
       <c r="A98">
         <v>2025</v>
       </c>
       <c r="B98" t="s">
+        <v>130</v>
+      </c>
+      <c r="C98" t="s">
         <v>131</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>132</v>
       </c>
-      <c r="D98" t="s">
-        <v>133</v>
-      </c>
       <c r="E98" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F98" s="1">
         <v>45808</v>
       </c>
       <c r="G98" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15">
       <c r="A99">
         <v>2024</v>
       </c>
       <c r="B99" t="s">
+        <v>130</v>
+      </c>
+      <c r="C99" t="s">
         <v>131</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>132</v>
       </c>
-      <c r="D99" t="s">
-        <v>133</v>
-      </c>
       <c r="E99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F99" s="1">
         <v>45443</v>
       </c>
       <c r="G99" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15">
       <c r="A100">
         <v>2023</v>
       </c>
       <c r="B100" t="s">
+        <v>130</v>
+      </c>
+      <c r="C100" t="s">
         <v>131</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>132</v>
       </c>
-      <c r="D100" t="s">
-        <v>133</v>
-      </c>
       <c r="E100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F100" s="1">
         <v>45077</v>
       </c>
       <c r="G100" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15">
       <c r="A101">
         <v>2026</v>
       </c>
       <c r="B101" t="s">
+        <v>134</v>
+      </c>
+      <c r="C101" t="s">
         <v>135</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>136</v>
       </c>
-      <c r="D101" t="s">
-        <v>137</v>
-      </c>
       <c r="E101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F101" s="1">
         <v>46135</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="15">
       <c r="A102">
         <v>2025</v>
       </c>
       <c r="B102" t="s">
+        <v>134</v>
+      </c>
+      <c r="C102" t="s">
         <v>135</v>
       </c>
-      <c r="C102" t="s">
-        <v>136</v>
-      </c>
       <c r="D102" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E102" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F102" s="1">
         <v>45736</v>
       </c>
       <c r="G102" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15">
       <c r="A103">
         <v>2024</v>
       </c>
       <c r="B103" t="s">
+        <v>134</v>
+      </c>
+      <c r="C103" t="s">
         <v>135</v>
       </c>
-      <c r="C103" t="s">
-        <v>136</v>
-      </c>
       <c r="D103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F103" s="1">
         <v>45371</v>
       </c>
       <c r="G103" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15">
       <c r="A104">
         <v>2023</v>
       </c>
       <c r="B104" t="s">
+        <v>134</v>
+      </c>
+      <c r="C104" t="s">
         <v>135</v>
       </c>
-      <c r="C104" t="s">
-        <v>136</v>
-      </c>
       <c r="D104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F104" s="1">
         <v>45005</v>
       </c>
       <c r="G104" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15">
       <c r="A105">
         <v>2026</v>
       </c>
       <c r="B105" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105" t="s">
         <v>140</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>141</v>
       </c>
-      <c r="D105" t="s">
-        <v>142</v>
-      </c>
       <c r="E105" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F105" s="1">
         <v>46121</v>
       </c>
       <c r="G105" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15">
       <c r="A106">
         <v>2025</v>
       </c>
       <c r="B106" t="s">
+        <v>139</v>
+      </c>
+      <c r="C106" t="s">
         <v>140</v>
       </c>
-      <c r="C106" t="s">
-        <v>141</v>
-      </c>
       <c r="D106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F106" s="1">
         <v>45735</v>
       </c>
       <c r="G106" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="15">
       <c r="A107">
         <v>2024</v>
       </c>
       <c r="B107" t="s">
+        <v>139</v>
+      </c>
+      <c r="C107" t="s">
         <v>140</v>
       </c>
-      <c r="C107" t="s">
-        <v>141</v>
-      </c>
       <c r="D107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F107" s="1">
         <v>45370</v>
       </c>
       <c r="G107" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15">
       <c r="A108">
         <v>2023</v>
       </c>
       <c r="B108" t="s">
+        <v>139</v>
+      </c>
+      <c r="C108" t="s">
         <v>140</v>
       </c>
-      <c r="C108" t="s">
-        <v>141</v>
-      </c>
       <c r="D108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F108" s="1">
         <v>45004</v>
       </c>
       <c r="G108" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15">
       <c r="A109">
         <v>2026</v>
       </c>
       <c r="B109" t="s">
+        <v>144</v>
+      </c>
+      <c r="C109" t="s">
         <v>145</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>146</v>
       </c>
-      <c r="D109" t="s">
-        <v>147</v>
-      </c>
       <c r="E109" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F109" s="1">
         <v>46126</v>
       </c>
       <c r="G109" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15">
       <c r="A110">
         <v>2025</v>
       </c>
       <c r="B110" t="s">
+        <v>144</v>
+      </c>
+      <c r="C110" t="s">
         <v>145</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>146</v>
       </c>
-      <c r="D110" t="s">
-        <v>147</v>
-      </c>
       <c r="E110" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F110" s="1">
         <v>45741</v>
       </c>
       <c r="G110" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15">
       <c r="A111">
         <v>2024</v>
       </c>
       <c r="B111" t="s">
+        <v>144</v>
+      </c>
+      <c r="C111" t="s">
         <v>145</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>146</v>
       </c>
-      <c r="D111" t="s">
-        <v>147</v>
-      </c>
       <c r="E111" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F111" s="1">
         <v>45376</v>
       </c>
       <c r="G111" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15">
       <c r="A112">
         <v>2023</v>
       </c>
       <c r="B112" t="s">
+        <v>144</v>
+      </c>
+      <c r="C112" t="s">
         <v>145</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>146</v>
       </c>
-      <c r="D112" t="s">
-        <v>147</v>
-      </c>
       <c r="E112" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F112" s="1">
         <v>45010</v>
       </c>
       <c r="G112" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15">
       <c r="A113" s="10">
         <v>2025</v>
       </c>
       <c r="B113" t="s">
+        <v>148</v>
+      </c>
+      <c r="C113" t="s">
         <v>149</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>150</v>
       </c>
-      <c r="D113" t="s">
-        <v>151</v>
-      </c>
       <c r="E113" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F113" s="1">
         <v>45751</v>
       </c>
       <c r="G113" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15">
       <c r="A114">
         <v>2024</v>
       </c>
       <c r="B114" t="s">
+        <v>148</v>
+      </c>
+      <c r="C114" t="s">
         <v>149</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>150</v>
       </c>
-      <c r="D114" t="s">
-        <v>151</v>
-      </c>
       <c r="E114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F114" s="1">
         <v>45386</v>
       </c>
       <c r="G114" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="15">
       <c r="A115">
         <v>2023</v>
       </c>
       <c r="B115" t="s">
+        <v>148</v>
+      </c>
+      <c r="C115" t="s">
         <v>149</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>150</v>
       </c>
-      <c r="D115" t="s">
-        <v>151</v>
-      </c>
       <c r="E115" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F115" s="1">
         <v>45020</v>
       </c>
       <c r="G115" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15">
       <c r="A116">
         <v>2026</v>
       </c>
       <c r="B116" t="s">
+        <v>152</v>
+      </c>
+      <c r="C116" t="s">
         <v>153</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>154</v>
       </c>
-      <c r="D116" t="s">
-        <v>155</v>
-      </c>
       <c r="E116" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F116" s="1">
         <v>46120</v>
       </c>
       <c r="G116" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15">
       <c r="A117">
         <v>2025</v>
       </c>
       <c r="B117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C117" t="s">
         <v>153</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>154</v>
       </c>
-      <c r="D117" t="s">
-        <v>155</v>
-      </c>
       <c r="E117" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F117" s="1">
         <v>45810</v>
       </c>
       <c r="G117" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15">
       <c r="A118">
         <v>2024</v>
       </c>
       <c r="B118" t="s">
+        <v>152</v>
+      </c>
+      <c r="C118" t="s">
         <v>153</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>154</v>
       </c>
-      <c r="D118" t="s">
-        <v>155</v>
-      </c>
       <c r="E118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F118" s="1">
         <v>45445</v>
       </c>
       <c r="G118" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15">
       <c r="A119">
         <v>2023</v>
       </c>
       <c r="B119" t="s">
+        <v>152</v>
+      </c>
+      <c r="C119" t="s">
         <v>153</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>154</v>
       </c>
-      <c r="D119" t="s">
-        <v>155</v>
-      </c>
       <c r="E119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F119" s="1">
         <v>45079</v>
       </c>
       <c r="G119" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15">
       <c r="A120">
         <v>2026</v>
       </c>
       <c r="B120" t="s">
+        <v>156</v>
+      </c>
+      <c r="C120" t="s">
         <v>157</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>158</v>
       </c>
-      <c r="D120" t="s">
-        <v>159</v>
-      </c>
       <c r="E120" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F120" s="1">
         <v>46126</v>
       </c>
       <c r="G120" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15">
       <c r="A121">
         <v>2025</v>
       </c>
       <c r="B121" t="s">
+        <v>156</v>
+      </c>
+      <c r="C121" t="s">
         <v>157</v>
       </c>
-      <c r="C121" t="s">
-        <v>158</v>
-      </c>
       <c r="D121" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E121" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F121" s="1">
         <v>45735</v>
       </c>
       <c r="G121" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15">
       <c r="A122">
         <v>2024</v>
       </c>
       <c r="B122" t="s">
+        <v>156</v>
+      </c>
+      <c r="C122" t="s">
         <v>157</v>
       </c>
-      <c r="C122" t="s">
-        <v>158</v>
-      </c>
       <c r="D122" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E122" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F122" s="1">
         <v>45370</v>
       </c>
       <c r="G122" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="15">
       <c r="A123">
         <v>2023</v>
       </c>
       <c r="B123" t="s">
+        <v>156</v>
+      </c>
+      <c r="C123" t="s">
         <v>157</v>
       </c>
-      <c r="C123" t="s">
-        <v>158</v>
-      </c>
       <c r="D123" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E123" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F123" s="1">
         <v>45004</v>
       </c>
       <c r="G123" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15">
       <c r="A124" s="10">
         <v>2026</v>
       </c>
       <c r="B124" t="s">
+        <v>161</v>
+      </c>
+      <c r="C124" t="s">
         <v>162</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>163</v>
       </c>
-      <c r="D124" t="s">
-        <v>164</v>
-      </c>
       <c r="E124" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F124" s="1">
         <v>46120</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" ht="15">
       <c r="A125">
         <v>2025</v>
       </c>
       <c r="B125" t="s">
+        <v>161</v>
+      </c>
+      <c r="C125" t="s">
         <v>162</v>
       </c>
-      <c r="C125" t="s">
-        <v>163</v>
-      </c>
       <c r="D125" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E125" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F125" s="1">
         <v>45840</v>
       </c>
       <c r="G125" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="15">
       <c r="A126">
         <v>2024</v>
       </c>
       <c r="B126" t="s">
+        <v>161</v>
+      </c>
+      <c r="C126" t="s">
         <v>162</v>
       </c>
-      <c r="C126" t="s">
-        <v>163</v>
-      </c>
       <c r="D126" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E126" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F126" s="1">
         <v>45475</v>
       </c>
       <c r="G126" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="15">
       <c r="A127">
         <v>2023</v>
       </c>
       <c r="B127" t="s">
+        <v>161</v>
+      </c>
+      <c r="C127" t="s">
         <v>162</v>
       </c>
-      <c r="C127" t="s">
-        <v>163</v>
-      </c>
       <c r="D127" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E127" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F127" s="1">
         <v>45109</v>
       </c>
       <c r="G127" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15">
       <c r="A128">
         <v>2026</v>
       </c>
       <c r="B128" t="s">
+        <v>166</v>
+      </c>
+      <c r="C128" t="s">
         <v>167</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>168</v>
       </c>
-      <c r="D128" t="s">
-        <v>169</v>
-      </c>
       <c r="E128" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F128" s="1">
         <v>46139</v>
       </c>
       <c r="G128" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="15">
       <c r="A129">
         <v>2025</v>
       </c>
       <c r="B129" t="s">
+        <v>166</v>
+      </c>
+      <c r="C129" t="s">
         <v>167</v>
       </c>
-      <c r="C129" t="s">
-        <v>168</v>
-      </c>
       <c r="D129" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E129" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F129" s="1">
         <v>45749</v>
       </c>
       <c r="G129" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="15">
       <c r="A130">
         <v>2024</v>
       </c>
       <c r="B130" t="s">
+        <v>166</v>
+      </c>
+      <c r="C130" t="s">
         <v>167</v>
       </c>
-      <c r="C130" t="s">
-        <v>168</v>
-      </c>
       <c r="D130" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E130" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F130" s="1">
         <v>45384</v>
       </c>
       <c r="G130" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15">
       <c r="A131">
         <v>2023</v>
       </c>
       <c r="B131" t="s">
+        <v>166</v>
+      </c>
+      <c r="C131" t="s">
         <v>167</v>
       </c>
-      <c r="C131" t="s">
-        <v>168</v>
-      </c>
       <c r="D131" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E131" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F131" s="1">
         <v>45018</v>
       </c>
       <c r="G131" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="15">
       <c r="A132">
         <v>2026</v>
       </c>
       <c r="B132" t="s">
+        <v>171</v>
+      </c>
+      <c r="C132" t="s">
         <v>172</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>173</v>
       </c>
-      <c r="D132" t="s">
-        <v>174</v>
-      </c>
       <c r="E132" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F132" s="1">
         <v>46161</v>
       </c>
       <c r="G132" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="15">
       <c r="A133">
         <v>2025</v>
       </c>
       <c r="B133" t="s">
+        <v>171</v>
+      </c>
+      <c r="C133" t="s">
         <v>172</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>173</v>
       </c>
-      <c r="D133" t="s">
-        <v>174</v>
-      </c>
       <c r="E133" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F133" s="1">
         <v>45744</v>
       </c>
       <c r="G133" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="15">
       <c r="A134">
         <v>2024</v>
       </c>
       <c r="B134" t="s">
+        <v>171</v>
+      </c>
+      <c r="C134" t="s">
         <v>172</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>173</v>
       </c>
-      <c r="D134" t="s">
-        <v>174</v>
-      </c>
       <c r="E134" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F134" s="1">
         <v>45379</v>
       </c>
       <c r="G134" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="15">
       <c r="A135">
         <v>2023</v>
       </c>
       <c r="B135" t="s">
+        <v>171</v>
+      </c>
+      <c r="C135" t="s">
         <v>172</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
         <v>173</v>
       </c>
-      <c r="D135" t="s">
-        <v>174</v>
-      </c>
       <c r="E135" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F135" s="1">
         <v>45013</v>
       </c>
       <c r="G135" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="15">
       <c r="A136">
         <v>2026</v>
       </c>
       <c r="B136" t="s">
+        <v>176</v>
+      </c>
+      <c r="C136" t="s">
         <v>177</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>178</v>
       </c>
-      <c r="D136" t="s">
-        <v>179</v>
-      </c>
       <c r="E136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F136" s="1">
         <v>46120</v>
       </c>
       <c r="G136" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="15">
       <c r="A137">
         <v>2025</v>
       </c>
       <c r="B137" t="s">
+        <v>176</v>
+      </c>
+      <c r="C137" t="s">
         <v>177</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
         <v>178</v>
       </c>
-      <c r="D137" t="s">
-        <v>179</v>
-      </c>
       <c r="E137" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F137" s="1">
         <v>45733</v>
       </c>
       <c r="G137" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="15">
       <c r="A138">
         <v>2024</v>
       </c>
       <c r="B138" t="s">
+        <v>176</v>
+      </c>
+      <c r="C138" t="s">
         <v>177</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>178</v>
       </c>
-      <c r="D138" t="s">
-        <v>179</v>
-      </c>
       <c r="E138" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F138" s="1">
         <v>45368</v>
       </c>
       <c r="G138" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="15">
       <c r="A139">
         <v>2023</v>
       </c>
       <c r="B139" t="s">
+        <v>176</v>
+      </c>
+      <c r="C139" t="s">
         <v>177</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
         <v>178</v>
       </c>
-      <c r="D139" t="s">
-        <v>179</v>
-      </c>
       <c r="E139" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F139" s="1">
         <v>45002</v>
       </c>
       <c r="G139" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="15">
       <c r="A140">
         <v>2026</v>
       </c>
       <c r="B140" t="s">
+        <v>180</v>
+      </c>
+      <c r="C140" t="s">
         <v>181</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>182</v>
       </c>
-      <c r="D140" t="s">
-        <v>183</v>
-      </c>
       <c r="E140" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F140" s="1">
         <v>46127</v>
       </c>
       <c r="G140" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="15">
       <c r="A141">
         <v>2025</v>
       </c>
       <c r="B141" t="s">
+        <v>180</v>
+      </c>
+      <c r="C141" t="s">
         <v>181</v>
       </c>
-      <c r="C141" t="s">
-        <v>182</v>
-      </c>
       <c r="D141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F141" s="1">
         <v>45735</v>
       </c>
       <c r="G141" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="15">
       <c r="A142">
         <v>2024</v>
       </c>
       <c r="B142" t="s">
+        <v>180</v>
+      </c>
+      <c r="C142" t="s">
         <v>181</v>
       </c>
-      <c r="C142" t="s">
-        <v>182</v>
-      </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E142" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F142" s="1">
         <v>45370</v>
       </c>
       <c r="G142" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15">
       <c r="A143">
         <v>2023</v>
       </c>
       <c r="B143" t="s">
+        <v>180</v>
+      </c>
+      <c r="C143" t="s">
         <v>181</v>
       </c>
-      <c r="C143" t="s">
-        <v>182</v>
-      </c>
       <c r="D143" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E143" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F143" s="1">
         <v>45004</v>
       </c>
       <c r="G143" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="15">
       <c r="A144">
         <v>2026</v>
       </c>
       <c r="B144" t="s">
+        <v>185</v>
+      </c>
+      <c r="C144" t="s">
         <v>186</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>187</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>188</v>
-      </c>
-      <c r="E144" t="s">
-        <v>189</v>
       </c>
       <c r="F144" s="1">
         <v>46140</v>
       </c>
       <c r="G144" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="15">
       <c r="A145">
         <v>2025</v>
       </c>
       <c r="B145" t="s">
+        <v>185</v>
+      </c>
+      <c r="C145" t="s">
         <v>186</v>
       </c>
-      <c r="C145" t="s">
-        <v>187</v>
-      </c>
       <c r="D145" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E145" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="1">
         <v>45705</v>
       </c>
       <c r="G145" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="15">
       <c r="A146">
         <v>2024</v>
       </c>
       <c r="B146" t="s">
+        <v>185</v>
+      </c>
+      <c r="C146" t="s">
         <v>186</v>
       </c>
-      <c r="C146" t="s">
-        <v>187</v>
-      </c>
       <c r="D146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="1">
         <v>45339</v>
       </c>
       <c r="G146" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="15">
       <c r="A147">
         <v>2023</v>
       </c>
       <c r="B147" t="s">
+        <v>185</v>
+      </c>
+      <c r="C147" t="s">
         <v>186</v>
       </c>
-      <c r="C147" t="s">
-        <v>187</v>
-      </c>
       <c r="D147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F147" s="1">
         <v>44974</v>
       </c>
       <c r="G147" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="15">
       <c r="A148">
         <v>2026</v>
       </c>
       <c r="B148" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C148" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D148" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E148" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F148" s="1">
         <v>46162</v>
       </c>
-      <c r="G148" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" s="10">
+      <c r="G148" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="15">
+      <c r="A149" s="12">
         <v>2025</v>
       </c>
       <c r="B149" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C149" t="s">
+        <v>192</v>
+      </c>
+      <c r="D149" t="s">
         <v>195</v>
       </c>
-      <c r="D149" t="s">
-        <v>196</v>
-      </c>
       <c r="E149" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F149" s="1">
         <v>45737</v>
       </c>
       <c r="G149" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="15">
       <c r="A150">
         <v>2024</v>
       </c>
       <c r="B150" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C150" t="s">
+        <v>192</v>
+      </c>
+      <c r="D150" t="s">
         <v>195</v>
       </c>
-      <c r="D150" t="s">
-        <v>196</v>
-      </c>
       <c r="E150" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F150" s="1">
         <v>45372</v>
       </c>
       <c r="G150" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="15">
       <c r="A151">
         <v>2023</v>
       </c>
       <c r="B151" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C151" t="s">
+        <v>192</v>
+      </c>
+      <c r="D151" t="s">
         <v>195</v>
       </c>
-      <c r="D151" t="s">
-        <v>196</v>
-      </c>
       <c r="E151" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F151" s="1">
         <v>45006</v>
       </c>
       <c r="G151" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" s="10">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="15">
+      <c r="A152" s="12">
         <v>2026</v>
       </c>
       <c r="B152" t="s">
+        <v>196</v>
+      </c>
+      <c r="C152" t="s">
         <v>197</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
         <v>198</v>
       </c>
-      <c r="D152" t="s">
-        <v>199</v>
-      </c>
       <c r="E152" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F152" s="1">
         <v>46125</v>
       </c>
       <c r="G152" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="15">
       <c r="A153" s="12">
         <v>2025</v>
       </c>
       <c r="B153" t="s">
+        <v>196</v>
+      </c>
+      <c r="C153" t="s">
         <v>197</v>
       </c>
-      <c r="C153" t="s">
-        <v>198</v>
-      </c>
       <c r="D153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E153" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F153" s="1">
         <v>45741</v>
       </c>
       <c r="G153" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="15">
       <c r="A154">
         <v>2024</v>
       </c>
       <c r="B154" t="s">
+        <v>196</v>
+      </c>
+      <c r="C154" t="s">
         <v>197</v>
       </c>
-      <c r="C154" t="s">
-        <v>198</v>
-      </c>
       <c r="D154" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E154" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F154" s="1">
         <v>45376</v>
       </c>
       <c r="G154" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="15">
       <c r="A155">
         <v>2023</v>
       </c>
       <c r="B155" t="s">
+        <v>196</v>
+      </c>
+      <c r="C155" t="s">
         <v>197</v>
       </c>
-      <c r="C155" t="s">
-        <v>198</v>
-      </c>
       <c r="D155" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E155" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F155" s="1">
         <v>45010</v>
       </c>
       <c r="G155" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="15">
       <c r="A156">
         <v>2026</v>
       </c>
       <c r="B156" t="s">
+        <v>201</v>
+      </c>
+      <c r="C156" t="s">
         <v>202</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
         <v>203</v>
       </c>
-      <c r="D156" t="s">
-        <v>204</v>
-      </c>
       <c r="E156" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F156" s="1">
         <v>46128</v>
       </c>
       <c r="G156" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="15">
       <c r="A157">
         <v>2025</v>
       </c>
       <c r="B157" t="s">
+        <v>201</v>
+      </c>
+      <c r="C157" t="s">
         <v>202</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D157" t="s">
         <v>203</v>
       </c>
-      <c r="D157" t="s">
-        <v>204</v>
-      </c>
       <c r="E157" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F157" s="1">
         <v>45763</v>
       </c>
       <c r="G157" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="15">
       <c r="A158">
         <v>2024</v>
       </c>
       <c r="B158" t="s">
+        <v>201</v>
+      </c>
+      <c r="C158" t="s">
         <v>202</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
         <v>203</v>
       </c>
-      <c r="D158" t="s">
-        <v>204</v>
-      </c>
       <c r="E158" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F158" s="1">
         <v>45398</v>
       </c>
       <c r="G158" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="15">
       <c r="A159">
         <v>2023</v>
       </c>
       <c r="B159" t="s">
+        <v>201</v>
+      </c>
+      <c r="C159" t="s">
         <v>202</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D159" t="s">
         <v>203</v>
       </c>
-      <c r="D159" t="s">
-        <v>204</v>
-      </c>
       <c r="E159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F159" s="1">
         <v>45032</v>
       </c>
       <c r="G159" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="15">
       <c r="A160">
         <v>2026</v>
       </c>
       <c r="B160" t="s">
+        <v>206</v>
+      </c>
+      <c r="C160" t="s">
         <v>207</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>208</v>
       </c>
-      <c r="D160" t="s">
-        <v>209</v>
-      </c>
       <c r="E160" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F160" s="1">
         <v>46128</v>
       </c>
       <c r="G160" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="15">
       <c r="A161">
         <v>2025</v>
       </c>
       <c r="B161" t="s">
+        <v>206</v>
+      </c>
+      <c r="C161" t="s">
         <v>207</v>
       </c>
-      <c r="C161" t="s">
-        <v>208</v>
-      </c>
       <c r="D161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F161" s="1">
         <v>45819</v>
       </c>
       <c r="G161" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="15">
       <c r="A162">
         <v>2024</v>
       </c>
       <c r="B162" t="s">
+        <v>206</v>
+      </c>
+      <c r="C162" t="s">
         <v>207</v>
       </c>
-      <c r="C162" t="s">
-        <v>208</v>
-      </c>
       <c r="D162" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E162" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F162" s="1">
         <v>45454</v>
       </c>
       <c r="G162" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="15">
       <c r="A163">
         <v>2023</v>
       </c>
       <c r="B163" t="s">
+        <v>206</v>
+      </c>
+      <c r="C163" t="s">
         <v>207</v>
       </c>
-      <c r="C163" t="s">
-        <v>208</v>
-      </c>
       <c r="D163" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E163" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F163" s="1">
         <v>45088</v>
       </c>
       <c r="G163" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="15">
       <c r="A164">
         <v>2026</v>
       </c>
       <c r="B164" t="s">
+        <v>211</v>
+      </c>
+      <c r="C164" t="s">
         <v>212</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>213</v>
       </c>
-      <c r="D164" t="s">
-        <v>214</v>
-      </c>
       <c r="E164" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F164" s="1">
         <v>46170</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="15">
       <c r="A165">
         <v>2025</v>
       </c>
       <c r="B165" t="s">
+        <v>211</v>
+      </c>
+      <c r="C165" t="s">
         <v>212</v>
       </c>
-      <c r="C165" t="s">
-        <v>213</v>
-      </c>
       <c r="D165" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E165" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F165" s="1">
         <v>45862</v>
       </c>
-      <c r="G165" s="15" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="G165" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="15">
       <c r="A166">
         <v>2024</v>
       </c>
       <c r="B166" t="s">
+        <v>211</v>
+      </c>
+      <c r="C166" t="s">
         <v>212</v>
       </c>
-      <c r="C166" t="s">
-        <v>213</v>
-      </c>
       <c r="D166" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E166" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F166" s="1">
         <v>45497</v>
       </c>
       <c r="G166" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="15">
       <c r="A167">
         <v>2023</v>
       </c>
       <c r="B167" t="s">
+        <v>211</v>
+      </c>
+      <c r="C167" t="s">
         <v>212</v>
       </c>
-      <c r="C167" t="s">
-        <v>213</v>
-      </c>
       <c r="D167" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E167" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F167" s="1">
         <v>45131</v>
       </c>
       <c r="G167" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="15">
       <c r="A168">
         <v>2026</v>
       </c>
       <c r="B168" t="s">
+        <v>216</v>
+      </c>
+      <c r="C168" t="s">
         <v>217</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>218</v>
       </c>
-      <c r="D168" t="s">
-        <v>219</v>
-      </c>
       <c r="E168" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F168" s="1">
         <v>46128</v>
       </c>
       <c r="G168" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="15">
       <c r="A169">
         <v>2025</v>
       </c>
       <c r="B169" t="s">
+        <v>216</v>
+      </c>
+      <c r="C169" t="s">
         <v>217</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
         <v>218</v>
       </c>
-      <c r="D169" t="s">
-        <v>219</v>
-      </c>
       <c r="E169" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F169" s="1">
         <v>45819</v>
       </c>
       <c r="G169" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="15">
       <c r="A170">
         <v>2024</v>
       </c>
       <c r="B170" t="s">
+        <v>216</v>
+      </c>
+      <c r="C170" t="s">
         <v>217</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>218</v>
       </c>
-      <c r="D170" t="s">
-        <v>219</v>
-      </c>
       <c r="E170" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F170" s="1">
         <v>45454</v>
       </c>
       <c r="G170" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="15">
       <c r="A171">
         <v>2023</v>
       </c>
       <c r="B171" t="s">
+        <v>216</v>
+      </c>
+      <c r="C171" t="s">
         <v>217</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>218</v>
       </c>
-      <c r="D171" t="s">
-        <v>219</v>
-      </c>
       <c r="E171" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F171" s="1">
         <v>45088</v>
       </c>
       <c r="G171" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="15">
       <c r="A172">
         <v>2026</v>
       </c>
       <c r="B172" t="s">
+        <v>220</v>
+      </c>
+      <c r="C172" t="s">
         <v>221</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>222</v>
       </c>
-      <c r="D172" t="s">
-        <v>223</v>
-      </c>
       <c r="E172" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F172" s="1">
         <v>46162</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="15">
       <c r="A173">
         <v>2025</v>
       </c>
       <c r="B173" t="s">
+        <v>220</v>
+      </c>
+      <c r="C173" t="s">
         <v>221</v>
       </c>
-      <c r="C173" t="s">
-        <v>222</v>
-      </c>
       <c r="D173" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E173" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F173" s="1">
         <v>45740</v>
       </c>
       <c r="G173" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="15">
       <c r="A174">
         <v>2024</v>
       </c>
       <c r="B174" t="s">
+        <v>220</v>
+      </c>
+      <c r="C174" t="s">
         <v>221</v>
       </c>
-      <c r="C174" t="s">
-        <v>222</v>
-      </c>
       <c r="D174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F174" s="1">
         <v>45375</v>
       </c>
       <c r="G174" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="15">
       <c r="A175">
         <v>2023</v>
       </c>
       <c r="B175" t="s">
+        <v>220</v>
+      </c>
+      <c r="C175" t="s">
         <v>221</v>
       </c>
-      <c r="C175" t="s">
-        <v>222</v>
-      </c>
       <c r="D175" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E175" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F175" s="1">
         <v>45009</v>
       </c>
       <c r="G175" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="15">
       <c r="A176">
         <v>2026</v>
       </c>
       <c r="B176" t="s">
+        <v>225</v>
+      </c>
+      <c r="C176" t="s">
         <v>226</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>227</v>
       </c>
-      <c r="D176" t="s">
-        <v>228</v>
-      </c>
       <c r="E176" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F176" s="1">
         <v>46125</v>
       </c>
       <c r="G176" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="15">
       <c r="A177">
         <v>2025</v>
       </c>
       <c r="B177" t="s">
+        <v>225</v>
+      </c>
+      <c r="C177" t="s">
         <v>226</v>
       </c>
-      <c r="C177" t="s">
-        <v>227</v>
-      </c>
       <c r="D177" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E177" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F177" s="1">
         <v>45733</v>
       </c>
       <c r="G177" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="15">
       <c r="A178">
         <v>2024</v>
       </c>
       <c r="B178" t="s">
+        <v>225</v>
+      </c>
+      <c r="C178" t="s">
         <v>226</v>
       </c>
-      <c r="C178" t="s">
-        <v>227</v>
-      </c>
       <c r="D178" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E178" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F178" s="1">
         <v>45368</v>
       </c>
       <c r="G178" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="15">
       <c r="A179">
         <v>2023</v>
       </c>
       <c r="B179" t="s">
+        <v>225</v>
+      </c>
+      <c r="C179" t="s">
         <v>226</v>
       </c>
-      <c r="C179" t="s">
-        <v>227</v>
-      </c>
       <c r="D179" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E179" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F179" s="1">
         <v>45002</v>
       </c>
       <c r="G179" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="15">
       <c r="A180">
         <v>2026</v>
       </c>
       <c r="B180" t="s">
+        <v>230</v>
+      </c>
+      <c r="C180" t="s">
         <v>231</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>232</v>
       </c>
-      <c r="D180" t="s">
-        <v>233</v>
-      </c>
       <c r="E180" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F180" s="1">
         <v>46121</v>
       </c>
       <c r="G180" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="15">
       <c r="A181">
         <v>2025</v>
       </c>
       <c r="B181" t="s">
+        <v>230</v>
+      </c>
+      <c r="C181" t="s">
         <v>231</v>
       </c>
-      <c r="C181" t="s">
-        <v>232</v>
-      </c>
       <c r="D181" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E181" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F181" s="1">
         <v>45713</v>
       </c>
       <c r="G181" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="15">
       <c r="A182">
         <v>2024</v>
       </c>
       <c r="B182" t="s">
+        <v>230</v>
+      </c>
+      <c r="C182" t="s">
         <v>231</v>
       </c>
-      <c r="C182" t="s">
-        <v>232</v>
-      </c>
       <c r="D182" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E182" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F182" s="1">
         <v>45347</v>
       </c>
       <c r="G182" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="15">
       <c r="A183">
         <v>2023</v>
       </c>
       <c r="B183" t="s">
+        <v>230</v>
+      </c>
+      <c r="C183" t="s">
         <v>231</v>
       </c>
-      <c r="C183" t="s">
-        <v>232</v>
-      </c>
       <c r="D183" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E183" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F183" s="1">
         <v>44982</v>
       </c>
       <c r="G183" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="15">
       <c r="A184" s="10">
         <v>2025</v>
       </c>
       <c r="B184" t="s">
+        <v>235</v>
+      </c>
+      <c r="C184" t="s">
         <v>236</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
         <v>237</v>
       </c>
-      <c r="D184" t="s">
-        <v>238</v>
-      </c>
       <c r="E184" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F184" s="1">
         <v>45821</v>
       </c>
       <c r="G184" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="15">
       <c r="A185">
         <v>2024</v>
       </c>
       <c r="B185" t="s">
+        <v>235</v>
+      </c>
+      <c r="C185" t="s">
         <v>236</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
         <v>237</v>
       </c>
-      <c r="D185" t="s">
-        <v>238</v>
-      </c>
       <c r="E185" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F185" s="1">
         <v>45456</v>
       </c>
       <c r="G185" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="15">
       <c r="A186">
         <v>2023</v>
       </c>
       <c r="B186" t="s">
+        <v>235</v>
+      </c>
+      <c r="C186" t="s">
         <v>236</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
         <v>237</v>
       </c>
-      <c r="D186" t="s">
-        <v>238</v>
-      </c>
       <c r="E186" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F186" s="1">
         <v>45090</v>
       </c>
       <c r="G186" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="15">
       <c r="A187">
         <v>2026</v>
       </c>
       <c r="B187" t="s">
+        <v>239</v>
+      </c>
+      <c r="C187" t="s">
         <v>240</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>241</v>
       </c>
-      <c r="D187" t="s">
-        <v>242</v>
-      </c>
       <c r="E187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F187" s="1">
         <v>46170</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="15">
       <c r="A188">
         <v>2025</v>
       </c>
       <c r="B188" t="s">
+        <v>239</v>
+      </c>
+      <c r="C188" t="s">
         <v>240</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
         <v>241</v>
       </c>
-      <c r="D188" t="s">
-        <v>242</v>
-      </c>
       <c r="E188" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F188" s="1">
         <v>45805</v>
       </c>
       <c r="G188" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="15">
       <c r="A189">
         <v>2024</v>
       </c>
       <c r="B189" t="s">
+        <v>239</v>
+      </c>
+      <c r="C189" t="s">
         <v>240</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
         <v>241</v>
       </c>
-      <c r="D189" t="s">
-        <v>242</v>
-      </c>
       <c r="E189" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F189" s="1">
         <v>45440</v>
       </c>
       <c r="G189" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="15">
       <c r="A190">
         <v>2023</v>
       </c>
       <c r="B190" t="s">
+        <v>239</v>
+      </c>
+      <c r="C190" t="s">
         <v>240</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" t="s">
         <v>241</v>
       </c>
-      <c r="D190" t="s">
-        <v>242</v>
-      </c>
       <c r="E190" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F190" s="1">
         <v>45074</v>
       </c>
       <c r="G190" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="15">
       <c r="A191">
         <v>2026</v>
       </c>
       <c r="B191" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C191" t="s">
         <v>244</v>
       </c>
-      <c r="C191" t="s">
-        <v>245</v>
-      </c>
       <c r="D191" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E191" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F191" s="1">
         <v>46125</v>
       </c>
       <c r="G191" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="15">
       <c r="A192">
         <v>2025</v>
       </c>
       <c r="B192" t="s">
+        <v>243</v>
+      </c>
+      <c r="C192" t="s">
         <v>244</v>
       </c>
-      <c r="C192" t="s">
-        <v>245</v>
-      </c>
       <c r="D192" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E192" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F192" s="1">
         <v>45748</v>
       </c>
       <c r="G192" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="15">
       <c r="A193">
         <v>2024</v>
       </c>
       <c r="B193" t="s">
+        <v>243</v>
+      </c>
+      <c r="C193" t="s">
         <v>244</v>
       </c>
-      <c r="C193" t="s">
-        <v>245</v>
-      </c>
       <c r="D193" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E193" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F193" s="1">
         <v>45383</v>
       </c>
       <c r="G193" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="15">
       <c r="A194">
         <v>2023</v>
       </c>
       <c r="B194" t="s">
+        <v>243</v>
+      </c>
+      <c r="C194" t="s">
         <v>244</v>
       </c>
-      <c r="C194" t="s">
-        <v>245</v>
-      </c>
       <c r="D194" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E194" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F194" s="1">
         <v>45017</v>
       </c>
       <c r="G194" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="15">
       <c r="A195">
         <v>2026</v>
       </c>
       <c r="B195" t="s">
+        <v>247</v>
+      </c>
+      <c r="C195" t="s">
         <v>248</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
         <v>249</v>
       </c>
-      <c r="D195" t="s">
-        <v>250</v>
-      </c>
       <c r="E195" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F195" s="1">
         <v>46128</v>
       </c>
       <c r="G195" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="15">
       <c r="A196">
         <v>2025</v>
       </c>
       <c r="B196" t="s">
+        <v>247</v>
+      </c>
+      <c r="C196" t="s">
         <v>248</v>
       </c>
-      <c r="C196" t="s">
-        <v>249</v>
-      </c>
       <c r="D196" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E196" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F196" s="1">
         <v>45744</v>
       </c>
-      <c r="G196" s="15" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
+      <c r="G196" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="15">
       <c r="A197">
         <v>2024</v>
       </c>
       <c r="B197" t="s">
+        <v>247</v>
+      </c>
+      <c r="C197" t="s">
         <v>248</v>
       </c>
-      <c r="C197" t="s">
-        <v>249</v>
-      </c>
       <c r="D197" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E197" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F197" s="1">
         <v>45379</v>
       </c>
       <c r="G197" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="15">
       <c r="A198">
         <v>2023</v>
       </c>
       <c r="B198" t="s">
+        <v>247</v>
+      </c>
+      <c r="C198" t="s">
         <v>248</v>
       </c>
-      <c r="C198" t="s">
-        <v>249</v>
-      </c>
       <c r="D198" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E198" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F198" s="1">
         <v>45013</v>
       </c>
       <c r="G198" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="15">
       <c r="A199">
         <v>2026</v>
       </c>
       <c r="B199" t="s">
+        <v>252</v>
+      </c>
+      <c r="C199" t="s">
         <v>253</v>
       </c>
-      <c r="C199" t="s">
+      <c r="D199" t="s">
         <v>254</v>
-      </c>
-      <c r="D199" t="s">
-        <v>255</v>
       </c>
       <c r="F199" s="1">
         <v>46122</v>
       </c>
       <c r="G199" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="15">
       <c r="A200">
         <v>2025</v>
       </c>
       <c r="B200" t="s">
+        <v>252</v>
+      </c>
+      <c r="C200" t="s">
         <v>253</v>
       </c>
-      <c r="C200" t="s">
-        <v>254</v>
-      </c>
       <c r="D200" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E200" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F200" s="1">
         <v>45737</v>
       </c>
       <c r="G200" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="15">
       <c r="A201">
         <v>2024</v>
       </c>
       <c r="B201" t="s">
+        <v>252</v>
+      </c>
+      <c r="C201" t="s">
         <v>253</v>
       </c>
-      <c r="C201" t="s">
-        <v>254</v>
-      </c>
       <c r="D201" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E201" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F201" s="1">
         <v>45372</v>
       </c>
       <c r="G201" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="15">
       <c r="A202">
         <v>2023</v>
       </c>
       <c r="B202" t="s">
+        <v>252</v>
+      </c>
+      <c r="C202" t="s">
         <v>253</v>
       </c>
-      <c r="C202" t="s">
-        <v>254</v>
-      </c>
       <c r="D202" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E202" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F202" s="1">
         <v>45006</v>
       </c>
       <c r="G202" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="251" spans="11:11">

--- a/upload/orgao_sem_informacoes_classificadas.xlsx
+++ b/upload/orgao_sem_informacoes_classificadas.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3223EA1F-5529-4FA6-A31B-EFBE6A582F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$1</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="257">
   <si>
     <t>ano</t>
   </si>
@@ -815,7 +814,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -920,7 +919,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -940,10 +939,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Hyperlink" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1275,15 +1275,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K251"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K252"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.25" customWidth="1"/>
+    <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1332,7 +1332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>2024</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>2025</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>2024</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2026</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2023</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2026</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2025</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2024</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2023</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2026</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2025</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2024</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2023</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>2026</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>2025</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>2024</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>2023</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>2026</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>2025</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>2024</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>2023</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>2026</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>2025</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>2024</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>2023</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>2026</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>2025</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>2024</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>2023</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>2026</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>2025</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>2024</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>2023</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>2026</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>2025</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>2024</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>2023</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75">
+    <row r="47" spans="1:7" ht="15">
       <c r="A47">
         <v>2026</v>
       </c>
@@ -2367,9 +2367,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15">
+    <row r="48" spans="1:7">
       <c r="A48">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B48" t="s">
         <v>65</v>
@@ -2384,15 +2384,15 @@
         <v>70</v>
       </c>
       <c r="F48" s="1">
-        <v>45657</v>
+        <v>46022</v>
       </c>
       <c r="G48" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15">
+    <row r="49" spans="1:9">
       <c r="A49">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B49" t="s">
         <v>65</v>
@@ -2407,35 +2407,38 @@
         <v>70</v>
       </c>
       <c r="F49" s="1">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="G49" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15">
+    <row r="50" spans="1:9">
       <c r="A50">
+        <v>2023</v>
+      </c>
+      <c r="B50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D50" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="1">
+        <v>45291</v>
+      </c>
+      <c r="G50" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51">
         <v>2026</v>
-      </c>
-      <c r="B50" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" t="s">
-        <v>72</v>
-      </c>
-      <c r="D50" t="s">
-        <v>73</v>
-      </c>
-      <c r="F50" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15">
-      <c r="A51">
-        <v>2025</v>
       </c>
       <c r="B51" t="s">
         <v>71</v>
@@ -2444,21 +2447,18 @@
         <v>72</v>
       </c>
       <c r="D51" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F51" s="1">
-        <v>45883</v>
-      </c>
-      <c r="G51" t="s">
+        <v>46140</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15">
+    <row r="52" spans="1:9">
       <c r="A52">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B52" t="s">
         <v>71</v>
@@ -2473,16 +2473,15 @@
         <v>75</v>
       </c>
       <c r="F52" s="1">
-        <v>45518</v>
+        <v>45883</v>
       </c>
       <c r="G52" t="s">
         <v>74</v>
       </c>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:9" ht="15">
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B53" t="s">
         <v>71</v>
@@ -2497,38 +2496,39 @@
         <v>75</v>
       </c>
       <c r="F53" s="1">
-        <v>45152</v>
+        <v>45518</v>
       </c>
       <c r="G53" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="15">
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54">
+        <v>2023</v>
+      </c>
+      <c r="B54" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E54" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54" s="1">
+        <v>45152</v>
+      </c>
+      <c r="G54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
         <v>2026</v>
-      </c>
-      <c r="B54" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" t="s">
-        <v>77</v>
-      </c>
-      <c r="D54" t="s">
-        <v>78</v>
-      </c>
-      <c r="E54" t="s">
-        <v>78</v>
-      </c>
-      <c r="F54" s="1">
-        <v>46082</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15">
-      <c r="A55">
-        <v>2025</v>
       </c>
       <c r="B55" t="s">
         <v>76</v>
@@ -2543,15 +2543,15 @@
         <v>78</v>
       </c>
       <c r="F55" s="1">
-        <v>45717</v>
-      </c>
-      <c r="G55" t="s">
+        <v>46082</v>
+      </c>
+      <c r="G55" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15">
+    <row r="56" spans="1:9">
       <c r="A56">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B56" t="s">
         <v>76</v>
@@ -2566,15 +2566,15 @@
         <v>78</v>
       </c>
       <c r="F56" s="1">
-        <v>45352</v>
+        <v>45717</v>
       </c>
       <c r="G56" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15">
+    <row r="57" spans="1:9">
       <c r="A57">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B57" t="s">
         <v>76</v>
@@ -2589,38 +2589,38 @@
         <v>78</v>
       </c>
       <c r="F57" s="1">
-        <v>44986</v>
+        <v>45352</v>
       </c>
       <c r="G57" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15">
+    <row r="58" spans="1:9">
       <c r="A58">
+        <v>2023</v>
+      </c>
+      <c r="B58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" t="s">
+        <v>78</v>
+      </c>
+      <c r="F58" s="1">
+        <v>44986</v>
+      </c>
+      <c r="G58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59">
         <v>2026</v>
-      </c>
-      <c r="B58" t="s">
-        <v>80</v>
-      </c>
-      <c r="C58" t="s">
-        <v>81</v>
-      </c>
-      <c r="D58" t="s">
-        <v>82</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F58" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15">
-      <c r="A59">
-        <v>2025</v>
       </c>
       <c r="B59" t="s">
         <v>80</v>
@@ -2629,21 +2629,21 @@
         <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>84</v>
-      </c>
-      <c r="E59" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="F59" s="1">
-        <v>45742</v>
-      </c>
-      <c r="G59" t="s">
+        <v>46125</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15">
+    <row r="60" spans="1:9">
       <c r="A60">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B60" t="s">
         <v>80</v>
@@ -2658,15 +2658,15 @@
         <v>84</v>
       </c>
       <c r="F60" s="1">
-        <v>45377</v>
+        <v>45742</v>
       </c>
       <c r="G60" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15">
+    <row r="61" spans="1:9">
       <c r="A61">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B61" t="s">
         <v>80</v>
@@ -2681,38 +2681,38 @@
         <v>84</v>
       </c>
       <c r="F61" s="1">
-        <v>45011</v>
+        <v>45377</v>
       </c>
       <c r="G61" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15">
+    <row r="62" spans="1:9">
       <c r="A62">
+        <v>2023</v>
+      </c>
+      <c r="B62" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" s="1">
+        <v>45011</v>
+      </c>
+      <c r="G62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
         <v>2026</v>
-      </c>
-      <c r="B62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" t="s">
-        <v>86</v>
-      </c>
-      <c r="D62" t="s">
-        <v>87</v>
-      </c>
-      <c r="E62" t="s">
-        <v>87</v>
-      </c>
-      <c r="F62" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15">
-      <c r="A63">
-        <v>2025</v>
       </c>
       <c r="B63" t="s">
         <v>85</v>
@@ -2721,21 +2721,21 @@
         <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F63" s="1">
-        <v>45792</v>
-      </c>
-      <c r="G63" t="s">
+        <v>46120</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15">
+    <row r="64" spans="1:9">
       <c r="A64">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B64" t="s">
         <v>85</v>
@@ -2750,15 +2750,15 @@
         <v>89</v>
       </c>
       <c r="F64" s="1">
-        <v>45427</v>
+        <v>45792</v>
       </c>
       <c r="G64" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15">
+    <row r="65" spans="1:7">
       <c r="A65">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B65" t="s">
         <v>85</v>
@@ -2773,38 +2773,38 @@
         <v>89</v>
       </c>
       <c r="F65" s="1">
-        <v>45061</v>
+        <v>45427</v>
       </c>
       <c r="G65" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15">
+    <row r="66" spans="1:7">
       <c r="A66">
+        <v>2023</v>
+      </c>
+      <c r="B66" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" t="s">
+        <v>86</v>
+      </c>
+      <c r="D66" t="s">
+        <v>89</v>
+      </c>
+      <c r="E66" t="s">
+        <v>89</v>
+      </c>
+      <c r="F66" s="1">
+        <v>45061</v>
+      </c>
+      <c r="G66" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
         <v>2026</v>
-      </c>
-      <c r="B66" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" t="s">
-        <v>91</v>
-      </c>
-      <c r="D66" t="s">
-        <v>92</v>
-      </c>
-      <c r="E66" t="s">
-        <v>92</v>
-      </c>
-      <c r="F66" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15">
-      <c r="A67">
-        <v>2025</v>
       </c>
       <c r="B67" t="s">
         <v>90</v>
@@ -2813,21 +2813,21 @@
         <v>91</v>
       </c>
       <c r="D67" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E67" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F67" s="1">
-        <v>45730</v>
-      </c>
-      <c r="G67" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15">
+        <v>46140</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B68" t="s">
         <v>90</v>
@@ -2842,15 +2842,15 @@
         <v>94</v>
       </c>
       <c r="F68" s="1">
-        <v>45365</v>
+        <v>45730</v>
       </c>
       <c r="G68" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15">
+    <row r="69" spans="1:7">
       <c r="A69">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B69" t="s">
         <v>90</v>
@@ -2865,38 +2865,38 @@
         <v>94</v>
       </c>
       <c r="F69" s="1">
-        <v>44999</v>
+        <v>45365</v>
       </c>
       <c r="G69" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15">
+    <row r="70" spans="1:7">
       <c r="A70">
+        <v>2023</v>
+      </c>
+      <c r="B70" t="s">
+        <v>90</v>
+      </c>
+      <c r="C70" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70" t="s">
+        <v>94</v>
+      </c>
+      <c r="E70" t="s">
+        <v>94</v>
+      </c>
+      <c r="F70" s="1">
+        <v>44999</v>
+      </c>
+      <c r="G70" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
         <v>2026</v>
-      </c>
-      <c r="B70" t="s">
-        <v>96</v>
-      </c>
-      <c r="C70" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" t="s">
-        <v>98</v>
-      </c>
-      <c r="E70" t="s">
-        <v>98</v>
-      </c>
-      <c r="F70" s="1">
-        <v>46161</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15">
-      <c r="A71">
-        <v>2025</v>
       </c>
       <c r="B71" t="s">
         <v>96</v>
@@ -2905,21 +2905,21 @@
         <v>97</v>
       </c>
       <c r="D71" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F71" s="1">
-        <v>45756</v>
-      </c>
-      <c r="G71" t="s">
+        <v>46161</v>
+      </c>
+      <c r="G71" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15">
+    <row r="72" spans="1:7">
       <c r="A72">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B72" t="s">
         <v>96</v>
@@ -2934,15 +2934,15 @@
         <v>100</v>
       </c>
       <c r="F72" s="1">
-        <v>45391</v>
+        <v>45756</v>
       </c>
       <c r="G72" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15">
+    <row r="73" spans="1:7">
       <c r="A73">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B73" t="s">
         <v>96</v>
@@ -2957,38 +2957,38 @@
         <v>100</v>
       </c>
       <c r="F73" s="1">
-        <v>45025</v>
+        <v>45391</v>
       </c>
       <c r="G73" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15">
+    <row r="74" spans="1:7">
       <c r="A74">
+        <v>2023</v>
+      </c>
+      <c r="B74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" t="s">
+        <v>100</v>
+      </c>
+      <c r="F74" s="1">
+        <v>45025</v>
+      </c>
+      <c r="G74" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
         <v>2026</v>
-      </c>
-      <c r="B74" t="s">
-        <v>101</v>
-      </c>
-      <c r="C74" t="s">
-        <v>102</v>
-      </c>
-      <c r="D74" t="s">
-        <v>103</v>
-      </c>
-      <c r="E74" t="s">
-        <v>104</v>
-      </c>
-      <c r="F74" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="15">
-      <c r="A75">
-        <v>2025</v>
       </c>
       <c r="B75" t="s">
         <v>101</v>
@@ -2997,21 +2997,21 @@
         <v>102</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E75" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F75" s="1">
-        <v>45820</v>
-      </c>
-      <c r="G75" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15">
+        <v>46128</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B76" t="s">
         <v>101</v>
@@ -3026,15 +3026,15 @@
         <v>106</v>
       </c>
       <c r="F76" s="1">
-        <v>45455</v>
+        <v>45820</v>
       </c>
       <c r="G76" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15">
+    <row r="77" spans="1:7">
       <c r="A77">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B77" t="s">
         <v>101</v>
@@ -3049,38 +3049,38 @@
         <v>106</v>
       </c>
       <c r="F77" s="1">
-        <v>45089</v>
+        <v>45455</v>
       </c>
       <c r="G77" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15">
+    <row r="78" spans="1:7">
       <c r="A78">
+        <v>2023</v>
+      </c>
+      <c r="B78" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E78" t="s">
+        <v>106</v>
+      </c>
+      <c r="F78" s="1">
+        <v>45089</v>
+      </c>
+      <c r="G78" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79">
         <v>2026</v>
-      </c>
-      <c r="B78" t="s">
-        <v>108</v>
-      </c>
-      <c r="C78" t="s">
-        <v>109</v>
-      </c>
-      <c r="D78" t="s">
-        <v>110</v>
-      </c>
-      <c r="E78" t="s">
-        <v>110</v>
-      </c>
-      <c r="F78" s="1">
-        <v>46142</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15">
-      <c r="A79">
-        <v>2025</v>
       </c>
       <c r="B79" t="s">
         <v>108</v>
@@ -3089,21 +3089,21 @@
         <v>109</v>
       </c>
       <c r="D79" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E79" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F79" s="1">
-        <v>45813</v>
-      </c>
-      <c r="G79" t="s">
+        <v>46142</v>
+      </c>
+      <c r="G79" s="8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15">
+    <row r="80" spans="1:7">
       <c r="A80">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B80" t="s">
         <v>108</v>
@@ -3118,15 +3118,15 @@
         <v>112</v>
       </c>
       <c r="F80" s="1">
-        <v>45448</v>
+        <v>45813</v>
       </c>
       <c r="G80" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15">
+    <row r="81" spans="1:7">
       <c r="A81">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B81" t="s">
         <v>108</v>
@@ -3141,38 +3141,38 @@
         <v>112</v>
       </c>
       <c r="F81" s="1">
-        <v>45082</v>
+        <v>45448</v>
       </c>
       <c r="G81" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15">
-      <c r="A82" s="11">
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>2023</v>
+      </c>
+      <c r="B82" t="s">
+        <v>108</v>
+      </c>
+      <c r="C82" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" t="s">
+        <v>112</v>
+      </c>
+      <c r="E82" t="s">
+        <v>112</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45082</v>
+      </c>
+      <c r="G82" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="11">
         <v>2025</v>
-      </c>
-      <c r="B82" t="s">
-        <v>113</v>
-      </c>
-      <c r="C82" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" t="s">
-        <v>115</v>
-      </c>
-      <c r="E82" t="s">
-        <v>115</v>
-      </c>
-      <c r="F82" s="1">
-        <v>45730</v>
-      </c>
-      <c r="G82" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15">
-      <c r="A83">
-        <v>2024</v>
       </c>
       <c r="B83" t="s">
         <v>113</v>
@@ -3187,15 +3187,15 @@
         <v>115</v>
       </c>
       <c r="F83" s="1">
-        <v>45365</v>
+        <v>45730</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15">
+    <row r="84" spans="1:7">
       <c r="A84">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B84" t="s">
         <v>113</v>
@@ -3210,38 +3210,38 @@
         <v>115</v>
       </c>
       <c r="F84" s="1">
-        <v>44999</v>
+        <v>45365</v>
       </c>
       <c r="G84" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15">
-      <c r="A85" s="14">
+    <row r="85" spans="1:7">
+      <c r="A85">
+        <v>2023</v>
+      </c>
+      <c r="B85" t="s">
+        <v>113</v>
+      </c>
+      <c r="C85" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" t="s">
+        <v>115</v>
+      </c>
+      <c r="E85" t="s">
+        <v>115</v>
+      </c>
+      <c r="F85" s="1">
+        <v>44999</v>
+      </c>
+      <c r="G85" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="14">
         <v>2026</v>
-      </c>
-      <c r="B85" t="s">
-        <v>117</v>
-      </c>
-      <c r="C85" t="s">
-        <v>118</v>
-      </c>
-      <c r="D85" t="s">
-        <v>119</v>
-      </c>
-      <c r="E85" t="s">
-        <v>119</v>
-      </c>
-      <c r="F85" s="1">
-        <v>46168</v>
-      </c>
-      <c r="G85" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15">
-      <c r="A86" s="14">
-        <v>2025</v>
       </c>
       <c r="B86" t="s">
         <v>117</v>
@@ -3256,15 +3256,15 @@
         <v>119</v>
       </c>
       <c r="F86" s="1">
-        <v>45736</v>
+        <v>46168</v>
       </c>
       <c r="G86" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15">
-      <c r="A87">
-        <v>2024</v>
+    <row r="87" spans="1:7">
+      <c r="A87" s="14">
+        <v>2025</v>
       </c>
       <c r="B87" t="s">
         <v>117</v>
@@ -3279,15 +3279,15 @@
         <v>119</v>
       </c>
       <c r="F87" s="1">
-        <v>45371</v>
+        <v>45736</v>
       </c>
       <c r="G87" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15">
+    <row r="88" spans="1:7">
       <c r="A88">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B88" t="s">
         <v>117</v>
@@ -3302,35 +3302,38 @@
         <v>119</v>
       </c>
       <c r="F88" s="1">
-        <v>45005</v>
+        <v>45371</v>
       </c>
       <c r="G88" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15">
+    <row r="89" spans="1:7">
       <c r="A89">
+        <v>2023</v>
+      </c>
+      <c r="B89" t="s">
+        <v>117</v>
+      </c>
+      <c r="C89" t="s">
+        <v>118</v>
+      </c>
+      <c r="D89" t="s">
+        <v>119</v>
+      </c>
+      <c r="E89" t="s">
+        <v>119</v>
+      </c>
+      <c r="F89" s="1">
+        <v>45005</v>
+      </c>
+      <c r="G89" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
         <v>2026</v>
-      </c>
-      <c r="B89" t="s">
-        <v>121</v>
-      </c>
-      <c r="C89" t="s">
-        <v>122</v>
-      </c>
-      <c r="D89" t="s">
-        <v>123</v>
-      </c>
-      <c r="F89" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15">
-      <c r="A90">
-        <v>2025</v>
       </c>
       <c r="B90" t="s">
         <v>121</v>
@@ -3339,21 +3342,18 @@
         <v>122</v>
       </c>
       <c r="D90" t="s">
-        <v>125</v>
-      </c>
-      <c r="E90" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F90" s="1">
-        <v>45838</v>
-      </c>
-      <c r="G90" t="s">
+        <v>46128</v>
+      </c>
+      <c r="G90" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15">
+    <row r="91" spans="1:7">
       <c r="A91">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B91" t="s">
         <v>121</v>
@@ -3368,15 +3368,15 @@
         <v>125</v>
       </c>
       <c r="F91" s="1">
-        <v>45473</v>
+        <v>45838</v>
       </c>
       <c r="G91" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15">
+    <row r="92" spans="1:7">
       <c r="A92">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B92" t="s">
         <v>121</v>
@@ -3391,38 +3391,38 @@
         <v>125</v>
       </c>
       <c r="F92" s="1">
-        <v>45107</v>
+        <v>45473</v>
       </c>
       <c r="G92" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15">
+    <row r="93" spans="1:7">
       <c r="A93">
+        <v>2023</v>
+      </c>
+      <c r="B93" t="s">
+        <v>121</v>
+      </c>
+      <c r="C93" t="s">
+        <v>122</v>
+      </c>
+      <c r="D93" t="s">
+        <v>125</v>
+      </c>
+      <c r="E93" t="s">
+        <v>125</v>
+      </c>
+      <c r="F93" s="1">
+        <v>45107</v>
+      </c>
+      <c r="G93" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
         <v>2026</v>
-      </c>
-      <c r="B93" t="s">
-        <v>126</v>
-      </c>
-      <c r="C93" t="s">
-        <v>127</v>
-      </c>
-      <c r="D93" t="s">
-        <v>128</v>
-      </c>
-      <c r="E93" t="s">
-        <v>128</v>
-      </c>
-      <c r="F93" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="15">
-      <c r="A94">
-        <v>2025</v>
       </c>
       <c r="B94" t="s">
         <v>126</v>
@@ -3437,15 +3437,15 @@
         <v>128</v>
       </c>
       <c r="F94" s="1">
-        <v>45742</v>
-      </c>
-      <c r="G94" t="s">
+        <v>46126</v>
+      </c>
+      <c r="G94" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15">
+    <row r="95" spans="1:7">
       <c r="A95">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B95" t="s">
         <v>126</v>
@@ -3460,15 +3460,15 @@
         <v>128</v>
       </c>
       <c r="F95" s="1">
-        <v>45377</v>
+        <v>45742</v>
       </c>
       <c r="G95" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15">
+    <row r="96" spans="1:7">
       <c r="A96">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B96" t="s">
         <v>126</v>
@@ -3483,38 +3483,38 @@
         <v>128</v>
       </c>
       <c r="F96" s="1">
-        <v>45011</v>
+        <v>45377</v>
       </c>
       <c r="G96" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15">
+    <row r="97" spans="1:7">
       <c r="A97">
+        <v>2023</v>
+      </c>
+      <c r="B97" t="s">
+        <v>126</v>
+      </c>
+      <c r="C97" t="s">
+        <v>127</v>
+      </c>
+      <c r="D97" t="s">
+        <v>128</v>
+      </c>
+      <c r="E97" t="s">
+        <v>128</v>
+      </c>
+      <c r="F97" s="1">
+        <v>45011</v>
+      </c>
+      <c r="G97" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
         <v>2026</v>
-      </c>
-      <c r="B97" t="s">
-        <v>130</v>
-      </c>
-      <c r="C97" t="s">
-        <v>131</v>
-      </c>
-      <c r="D97" t="s">
-        <v>132</v>
-      </c>
-      <c r="E97" t="s">
-        <v>132</v>
-      </c>
-      <c r="F97" s="1">
-        <v>46127</v>
-      </c>
-      <c r="G97" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="15">
-      <c r="A98">
-        <v>2025</v>
       </c>
       <c r="B98" t="s">
         <v>130</v>
@@ -3529,15 +3529,15 @@
         <v>132</v>
       </c>
       <c r="F98" s="1">
-        <v>45808</v>
+        <v>46127</v>
       </c>
       <c r="G98" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15">
+    <row r="99" spans="1:7">
       <c r="A99">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B99" t="s">
         <v>130</v>
@@ -3552,15 +3552,15 @@
         <v>132</v>
       </c>
       <c r="F99" s="1">
-        <v>45443</v>
+        <v>45808</v>
       </c>
       <c r="G99" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15">
+    <row r="100" spans="1:7">
       <c r="A100">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B100" t="s">
         <v>130</v>
@@ -3575,38 +3575,38 @@
         <v>132</v>
       </c>
       <c r="F100" s="1">
-        <v>45077</v>
+        <v>45443</v>
       </c>
       <c r="G100" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15">
+    <row r="101" spans="1:7">
       <c r="A101">
+        <v>2023</v>
+      </c>
+      <c r="B101" t="s">
+        <v>130</v>
+      </c>
+      <c r="C101" t="s">
+        <v>131</v>
+      </c>
+      <c r="D101" t="s">
+        <v>132</v>
+      </c>
+      <c r="E101" t="s">
+        <v>132</v>
+      </c>
+      <c r="F101" s="1">
+        <v>45077</v>
+      </c>
+      <c r="G101" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102">
         <v>2026</v>
-      </c>
-      <c r="B101" t="s">
-        <v>134</v>
-      </c>
-      <c r="C101" t="s">
-        <v>135</v>
-      </c>
-      <c r="D101" t="s">
-        <v>136</v>
-      </c>
-      <c r="E101" t="s">
-        <v>136</v>
-      </c>
-      <c r="F101" s="1">
-        <v>46135</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="15">
-      <c r="A102">
-        <v>2025</v>
       </c>
       <c r="B102" t="s">
         <v>134</v>
@@ -3615,21 +3615,21 @@
         <v>135</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E102" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F102" s="1">
-        <v>45736</v>
-      </c>
-      <c r="G102" t="s">
+        <v>46135</v>
+      </c>
+      <c r="G102" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15">
+    <row r="103" spans="1:7">
       <c r="A103">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B103" t="s">
         <v>134</v>
@@ -3644,15 +3644,15 @@
         <v>138</v>
       </c>
       <c r="F103" s="1">
-        <v>45371</v>
+        <v>45736</v>
       </c>
       <c r="G103" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15">
+    <row r="104" spans="1:7">
       <c r="A104">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B104" t="s">
         <v>134</v>
@@ -3667,38 +3667,38 @@
         <v>138</v>
       </c>
       <c r="F104" s="1">
-        <v>45005</v>
+        <v>45371</v>
       </c>
       <c r="G104" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15">
+    <row r="105" spans="1:7">
       <c r="A105">
+        <v>2023</v>
+      </c>
+      <c r="B105" t="s">
+        <v>134</v>
+      </c>
+      <c r="C105" t="s">
+        <v>135</v>
+      </c>
+      <c r="D105" t="s">
+        <v>138</v>
+      </c>
+      <c r="E105" t="s">
+        <v>138</v>
+      </c>
+      <c r="F105" s="1">
+        <v>45005</v>
+      </c>
+      <c r="G105" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106">
         <v>2026</v>
-      </c>
-      <c r="B105" t="s">
-        <v>139</v>
-      </c>
-      <c r="C105" t="s">
-        <v>140</v>
-      </c>
-      <c r="D105" t="s">
-        <v>141</v>
-      </c>
-      <c r="E105" t="s">
-        <v>141</v>
-      </c>
-      <c r="F105" s="1">
-        <v>46121</v>
-      </c>
-      <c r="G105" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="15">
-      <c r="A106">
-        <v>2025</v>
       </c>
       <c r="B106" t="s">
         <v>139</v>
@@ -3707,21 +3707,21 @@
         <v>140</v>
       </c>
       <c r="D106" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E106" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F106" s="1">
-        <v>45735</v>
+        <v>46121</v>
       </c>
       <c r="G106" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15">
+    <row r="107" spans="1:7">
       <c r="A107">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B107" t="s">
         <v>139</v>
@@ -3736,15 +3736,15 @@
         <v>143</v>
       </c>
       <c r="F107" s="1">
-        <v>45370</v>
+        <v>45735</v>
       </c>
       <c r="G107" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15">
+    <row r="108" spans="1:7">
       <c r="A108">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B108" t="s">
         <v>139</v>
@@ -3759,38 +3759,38 @@
         <v>143</v>
       </c>
       <c r="F108" s="1">
-        <v>45004</v>
+        <v>45370</v>
       </c>
       <c r="G108" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15">
+    <row r="109" spans="1:7">
       <c r="A109">
+        <v>2023</v>
+      </c>
+      <c r="B109" t="s">
+        <v>139</v>
+      </c>
+      <c r="C109" t="s">
+        <v>140</v>
+      </c>
+      <c r="D109" t="s">
+        <v>143</v>
+      </c>
+      <c r="E109" t="s">
+        <v>143</v>
+      </c>
+      <c r="F109" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G109" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110">
         <v>2026</v>
-      </c>
-      <c r="B109" t="s">
-        <v>144</v>
-      </c>
-      <c r="C109" t="s">
-        <v>145</v>
-      </c>
-      <c r="D109" t="s">
-        <v>146</v>
-      </c>
-      <c r="E109" t="s">
-        <v>146</v>
-      </c>
-      <c r="F109" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G109" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="15">
-      <c r="A110">
-        <v>2025</v>
       </c>
       <c r="B110" t="s">
         <v>144</v>
@@ -3805,15 +3805,15 @@
         <v>146</v>
       </c>
       <c r="F110" s="1">
-        <v>45741</v>
+        <v>46126</v>
       </c>
       <c r="G110" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15">
+    <row r="111" spans="1:7">
       <c r="A111">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B111" t="s">
         <v>144</v>
@@ -3828,15 +3828,15 @@
         <v>146</v>
       </c>
       <c r="F111" s="1">
-        <v>45376</v>
+        <v>45741</v>
       </c>
       <c r="G111" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15">
+    <row r="112" spans="1:7">
       <c r="A112">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B112" t="s">
         <v>144</v>
@@ -3851,38 +3851,38 @@
         <v>146</v>
       </c>
       <c r="F112" s="1">
-        <v>45010</v>
+        <v>45376</v>
       </c>
       <c r="G112" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15">
-      <c r="A113" s="10">
+    <row r="113" spans="1:7">
+      <c r="A113">
+        <v>2023</v>
+      </c>
+      <c r="B113" t="s">
+        <v>144</v>
+      </c>
+      <c r="C113" t="s">
+        <v>145</v>
+      </c>
+      <c r="D113" t="s">
+        <v>146</v>
+      </c>
+      <c r="E113" t="s">
+        <v>146</v>
+      </c>
+      <c r="F113" s="1">
+        <v>45010</v>
+      </c>
+      <c r="G113" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="10">
         <v>2025</v>
-      </c>
-      <c r="B113" t="s">
-        <v>148</v>
-      </c>
-      <c r="C113" t="s">
-        <v>149</v>
-      </c>
-      <c r="D113" t="s">
-        <v>150</v>
-      </c>
-      <c r="E113" t="s">
-        <v>150</v>
-      </c>
-      <c r="F113" s="1">
-        <v>45751</v>
-      </c>
-      <c r="G113" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="15">
-      <c r="A114">
-        <v>2024</v>
       </c>
       <c r="B114" t="s">
         <v>148</v>
@@ -3897,15 +3897,15 @@
         <v>150</v>
       </c>
       <c r="F114" s="1">
-        <v>45386</v>
+        <v>45751</v>
       </c>
       <c r="G114" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15">
+    <row r="115" spans="1:7">
       <c r="A115">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B115" t="s">
         <v>148</v>
@@ -3920,38 +3920,38 @@
         <v>150</v>
       </c>
       <c r="F115" s="1">
-        <v>45020</v>
+        <v>45386</v>
       </c>
       <c r="G115" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15">
+    <row r="116" spans="1:7">
       <c r="A116">
+        <v>2023</v>
+      </c>
+      <c r="B116" t="s">
+        <v>148</v>
+      </c>
+      <c r="C116" t="s">
+        <v>149</v>
+      </c>
+      <c r="D116" t="s">
+        <v>150</v>
+      </c>
+      <c r="E116" t="s">
+        <v>150</v>
+      </c>
+      <c r="F116" s="1">
+        <v>45020</v>
+      </c>
+      <c r="G116" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117">
         <v>2026</v>
-      </c>
-      <c r="B116" t="s">
-        <v>152</v>
-      </c>
-      <c r="C116" t="s">
-        <v>153</v>
-      </c>
-      <c r="D116" t="s">
-        <v>154</v>
-      </c>
-      <c r="E116" t="s">
-        <v>154</v>
-      </c>
-      <c r="F116" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G116" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="15">
-      <c r="A117">
-        <v>2025</v>
       </c>
       <c r="B117" t="s">
         <v>152</v>
@@ -3966,15 +3966,15 @@
         <v>154</v>
       </c>
       <c r="F117" s="1">
-        <v>45810</v>
+        <v>46120</v>
       </c>
       <c r="G117" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15">
+    <row r="118" spans="1:7">
       <c r="A118">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B118" t="s">
         <v>152</v>
@@ -3989,15 +3989,15 @@
         <v>154</v>
       </c>
       <c r="F118" s="1">
-        <v>45445</v>
+        <v>45810</v>
       </c>
       <c r="G118" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15">
+    <row r="119" spans="1:7">
       <c r="A119">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B119" t="s">
         <v>152</v>
@@ -4012,38 +4012,38 @@
         <v>154</v>
       </c>
       <c r="F119" s="1">
-        <v>45079</v>
+        <v>45445</v>
       </c>
       <c r="G119" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15">
+    <row r="120" spans="1:7">
       <c r="A120">
+        <v>2023</v>
+      </c>
+      <c r="B120" t="s">
+        <v>152</v>
+      </c>
+      <c r="C120" t="s">
+        <v>153</v>
+      </c>
+      <c r="D120" t="s">
+        <v>154</v>
+      </c>
+      <c r="E120" t="s">
+        <v>154</v>
+      </c>
+      <c r="F120" s="1">
+        <v>45079</v>
+      </c>
+      <c r="G120" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121">
         <v>2026</v>
-      </c>
-      <c r="B120" t="s">
-        <v>156</v>
-      </c>
-      <c r="C120" t="s">
-        <v>157</v>
-      </c>
-      <c r="D120" t="s">
-        <v>158</v>
-      </c>
-      <c r="E120" t="s">
-        <v>158</v>
-      </c>
-      <c r="F120" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G120" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="15">
-      <c r="A121">
-        <v>2025</v>
       </c>
       <c r="B121" t="s">
         <v>156</v>
@@ -4052,21 +4052,21 @@
         <v>157</v>
       </c>
       <c r="D121" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E121" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F121" s="1">
-        <v>45735</v>
+        <v>46126</v>
       </c>
       <c r="G121" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15">
+    <row r="122" spans="1:7">
       <c r="A122">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B122" t="s">
         <v>156</v>
@@ -4081,15 +4081,15 @@
         <v>160</v>
       </c>
       <c r="F122" s="1">
-        <v>45370</v>
+        <v>45735</v>
       </c>
       <c r="G122" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15">
+    <row r="123" spans="1:7">
       <c r="A123">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B123" t="s">
         <v>156</v>
@@ -4104,35 +4104,38 @@
         <v>160</v>
       </c>
       <c r="F123" s="1">
-        <v>45004</v>
+        <v>45370</v>
       </c>
       <c r="G123" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15">
-      <c r="A124" s="10">
+    <row r="124" spans="1:7">
+      <c r="A124">
+        <v>2023</v>
+      </c>
+      <c r="B124" t="s">
+        <v>156</v>
+      </c>
+      <c r="C124" t="s">
+        <v>157</v>
+      </c>
+      <c r="D124" t="s">
+        <v>160</v>
+      </c>
+      <c r="E124" t="s">
+        <v>160</v>
+      </c>
+      <c r="F124" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G124" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="15">
         <v>2026</v>
-      </c>
-      <c r="B124" t="s">
-        <v>161</v>
-      </c>
-      <c r="C124" t="s">
-        <v>162</v>
-      </c>
-      <c r="D124" t="s">
-        <v>163</v>
-      </c>
-      <c r="E124" t="s">
-        <v>163</v>
-      </c>
-      <c r="F124" s="1">
-        <v>46120</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="15">
-      <c r="A125">
-        <v>2025</v>
       </c>
       <c r="B125" t="s">
         <v>161</v>
@@ -4141,21 +4144,21 @@
         <v>162</v>
       </c>
       <c r="D125" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E125" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F125" s="1">
-        <v>45840</v>
+        <v>46120</v>
       </c>
       <c r="G125" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15">
+    <row r="126" spans="1:7">
       <c r="A126">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B126" t="s">
         <v>161</v>
@@ -4170,15 +4173,15 @@
         <v>164</v>
       </c>
       <c r="F126" s="1">
-        <v>45475</v>
+        <v>45840</v>
       </c>
       <c r="G126" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15">
+    <row r="127" spans="1:7">
       <c r="A127">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B127" t="s">
         <v>161</v>
@@ -4193,38 +4196,38 @@
         <v>164</v>
       </c>
       <c r="F127" s="1">
-        <v>45109</v>
+        <v>45475</v>
       </c>
       <c r="G127" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15">
+    <row r="128" spans="1:7">
       <c r="A128">
+        <v>2023</v>
+      </c>
+      <c r="B128" t="s">
+        <v>161</v>
+      </c>
+      <c r="C128" t="s">
+        <v>162</v>
+      </c>
+      <c r="D128" t="s">
+        <v>164</v>
+      </c>
+      <c r="E128" t="s">
+        <v>164</v>
+      </c>
+      <c r="F128" s="1">
+        <v>45109</v>
+      </c>
+      <c r="G128" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129">
         <v>2026</v>
-      </c>
-      <c r="B128" t="s">
-        <v>166</v>
-      </c>
-      <c r="C128" t="s">
-        <v>167</v>
-      </c>
-      <c r="D128" t="s">
-        <v>168</v>
-      </c>
-      <c r="E128" t="s">
-        <v>168</v>
-      </c>
-      <c r="F128" s="1">
-        <v>46139</v>
-      </c>
-      <c r="G128" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="15">
-      <c r="A129">
-        <v>2025</v>
       </c>
       <c r="B129" t="s">
         <v>166</v>
@@ -4233,21 +4236,21 @@
         <v>167</v>
       </c>
       <c r="D129" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E129" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F129" s="1">
-        <v>45749</v>
+        <v>46139</v>
       </c>
       <c r="G129" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15">
+    <row r="130" spans="1:7">
       <c r="A130">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B130" t="s">
         <v>166</v>
@@ -4262,15 +4265,15 @@
         <v>170</v>
       </c>
       <c r="F130" s="1">
-        <v>45384</v>
+        <v>45749</v>
       </c>
       <c r="G130" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15">
+    <row r="131" spans="1:7">
       <c r="A131">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B131" t="s">
         <v>166</v>
@@ -4285,38 +4288,38 @@
         <v>170</v>
       </c>
       <c r="F131" s="1">
-        <v>45018</v>
+        <v>45384</v>
       </c>
       <c r="G131" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15">
+    <row r="132" spans="1:7">
       <c r="A132">
+        <v>2023</v>
+      </c>
+      <c r="B132" t="s">
+        <v>166</v>
+      </c>
+      <c r="C132" t="s">
+        <v>167</v>
+      </c>
+      <c r="D132" t="s">
+        <v>170</v>
+      </c>
+      <c r="E132" t="s">
+        <v>170</v>
+      </c>
+      <c r="F132" s="1">
+        <v>45018</v>
+      </c>
+      <c r="G132" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133">
         <v>2026</v>
-      </c>
-      <c r="B132" t="s">
-        <v>171</v>
-      </c>
-      <c r="C132" t="s">
-        <v>172</v>
-      </c>
-      <c r="D132" t="s">
-        <v>173</v>
-      </c>
-      <c r="E132" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F132" s="1">
-        <v>46161</v>
-      </c>
-      <c r="G132" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="15">
-      <c r="A133">
-        <v>2025</v>
       </c>
       <c r="B133" t="s">
         <v>171</v>
@@ -4327,19 +4330,19 @@
       <c r="D133" t="s">
         <v>173</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="13" t="s">
         <v>173</v>
       </c>
       <c r="F133" s="1">
-        <v>45744</v>
+        <v>46161</v>
       </c>
       <c r="G133" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="15">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B134" t="s">
         <v>171</v>
@@ -4354,15 +4357,15 @@
         <v>173</v>
       </c>
       <c r="F134" s="1">
-        <v>45379</v>
+        <v>45744</v>
       </c>
       <c r="G134" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15">
+    <row r="135" spans="1:7">
       <c r="A135">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B135" t="s">
         <v>171</v>
@@ -4377,38 +4380,38 @@
         <v>173</v>
       </c>
       <c r="F135" s="1">
-        <v>45013</v>
+        <v>45379</v>
       </c>
       <c r="G135" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15">
+    <row r="136" spans="1:7">
       <c r="A136">
+        <v>2023</v>
+      </c>
+      <c r="B136" t="s">
+        <v>171</v>
+      </c>
+      <c r="C136" t="s">
+        <v>172</v>
+      </c>
+      <c r="D136" t="s">
+        <v>173</v>
+      </c>
+      <c r="E136" t="s">
+        <v>173</v>
+      </c>
+      <c r="F136" s="1">
+        <v>45013</v>
+      </c>
+      <c r="G136" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137">
         <v>2026</v>
-      </c>
-      <c r="B136" t="s">
-        <v>176</v>
-      </c>
-      <c r="C136" t="s">
-        <v>177</v>
-      </c>
-      <c r="D136" t="s">
-        <v>178</v>
-      </c>
-      <c r="E136" t="s">
-        <v>178</v>
-      </c>
-      <c r="F136" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G136" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="15">
-      <c r="A137">
-        <v>2025</v>
       </c>
       <c r="B137" t="s">
         <v>176</v>
@@ -4423,15 +4426,15 @@
         <v>178</v>
       </c>
       <c r="F137" s="1">
-        <v>45733</v>
+        <v>46120</v>
       </c>
       <c r="G137" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15">
+    <row r="138" spans="1:7">
       <c r="A138">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B138" t="s">
         <v>176</v>
@@ -4446,15 +4449,15 @@
         <v>178</v>
       </c>
       <c r="F138" s="1">
-        <v>45368</v>
+        <v>45733</v>
       </c>
       <c r="G138" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15">
+    <row r="139" spans="1:7">
       <c r="A139">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B139" t="s">
         <v>176</v>
@@ -4469,38 +4472,38 @@
         <v>178</v>
       </c>
       <c r="F139" s="1">
-        <v>45002</v>
+        <v>45368</v>
       </c>
       <c r="G139" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15">
+    <row r="140" spans="1:7">
       <c r="A140">
+        <v>2023</v>
+      </c>
+      <c r="B140" t="s">
+        <v>176</v>
+      </c>
+      <c r="C140" t="s">
+        <v>177</v>
+      </c>
+      <c r="D140" t="s">
+        <v>178</v>
+      </c>
+      <c r="E140" t="s">
+        <v>178</v>
+      </c>
+      <c r="F140" s="1">
+        <v>45002</v>
+      </c>
+      <c r="G140" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141">
         <v>2026</v>
-      </c>
-      <c r="B140" t="s">
-        <v>180</v>
-      </c>
-      <c r="C140" t="s">
-        <v>181</v>
-      </c>
-      <c r="D140" t="s">
-        <v>182</v>
-      </c>
-      <c r="E140" t="s">
-        <v>182</v>
-      </c>
-      <c r="F140" s="1">
-        <v>46127</v>
-      </c>
-      <c r="G140" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="15">
-      <c r="A141">
-        <v>2025</v>
       </c>
       <c r="B141" t="s">
         <v>180</v>
@@ -4509,21 +4512,21 @@
         <v>181</v>
       </c>
       <c r="D141" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E141" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F141" s="1">
-        <v>45735</v>
+        <v>46127</v>
       </c>
       <c r="G141" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15">
+    <row r="142" spans="1:7">
       <c r="A142">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B142" t="s">
         <v>180</v>
@@ -4538,15 +4541,15 @@
         <v>184</v>
       </c>
       <c r="F142" s="1">
-        <v>45370</v>
+        <v>45735</v>
       </c>
       <c r="G142" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15">
+    <row r="143" spans="1:7">
       <c r="A143">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B143" t="s">
         <v>180</v>
@@ -4561,38 +4564,38 @@
         <v>184</v>
       </c>
       <c r="F143" s="1">
-        <v>45004</v>
+        <v>45370</v>
       </c>
       <c r="G143" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15">
+    <row r="144" spans="1:7">
       <c r="A144">
+        <v>2023</v>
+      </c>
+      <c r="B144" t="s">
+        <v>180</v>
+      </c>
+      <c r="C144" t="s">
+        <v>181</v>
+      </c>
+      <c r="D144" t="s">
+        <v>184</v>
+      </c>
+      <c r="E144" t="s">
+        <v>184</v>
+      </c>
+      <c r="F144" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G144" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145">
         <v>2026</v>
-      </c>
-      <c r="B144" t="s">
-        <v>185</v>
-      </c>
-      <c r="C144" t="s">
-        <v>186</v>
-      </c>
-      <c r="D144" t="s">
-        <v>187</v>
-      </c>
-      <c r="E144" t="s">
-        <v>188</v>
-      </c>
-      <c r="F144" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G144" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="15">
-      <c r="A145">
-        <v>2025</v>
       </c>
       <c r="B145" t="s">
         <v>185</v>
@@ -4601,21 +4604,21 @@
         <v>186</v>
       </c>
       <c r="D145" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E145" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F145" s="1">
-        <v>45705</v>
+        <v>46140</v>
       </c>
       <c r="G145" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15">
+    <row r="146" spans="1:7">
       <c r="A146">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B146" t="s">
         <v>185</v>
@@ -4630,15 +4633,15 @@
         <v>190</v>
       </c>
       <c r="F146" s="1">
-        <v>45339</v>
+        <v>45705</v>
       </c>
       <c r="G146" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15">
+    <row r="147" spans="1:7">
       <c r="A147">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B147" t="s">
         <v>185</v>
@@ -4653,38 +4656,38 @@
         <v>190</v>
       </c>
       <c r="F147" s="1">
-        <v>44974</v>
+        <v>45339</v>
       </c>
       <c r="G147" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15">
+    <row r="148" spans="1:7">
       <c r="A148">
+        <v>2023</v>
+      </c>
+      <c r="B148" t="s">
+        <v>185</v>
+      </c>
+      <c r="C148" t="s">
+        <v>186</v>
+      </c>
+      <c r="D148" t="s">
+        <v>190</v>
+      </c>
+      <c r="E148" t="s">
+        <v>190</v>
+      </c>
+      <c r="F148" s="1">
+        <v>44974</v>
+      </c>
+      <c r="G148" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149">
         <v>2026</v>
-      </c>
-      <c r="B148" t="s">
-        <v>191</v>
-      </c>
-      <c r="C148" t="s">
-        <v>192</v>
-      </c>
-      <c r="D148" t="s">
-        <v>193</v>
-      </c>
-      <c r="E148" t="s">
-        <v>193</v>
-      </c>
-      <c r="F148" s="1">
-        <v>46162</v>
-      </c>
-      <c r="G148" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="15">
-      <c r="A149" s="12">
-        <v>2025</v>
       </c>
       <c r="B149" t="s">
         <v>191</v>
@@ -4693,21 +4696,21 @@
         <v>192</v>
       </c>
       <c r="D149" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E149" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F149" s="1">
-        <v>45737</v>
+        <v>46162</v>
       </c>
       <c r="G149" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15">
-      <c r="A150">
-        <v>2024</v>
+    <row r="150" spans="1:7">
+      <c r="A150" s="12">
+        <v>2025</v>
       </c>
       <c r="B150" t="s">
         <v>191</v>
@@ -4722,15 +4725,15 @@
         <v>195</v>
       </c>
       <c r="F150" s="1">
-        <v>45372</v>
+        <v>45737</v>
       </c>
       <c r="G150" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15">
+    <row r="151" spans="1:7">
       <c r="A151">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B151" t="s">
         <v>191</v>
@@ -4745,38 +4748,38 @@
         <v>195</v>
       </c>
       <c r="F151" s="1">
-        <v>45006</v>
+        <v>45372</v>
       </c>
       <c r="G151" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15">
-      <c r="A152" s="12">
+    <row r="152" spans="1:7">
+      <c r="A152">
+        <v>2023</v>
+      </c>
+      <c r="B152" t="s">
+        <v>191</v>
+      </c>
+      <c r="C152" t="s">
+        <v>192</v>
+      </c>
+      <c r="D152" t="s">
+        <v>195</v>
+      </c>
+      <c r="E152" t="s">
+        <v>195</v>
+      </c>
+      <c r="F152" s="1">
+        <v>45006</v>
+      </c>
+      <c r="G152" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="12">
         <v>2026</v>
-      </c>
-      <c r="B152" t="s">
-        <v>196</v>
-      </c>
-      <c r="C152" t="s">
-        <v>197</v>
-      </c>
-      <c r="D152" t="s">
-        <v>198</v>
-      </c>
-      <c r="E152" t="s">
-        <v>198</v>
-      </c>
-      <c r="F152" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G152" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="15">
-      <c r="A153" s="12">
-        <v>2025</v>
       </c>
       <c r="B153" t="s">
         <v>196</v>
@@ -4785,21 +4788,21 @@
         <v>197</v>
       </c>
       <c r="D153" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E153" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F153" s="1">
-        <v>45741</v>
+        <v>46125</v>
       </c>
       <c r="G153" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="15">
-      <c r="A154">
-        <v>2024</v>
+    <row r="154" spans="1:7">
+      <c r="A154" s="12">
+        <v>2025</v>
       </c>
       <c r="B154" t="s">
         <v>196</v>
@@ -4814,15 +4817,15 @@
         <v>200</v>
       </c>
       <c r="F154" s="1">
-        <v>45376</v>
+        <v>45741</v>
       </c>
       <c r="G154" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="15">
+    <row r="155" spans="1:7">
       <c r="A155">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B155" t="s">
         <v>196</v>
@@ -4837,38 +4840,38 @@
         <v>200</v>
       </c>
       <c r="F155" s="1">
-        <v>45010</v>
+        <v>45376</v>
       </c>
       <c r="G155" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15">
+    <row r="156" spans="1:7">
       <c r="A156">
+        <v>2023</v>
+      </c>
+      <c r="B156" t="s">
+        <v>196</v>
+      </c>
+      <c r="C156" t="s">
+        <v>197</v>
+      </c>
+      <c r="D156" t="s">
+        <v>200</v>
+      </c>
+      <c r="E156" t="s">
+        <v>200</v>
+      </c>
+      <c r="F156" s="1">
+        <v>45010</v>
+      </c>
+      <c r="G156" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157">
         <v>2026</v>
-      </c>
-      <c r="B156" t="s">
-        <v>201</v>
-      </c>
-      <c r="C156" t="s">
-        <v>202</v>
-      </c>
-      <c r="D156" t="s">
-        <v>203</v>
-      </c>
-      <c r="E156" t="s">
-        <v>203</v>
-      </c>
-      <c r="F156" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G156" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="15">
-      <c r="A157">
-        <v>2025</v>
       </c>
       <c r="B157" t="s">
         <v>201</v>
@@ -4883,15 +4886,15 @@
         <v>203</v>
       </c>
       <c r="F157" s="1">
-        <v>45763</v>
+        <v>46128</v>
       </c>
       <c r="G157" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="15">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B158" t="s">
         <v>201</v>
@@ -4906,15 +4909,15 @@
         <v>203</v>
       </c>
       <c r="F158" s="1">
-        <v>45398</v>
+        <v>45763</v>
       </c>
       <c r="G158" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="15">
+    <row r="159" spans="1:7">
       <c r="A159">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B159" t="s">
         <v>201</v>
@@ -4929,38 +4932,38 @@
         <v>203</v>
       </c>
       <c r="F159" s="1">
-        <v>45032</v>
+        <v>45398</v>
       </c>
       <c r="G159" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="15">
+    <row r="160" spans="1:7">
       <c r="A160">
+        <v>2023</v>
+      </c>
+      <c r="B160" t="s">
+        <v>201</v>
+      </c>
+      <c r="C160" t="s">
+        <v>202</v>
+      </c>
+      <c r="D160" t="s">
+        <v>203</v>
+      </c>
+      <c r="E160" t="s">
+        <v>203</v>
+      </c>
+      <c r="F160" s="1">
+        <v>45032</v>
+      </c>
+      <c r="G160" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161">
         <v>2026</v>
-      </c>
-      <c r="B160" t="s">
-        <v>206</v>
-      </c>
-      <c r="C160" t="s">
-        <v>207</v>
-      </c>
-      <c r="D160" t="s">
-        <v>208</v>
-      </c>
-      <c r="E160" t="s">
-        <v>208</v>
-      </c>
-      <c r="F160" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G160" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" ht="15">
-      <c r="A161">
-        <v>2025</v>
       </c>
       <c r="B161" t="s">
         <v>206</v>
@@ -4969,21 +4972,21 @@
         <v>207</v>
       </c>
       <c r="D161" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E161" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F161" s="1">
-        <v>45819</v>
+        <v>46128</v>
       </c>
       <c r="G161" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15">
+    <row r="162" spans="1:7">
       <c r="A162">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B162" t="s">
         <v>206</v>
@@ -4998,15 +5001,15 @@
         <v>210</v>
       </c>
       <c r="F162" s="1">
-        <v>45454</v>
+        <v>45819</v>
       </c>
       <c r="G162" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15">
+    <row r="163" spans="1:7">
       <c r="A163">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B163" t="s">
         <v>206</v>
@@ -5021,38 +5024,38 @@
         <v>210</v>
       </c>
       <c r="F163" s="1">
-        <v>45088</v>
+        <v>45454</v>
       </c>
       <c r="G163" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15">
+    <row r="164" spans="1:7">
       <c r="A164">
+        <v>2023</v>
+      </c>
+      <c r="B164" t="s">
+        <v>206</v>
+      </c>
+      <c r="C164" t="s">
+        <v>207</v>
+      </c>
+      <c r="D164" t="s">
+        <v>210</v>
+      </c>
+      <c r="E164" t="s">
+        <v>210</v>
+      </c>
+      <c r="F164" s="1">
+        <v>45088</v>
+      </c>
+      <c r="G164" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165">
         <v>2026</v>
-      </c>
-      <c r="B164" t="s">
-        <v>211</v>
-      </c>
-      <c r="C164" t="s">
-        <v>212</v>
-      </c>
-      <c r="D164" t="s">
-        <v>213</v>
-      </c>
-      <c r="E164" t="s">
-        <v>213</v>
-      </c>
-      <c r="F164" s="1">
-        <v>46170</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="15">
-      <c r="A165">
-        <v>2025</v>
       </c>
       <c r="B165" t="s">
         <v>211</v>
@@ -5061,21 +5064,21 @@
         <v>212</v>
       </c>
       <c r="D165" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E165" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F165" s="1">
-        <v>45862</v>
-      </c>
-      <c r="G165" t="s">
+        <v>46170</v>
+      </c>
+      <c r="G165" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15">
+    <row r="166" spans="1:7">
       <c r="A166">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B166" t="s">
         <v>211</v>
@@ -5090,15 +5093,15 @@
         <v>215</v>
       </c>
       <c r="F166" s="1">
-        <v>45497</v>
+        <v>45862</v>
       </c>
       <c r="G166" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15">
+    <row r="167" spans="1:7">
       <c r="A167">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B167" t="s">
         <v>211</v>
@@ -5113,38 +5116,38 @@
         <v>215</v>
       </c>
       <c r="F167" s="1">
-        <v>45131</v>
+        <v>45497</v>
       </c>
       <c r="G167" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15">
+    <row r="168" spans="1:7">
       <c r="A168">
+        <v>2023</v>
+      </c>
+      <c r="B168" t="s">
+        <v>211</v>
+      </c>
+      <c r="C168" t="s">
+        <v>212</v>
+      </c>
+      <c r="D168" t="s">
+        <v>215</v>
+      </c>
+      <c r="E168" t="s">
+        <v>215</v>
+      </c>
+      <c r="F168" s="1">
+        <v>45131</v>
+      </c>
+      <c r="G168" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169">
         <v>2026</v>
-      </c>
-      <c r="B168" t="s">
-        <v>216</v>
-      </c>
-      <c r="C168" t="s">
-        <v>217</v>
-      </c>
-      <c r="D168" t="s">
-        <v>218</v>
-      </c>
-      <c r="E168" t="s">
-        <v>218</v>
-      </c>
-      <c r="F168" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G168" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="15">
-      <c r="A169">
-        <v>2025</v>
       </c>
       <c r="B169" t="s">
         <v>216</v>
@@ -5159,15 +5162,15 @@
         <v>218</v>
       </c>
       <c r="F169" s="1">
-        <v>45819</v>
+        <v>46128</v>
       </c>
       <c r="G169" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15">
+    <row r="170" spans="1:7">
       <c r="A170">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B170" t="s">
         <v>216</v>
@@ -5182,15 +5185,15 @@
         <v>218</v>
       </c>
       <c r="F170" s="1">
-        <v>45454</v>
+        <v>45819</v>
       </c>
       <c r="G170" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15">
+    <row r="171" spans="1:7">
       <c r="A171">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B171" t="s">
         <v>216</v>
@@ -5205,38 +5208,38 @@
         <v>218</v>
       </c>
       <c r="F171" s="1">
-        <v>45088</v>
+        <v>45454</v>
       </c>
       <c r="G171" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15">
+    <row r="172" spans="1:7">
       <c r="A172">
+        <v>2023</v>
+      </c>
+      <c r="B172" t="s">
+        <v>216</v>
+      </c>
+      <c r="C172" t="s">
+        <v>217</v>
+      </c>
+      <c r="D172" t="s">
+        <v>218</v>
+      </c>
+      <c r="E172" t="s">
+        <v>218</v>
+      </c>
+      <c r="F172" s="1">
+        <v>45088</v>
+      </c>
+      <c r="G172" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173">
         <v>2026</v>
-      </c>
-      <c r="B172" t="s">
-        <v>220</v>
-      </c>
-      <c r="C172" t="s">
-        <v>221</v>
-      </c>
-      <c r="D172" t="s">
-        <v>222</v>
-      </c>
-      <c r="E172" t="s">
-        <v>222</v>
-      </c>
-      <c r="F172" s="1">
-        <v>46162</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="15">
-      <c r="A173">
-        <v>2025</v>
       </c>
       <c r="B173" t="s">
         <v>220</v>
@@ -5245,21 +5248,21 @@
         <v>221</v>
       </c>
       <c r="D173" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E173" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F173" s="1">
-        <v>45740</v>
-      </c>
-      <c r="G173" t="s">
+        <v>46162</v>
+      </c>
+      <c r="G173" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15">
+    <row r="174" spans="1:7">
       <c r="A174">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B174" t="s">
         <v>220</v>
@@ -5274,15 +5277,15 @@
         <v>224</v>
       </c>
       <c r="F174" s="1">
-        <v>45375</v>
+        <v>45740</v>
       </c>
       <c r="G174" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15">
+    <row r="175" spans="1:7">
       <c r="A175">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B175" t="s">
         <v>220</v>
@@ -5297,38 +5300,38 @@
         <v>224</v>
       </c>
       <c r="F175" s="1">
-        <v>45009</v>
+        <v>45375</v>
       </c>
       <c r="G175" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15">
+    <row r="176" spans="1:7">
       <c r="A176">
+        <v>2023</v>
+      </c>
+      <c r="B176" t="s">
+        <v>220</v>
+      </c>
+      <c r="C176" t="s">
+        <v>221</v>
+      </c>
+      <c r="D176" t="s">
+        <v>224</v>
+      </c>
+      <c r="E176" t="s">
+        <v>224</v>
+      </c>
+      <c r="F176" s="1">
+        <v>45009</v>
+      </c>
+      <c r="G176" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177">
         <v>2026</v>
-      </c>
-      <c r="B176" t="s">
-        <v>225</v>
-      </c>
-      <c r="C176" t="s">
-        <v>226</v>
-      </c>
-      <c r="D176" t="s">
-        <v>227</v>
-      </c>
-      <c r="E176" t="s">
-        <v>227</v>
-      </c>
-      <c r="F176" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G176" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="15">
-      <c r="A177">
-        <v>2025</v>
       </c>
       <c r="B177" t="s">
         <v>225</v>
@@ -5337,21 +5340,21 @@
         <v>226</v>
       </c>
       <c r="D177" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E177" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F177" s="1">
-        <v>45733</v>
+        <v>46125</v>
       </c>
       <c r="G177" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15">
+    <row r="178" spans="1:7">
       <c r="A178">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B178" t="s">
         <v>225</v>
@@ -5366,15 +5369,15 @@
         <v>229</v>
       </c>
       <c r="F178" s="1">
-        <v>45368</v>
+        <v>45733</v>
       </c>
       <c r="G178" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15">
+    <row r="179" spans="1:7">
       <c r="A179">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B179" t="s">
         <v>225</v>
@@ -5389,38 +5392,38 @@
         <v>229</v>
       </c>
       <c r="F179" s="1">
-        <v>45002</v>
+        <v>45368</v>
       </c>
       <c r="G179" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15">
+    <row r="180" spans="1:7">
       <c r="A180">
+        <v>2023</v>
+      </c>
+      <c r="B180" t="s">
+        <v>225</v>
+      </c>
+      <c r="C180" t="s">
+        <v>226</v>
+      </c>
+      <c r="D180" t="s">
+        <v>229</v>
+      </c>
+      <c r="E180" t="s">
+        <v>229</v>
+      </c>
+      <c r="F180" s="1">
+        <v>45002</v>
+      </c>
+      <c r="G180" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181">
         <v>2026</v>
-      </c>
-      <c r="B180" t="s">
-        <v>230</v>
-      </c>
-      <c r="C180" t="s">
-        <v>231</v>
-      </c>
-      <c r="D180" t="s">
-        <v>232</v>
-      </c>
-      <c r="E180" t="s">
-        <v>232</v>
-      </c>
-      <c r="F180" s="1">
-        <v>46121</v>
-      </c>
-      <c r="G180" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="15">
-      <c r="A181">
-        <v>2025</v>
       </c>
       <c r="B181" t="s">
         <v>230</v>
@@ -5429,21 +5432,21 @@
         <v>231</v>
       </c>
       <c r="D181" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E181" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F181" s="1">
-        <v>45713</v>
+        <v>46121</v>
       </c>
       <c r="G181" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15">
+    <row r="182" spans="1:7">
       <c r="A182">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B182" t="s">
         <v>230</v>
@@ -5458,15 +5461,15 @@
         <v>234</v>
       </c>
       <c r="F182" s="1">
-        <v>45347</v>
+        <v>45713</v>
       </c>
       <c r="G182" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15">
+    <row r="183" spans="1:7">
       <c r="A183">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B183" t="s">
         <v>230</v>
@@ -5481,38 +5484,38 @@
         <v>234</v>
       </c>
       <c r="F183" s="1">
-        <v>44982</v>
+        <v>45347</v>
       </c>
       <c r="G183" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15">
-      <c r="A184" s="10">
+    <row r="184" spans="1:7">
+      <c r="A184">
+        <v>2023</v>
+      </c>
+      <c r="B184" t="s">
+        <v>230</v>
+      </c>
+      <c r="C184" t="s">
+        <v>231</v>
+      </c>
+      <c r="D184" t="s">
+        <v>234</v>
+      </c>
+      <c r="E184" t="s">
+        <v>234</v>
+      </c>
+      <c r="F184" s="1">
+        <v>44982</v>
+      </c>
+      <c r="G184" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="15">
         <v>2025</v>
-      </c>
-      <c r="B184" t="s">
-        <v>235</v>
-      </c>
-      <c r="C184" t="s">
-        <v>236</v>
-      </c>
-      <c r="D184" t="s">
-        <v>237</v>
-      </c>
-      <c r="E184" t="s">
-        <v>237</v>
-      </c>
-      <c r="F184" s="1">
-        <v>45821</v>
-      </c>
-      <c r="G184" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="15">
-      <c r="A185">
-        <v>2024</v>
       </c>
       <c r="B185" t="s">
         <v>235</v>
@@ -5527,15 +5530,15 @@
         <v>237</v>
       </c>
       <c r="F185" s="1">
-        <v>45456</v>
+        <v>45821</v>
       </c>
       <c r="G185" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15">
+    <row r="186" spans="1:7">
       <c r="A186">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B186" t="s">
         <v>235</v>
@@ -5550,38 +5553,38 @@
         <v>237</v>
       </c>
       <c r="F186" s="1">
-        <v>45090</v>
+        <v>45456</v>
       </c>
       <c r="G186" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15">
+    <row r="187" spans="1:7">
       <c r="A187">
+        <v>2023</v>
+      </c>
+      <c r="B187" t="s">
+        <v>235</v>
+      </c>
+      <c r="C187" t="s">
+        <v>236</v>
+      </c>
+      <c r="D187" t="s">
+        <v>237</v>
+      </c>
+      <c r="E187" t="s">
+        <v>237</v>
+      </c>
+      <c r="F187" s="1">
+        <v>45090</v>
+      </c>
+      <c r="G187" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188">
         <v>2026</v>
-      </c>
-      <c r="B187" t="s">
-        <v>239</v>
-      </c>
-      <c r="C187" t="s">
-        <v>240</v>
-      </c>
-      <c r="D187" t="s">
-        <v>241</v>
-      </c>
-      <c r="E187" t="s">
-        <v>241</v>
-      </c>
-      <c r="F187" s="1">
-        <v>46170</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="15">
-      <c r="A188">
-        <v>2025</v>
       </c>
       <c r="B188" t="s">
         <v>239</v>
@@ -5596,15 +5599,15 @@
         <v>241</v>
       </c>
       <c r="F188" s="1">
-        <v>45805</v>
-      </c>
-      <c r="G188" t="s">
+        <v>46170</v>
+      </c>
+      <c r="G188" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15">
+    <row r="189" spans="1:7">
       <c r="A189">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B189" t="s">
         <v>239</v>
@@ -5619,15 +5622,15 @@
         <v>241</v>
       </c>
       <c r="F189" s="1">
-        <v>45440</v>
+        <v>45805</v>
       </c>
       <c r="G189" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15">
+    <row r="190" spans="1:7">
       <c r="A190">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B190" t="s">
         <v>239</v>
@@ -5642,61 +5645,61 @@
         <v>241</v>
       </c>
       <c r="F190" s="1">
-        <v>45074</v>
+        <v>45440</v>
       </c>
       <c r="G190" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15">
+    <row r="191" spans="1:7">
       <c r="A191">
+        <v>2023</v>
+      </c>
+      <c r="B191" t="s">
+        <v>239</v>
+      </c>
+      <c r="C191" t="s">
+        <v>240</v>
+      </c>
+      <c r="D191" t="s">
+        <v>241</v>
+      </c>
+      <c r="E191" t="s">
+        <v>241</v>
+      </c>
+      <c r="F191" s="1">
+        <v>45074</v>
+      </c>
+      <c r="G191" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192">
         <v>2026</v>
       </c>
-      <c r="B191" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="C191" t="s">
-        <v>244</v>
-      </c>
-      <c r="D191" t="s">
-        <v>227</v>
-      </c>
-      <c r="E191" t="s">
-        <v>227</v>
-      </c>
-      <c r="F191" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G191" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="15">
-      <c r="A192">
-        <v>2025</v>
-      </c>
-      <c r="B192" t="s">
+      <c r="B192" s="9" t="s">
         <v>243</v>
       </c>
       <c r="C192" t="s">
         <v>244</v>
       </c>
       <c r="D192" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E192" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="F192" s="1">
-        <v>45748</v>
+        <v>46125</v>
       </c>
       <c r="G192" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15">
+    <row r="193" spans="1:7">
       <c r="A193">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B193" t="s">
         <v>243</v>
@@ -5711,15 +5714,15 @@
         <v>246</v>
       </c>
       <c r="F193" s="1">
-        <v>45383</v>
+        <v>45748</v>
       </c>
       <c r="G193" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15">
+    <row r="194" spans="1:7">
       <c r="A194">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B194" t="s">
         <v>243</v>
@@ -5734,38 +5737,38 @@
         <v>246</v>
       </c>
       <c r="F194" s="1">
-        <v>45017</v>
+        <v>45383</v>
       </c>
       <c r="G194" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15">
+    <row r="195" spans="1:7">
       <c r="A195">
+        <v>2023</v>
+      </c>
+      <c r="B195" t="s">
+        <v>243</v>
+      </c>
+      <c r="C195" t="s">
+        <v>244</v>
+      </c>
+      <c r="D195" t="s">
+        <v>246</v>
+      </c>
+      <c r="E195" t="s">
+        <v>246</v>
+      </c>
+      <c r="F195" s="1">
+        <v>45017</v>
+      </c>
+      <c r="G195" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196">
         <v>2026</v>
-      </c>
-      <c r="B195" t="s">
-        <v>247</v>
-      </c>
-      <c r="C195" t="s">
-        <v>248</v>
-      </c>
-      <c r="D195" t="s">
-        <v>249</v>
-      </c>
-      <c r="E195" t="s">
-        <v>249</v>
-      </c>
-      <c r="F195" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G195" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="15">
-      <c r="A196">
-        <v>2025</v>
       </c>
       <c r="B196" t="s">
         <v>247</v>
@@ -5774,21 +5777,21 @@
         <v>248</v>
       </c>
       <c r="D196" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E196" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F196" s="1">
-        <v>45744</v>
+        <v>46128</v>
       </c>
       <c r="G196" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="15">
+    <row r="197" spans="1:7">
       <c r="A197">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B197" t="s">
         <v>247</v>
@@ -5803,15 +5806,15 @@
         <v>251</v>
       </c>
       <c r="F197" s="1">
-        <v>45379</v>
+        <v>45744</v>
       </c>
       <c r="G197" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="15">
+    <row r="198" spans="1:7">
       <c r="A198">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B198" t="s">
         <v>247</v>
@@ -5826,35 +5829,38 @@
         <v>251</v>
       </c>
       <c r="F198" s="1">
-        <v>45013</v>
+        <v>45379</v>
       </c>
       <c r="G198" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15">
+    <row r="199" spans="1:7">
       <c r="A199">
+        <v>2023</v>
+      </c>
+      <c r="B199" t="s">
+        <v>247</v>
+      </c>
+      <c r="C199" t="s">
+        <v>248</v>
+      </c>
+      <c r="D199" t="s">
+        <v>251</v>
+      </c>
+      <c r="E199" t="s">
+        <v>251</v>
+      </c>
+      <c r="F199" s="1">
+        <v>45013</v>
+      </c>
+      <c r="G199" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200">
         <v>2026</v>
-      </c>
-      <c r="B199" t="s">
-        <v>252</v>
-      </c>
-      <c r="C199" t="s">
-        <v>253</v>
-      </c>
-      <c r="D199" t="s">
-        <v>254</v>
-      </c>
-      <c r="F199" s="1">
-        <v>46122</v>
-      </c>
-      <c r="G199" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="15">
-      <c r="A200">
-        <v>2025</v>
       </c>
       <c r="B200" t="s">
         <v>252</v>
@@ -5863,21 +5869,18 @@
         <v>253</v>
       </c>
       <c r="D200" t="s">
-        <v>256</v>
-      </c>
-      <c r="E200" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F200" s="1">
-        <v>45737</v>
+        <v>46122</v>
       </c>
       <c r="G200" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="15">
+    <row r="201" spans="1:7">
       <c r="A201">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B201" t="s">
         <v>252</v>
@@ -5892,15 +5895,15 @@
         <v>256</v>
       </c>
       <c r="F201" s="1">
-        <v>45372</v>
+        <v>45737</v>
       </c>
       <c r="G201" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15">
+    <row r="202" spans="1:7">
       <c r="A202">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B202" t="s">
         <v>252</v>
@@ -5915,70 +5918,93 @@
         <v>256</v>
       </c>
       <c r="F202" s="1">
-        <v>45006</v>
+        <v>45372</v>
       </c>
       <c r="G202" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="251" spans="11:11">
-      <c r="K251" s="1"/>
+    <row r="203" spans="1:7">
+      <c r="A203">
+        <v>2023</v>
+      </c>
+      <c r="B203" t="s">
+        <v>252</v>
+      </c>
+      <c r="C203" t="s">
+        <v>253</v>
+      </c>
+      <c r="D203" t="s">
+        <v>256</v>
+      </c>
+      <c r="E203" t="s">
+        <v>256</v>
+      </c>
+      <c r="F203" s="1">
+        <v>45006</v>
+      </c>
+      <c r="G203" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="11:11">
+      <c r="K252" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G202" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G202">
+  <autoFilter ref="A1:G203">
+    <sortState ref="A2:G202">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G43" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G45" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G46" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G44" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G18" r:id="rId5" xr:uid="{3F701E59-5D29-4E9C-8705-ECF744F7C80B}"/>
-    <hyperlink ref="G23" r:id="rId6" xr:uid="{F86867FF-E0A1-4B23-8E20-1EE5F172C1F2}"/>
-    <hyperlink ref="G31" r:id="rId7" xr:uid="{7B92F4FE-45A5-4FC3-BEF6-89060A75A0CF}"/>
-    <hyperlink ref="G35" r:id="rId8" xr:uid="{44483B5F-1D9D-4382-A3BB-08CC848203BB}"/>
-    <hyperlink ref="G39" r:id="rId9" xr:uid="{80C8F108-86E1-4547-810D-49EE9748B088}"/>
-    <hyperlink ref="G47" r:id="rId10" xr:uid="{44A2B85F-2D5D-4501-BD0D-1A1075EEBD87}"/>
-    <hyperlink ref="G50" r:id="rId11" xr:uid="{974F12BA-311E-4775-9C79-6B2367EE4C00}"/>
-    <hyperlink ref="G54" r:id="rId12" xr:uid="{9FD43934-382B-448D-9E13-39FD5028C9E3}"/>
-    <hyperlink ref="G58" r:id="rId13" xr:uid="{F5EC8224-9440-476C-B04B-BCD61BFD11DD}"/>
-    <hyperlink ref="G62" r:id="rId14" xr:uid="{6715A407-CEDE-4462-83D2-BA6A21538E94}"/>
-    <hyperlink ref="G66" r:id="rId15" xr:uid="{8C180C1D-CF21-400B-8B35-ACDD613A2648}"/>
-    <hyperlink ref="G74" r:id="rId16" xr:uid="{E80524B7-0871-4464-985C-CA93DB159F96}"/>
-    <hyperlink ref="E74" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto" xr:uid="{44E53C8F-307F-4558-8C5E-5645D7067E09}"/>
-    <hyperlink ref="G78" r:id="rId18" xr:uid="{BB1A3C55-886C-4149-9192-8222A522CCA0}"/>
-    <hyperlink ref="G93" r:id="rId19" location="informacoes-classificadas-e-desclassificadas" xr:uid="{F06BDAE5-9ADF-4DA7-920D-01903454D462}"/>
-    <hyperlink ref="G110" r:id="rId20" xr:uid="{CD1703C5-F786-4C99-88D4-BEA8E70C4138}"/>
-    <hyperlink ref="G109" r:id="rId21" xr:uid="{C77BD8BE-59BD-4BD4-9FAB-2123370B5889}"/>
-    <hyperlink ref="G105" r:id="rId22" xr:uid="{9388516A-40C8-4110-A15B-D0B6EE32A150}"/>
-    <hyperlink ref="G116" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{3301EBB6-9A25-48B2-9D8C-70083F27B1EA}"/>
-    <hyperlink ref="G120" r:id="rId24" location="informacoes-classificadas-e-desclassificadas" xr:uid="{7434A183-8C1E-4E4A-8E52-8EF290090E88}"/>
-    <hyperlink ref="G128" r:id="rId25" xr:uid="{4A3115E8-4CE5-4DFF-BF8C-76F55E18523A}"/>
-    <hyperlink ref="G136" r:id="rId26" xr:uid="{E28EBD52-B071-49FC-B6F4-D7C185EC3BD1}"/>
-    <hyperlink ref="G140" r:id="rId27" xr:uid="{995FBC4C-1A02-4126-AA25-76E795A0EB48}"/>
-    <hyperlink ref="G144" r:id="rId28" xr:uid="{80237B8F-DF43-47F0-80AC-616D77A1082D}"/>
-    <hyperlink ref="G156" r:id="rId29" xr:uid="{6AC60654-C774-4732-B0F1-240E2D6C4490}"/>
-    <hyperlink ref="G160" r:id="rId30" xr:uid="{AAF4FD60-6234-4214-BA5D-07ACABA79556}"/>
-    <hyperlink ref="G168" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas" xr:uid="{6EF2BF0D-AFAC-4C21-81A1-0D63CF1FEEE4}"/>
-    <hyperlink ref="G176" r:id="rId32" xr:uid="{81356907-EB5D-4FC6-90E5-4BC94C925F5E}"/>
-    <hyperlink ref="G191" r:id="rId33" xr:uid="{89F50D9C-749D-4ED1-B9C3-FA541C5DBEA0}"/>
-    <hyperlink ref="G195" r:id="rId34" location="info-class-des" xr:uid="{9E908A83-E592-48E3-A960-E01C6B504A9F}"/>
-    <hyperlink ref="G199" r:id="rId35" xr:uid="{6ACD1A2A-A2ED-4326-AB6D-AC1CAEB49DD3}"/>
-    <hyperlink ref="G89" r:id="rId36" xr:uid="{E8F08860-DEED-4B1D-A48C-6C1359300175}"/>
-    <hyperlink ref="G101" r:id="rId37" xr:uid="{0E98023C-AB1F-4285-BFD2-EFD188CCDF4C}"/>
-    <hyperlink ref="G180" r:id="rId38" xr:uid="{9F2C91F1-3B9F-4B72-A797-85FFBDD348E1}"/>
-    <hyperlink ref="G14" r:id="rId39" xr:uid="{3841C1FD-CD06-45B5-9491-60778AF8477D}"/>
-    <hyperlink ref="G152" r:id="rId40" xr:uid="{50E2C31A-C16A-4D5A-AC7B-F44D64FFCDE4}"/>
-    <hyperlink ref="G70" r:id="rId41" xr:uid="{412A2619-2166-4F75-B6DF-857DB3022D0B}"/>
-    <hyperlink ref="G27" r:id="rId42" xr:uid="{CFD576E9-D051-4785-9895-0E307BF07A08}"/>
-    <hyperlink ref="G132" r:id="rId43" xr:uid="{10B23B64-B59B-4B30-BA79-B99439662FFE}"/>
-    <hyperlink ref="G172" r:id="rId44" xr:uid="{27BD0F6F-7EC5-4457-BF58-174C23DCA541}"/>
-    <hyperlink ref="G148" r:id="rId45" xr:uid="{A44713B8-367B-4042-8C89-E38A146C20FF}"/>
-    <hyperlink ref="G19" r:id="rId46" xr:uid="{CEFC8C9F-1526-42F4-87B8-14AC13D05E87}"/>
-    <hyperlink ref="G187" r:id="rId47" xr:uid="{7DF0A33C-D34B-4B22-B997-A95185545180}"/>
-    <hyperlink ref="G164" r:id="rId48" xr:uid="{E197C950-CA23-4E94-BD2B-35727B2E87CC}"/>
+    <hyperlink ref="G43" r:id="rId1"/>
+    <hyperlink ref="G45" r:id="rId2"/>
+    <hyperlink ref="G46" r:id="rId3"/>
+    <hyperlink ref="G44" r:id="rId4"/>
+    <hyperlink ref="G18" r:id="rId5"/>
+    <hyperlink ref="G23" r:id="rId6"/>
+    <hyperlink ref="G31" r:id="rId7"/>
+    <hyperlink ref="G35" r:id="rId8"/>
+    <hyperlink ref="G39" r:id="rId9"/>
+    <hyperlink ref="G47" r:id="rId10"/>
+    <hyperlink ref="G51" r:id="rId11"/>
+    <hyperlink ref="G55" r:id="rId12"/>
+    <hyperlink ref="G59" r:id="rId13"/>
+    <hyperlink ref="G63" r:id="rId14"/>
+    <hyperlink ref="G67" r:id="rId15"/>
+    <hyperlink ref="G75" r:id="rId16"/>
+    <hyperlink ref="E75" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto"/>
+    <hyperlink ref="G79" r:id="rId18"/>
+    <hyperlink ref="G94" r:id="rId19" location="informacoes-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G111" r:id="rId20"/>
+    <hyperlink ref="G110" r:id="rId21"/>
+    <hyperlink ref="G106" r:id="rId22"/>
+    <hyperlink ref="G117" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G121" r:id="rId24" location="informacoes-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G129" r:id="rId25"/>
+    <hyperlink ref="G137" r:id="rId26"/>
+    <hyperlink ref="G141" r:id="rId27"/>
+    <hyperlink ref="G145" r:id="rId28"/>
+    <hyperlink ref="G157" r:id="rId29"/>
+    <hyperlink ref="G161" r:id="rId30"/>
+    <hyperlink ref="G169" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G177" r:id="rId32"/>
+    <hyperlink ref="G192" r:id="rId33"/>
+    <hyperlink ref="G196" r:id="rId34" location="info-class-des"/>
+    <hyperlink ref="G200" r:id="rId35"/>
+    <hyperlink ref="G90" r:id="rId36"/>
+    <hyperlink ref="G102" r:id="rId37"/>
+    <hyperlink ref="G181" r:id="rId38"/>
+    <hyperlink ref="G14" r:id="rId39"/>
+    <hyperlink ref="G153" r:id="rId40"/>
+    <hyperlink ref="G71" r:id="rId41"/>
+    <hyperlink ref="G27" r:id="rId42"/>
+    <hyperlink ref="G133" r:id="rId43"/>
+    <hyperlink ref="G173" r:id="rId44"/>
+    <hyperlink ref="G149" r:id="rId45"/>
+    <hyperlink ref="G19" r:id="rId46"/>
+    <hyperlink ref="G188" r:id="rId47"/>
+    <hyperlink ref="G165" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/orgao_sem_informacoes_classificadas.xlsx
+++ b/upload/orgao_sem_informacoes_classificadas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="253">
   <si>
     <t>ano</t>
   </si>
@@ -223,18 +223,6 @@
     <t>https://privacidade.cemig.com.br/a-lai/</t>
   </si>
   <si>
-    <t>Corpo de Bombeiros Militar do Estado de Minas Gerais - CBMMG</t>
-  </si>
-  <si>
-    <t>CBMMG</t>
-  </si>
-  <si>
-    <t>Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, o Corpo de Bombeiros Militar de Minas Gerais informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto</t>
-  </si>
-  <si>
-    <t>https://www.bombeiros.mg.gov.br/informacoes-classificadas-e-desclassificadas</t>
-  </si>
-  <si>
     <t>Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER</t>
   </si>
   <si>
@@ -532,10 +520,10 @@
     <t>O Instituto Mineiro de Gestão das Águas - Igam não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta</t>
   </si>
   <si>
+    <t>https://igam.mg.gov.br/informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
+  </si>
+  <si>
     <t>O IGAM não possui informações classificadas ou desclassificadas nos graus de sigilo reservada, secreta e ultrassecreta, definidos no art. 23 da Lei Federal nº 12.527/11 (Lei de Acesso à Informação)</t>
-  </si>
-  <si>
-    <t>https://igam.mg.gov.br/informa%C3%A7%C3%B5es-classificadas-e-desclassificadas</t>
   </si>
   <si>
     <t>Junta Comercial do Estado de Minas Gerais - JUCEMG</t>
@@ -914,23 +902,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -939,11 +925,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Hyperlink" xfId="2"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1276,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K252"/>
+  <dimension ref="A1:K247"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="92" bestFit="1" customWidth="1"/>
@@ -1719,7 +1703,7 @@
       <c r="F19" s="1">
         <v>46112</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1811,7 +1795,7 @@
       <c r="F23" s="1">
         <v>46127</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1995,7 +1979,7 @@
       <c r="F31" s="1">
         <v>46099</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2022,7 +2006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>2024</v>
       </c>
@@ -2045,7 +2029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>2023</v>
       </c>
@@ -2068,7 +2052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>2026</v>
       </c>
@@ -2081,17 +2065,17 @@
       <c r="D35" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F35" s="1">
         <v>46128</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>2025</v>
       </c>
@@ -2114,7 +2098,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>2024</v>
       </c>
@@ -2137,7 +2121,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>2023</v>
       </c>
@@ -2160,7 +2144,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:9">
       <c r="A39">
         <v>2026</v>
       </c>
@@ -2179,11 +2163,11 @@
       <c r="F39" s="1">
         <v>46120</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:9">
       <c r="A40">
         <v>2025</v>
       </c>
@@ -2206,7 +2190,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:9">
       <c r="A41">
         <v>2024</v>
       </c>
@@ -2229,7 +2213,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:9">
       <c r="A42">
         <v>2023</v>
       </c>
@@ -2252,7 +2236,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:9" ht="15">
       <c r="A43">
         <v>2026</v>
       </c>
@@ -2265,19 +2249,19 @@
       <c r="D43" t="s">
         <v>63</v>
       </c>
-      <c r="E43" t="s">
-        <v>63</v>
+      <c r="E43" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="F43" s="1">
-        <v>46073</v>
+        <v>46135</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B44" t="s">
         <v>61</v>
@@ -2286,21 +2270,21 @@
         <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F44" s="1">
-        <v>45708</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>45657</v>
+      </c>
+      <c r="G44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B45" t="s">
         <v>61</v>
@@ -2309,226 +2293,226 @@
         <v>62</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E45" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F45" s="1">
-        <v>45342</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>45291</v>
+      </c>
+      <c r="G45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="1">
+        <v>46140</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" t="s">
+        <v>71</v>
+      </c>
+      <c r="F47" s="1">
+        <v>45883</v>
+      </c>
+      <c r="G47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48">
+        <v>2024</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" s="1">
+        <v>45518</v>
+      </c>
+      <c r="G48" t="s">
+        <v>70</v>
+      </c>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
         <v>2023</v>
       </c>
-      <c r="B46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" t="s">
-        <v>63</v>
-      </c>
-      <c r="F46" s="1">
-        <v>44977</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15">
-      <c r="A47">
+      <c r="B49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s">
+        <v>71</v>
+      </c>
+      <c r="F49" s="1">
+        <v>45152</v>
+      </c>
+      <c r="G49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
         <v>2026</v>
       </c>
-      <c r="B47" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F47" s="1">
-        <v>46135</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46082</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
         <v>2025</v>
       </c>
-      <c r="B48" t="s">
-        <v>65</v>
-      </c>
-      <c r="C48" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" t="s">
-        <v>70</v>
-      </c>
-      <c r="F48" s="1">
-        <v>46022</v>
-      </c>
-      <c r="G48" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49">
+      <c r="B51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="1">
+        <v>45717</v>
+      </c>
+      <c r="G51" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
         <v>2024</v>
       </c>
-      <c r="B49" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" t="s">
-        <v>66</v>
-      </c>
-      <c r="D49" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" t="s">
-        <v>70</v>
-      </c>
-      <c r="F49" s="1">
-        <v>45657</v>
-      </c>
-      <c r="G49" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50">
+      <c r="B52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" t="s">
+        <v>74</v>
+      </c>
+      <c r="E52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" s="1">
+        <v>45352</v>
+      </c>
+      <c r="G52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
         <v>2023</v>
       </c>
-      <c r="B50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" t="s">
-        <v>66</v>
-      </c>
-      <c r="D50" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F50" s="1">
-        <v>45291</v>
-      </c>
-      <c r="G50" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51">
+      <c r="B53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F53" s="1">
+        <v>44986</v>
+      </c>
+      <c r="G53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
         <v>2026</v>
       </c>
-      <c r="B51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" t="s">
-        <v>72</v>
-      </c>
-      <c r="D51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F51" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52">
+      <c r="B54" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" t="s">
+        <v>77</v>
+      </c>
+      <c r="D54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
         <v>2025</v>
-      </c>
-      <c r="B52" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" t="s">
-        <v>75</v>
-      </c>
-      <c r="F52" s="1">
-        <v>45883</v>
-      </c>
-      <c r="G52" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53">
-        <v>2024</v>
-      </c>
-      <c r="B53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D53" t="s">
-        <v>75</v>
-      </c>
-      <c r="E53" t="s">
-        <v>75</v>
-      </c>
-      <c r="F53" s="1">
-        <v>45518</v>
-      </c>
-      <c r="G53" t="s">
-        <v>74</v>
-      </c>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54">
-        <v>2023</v>
-      </c>
-      <c r="B54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C54" t="s">
-        <v>72</v>
-      </c>
-      <c r="D54" t="s">
-        <v>75</v>
-      </c>
-      <c r="E54" t="s">
-        <v>75</v>
-      </c>
-      <c r="F54" s="1">
-        <v>45152</v>
-      </c>
-      <c r="G54" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55">
-        <v>2026</v>
       </c>
       <c r="B55" t="s">
         <v>76</v>
@@ -2537,21 +2521,21 @@
         <v>77</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E55" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F55" s="1">
-        <v>46082</v>
-      </c>
-      <c r="G55" s="6" t="s">
+        <v>45742</v>
+      </c>
+      <c r="G55" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:7">
       <c r="A56">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B56" t="s">
         <v>76</v>
@@ -2560,21 +2544,21 @@
         <v>77</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F56" s="1">
-        <v>45717</v>
+        <v>45377</v>
       </c>
       <c r="G56" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:7">
       <c r="A57">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B57" t="s">
         <v>76</v>
@@ -2583,266 +2567,266 @@
         <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F57" s="1">
-        <v>45352</v>
+        <v>45011</v>
       </c>
       <c r="G57" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:7">
       <c r="A58">
+        <v>2026</v>
+      </c>
+      <c r="B58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" t="s">
+        <v>83</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46120</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>2025</v>
+      </c>
+      <c r="B59" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" s="1">
+        <v>45792</v>
+      </c>
+      <c r="G59" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>2024</v>
+      </c>
+      <c r="B60" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" s="1">
+        <v>45427</v>
+      </c>
+      <c r="G60" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
         <v>2023</v>
       </c>
-      <c r="B58" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" t="s">
-        <v>77</v>
-      </c>
-      <c r="D58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" t="s">
-        <v>78</v>
-      </c>
-      <c r="F58" s="1">
-        <v>44986</v>
-      </c>
-      <c r="G58" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59">
+      <c r="B61" t="s">
+        <v>81</v>
+      </c>
+      <c r="C61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" t="s">
+        <v>85</v>
+      </c>
+      <c r="F61" s="1">
+        <v>45061</v>
+      </c>
+      <c r="G61" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
         <v>2026</v>
       </c>
-      <c r="B59" t="s">
-        <v>80</v>
-      </c>
-      <c r="C59" t="s">
-        <v>81</v>
-      </c>
-      <c r="D59" t="s">
-        <v>82</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F59" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60">
+      <c r="B62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46140</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
         <v>2025</v>
       </c>
-      <c r="B60" t="s">
-        <v>80</v>
-      </c>
-      <c r="C60" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" t="s">
-        <v>84</v>
-      </c>
-      <c r="E60" t="s">
-        <v>84</v>
-      </c>
-      <c r="F60" s="1">
-        <v>45742</v>
-      </c>
-      <c r="G60" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61">
+      <c r="B63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="1">
+        <v>45730</v>
+      </c>
+      <c r="G63" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
         <v>2024</v>
       </c>
-      <c r="B61" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D61" t="s">
-        <v>84</v>
-      </c>
-      <c r="E61" t="s">
-        <v>84</v>
-      </c>
-      <c r="F61" s="1">
-        <v>45377</v>
-      </c>
-      <c r="G61" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62">
-        <v>2023</v>
-      </c>
-      <c r="B62" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" t="s">
-        <v>81</v>
-      </c>
-      <c r="D62" t="s">
-        <v>84</v>
-      </c>
-      <c r="E62" t="s">
-        <v>84</v>
-      </c>
-      <c r="F62" s="1">
-        <v>45011</v>
-      </c>
-      <c r="G62" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63">
-        <v>2026</v>
-      </c>
-      <c r="B63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="B64" t="s">
         <v>86</v>
       </c>
-      <c r="D63" t="s">
+      <c r="C64" t="s">
         <v>87</v>
       </c>
-      <c r="E63" t="s">
-        <v>87</v>
-      </c>
-      <c r="F63" s="1">
-        <v>46120</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64">
-        <v>2025</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>86</v>
-      </c>
       <c r="D64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F64" s="1">
-        <v>45792</v>
+        <v>45365</v>
       </c>
       <c r="G64" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F65" s="1">
-        <v>45427</v>
+        <v>44999</v>
       </c>
       <c r="G65" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D66" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E66" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F66" s="1">
-        <v>45061</v>
-      </c>
-      <c r="G66" t="s">
-        <v>88</v>
+        <v>46161</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E67" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F67" s="1">
-        <v>46140</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>93</v>
+        <v>45756</v>
+      </c>
+      <c r="G67" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E68" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F68" s="1">
-        <v>45730</v>
+        <v>45391</v>
       </c>
       <c r="G68" t="s">
         <v>95</v>
@@ -2850,22 +2834,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D69" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F69" s="1">
-        <v>45365</v>
+        <v>45025</v>
       </c>
       <c r="G69" t="s">
         <v>95</v>
@@ -2873,160 +2857,160 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B70" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D70" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E70" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F70" s="1">
-        <v>44999</v>
-      </c>
-      <c r="G70" t="s">
-        <v>95</v>
+        <v>46128</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D71" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E71" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F71" s="1">
-        <v>46161</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>99</v>
+        <v>45820</v>
+      </c>
+      <c r="G71" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D72" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E72" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F72" s="1">
-        <v>45756</v>
+        <v>45455</v>
       </c>
       <c r="G72" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C73" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E73" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F73" s="1">
-        <v>45391</v>
+        <v>45089</v>
       </c>
       <c r="G73" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D74" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E74" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F74" s="1">
-        <v>45025</v>
-      </c>
-      <c r="G74" t="s">
-        <v>99</v>
+        <v>46142</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B75" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C75" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E75" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F75" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>105</v>
+        <v>45813</v>
+      </c>
+      <c r="G75" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F76" s="1">
-        <v>45820</v>
+        <v>45448</v>
       </c>
       <c r="G76" t="s">
         <v>107</v>
@@ -3034,145 +3018,145 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F77" s="1">
-        <v>45455</v>
+        <v>45082</v>
       </c>
       <c r="G77" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78">
-        <v>2023</v>
+      <c r="A78" s="10">
+        <v>2025</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E78" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F78" s="1">
-        <v>45089</v>
+        <v>45730</v>
       </c>
       <c r="G78" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D79" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E79" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F79" s="1">
-        <v>46142</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>111</v>
+        <v>45365</v>
+      </c>
+      <c r="G79" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
+        <v>2023</v>
+      </c>
+      <c r="B80" t="s">
+        <v>109</v>
+      </c>
+      <c r="C80" t="s">
+        <v>110</v>
+      </c>
+      <c r="D80" t="s">
+        <v>111</v>
+      </c>
+      <c r="E80" t="s">
+        <v>111</v>
+      </c>
+      <c r="F80" s="1">
+        <v>44999</v>
+      </c>
+      <c r="G80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="13">
+        <v>2026</v>
+      </c>
+      <c r="B81" t="s">
+        <v>113</v>
+      </c>
+      <c r="C81" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" t="s">
+        <v>115</v>
+      </c>
+      <c r="E81" t="s">
+        <v>115</v>
+      </c>
+      <c r="F81" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="13">
         <v>2025</v>
       </c>
-      <c r="B80" t="s">
-        <v>108</v>
-      </c>
-      <c r="C80" t="s">
-        <v>109</v>
-      </c>
-      <c r="D80" t="s">
-        <v>112</v>
-      </c>
-      <c r="E80" t="s">
-        <v>112</v>
-      </c>
-      <c r="F80" s="1">
-        <v>45813</v>
-      </c>
-      <c r="G80" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81">
+      <c r="B82" t="s">
+        <v>113</v>
+      </c>
+      <c r="C82" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" s="1">
+        <v>45736</v>
+      </c>
+      <c r="G82" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83">
         <v>2024</v>
-      </c>
-      <c r="B81" t="s">
-        <v>108</v>
-      </c>
-      <c r="C81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D81" t="s">
-        <v>112</v>
-      </c>
-      <c r="E81" t="s">
-        <v>112</v>
-      </c>
-      <c r="F81" s="1">
-        <v>45448</v>
-      </c>
-      <c r="G81" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82">
-        <v>2023</v>
-      </c>
-      <c r="B82" t="s">
-        <v>108</v>
-      </c>
-      <c r="C82" t="s">
-        <v>109</v>
-      </c>
-      <c r="D82" t="s">
-        <v>112</v>
-      </c>
-      <c r="E82" t="s">
-        <v>112</v>
-      </c>
-      <c r="F82" s="1">
-        <v>45082</v>
-      </c>
-      <c r="G82" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="11">
-        <v>2025</v>
       </c>
       <c r="B83" t="s">
         <v>113</v>
@@ -3187,7 +3171,7 @@
         <v>115</v>
       </c>
       <c r="F83" s="1">
-        <v>45730</v>
+        <v>45371</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3195,7 +3179,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B84" t="s">
         <v>113</v>
@@ -3210,7 +3194,7 @@
         <v>115</v>
       </c>
       <c r="F84" s="1">
-        <v>45365</v>
+        <v>45005</v>
       </c>
       <c r="G84" t="s">
         <v>116</v>
@@ -3218,30 +3202,27 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B85" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C85" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
-        <v>115</v>
-      </c>
-      <c r="E85" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F85" s="1">
-        <v>44999</v>
-      </c>
-      <c r="G85" t="s">
-        <v>116</v>
+        <v>46128</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="14">
-        <v>2026</v>
+      <c r="A86">
+        <v>2025</v>
       </c>
       <c r="B86" t="s">
         <v>117</v>
@@ -3250,21 +3231,21 @@
         <v>118</v>
       </c>
       <c r="D86" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E86" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F86" s="1">
-        <v>46168</v>
+        <v>45838</v>
       </c>
       <c r="G86" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="14">
-        <v>2025</v>
+      <c r="A87">
+        <v>2024</v>
       </c>
       <c r="B87" t="s">
         <v>117</v>
@@ -3273,13 +3254,13 @@
         <v>118</v>
       </c>
       <c r="D87" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E87" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F87" s="1">
-        <v>45736</v>
+        <v>45473</v>
       </c>
       <c r="G87" t="s">
         <v>120</v>
@@ -3287,7 +3268,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B88" t="s">
         <v>117</v>
@@ -3296,13 +3277,13 @@
         <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E88" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F88" s="1">
-        <v>45371</v>
+        <v>45107</v>
       </c>
       <c r="G88" t="s">
         <v>120</v>
@@ -3310,119 +3291,122 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B89" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D89" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E89" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F89" s="1">
-        <v>45005</v>
-      </c>
-      <c r="G89" t="s">
-        <v>120</v>
+        <v>46126</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B90" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="E90" t="s">
+        <v>124</v>
       </c>
       <c r="F90" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>124</v>
+        <v>45742</v>
+      </c>
+      <c r="G90" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B91" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D91" t="s">
+        <v>124</v>
+      </c>
+      <c r="E91" t="s">
+        <v>124</v>
+      </c>
+      <c r="F91" s="1">
+        <v>45377</v>
+      </c>
+      <c r="G91" t="s">
         <v>125</v>
-      </c>
-      <c r="E91" t="s">
-        <v>125</v>
-      </c>
-      <c r="F91" s="1">
-        <v>45838</v>
-      </c>
-      <c r="G91" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B92" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D92" t="s">
+        <v>124</v>
+      </c>
+      <c r="E92" t="s">
+        <v>124</v>
+      </c>
+      <c r="F92" s="1">
+        <v>45011</v>
+      </c>
+      <c r="G92" t="s">
         <v>125</v>
-      </c>
-      <c r="E92" t="s">
-        <v>125</v>
-      </c>
-      <c r="F92" s="1">
-        <v>45473</v>
-      </c>
-      <c r="G92" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B93" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E93" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F93" s="1">
-        <v>45107</v>
+        <v>46127</v>
       </c>
       <c r="G93" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B94" t="s">
         <v>126</v>
@@ -3437,15 +3421,15 @@
         <v>128</v>
       </c>
       <c r="F94" s="1">
-        <v>46126</v>
-      </c>
-      <c r="G94" s="3" t="s">
+        <v>45808</v>
+      </c>
+      <c r="G94" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B95" t="s">
         <v>126</v>
@@ -3460,7 +3444,7 @@
         <v>128</v>
       </c>
       <c r="F95" s="1">
-        <v>45742</v>
+        <v>45443</v>
       </c>
       <c r="G95" t="s">
         <v>129</v>
@@ -3468,7 +3452,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B96" t="s">
         <v>126</v>
@@ -3483,7 +3467,7 @@
         <v>128</v>
       </c>
       <c r="F96" s="1">
-        <v>45377</v>
+        <v>45077</v>
       </c>
       <c r="G96" t="s">
         <v>129</v>
@@ -3491,30 +3475,30 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B97" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D97" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E97" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F97" s="1">
-        <v>45011</v>
-      </c>
-      <c r="G97" t="s">
-        <v>129</v>
+        <v>46135</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B98" t="s">
         <v>130</v>
@@ -3523,13 +3507,13 @@
         <v>131</v>
       </c>
       <c r="D98" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E98" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F98" s="1">
-        <v>46127</v>
+        <v>45736</v>
       </c>
       <c r="G98" t="s">
         <v>133</v>
@@ -3537,7 +3521,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B99" t="s">
         <v>130</v>
@@ -3546,13 +3530,13 @@
         <v>131</v>
       </c>
       <c r="D99" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E99" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F99" s="1">
-        <v>45808</v>
+        <v>45371</v>
       </c>
       <c r="G99" t="s">
         <v>133</v>
@@ -3560,7 +3544,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B100" t="s">
         <v>130</v>
@@ -3569,13 +3553,13 @@
         <v>131</v>
       </c>
       <c r="D100" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E100" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F100" s="1">
-        <v>45443</v>
+        <v>45005</v>
       </c>
       <c r="G100" t="s">
         <v>133</v>
@@ -3583,214 +3567,214 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B101" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C101" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D101" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E101" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F101" s="1">
-        <v>45077</v>
+        <v>46121</v>
       </c>
       <c r="G101" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B102" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C102" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D102" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E102" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F102" s="1">
-        <v>46135</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>137</v>
+        <v>45735</v>
+      </c>
+      <c r="G102" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B103" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D103" t="s">
+        <v>139</v>
+      </c>
+      <c r="E103" t="s">
+        <v>139</v>
+      </c>
+      <c r="F103" s="1">
+        <v>45370</v>
+      </c>
+      <c r="G103" t="s">
         <v>138</v>
-      </c>
-      <c r="E103" t="s">
-        <v>138</v>
-      </c>
-      <c r="F103" s="1">
-        <v>45736</v>
-      </c>
-      <c r="G103" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B104" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C104" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D104" t="s">
+        <v>139</v>
+      </c>
+      <c r="E104" t="s">
+        <v>139</v>
+      </c>
+      <c r="F104" s="1">
+        <v>45004</v>
+      </c>
+      <c r="G104" t="s">
         <v>138</v>
-      </c>
-      <c r="E104" t="s">
-        <v>138</v>
-      </c>
-      <c r="F104" s="1">
-        <v>45371</v>
-      </c>
-      <c r="G104" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B105" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D105" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E105" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F105" s="1">
-        <v>45005</v>
+        <v>46126</v>
       </c>
       <c r="G105" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B106" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C106" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D106" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E106" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F106" s="1">
-        <v>46121</v>
+        <v>45741</v>
       </c>
       <c r="G106" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B107" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C107" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D107" t="s">
+        <v>142</v>
+      </c>
+      <c r="E107" t="s">
+        <v>142</v>
+      </c>
+      <c r="F107" s="1">
+        <v>45376</v>
+      </c>
+      <c r="G107" t="s">
         <v>143</v>
-      </c>
-      <c r="E107" t="s">
-        <v>143</v>
-      </c>
-      <c r="F107" s="1">
-        <v>45735</v>
-      </c>
-      <c r="G107" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B108" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C108" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D108" t="s">
+        <v>142</v>
+      </c>
+      <c r="E108" t="s">
+        <v>142</v>
+      </c>
+      <c r="F108" s="1">
+        <v>45010</v>
+      </c>
+      <c r="G108" t="s">
         <v>143</v>
       </c>
-      <c r="E108" t="s">
-        <v>143</v>
-      </c>
-      <c r="F108" s="1">
-        <v>45370</v>
-      </c>
-      <c r="G108" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="109" spans="1:7">
-      <c r="A109">
-        <v>2023</v>
+      <c r="A109" s="9">
+        <v>2025</v>
       </c>
       <c r="B109" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C109" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D109" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F109" s="1">
-        <v>45004</v>
+        <v>45751</v>
       </c>
       <c r="G109" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B110" t="s">
         <v>144</v>
@@ -3805,7 +3789,7 @@
         <v>146</v>
       </c>
       <c r="F110" s="1">
-        <v>46126</v>
+        <v>45386</v>
       </c>
       <c r="G110" t="s">
         <v>147</v>
@@ -3813,7 +3797,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B111" t="s">
         <v>144</v>
@@ -3828,7 +3812,7 @@
         <v>146</v>
       </c>
       <c r="F111" s="1">
-        <v>45741</v>
+        <v>45020</v>
       </c>
       <c r="G111" t="s">
         <v>147</v>
@@ -3836,53 +3820,53 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B112" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C112" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E112" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F112" s="1">
-        <v>45376</v>
+        <v>46120</v>
       </c>
       <c r="G112" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B113" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C113" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E113" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F113" s="1">
-        <v>45010</v>
+        <v>45810</v>
       </c>
       <c r="G113" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" spans="1:7">
-      <c r="A114" s="10">
-        <v>2025</v>
+      <c r="A114">
+        <v>2024</v>
       </c>
       <c r="B114" t="s">
         <v>148</v>
@@ -3897,7 +3881,7 @@
         <v>150</v>
       </c>
       <c r="F114" s="1">
-        <v>45751</v>
+        <v>45445</v>
       </c>
       <c r="G114" t="s">
         <v>151</v>
@@ -3905,7 +3889,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B115" t="s">
         <v>148</v>
@@ -3920,7 +3904,7 @@
         <v>150</v>
       </c>
       <c r="F115" s="1">
-        <v>45386</v>
+        <v>45079</v>
       </c>
       <c r="G115" t="s">
         <v>151</v>
@@ -3928,30 +3912,30 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B116" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C116" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D116" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E116" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F116" s="1">
-        <v>45020</v>
+        <v>46126</v>
       </c>
       <c r="G116" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B117" t="s">
         <v>152</v>
@@ -3960,13 +3944,13 @@
         <v>153</v>
       </c>
       <c r="D117" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E117" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F117" s="1">
-        <v>46120</v>
+        <v>45735</v>
       </c>
       <c r="G117" t="s">
         <v>155</v>
@@ -3974,7 +3958,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B118" t="s">
         <v>152</v>
@@ -3983,13 +3967,13 @@
         <v>153</v>
       </c>
       <c r="D118" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E118" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F118" s="1">
-        <v>45810</v>
+        <v>45370</v>
       </c>
       <c r="G118" t="s">
         <v>155</v>
@@ -3997,7 +3981,7 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B119" t="s">
         <v>152</v>
@@ -4006,151 +3990,151 @@
         <v>153</v>
       </c>
       <c r="D119" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E119" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F119" s="1">
-        <v>45445</v>
+        <v>45004</v>
       </c>
       <c r="G119" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:7">
-      <c r="A120">
-        <v>2023</v>
+      <c r="A120" s="9">
+        <v>2026</v>
       </c>
       <c r="B120" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D120" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E120" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F120" s="1">
-        <v>45079</v>
-      </c>
-      <c r="G120" t="s">
-        <v>155</v>
+        <v>46120</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B121" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C121" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D121" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E121" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F121" s="1">
-        <v>46126</v>
+        <v>45840</v>
       </c>
       <c r="G121" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B122" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C122" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D122" t="s">
+        <v>161</v>
+      </c>
+      <c r="E122" t="s">
+        <v>161</v>
+      </c>
+      <c r="F122" s="1">
+        <v>45475</v>
+      </c>
+      <c r="G122" t="s">
         <v>160</v>
-      </c>
-      <c r="E122" t="s">
-        <v>160</v>
-      </c>
-      <c r="F122" s="1">
-        <v>45735</v>
-      </c>
-      <c r="G122" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B123" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C123" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
+        <v>161</v>
+      </c>
+      <c r="E123" t="s">
+        <v>161</v>
+      </c>
+      <c r="F123" s="1">
+        <v>45109</v>
+      </c>
+      <c r="G123" t="s">
         <v>160</v>
-      </c>
-      <c r="E123" t="s">
-        <v>160</v>
-      </c>
-      <c r="F123" s="1">
-        <v>45370</v>
-      </c>
-      <c r="G123" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B124" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C124" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D124" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E124" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F124" s="1">
-        <v>45004</v>
+        <v>46139</v>
       </c>
       <c r="G124" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
-      <c r="A125" s="15">
-        <v>2026</v>
+      <c r="A125">
+        <v>2025</v>
       </c>
       <c r="B125" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C125" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D125" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E125" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F125" s="1">
-        <v>46120</v>
+        <v>45749</v>
       </c>
       <c r="G125" t="s">
         <v>165</v>
@@ -4158,22 +4142,22 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B126" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C126" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D126" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E126" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F126" s="1">
-        <v>45840</v>
+        <v>45384</v>
       </c>
       <c r="G126" t="s">
         <v>165</v>
@@ -4181,22 +4165,22 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B127" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D127" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E127" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F127" s="1">
-        <v>45475</v>
+        <v>45018</v>
       </c>
       <c r="G127" t="s">
         <v>165</v>
@@ -4204,160 +4188,160 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B128" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C128" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D128" t="s">
-        <v>164</v>
-      </c>
-      <c r="E128" t="s">
-        <v>164</v>
+        <v>169</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="F128" s="1">
-        <v>45109</v>
+        <v>46161</v>
       </c>
       <c r="G128" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B129" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C129" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D129" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E129" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F129" s="1">
-        <v>46139</v>
+        <v>45744</v>
       </c>
       <c r="G129" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B130" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C130" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D130" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E130" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F130" s="1">
-        <v>45749</v>
+        <v>45379</v>
       </c>
       <c r="G130" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B131" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C131" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D131" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E131" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F131" s="1">
-        <v>45384</v>
+        <v>45013</v>
       </c>
       <c r="G131" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B132" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C132" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D132" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E132" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F132" s="1">
-        <v>45018</v>
+        <v>46120</v>
       </c>
       <c r="G132" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B133" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C133" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D133" t="s">
-        <v>173</v>
-      </c>
-      <c r="E133" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="E133" t="s">
+        <v>174</v>
       </c>
       <c r="F133" s="1">
-        <v>46161</v>
+        <v>45733</v>
       </c>
       <c r="G133" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B134" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C134" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D134" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E134" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F134" s="1">
-        <v>45744</v>
+        <v>45368</v>
       </c>
       <c r="G134" t="s">
         <v>175</v>
@@ -4365,22 +4349,22 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B135" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C135" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D135" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E135" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F135" s="1">
-        <v>45379</v>
+        <v>45002</v>
       </c>
       <c r="G135" t="s">
         <v>175</v>
@@ -4388,30 +4372,30 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B136" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C136" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D136" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E136" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F136" s="1">
-        <v>45013</v>
+        <v>46127</v>
       </c>
       <c r="G136" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B137" t="s">
         <v>176</v>
@@ -4420,13 +4404,13 @@
         <v>177</v>
       </c>
       <c r="D137" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E137" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F137" s="1">
-        <v>46120</v>
+        <v>45735</v>
       </c>
       <c r="G137" t="s">
         <v>179</v>
@@ -4434,7 +4418,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B138" t="s">
         <v>176</v>
@@ -4443,13 +4427,13 @@
         <v>177</v>
       </c>
       <c r="D138" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E138" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F138" s="1">
-        <v>45733</v>
+        <v>45370</v>
       </c>
       <c r="G138" t="s">
         <v>179</v>
@@ -4457,7 +4441,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B139" t="s">
         <v>176</v>
@@ -4466,13 +4450,13 @@
         <v>177</v>
       </c>
       <c r="D139" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E139" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F139" s="1">
-        <v>45368</v>
+        <v>45004</v>
       </c>
       <c r="G139" t="s">
         <v>179</v>
@@ -4480,436 +4464,436 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B140" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C140" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D140" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E140" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F140" s="1">
-        <v>45002</v>
+        <v>46140</v>
       </c>
       <c r="G140" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B141" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C141" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D141" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E141" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F141" s="1">
-        <v>46127</v>
+        <v>45705</v>
       </c>
       <c r="G141" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B142" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C142" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D142" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F142" s="1">
-        <v>45735</v>
+        <v>45339</v>
       </c>
       <c r="G142" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B143" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C143" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D143" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E143" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F143" s="1">
-        <v>45370</v>
+        <v>44974</v>
       </c>
       <c r="G143" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B144" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C144" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D144" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E144" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F144" s="1">
-        <v>45004</v>
+        <v>46162</v>
       </c>
       <c r="G144" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="145" spans="1:7">
-      <c r="A145">
-        <v>2026</v>
+      <c r="A145" s="11">
+        <v>2025</v>
       </c>
       <c r="B145" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C145" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D145" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E145" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F145" s="1">
-        <v>46140</v>
+        <v>45737</v>
       </c>
       <c r="G145" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B146" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C146" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D146" t="s">
+        <v>191</v>
+      </c>
+      <c r="E146" t="s">
+        <v>191</v>
+      </c>
+      <c r="F146" s="1">
+        <v>45372</v>
+      </c>
+      <c r="G146" t="s">
         <v>190</v>
-      </c>
-      <c r="E146" t="s">
-        <v>190</v>
-      </c>
-      <c r="F146" s="1">
-        <v>45705</v>
-      </c>
-      <c r="G146" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
+        <v>2023</v>
+      </c>
+      <c r="B147" t="s">
+        <v>187</v>
+      </c>
+      <c r="C147" t="s">
+        <v>188</v>
+      </c>
+      <c r="D147" t="s">
+        <v>191</v>
+      </c>
+      <c r="E147" t="s">
+        <v>191</v>
+      </c>
+      <c r="F147" s="1">
+        <v>45006</v>
+      </c>
+      <c r="G147" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B148" t="s">
+        <v>192</v>
+      </c>
+      <c r="C148" t="s">
+        <v>193</v>
+      </c>
+      <c r="D148" t="s">
+        <v>194</v>
+      </c>
+      <c r="E148" t="s">
+        <v>194</v>
+      </c>
+      <c r="F148" s="1">
+        <v>46125</v>
+      </c>
+      <c r="G148" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B149" t="s">
+        <v>192</v>
+      </c>
+      <c r="C149" t="s">
+        <v>193</v>
+      </c>
+      <c r="D149" t="s">
+        <v>196</v>
+      </c>
+      <c r="E149" t="s">
+        <v>196</v>
+      </c>
+      <c r="F149" s="1">
+        <v>45741</v>
+      </c>
+      <c r="G149" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150">
         <v>2024</v>
       </c>
-      <c r="B147" t="s">
-        <v>185</v>
-      </c>
-      <c r="C147" t="s">
-        <v>186</v>
-      </c>
-      <c r="D147" t="s">
-        <v>190</v>
-      </c>
-      <c r="E147" t="s">
-        <v>190</v>
-      </c>
-      <c r="F147" s="1">
-        <v>45339</v>
-      </c>
-      <c r="G147" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148">
-        <v>2023</v>
-      </c>
-      <c r="B148" t="s">
-        <v>185</v>
-      </c>
-      <c r="C148" t="s">
-        <v>186</v>
-      </c>
-      <c r="D148" t="s">
-        <v>190</v>
-      </c>
-      <c r="E148" t="s">
-        <v>190</v>
-      </c>
-      <c r="F148" s="1">
-        <v>44974</v>
-      </c>
-      <c r="G148" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149">
-        <v>2026</v>
-      </c>
-      <c r="B149" t="s">
-        <v>191</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="B150" t="s">
         <v>192</v>
       </c>
-      <c r="D149" t="s">
+      <c r="C150" t="s">
         <v>193</v>
       </c>
-      <c r="E149" t="s">
-        <v>193</v>
-      </c>
-      <c r="F149" s="1">
-        <v>46162</v>
-      </c>
-      <c r="G149" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" s="12">
-        <v>2025</v>
-      </c>
-      <c r="B150" t="s">
-        <v>191</v>
-      </c>
-      <c r="C150" t="s">
-        <v>192</v>
-      </c>
       <c r="D150" t="s">
+        <v>196</v>
+      </c>
+      <c r="E150" t="s">
+        <v>196</v>
+      </c>
+      <c r="F150" s="1">
+        <v>45376</v>
+      </c>
+      <c r="G150" t="s">
         <v>195</v>
-      </c>
-      <c r="E150" t="s">
-        <v>195</v>
-      </c>
-      <c r="F150" s="1">
-        <v>45737</v>
-      </c>
-      <c r="G150" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B151" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C151" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D151" t="s">
+        <v>196</v>
+      </c>
+      <c r="E151" t="s">
+        <v>196</v>
+      </c>
+      <c r="F151" s="1">
+        <v>45010</v>
+      </c>
+      <c r="G151" t="s">
         <v>195</v>
-      </c>
-      <c r="E151" t="s">
-        <v>195</v>
-      </c>
-      <c r="F151" s="1">
-        <v>45372</v>
-      </c>
-      <c r="G151" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B152" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C152" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D152" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E152" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F152" s="1">
-        <v>45006</v>
+        <v>46128</v>
       </c>
       <c r="G152" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="153" spans="1:7">
-      <c r="A153" s="12">
-        <v>2026</v>
+      <c r="A153">
+        <v>2025</v>
       </c>
       <c r="B153" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C153" t="s">
+        <v>198</v>
+      </c>
+      <c r="D153" t="s">
+        <v>199</v>
+      </c>
+      <c r="E153" t="s">
+        <v>199</v>
+      </c>
+      <c r="F153" s="1">
+        <v>45763</v>
+      </c>
+      <c r="G153" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154">
+        <v>2024</v>
+      </c>
+      <c r="B154" t="s">
         <v>197</v>
       </c>
-      <c r="D153" t="s">
+      <c r="C154" t="s">
         <v>198</v>
       </c>
-      <c r="E153" t="s">
-        <v>198</v>
-      </c>
-      <c r="F153" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G153" t="s">
+      <c r="D154" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" s="12">
-        <v>2025</v>
-      </c>
-      <c r="B154" t="s">
-        <v>196</v>
-      </c>
-      <c r="C154" t="s">
-        <v>197</v>
-      </c>
-      <c r="D154" t="s">
-        <v>200</v>
-      </c>
       <c r="E154" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F154" s="1">
-        <v>45741</v>
+        <v>45398</v>
       </c>
       <c r="G154" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B155" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C155" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D155" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E155" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F155" s="1">
-        <v>45376</v>
+        <v>45032</v>
       </c>
       <c r="G155" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B156" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C156" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D156" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E156" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F156" s="1">
-        <v>45010</v>
+        <v>46128</v>
       </c>
       <c r="G156" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B157" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C157" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D157" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E157" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F157" s="1">
-        <v>46128</v>
+        <v>45819</v>
       </c>
       <c r="G157" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B158" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C158" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D158" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E158" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F158" s="1">
-        <v>45763</v>
+        <v>45454</v>
       </c>
       <c r="G158" t="s">
         <v>205</v>
@@ -4917,22 +4901,22 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B159" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C159" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D159" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E159" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F159" s="1">
-        <v>45398</v>
+        <v>45088</v>
       </c>
       <c r="G159" t="s">
         <v>205</v>
@@ -4940,214 +4924,214 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B160" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C160" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D160" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E160" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F160" s="1">
-        <v>45032</v>
-      </c>
-      <c r="G160" t="s">
-        <v>205</v>
+        <v>46170</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B161" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C161" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D161" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E161" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F161" s="1">
-        <v>46128</v>
+        <v>45862</v>
       </c>
       <c r="G161" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B162" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C162" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D162" t="s">
+        <v>211</v>
+      </c>
+      <c r="E162" t="s">
+        <v>211</v>
+      </c>
+      <c r="F162" s="1">
+        <v>45497</v>
+      </c>
+      <c r="G162" t="s">
         <v>210</v>
-      </c>
-      <c r="E162" t="s">
-        <v>210</v>
-      </c>
-      <c r="F162" s="1">
-        <v>45819</v>
-      </c>
-      <c r="G162" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B163" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C163" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D163" t="s">
+        <v>211</v>
+      </c>
+      <c r="E163" t="s">
+        <v>211</v>
+      </c>
+      <c r="F163" s="1">
+        <v>45131</v>
+      </c>
+      <c r="G163" t="s">
         <v>210</v>
-      </c>
-      <c r="E163" t="s">
-        <v>210</v>
-      </c>
-      <c r="F163" s="1">
-        <v>45454</v>
-      </c>
-      <c r="G163" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B164" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C164" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D164" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E164" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F164" s="1">
-        <v>45088</v>
+        <v>46128</v>
       </c>
       <c r="G164" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B165" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C165" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D165" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E165" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F165" s="1">
-        <v>46170</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>214</v>
+        <v>45819</v>
+      </c>
+      <c r="G165" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B166" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C166" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D166" t="s">
+        <v>214</v>
+      </c>
+      <c r="E166" t="s">
+        <v>214</v>
+      </c>
+      <c r="F166" s="1">
+        <v>45454</v>
+      </c>
+      <c r="G166" t="s">
         <v>215</v>
-      </c>
-      <c r="E166" t="s">
-        <v>215</v>
-      </c>
-      <c r="F166" s="1">
-        <v>45862</v>
-      </c>
-      <c r="G166" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B167" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C167" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D167" t="s">
+        <v>214</v>
+      </c>
+      <c r="E167" t="s">
+        <v>214</v>
+      </c>
+      <c r="F167" s="1">
+        <v>45088</v>
+      </c>
+      <c r="G167" t="s">
         <v>215</v>
-      </c>
-      <c r="E167" t="s">
-        <v>215</v>
-      </c>
-      <c r="F167" s="1">
-        <v>45497</v>
-      </c>
-      <c r="G167" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B168" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C168" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D168" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E168" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F168" s="1">
-        <v>45131</v>
-      </c>
-      <c r="G168" t="s">
-        <v>214</v>
+        <v>46162</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B169" t="s">
         <v>216</v>
@@ -5156,13 +5140,13 @@
         <v>217</v>
       </c>
       <c r="D169" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E169" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F169" s="1">
-        <v>46128</v>
+        <v>45740</v>
       </c>
       <c r="G169" t="s">
         <v>219</v>
@@ -5170,7 +5154,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B170" t="s">
         <v>216</v>
@@ -5179,13 +5163,13 @@
         <v>217</v>
       </c>
       <c r="D170" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E170" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F170" s="1">
-        <v>45819</v>
+        <v>45375</v>
       </c>
       <c r="G170" t="s">
         <v>219</v>
@@ -5193,7 +5177,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B171" t="s">
         <v>216</v>
@@ -5202,13 +5186,13 @@
         <v>217</v>
       </c>
       <c r="D171" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E171" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F171" s="1">
-        <v>45454</v>
+        <v>45009</v>
       </c>
       <c r="G171" t="s">
         <v>219</v>
@@ -5216,306 +5200,306 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B172" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C172" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D172" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E172" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F172" s="1">
-        <v>45088</v>
+        <v>46125</v>
       </c>
       <c r="G172" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B173" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C173" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D173" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E173" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F173" s="1">
-        <v>46162</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>223</v>
+        <v>45733</v>
+      </c>
+      <c r="G173" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B174" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C174" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D174" t="s">
+        <v>225</v>
+      </c>
+      <c r="E174" t="s">
+        <v>225</v>
+      </c>
+      <c r="F174" s="1">
+        <v>45368</v>
+      </c>
+      <c r="G174" t="s">
         <v>224</v>
-      </c>
-      <c r="E174" t="s">
-        <v>224</v>
-      </c>
-      <c r="F174" s="1">
-        <v>45740</v>
-      </c>
-      <c r="G174" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B175" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C175" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D175" t="s">
+        <v>225</v>
+      </c>
+      <c r="E175" t="s">
+        <v>225</v>
+      </c>
+      <c r="F175" s="1">
+        <v>45002</v>
+      </c>
+      <c r="G175" t="s">
         <v>224</v>
-      </c>
-      <c r="E175" t="s">
-        <v>224</v>
-      </c>
-      <c r="F175" s="1">
-        <v>45375</v>
-      </c>
-      <c r="G175" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B176" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C176" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D176" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E176" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F176" s="1">
-        <v>45009</v>
+        <v>46121</v>
       </c>
       <c r="G176" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B177" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C177" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D177" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E177" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F177" s="1">
-        <v>46125</v>
+        <v>45713</v>
       </c>
       <c r="G177" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B178" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C178" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D178" t="s">
+        <v>230</v>
+      </c>
+      <c r="E178" t="s">
+        <v>230</v>
+      </c>
+      <c r="F178" s="1">
+        <v>45347</v>
+      </c>
+      <c r="G178" t="s">
         <v>229</v>
-      </c>
-      <c r="E178" t="s">
-        <v>229</v>
-      </c>
-      <c r="F178" s="1">
-        <v>45733</v>
-      </c>
-      <c r="G178" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B179" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C179" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D179" t="s">
+        <v>230</v>
+      </c>
+      <c r="E179" t="s">
+        <v>230</v>
+      </c>
+      <c r="F179" s="1">
+        <v>44982</v>
+      </c>
+      <c r="G179" t="s">
         <v>229</v>
       </c>
-      <c r="E179" t="s">
-        <v>229</v>
-      </c>
-      <c r="F179" s="1">
-        <v>45368</v>
-      </c>
-      <c r="G179" t="s">
-        <v>228</v>
-      </c>
     </row>
     <row r="180" spans="1:7">
-      <c r="A180">
-        <v>2023</v>
+      <c r="A180" s="9">
+        <v>2025</v>
       </c>
       <c r="B180" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C180" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D180" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E180" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F180" s="1">
-        <v>45002</v>
-      </c>
-      <c r="G180" t="s">
-        <v>228</v>
+        <v>45821</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B181" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C181" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D181" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E181" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F181" s="1">
-        <v>46121</v>
+        <v>45456</v>
       </c>
       <c r="G181" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B182" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C182" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D182" t="s">
+        <v>233</v>
+      </c>
+      <c r="E182" t="s">
+        <v>233</v>
+      </c>
+      <c r="F182" s="1">
+        <v>45090</v>
+      </c>
+      <c r="G182" t="s">
         <v>234</v>
-      </c>
-      <c r="E182" t="s">
-        <v>234</v>
-      </c>
-      <c r="F182" s="1">
-        <v>45713</v>
-      </c>
-      <c r="G182" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B183" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C183" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D183" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E183" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F183" s="1">
-        <v>45347</v>
-      </c>
-      <c r="G183" t="s">
-        <v>233</v>
+        <v>46170</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B184" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C184" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E184" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F184" s="1">
-        <v>44982</v>
+        <v>45805</v>
       </c>
       <c r="G184" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="185" spans="1:7">
-      <c r="A185" s="15">
-        <v>2025</v>
+      <c r="A185">
+        <v>2024</v>
       </c>
       <c r="B185" t="s">
         <v>235</v>
@@ -5530,7 +5514,7 @@
         <v>237</v>
       </c>
       <c r="F185" s="1">
-        <v>45821</v>
+        <v>45440</v>
       </c>
       <c r="G185" t="s">
         <v>238</v>
@@ -5538,7 +5522,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B186" t="s">
         <v>235</v>
@@ -5553,7 +5537,7 @@
         <v>237</v>
       </c>
       <c r="F186" s="1">
-        <v>45456</v>
+        <v>45074</v>
       </c>
       <c r="G186" t="s">
         <v>238</v>
@@ -5561,30 +5545,30 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>2023</v>
-      </c>
-      <c r="B187" t="s">
-        <v>235</v>
+        <v>2026</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="C187" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D187" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="E187" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="F187" s="1">
-        <v>45090</v>
+        <v>46125</v>
       </c>
       <c r="G187" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B188" t="s">
         <v>239</v>
@@ -5593,21 +5577,21 @@
         <v>240</v>
       </c>
       <c r="D188" t="s">
+        <v>242</v>
+      </c>
+      <c r="E188" t="s">
+        <v>242</v>
+      </c>
+      <c r="F188" s="1">
+        <v>45748</v>
+      </c>
+      <c r="G188" t="s">
         <v>241</v>
-      </c>
-      <c r="E188" t="s">
-        <v>241</v>
-      </c>
-      <c r="F188" s="1">
-        <v>46170</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B189" t="s">
         <v>239</v>
@@ -5616,21 +5600,21 @@
         <v>240</v>
       </c>
       <c r="D189" t="s">
+        <v>242</v>
+      </c>
+      <c r="E189" t="s">
+        <v>242</v>
+      </c>
+      <c r="F189" s="1">
+        <v>45383</v>
+      </c>
+      <c r="G189" t="s">
         <v>241</v>
-      </c>
-      <c r="E189" t="s">
-        <v>241</v>
-      </c>
-      <c r="F189" s="1">
-        <v>45805</v>
-      </c>
-      <c r="G189" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B190" t="s">
         <v>239</v>
@@ -5639,67 +5623,67 @@
         <v>240</v>
       </c>
       <c r="D190" t="s">
+        <v>242</v>
+      </c>
+      <c r="E190" t="s">
+        <v>242</v>
+      </c>
+      <c r="F190" s="1">
+        <v>45017</v>
+      </c>
+      <c r="G190" t="s">
         <v>241</v>
-      </c>
-      <c r="E190" t="s">
-        <v>241</v>
-      </c>
-      <c r="F190" s="1">
-        <v>45440</v>
-      </c>
-      <c r="G190" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B191" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C191" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D191" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E191" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F191" s="1">
-        <v>45074</v>
+        <v>46128</v>
       </c>
       <c r="G191" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192">
-        <v>2026</v>
-      </c>
-      <c r="B192" s="9" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B192" t="s">
         <v>243</v>
       </c>
       <c r="C192" t="s">
         <v>244</v>
       </c>
       <c r="D192" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="E192" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="F192" s="1">
-        <v>46125</v>
+        <v>45744</v>
       </c>
       <c r="G192" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B193" t="s">
         <v>243</v>
@@ -5708,21 +5692,21 @@
         <v>244</v>
       </c>
       <c r="D193" t="s">
+        <v>247</v>
+      </c>
+      <c r="E193" t="s">
+        <v>247</v>
+      </c>
+      <c r="F193" s="1">
+        <v>45379</v>
+      </c>
+      <c r="G193" t="s">
         <v>246</v>
-      </c>
-      <c r="E193" t="s">
-        <v>246</v>
-      </c>
-      <c r="F193" s="1">
-        <v>45748</v>
-      </c>
-      <c r="G193" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B194" t="s">
         <v>243</v>
@@ -5731,280 +5715,163 @@
         <v>244</v>
       </c>
       <c r="D194" t="s">
+        <v>247</v>
+      </c>
+      <c r="E194" t="s">
+        <v>247</v>
+      </c>
+      <c r="F194" s="1">
+        <v>45013</v>
+      </c>
+      <c r="G194" t="s">
         <v>246</v>
-      </c>
-      <c r="E194" t="s">
-        <v>246</v>
-      </c>
-      <c r="F194" s="1">
-        <v>45383</v>
-      </c>
-      <c r="G194" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B195" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C195" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D195" t="s">
-        <v>246</v>
-      </c>
-      <c r="E195" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F195" s="1">
-        <v>45017</v>
+        <v>46122</v>
       </c>
       <c r="G195" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B196" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C196" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D196" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E196" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F196" s="1">
-        <v>46128</v>
+        <v>45737</v>
       </c>
       <c r="G196" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B197" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C197" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D197" t="s">
+        <v>252</v>
+      </c>
+      <c r="E197" t="s">
+        <v>252</v>
+      </c>
+      <c r="F197" s="1">
+        <v>45372</v>
+      </c>
+      <c r="G197" t="s">
         <v>251</v>
-      </c>
-      <c r="E197" t="s">
-        <v>251</v>
-      </c>
-      <c r="F197" s="1">
-        <v>45744</v>
-      </c>
-      <c r="G197" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B198" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C198" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D198" t="s">
+        <v>252</v>
+      </c>
+      <c r="E198" t="s">
+        <v>252</v>
+      </c>
+      <c r="F198" s="1">
+        <v>45006</v>
+      </c>
+      <c r="G198" t="s">
         <v>251</v>
       </c>
-      <c r="E198" t="s">
-        <v>251</v>
-      </c>
-      <c r="F198" s="1">
-        <v>45379</v>
-      </c>
-      <c r="G198" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
-      <c r="A199">
-        <v>2023</v>
-      </c>
-      <c r="B199" t="s">
-        <v>247</v>
-      </c>
-      <c r="C199" t="s">
-        <v>248</v>
-      </c>
-      <c r="D199" t="s">
-        <v>251</v>
-      </c>
-      <c r="E199" t="s">
-        <v>251</v>
-      </c>
-      <c r="F199" s="1">
-        <v>45013</v>
-      </c>
-      <c r="G199" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
-      <c r="A200">
-        <v>2026</v>
-      </c>
-      <c r="B200" t="s">
-        <v>252</v>
-      </c>
-      <c r="C200" t="s">
-        <v>253</v>
-      </c>
-      <c r="D200" t="s">
-        <v>254</v>
-      </c>
-      <c r="F200" s="1">
-        <v>46122</v>
-      </c>
-      <c r="G200" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
-      <c r="A201">
-        <v>2025</v>
-      </c>
-      <c r="B201" t="s">
-        <v>252</v>
-      </c>
-      <c r="C201" t="s">
-        <v>253</v>
-      </c>
-      <c r="D201" t="s">
-        <v>256</v>
-      </c>
-      <c r="E201" t="s">
-        <v>256</v>
-      </c>
-      <c r="F201" s="1">
-        <v>45737</v>
-      </c>
-      <c r="G201" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
-      <c r="A202">
-        <v>2024</v>
-      </c>
-      <c r="B202" t="s">
-        <v>252</v>
-      </c>
-      <c r="C202" t="s">
-        <v>253</v>
-      </c>
-      <c r="D202" t="s">
-        <v>256</v>
-      </c>
-      <c r="E202" t="s">
-        <v>256</v>
-      </c>
-      <c r="F202" s="1">
-        <v>45372</v>
-      </c>
-      <c r="G202" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7">
-      <c r="A203">
-        <v>2023</v>
-      </c>
-      <c r="B203" t="s">
-        <v>252</v>
-      </c>
-      <c r="C203" t="s">
-        <v>253</v>
-      </c>
-      <c r="D203" t="s">
-        <v>256</v>
-      </c>
-      <c r="E203" t="s">
-        <v>256</v>
-      </c>
-      <c r="F203" s="1">
-        <v>45006</v>
-      </c>
-      <c r="G203" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="252" spans="11:11">
-      <c r="K252" s="1"/>
+    </row>
+    <row r="247" spans="11:11">
+      <c r="K247" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G203">
-    <sortState ref="A2:G202">
+  <autoFilter ref="A1:G198">
+    <sortState ref="A2:G198">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G43" r:id="rId1"/>
-    <hyperlink ref="G45" r:id="rId2"/>
-    <hyperlink ref="G46" r:id="rId3"/>
-    <hyperlink ref="G44" r:id="rId4"/>
-    <hyperlink ref="G18" r:id="rId5"/>
-    <hyperlink ref="G23" r:id="rId6"/>
-    <hyperlink ref="G31" r:id="rId7"/>
-    <hyperlink ref="G35" r:id="rId8"/>
-    <hyperlink ref="G39" r:id="rId9"/>
-    <hyperlink ref="G47" r:id="rId10"/>
-    <hyperlink ref="G51" r:id="rId11"/>
-    <hyperlink ref="G55" r:id="rId12"/>
-    <hyperlink ref="G59" r:id="rId13"/>
-    <hyperlink ref="G63" r:id="rId14"/>
-    <hyperlink ref="G67" r:id="rId15"/>
-    <hyperlink ref="G75" r:id="rId16"/>
-    <hyperlink ref="E75" r:id="rId17" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto"/>
-    <hyperlink ref="G79" r:id="rId18"/>
-    <hyperlink ref="G94" r:id="rId19" location="informacoes-classificadas-e-desclassificadas"/>
-    <hyperlink ref="G111" r:id="rId20"/>
-    <hyperlink ref="G110" r:id="rId21"/>
-    <hyperlink ref="G106" r:id="rId22"/>
-    <hyperlink ref="G117" r:id="rId23" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas"/>
-    <hyperlink ref="G121" r:id="rId24" location="informacoes-classificadas-e-desclassificadas"/>
-    <hyperlink ref="G129" r:id="rId25"/>
-    <hyperlink ref="G137" r:id="rId26"/>
-    <hyperlink ref="G141" r:id="rId27"/>
-    <hyperlink ref="G145" r:id="rId28"/>
-    <hyperlink ref="G157" r:id="rId29"/>
-    <hyperlink ref="G161" r:id="rId30"/>
-    <hyperlink ref="G169" r:id="rId31" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas"/>
-    <hyperlink ref="G177" r:id="rId32"/>
-    <hyperlink ref="G192" r:id="rId33"/>
-    <hyperlink ref="G196" r:id="rId34" location="info-class-des"/>
-    <hyperlink ref="G200" r:id="rId35"/>
-    <hyperlink ref="G90" r:id="rId36"/>
-    <hyperlink ref="G102" r:id="rId37"/>
-    <hyperlink ref="G181" r:id="rId38"/>
-    <hyperlink ref="G14" r:id="rId39"/>
-    <hyperlink ref="G153" r:id="rId40"/>
-    <hyperlink ref="G71" r:id="rId41"/>
-    <hyperlink ref="G27" r:id="rId42"/>
-    <hyperlink ref="G133" r:id="rId43"/>
-    <hyperlink ref="G173" r:id="rId44"/>
-    <hyperlink ref="G149" r:id="rId45"/>
-    <hyperlink ref="G19" r:id="rId46"/>
-    <hyperlink ref="G188" r:id="rId47"/>
-    <hyperlink ref="G165" r:id="rId48"/>
+    <hyperlink ref="G18" r:id="rId1"/>
+    <hyperlink ref="G23" r:id="rId2"/>
+    <hyperlink ref="G31" r:id="rId3"/>
+    <hyperlink ref="G35" r:id="rId4"/>
+    <hyperlink ref="G39" r:id="rId5"/>
+    <hyperlink ref="G43" r:id="rId6"/>
+    <hyperlink ref="G46" r:id="rId7"/>
+    <hyperlink ref="G50" r:id="rId8"/>
+    <hyperlink ref="G54" r:id="rId9"/>
+    <hyperlink ref="G58" r:id="rId10"/>
+    <hyperlink ref="G62" r:id="rId11"/>
+    <hyperlink ref="G70" r:id="rId12"/>
+    <hyperlink ref="E70" r:id="rId13" display="Em atendimento ao disposto no art. 46 do Decreto Estadual nº 45.969/2012, a Fundação de Amparo à Pesquisa do Estado de Minas Gerais (FAPEMIG) informa que não teve informações classificadas ou desclassificadas nos graus de sigilo reservado, secreto ou ultrassecreto"/>
+    <hyperlink ref="G74" r:id="rId14"/>
+    <hyperlink ref="G89" r:id="rId15" location="informacoes-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G106" r:id="rId16"/>
+    <hyperlink ref="G105" r:id="rId17"/>
+    <hyperlink ref="G101" r:id="rId18"/>
+    <hyperlink ref="G112" r:id="rId19" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G116" r:id="rId20" location="informacoes-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G124" r:id="rId21"/>
+    <hyperlink ref="G132" r:id="rId22"/>
+    <hyperlink ref="G136" r:id="rId23"/>
+    <hyperlink ref="G140" r:id="rId24"/>
+    <hyperlink ref="G152" r:id="rId25"/>
+    <hyperlink ref="G156" r:id="rId26"/>
+    <hyperlink ref="G164" r:id="rId27" location="informa%C3%A7%C3%B5es-classificadas-e-desclassificadas"/>
+    <hyperlink ref="G172" r:id="rId28"/>
+    <hyperlink ref="G187" r:id="rId29"/>
+    <hyperlink ref="G191" r:id="rId30" location="info-class-des"/>
+    <hyperlink ref="G195" r:id="rId31"/>
+    <hyperlink ref="G85" r:id="rId32"/>
+    <hyperlink ref="G97" r:id="rId33"/>
+    <hyperlink ref="G176" r:id="rId34"/>
+    <hyperlink ref="G14" r:id="rId35"/>
+    <hyperlink ref="G148" r:id="rId36"/>
+    <hyperlink ref="G66" r:id="rId37"/>
+    <hyperlink ref="G27" r:id="rId38"/>
+    <hyperlink ref="G128" r:id="rId39"/>
+    <hyperlink ref="G168" r:id="rId40"/>
+    <hyperlink ref="G144" r:id="rId41"/>
+    <hyperlink ref="G19" r:id="rId42"/>
+    <hyperlink ref="G183" r:id="rId43"/>
+    <hyperlink ref="G160" r:id="rId44"/>
+    <hyperlink ref="G120" r:id="rId45"/>
+    <hyperlink ref="G180" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
